--- a/ranking/results.xlsx
+++ b/ranking/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI8"/>
+  <dimension ref="A1:JC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -734,6 +734,1016 @@
           <t>theta_9_dgd</t>
         </is>
       </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>F1_Proposed</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>Kendall_Proposed</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>theta_10_true</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>theta_10_uadmm</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>theta_10_local</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>theta_10_pooled</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>theta_10_dgd</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>theta_11_true</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>theta_11_uadmm</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>theta_11_local</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>theta_11_pooled</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>theta_11_dgd</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>theta_12_true</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>theta_12_uadmm</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>theta_12_local</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>theta_12_pooled</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>theta_12_dgd</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>theta_13_true</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>theta_13_uadmm</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>theta_13_local</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>theta_13_pooled</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>theta_13_dgd</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>theta_14_true</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>theta_14_uadmm</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>theta_14_local</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>theta_14_pooled</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>theta_14_dgd</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>theta_15_true</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>theta_15_uadmm</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>theta_15_local</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>theta_15_pooled</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>theta_15_dgd</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>theta_16_true</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>theta_16_uadmm</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>theta_16_local</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>theta_16_pooled</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>theta_16_dgd</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>theta_17_true</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>theta_17_uadmm</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>theta_17_local</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>theta_17_pooled</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>theta_17_dgd</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>theta_18_true</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>theta_18_uadmm</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>theta_18_local</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>theta_18_pooled</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>theta_18_dgd</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>theta_19_true</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>theta_19_uadmm</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>theta_19_local</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>theta_19_pooled</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>theta_19_dgd</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>theta_20_true</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>theta_20_uadmm</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>theta_20_local</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>theta_20_pooled</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>theta_20_dgd</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>theta_21_true</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>theta_21_uadmm</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>theta_21_local</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>theta_21_pooled</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>theta_21_dgd</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>theta_22_true</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>theta_22_uadmm</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>theta_22_local</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>theta_22_pooled</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>theta_22_dgd</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>theta_23_true</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>theta_23_uadmm</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>theta_23_local</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>theta_23_pooled</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>theta_23_dgd</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>theta_24_true</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>theta_24_uadmm</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>theta_24_local</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>theta_24_pooled</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>theta_24_dgd</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>theta_25_true</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>theta_25_uadmm</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>theta_25_local</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>theta_25_pooled</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>theta_25_dgd</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>theta_26_true</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>theta_26_uadmm</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>theta_26_local</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>theta_26_pooled</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>theta_26_dgd</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>theta_27_true</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>theta_27_uadmm</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>theta_27_local</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>theta_27_pooled</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>theta_27_dgd</t>
+        </is>
+      </c>
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>theta_28_true</t>
+        </is>
+      </c>
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>theta_28_uadmm</t>
+        </is>
+      </c>
+      <c r="EZ1" s="1" t="inlineStr">
+        <is>
+          <t>theta_28_local</t>
+        </is>
+      </c>
+      <c r="FA1" s="1" t="inlineStr">
+        <is>
+          <t>theta_28_pooled</t>
+        </is>
+      </c>
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>theta_28_dgd</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
+        <is>
+          <t>theta_29_true</t>
+        </is>
+      </c>
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
+          <t>theta_29_uadmm</t>
+        </is>
+      </c>
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>theta_29_local</t>
+        </is>
+      </c>
+      <c r="FF1" s="1" t="inlineStr">
+        <is>
+          <t>theta_29_pooled</t>
+        </is>
+      </c>
+      <c r="FG1" s="1" t="inlineStr">
+        <is>
+          <t>theta_29_dgd</t>
+        </is>
+      </c>
+      <c r="FH1" s="1" t="inlineStr">
+        <is>
+          <t>theta_30_true</t>
+        </is>
+      </c>
+      <c r="FI1" s="1" t="inlineStr">
+        <is>
+          <t>theta_30_uadmm</t>
+        </is>
+      </c>
+      <c r="FJ1" s="1" t="inlineStr">
+        <is>
+          <t>theta_30_local</t>
+        </is>
+      </c>
+      <c r="FK1" s="1" t="inlineStr">
+        <is>
+          <t>theta_30_pooled</t>
+        </is>
+      </c>
+      <c r="FL1" s="1" t="inlineStr">
+        <is>
+          <t>theta_30_dgd</t>
+        </is>
+      </c>
+      <c r="FM1" s="1" t="inlineStr">
+        <is>
+          <t>theta_31_true</t>
+        </is>
+      </c>
+      <c r="FN1" s="1" t="inlineStr">
+        <is>
+          <t>theta_31_uadmm</t>
+        </is>
+      </c>
+      <c r="FO1" s="1" t="inlineStr">
+        <is>
+          <t>theta_31_local</t>
+        </is>
+      </c>
+      <c r="FP1" s="1" t="inlineStr">
+        <is>
+          <t>theta_31_pooled</t>
+        </is>
+      </c>
+      <c r="FQ1" s="1" t="inlineStr">
+        <is>
+          <t>theta_31_dgd</t>
+        </is>
+      </c>
+      <c r="FR1" s="1" t="inlineStr">
+        <is>
+          <t>theta_32_true</t>
+        </is>
+      </c>
+      <c r="FS1" s="1" t="inlineStr">
+        <is>
+          <t>theta_32_uadmm</t>
+        </is>
+      </c>
+      <c r="FT1" s="1" t="inlineStr">
+        <is>
+          <t>theta_32_local</t>
+        </is>
+      </c>
+      <c r="FU1" s="1" t="inlineStr">
+        <is>
+          <t>theta_32_pooled</t>
+        </is>
+      </c>
+      <c r="FV1" s="1" t="inlineStr">
+        <is>
+          <t>theta_32_dgd</t>
+        </is>
+      </c>
+      <c r="FW1" s="1" t="inlineStr">
+        <is>
+          <t>theta_33_true</t>
+        </is>
+      </c>
+      <c r="FX1" s="1" t="inlineStr">
+        <is>
+          <t>theta_33_uadmm</t>
+        </is>
+      </c>
+      <c r="FY1" s="1" t="inlineStr">
+        <is>
+          <t>theta_33_local</t>
+        </is>
+      </c>
+      <c r="FZ1" s="1" t="inlineStr">
+        <is>
+          <t>theta_33_pooled</t>
+        </is>
+      </c>
+      <c r="GA1" s="1" t="inlineStr">
+        <is>
+          <t>theta_33_dgd</t>
+        </is>
+      </c>
+      <c r="GB1" s="1" t="inlineStr">
+        <is>
+          <t>theta_34_true</t>
+        </is>
+      </c>
+      <c r="GC1" s="1" t="inlineStr">
+        <is>
+          <t>theta_34_uadmm</t>
+        </is>
+      </c>
+      <c r="GD1" s="1" t="inlineStr">
+        <is>
+          <t>theta_34_local</t>
+        </is>
+      </c>
+      <c r="GE1" s="1" t="inlineStr">
+        <is>
+          <t>theta_34_pooled</t>
+        </is>
+      </c>
+      <c r="GF1" s="1" t="inlineStr">
+        <is>
+          <t>theta_34_dgd</t>
+        </is>
+      </c>
+      <c r="GG1" s="1" t="inlineStr">
+        <is>
+          <t>theta_35_true</t>
+        </is>
+      </c>
+      <c r="GH1" s="1" t="inlineStr">
+        <is>
+          <t>theta_35_uadmm</t>
+        </is>
+      </c>
+      <c r="GI1" s="1" t="inlineStr">
+        <is>
+          <t>theta_35_local</t>
+        </is>
+      </c>
+      <c r="GJ1" s="1" t="inlineStr">
+        <is>
+          <t>theta_35_pooled</t>
+        </is>
+      </c>
+      <c r="GK1" s="1" t="inlineStr">
+        <is>
+          <t>theta_35_dgd</t>
+        </is>
+      </c>
+      <c r="GL1" s="1" t="inlineStr">
+        <is>
+          <t>theta_36_true</t>
+        </is>
+      </c>
+      <c r="GM1" s="1" t="inlineStr">
+        <is>
+          <t>theta_36_uadmm</t>
+        </is>
+      </c>
+      <c r="GN1" s="1" t="inlineStr">
+        <is>
+          <t>theta_36_local</t>
+        </is>
+      </c>
+      <c r="GO1" s="1" t="inlineStr">
+        <is>
+          <t>theta_36_pooled</t>
+        </is>
+      </c>
+      <c r="GP1" s="1" t="inlineStr">
+        <is>
+          <t>theta_36_dgd</t>
+        </is>
+      </c>
+      <c r="GQ1" s="1" t="inlineStr">
+        <is>
+          <t>theta_37_true</t>
+        </is>
+      </c>
+      <c r="GR1" s="1" t="inlineStr">
+        <is>
+          <t>theta_37_uadmm</t>
+        </is>
+      </c>
+      <c r="GS1" s="1" t="inlineStr">
+        <is>
+          <t>theta_37_local</t>
+        </is>
+      </c>
+      <c r="GT1" s="1" t="inlineStr">
+        <is>
+          <t>theta_37_pooled</t>
+        </is>
+      </c>
+      <c r="GU1" s="1" t="inlineStr">
+        <is>
+          <t>theta_37_dgd</t>
+        </is>
+      </c>
+      <c r="GV1" s="1" t="inlineStr">
+        <is>
+          <t>theta_38_true</t>
+        </is>
+      </c>
+      <c r="GW1" s="1" t="inlineStr">
+        <is>
+          <t>theta_38_uadmm</t>
+        </is>
+      </c>
+      <c r="GX1" s="1" t="inlineStr">
+        <is>
+          <t>theta_38_local</t>
+        </is>
+      </c>
+      <c r="GY1" s="1" t="inlineStr">
+        <is>
+          <t>theta_38_pooled</t>
+        </is>
+      </c>
+      <c r="GZ1" s="1" t="inlineStr">
+        <is>
+          <t>theta_38_dgd</t>
+        </is>
+      </c>
+      <c r="HA1" s="1" t="inlineStr">
+        <is>
+          <t>theta_39_true</t>
+        </is>
+      </c>
+      <c r="HB1" s="1" t="inlineStr">
+        <is>
+          <t>theta_39_uadmm</t>
+        </is>
+      </c>
+      <c r="HC1" s="1" t="inlineStr">
+        <is>
+          <t>theta_39_local</t>
+        </is>
+      </c>
+      <c r="HD1" s="1" t="inlineStr">
+        <is>
+          <t>theta_39_pooled</t>
+        </is>
+      </c>
+      <c r="HE1" s="1" t="inlineStr">
+        <is>
+          <t>theta_39_dgd</t>
+        </is>
+      </c>
+      <c r="HF1" s="1" t="inlineStr">
+        <is>
+          <t>theta_40_true</t>
+        </is>
+      </c>
+      <c r="HG1" s="1" t="inlineStr">
+        <is>
+          <t>theta_40_uadmm</t>
+        </is>
+      </c>
+      <c r="HH1" s="1" t="inlineStr">
+        <is>
+          <t>theta_40_local</t>
+        </is>
+      </c>
+      <c r="HI1" s="1" t="inlineStr">
+        <is>
+          <t>theta_40_pooled</t>
+        </is>
+      </c>
+      <c r="HJ1" s="1" t="inlineStr">
+        <is>
+          <t>theta_40_dgd</t>
+        </is>
+      </c>
+      <c r="HK1" s="1" t="inlineStr">
+        <is>
+          <t>theta_41_true</t>
+        </is>
+      </c>
+      <c r="HL1" s="1" t="inlineStr">
+        <is>
+          <t>theta_41_uadmm</t>
+        </is>
+      </c>
+      <c r="HM1" s="1" t="inlineStr">
+        <is>
+          <t>theta_41_local</t>
+        </is>
+      </c>
+      <c r="HN1" s="1" t="inlineStr">
+        <is>
+          <t>theta_41_pooled</t>
+        </is>
+      </c>
+      <c r="HO1" s="1" t="inlineStr">
+        <is>
+          <t>theta_41_dgd</t>
+        </is>
+      </c>
+      <c r="HP1" s="1" t="inlineStr">
+        <is>
+          <t>theta_42_true</t>
+        </is>
+      </c>
+      <c r="HQ1" s="1" t="inlineStr">
+        <is>
+          <t>theta_42_uadmm</t>
+        </is>
+      </c>
+      <c r="HR1" s="1" t="inlineStr">
+        <is>
+          <t>theta_42_local</t>
+        </is>
+      </c>
+      <c r="HS1" s="1" t="inlineStr">
+        <is>
+          <t>theta_42_pooled</t>
+        </is>
+      </c>
+      <c r="HT1" s="1" t="inlineStr">
+        <is>
+          <t>theta_42_dgd</t>
+        </is>
+      </c>
+      <c r="HU1" s="1" t="inlineStr">
+        <is>
+          <t>theta_43_true</t>
+        </is>
+      </c>
+      <c r="HV1" s="1" t="inlineStr">
+        <is>
+          <t>theta_43_uadmm</t>
+        </is>
+      </c>
+      <c r="HW1" s="1" t="inlineStr">
+        <is>
+          <t>theta_43_local</t>
+        </is>
+      </c>
+      <c r="HX1" s="1" t="inlineStr">
+        <is>
+          <t>theta_43_pooled</t>
+        </is>
+      </c>
+      <c r="HY1" s="1" t="inlineStr">
+        <is>
+          <t>theta_43_dgd</t>
+        </is>
+      </c>
+      <c r="HZ1" s="1" t="inlineStr">
+        <is>
+          <t>theta_44_true</t>
+        </is>
+      </c>
+      <c r="IA1" s="1" t="inlineStr">
+        <is>
+          <t>theta_44_uadmm</t>
+        </is>
+      </c>
+      <c r="IB1" s="1" t="inlineStr">
+        <is>
+          <t>theta_44_local</t>
+        </is>
+      </c>
+      <c r="IC1" s="1" t="inlineStr">
+        <is>
+          <t>theta_44_pooled</t>
+        </is>
+      </c>
+      <c r="ID1" s="1" t="inlineStr">
+        <is>
+          <t>theta_44_dgd</t>
+        </is>
+      </c>
+      <c r="IE1" s="1" t="inlineStr">
+        <is>
+          <t>theta_45_true</t>
+        </is>
+      </c>
+      <c r="IF1" s="1" t="inlineStr">
+        <is>
+          <t>theta_45_uadmm</t>
+        </is>
+      </c>
+      <c r="IG1" s="1" t="inlineStr">
+        <is>
+          <t>theta_45_local</t>
+        </is>
+      </c>
+      <c r="IH1" s="1" t="inlineStr">
+        <is>
+          <t>theta_45_pooled</t>
+        </is>
+      </c>
+      <c r="II1" s="1" t="inlineStr">
+        <is>
+          <t>theta_45_dgd</t>
+        </is>
+      </c>
+      <c r="IJ1" s="1" t="inlineStr">
+        <is>
+          <t>theta_46_true</t>
+        </is>
+      </c>
+      <c r="IK1" s="1" t="inlineStr">
+        <is>
+          <t>theta_46_uadmm</t>
+        </is>
+      </c>
+      <c r="IL1" s="1" t="inlineStr">
+        <is>
+          <t>theta_46_local</t>
+        </is>
+      </c>
+      <c r="IM1" s="1" t="inlineStr">
+        <is>
+          <t>theta_46_pooled</t>
+        </is>
+      </c>
+      <c r="IN1" s="1" t="inlineStr">
+        <is>
+          <t>theta_46_dgd</t>
+        </is>
+      </c>
+      <c r="IO1" s="1" t="inlineStr">
+        <is>
+          <t>theta_47_true</t>
+        </is>
+      </c>
+      <c r="IP1" s="1" t="inlineStr">
+        <is>
+          <t>theta_47_uadmm</t>
+        </is>
+      </c>
+      <c r="IQ1" s="1" t="inlineStr">
+        <is>
+          <t>theta_47_local</t>
+        </is>
+      </c>
+      <c r="IR1" s="1" t="inlineStr">
+        <is>
+          <t>theta_47_pooled</t>
+        </is>
+      </c>
+      <c r="IS1" s="1" t="inlineStr">
+        <is>
+          <t>theta_47_dgd</t>
+        </is>
+      </c>
+      <c r="IT1" s="1" t="inlineStr">
+        <is>
+          <t>theta_48_true</t>
+        </is>
+      </c>
+      <c r="IU1" s="1" t="inlineStr">
+        <is>
+          <t>theta_48_uadmm</t>
+        </is>
+      </c>
+      <c r="IV1" s="1" t="inlineStr">
+        <is>
+          <t>theta_48_local</t>
+        </is>
+      </c>
+      <c r="IW1" s="1" t="inlineStr">
+        <is>
+          <t>theta_48_pooled</t>
+        </is>
+      </c>
+      <c r="IX1" s="1" t="inlineStr">
+        <is>
+          <t>theta_48_dgd</t>
+        </is>
+      </c>
+      <c r="IY1" s="1" t="inlineStr">
+        <is>
+          <t>theta_49_true</t>
+        </is>
+      </c>
+      <c r="IZ1" s="1" t="inlineStr">
+        <is>
+          <t>theta_49_uadmm</t>
+        </is>
+      </c>
+      <c r="JA1" s="1" t="inlineStr">
+        <is>
+          <t>theta_49_local</t>
+        </is>
+      </c>
+      <c r="JB1" s="1" t="inlineStr">
+        <is>
+          <t>theta_49_pooled</t>
+        </is>
+      </c>
+      <c r="JC1" s="1" t="inlineStr">
+        <is>
+          <t>theta_49_dgd</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -923,6 +1933,208 @@
       <c r="BI2" t="n">
         <v>0.1212439507557961</v>
       </c>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="inlineStr"/>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="inlineStr"/>
+      <c r="CA2" t="inlineStr"/>
+      <c r="CB2" t="inlineStr"/>
+      <c r="CC2" t="inlineStr"/>
+      <c r="CD2" t="inlineStr"/>
+      <c r="CE2" t="inlineStr"/>
+      <c r="CF2" t="inlineStr"/>
+      <c r="CG2" t="inlineStr"/>
+      <c r="CH2" t="inlineStr"/>
+      <c r="CI2" t="inlineStr"/>
+      <c r="CJ2" t="inlineStr"/>
+      <c r="CK2" t="inlineStr"/>
+      <c r="CL2" t="inlineStr"/>
+      <c r="CM2" t="inlineStr"/>
+      <c r="CN2" t="inlineStr"/>
+      <c r="CO2" t="inlineStr"/>
+      <c r="CP2" t="inlineStr"/>
+      <c r="CQ2" t="inlineStr"/>
+      <c r="CR2" t="inlineStr"/>
+      <c r="CS2" t="inlineStr"/>
+      <c r="CT2" t="inlineStr"/>
+      <c r="CU2" t="inlineStr"/>
+      <c r="CV2" t="inlineStr"/>
+      <c r="CW2" t="inlineStr"/>
+      <c r="CX2" t="inlineStr"/>
+      <c r="CY2" t="inlineStr"/>
+      <c r="CZ2" t="inlineStr"/>
+      <c r="DA2" t="inlineStr"/>
+      <c r="DB2" t="inlineStr"/>
+      <c r="DC2" t="inlineStr"/>
+      <c r="DD2" t="inlineStr"/>
+      <c r="DE2" t="inlineStr"/>
+      <c r="DF2" t="inlineStr"/>
+      <c r="DG2" t="inlineStr"/>
+      <c r="DH2" t="inlineStr"/>
+      <c r="DI2" t="inlineStr"/>
+      <c r="DJ2" t="inlineStr"/>
+      <c r="DK2" t="inlineStr"/>
+      <c r="DL2" t="inlineStr"/>
+      <c r="DM2" t="inlineStr"/>
+      <c r="DN2" t="inlineStr"/>
+      <c r="DO2" t="inlineStr"/>
+      <c r="DP2" t="inlineStr"/>
+      <c r="DQ2" t="inlineStr"/>
+      <c r="DR2" t="inlineStr"/>
+      <c r="DS2" t="inlineStr"/>
+      <c r="DT2" t="inlineStr"/>
+      <c r="DU2" t="inlineStr"/>
+      <c r="DV2" t="inlineStr"/>
+      <c r="DW2" t="inlineStr"/>
+      <c r="DX2" t="inlineStr"/>
+      <c r="DY2" t="inlineStr"/>
+      <c r="DZ2" t="inlineStr"/>
+      <c r="EA2" t="inlineStr"/>
+      <c r="EB2" t="inlineStr"/>
+      <c r="EC2" t="inlineStr"/>
+      <c r="ED2" t="inlineStr"/>
+      <c r="EE2" t="inlineStr"/>
+      <c r="EF2" t="inlineStr"/>
+      <c r="EG2" t="inlineStr"/>
+      <c r="EH2" t="inlineStr"/>
+      <c r="EI2" t="inlineStr"/>
+      <c r="EJ2" t="inlineStr"/>
+      <c r="EK2" t="inlineStr"/>
+      <c r="EL2" t="inlineStr"/>
+      <c r="EM2" t="inlineStr"/>
+      <c r="EN2" t="inlineStr"/>
+      <c r="EO2" t="inlineStr"/>
+      <c r="EP2" t="inlineStr"/>
+      <c r="EQ2" t="inlineStr"/>
+      <c r="ER2" t="inlineStr"/>
+      <c r="ES2" t="inlineStr"/>
+      <c r="ET2" t="inlineStr"/>
+      <c r="EU2" t="inlineStr"/>
+      <c r="EV2" t="inlineStr"/>
+      <c r="EW2" t="inlineStr"/>
+      <c r="EX2" t="inlineStr"/>
+      <c r="EY2" t="inlineStr"/>
+      <c r="EZ2" t="inlineStr"/>
+      <c r="FA2" t="inlineStr"/>
+      <c r="FB2" t="inlineStr"/>
+      <c r="FC2" t="inlineStr"/>
+      <c r="FD2" t="inlineStr"/>
+      <c r="FE2" t="inlineStr"/>
+      <c r="FF2" t="inlineStr"/>
+      <c r="FG2" t="inlineStr"/>
+      <c r="FH2" t="inlineStr"/>
+      <c r="FI2" t="inlineStr"/>
+      <c r="FJ2" t="inlineStr"/>
+      <c r="FK2" t="inlineStr"/>
+      <c r="FL2" t="inlineStr"/>
+      <c r="FM2" t="inlineStr"/>
+      <c r="FN2" t="inlineStr"/>
+      <c r="FO2" t="inlineStr"/>
+      <c r="FP2" t="inlineStr"/>
+      <c r="FQ2" t="inlineStr"/>
+      <c r="FR2" t="inlineStr"/>
+      <c r="FS2" t="inlineStr"/>
+      <c r="FT2" t="inlineStr"/>
+      <c r="FU2" t="inlineStr"/>
+      <c r="FV2" t="inlineStr"/>
+      <c r="FW2" t="inlineStr"/>
+      <c r="FX2" t="inlineStr"/>
+      <c r="FY2" t="inlineStr"/>
+      <c r="FZ2" t="inlineStr"/>
+      <c r="GA2" t="inlineStr"/>
+      <c r="GB2" t="inlineStr"/>
+      <c r="GC2" t="inlineStr"/>
+      <c r="GD2" t="inlineStr"/>
+      <c r="GE2" t="inlineStr"/>
+      <c r="GF2" t="inlineStr"/>
+      <c r="GG2" t="inlineStr"/>
+      <c r="GH2" t="inlineStr"/>
+      <c r="GI2" t="inlineStr"/>
+      <c r="GJ2" t="inlineStr"/>
+      <c r="GK2" t="inlineStr"/>
+      <c r="GL2" t="inlineStr"/>
+      <c r="GM2" t="inlineStr"/>
+      <c r="GN2" t="inlineStr"/>
+      <c r="GO2" t="inlineStr"/>
+      <c r="GP2" t="inlineStr"/>
+      <c r="GQ2" t="inlineStr"/>
+      <c r="GR2" t="inlineStr"/>
+      <c r="GS2" t="inlineStr"/>
+      <c r="GT2" t="inlineStr"/>
+      <c r="GU2" t="inlineStr"/>
+      <c r="GV2" t="inlineStr"/>
+      <c r="GW2" t="inlineStr"/>
+      <c r="GX2" t="inlineStr"/>
+      <c r="GY2" t="inlineStr"/>
+      <c r="GZ2" t="inlineStr"/>
+      <c r="HA2" t="inlineStr"/>
+      <c r="HB2" t="inlineStr"/>
+      <c r="HC2" t="inlineStr"/>
+      <c r="HD2" t="inlineStr"/>
+      <c r="HE2" t="inlineStr"/>
+      <c r="HF2" t="inlineStr"/>
+      <c r="HG2" t="inlineStr"/>
+      <c r="HH2" t="inlineStr"/>
+      <c r="HI2" t="inlineStr"/>
+      <c r="HJ2" t="inlineStr"/>
+      <c r="HK2" t="inlineStr"/>
+      <c r="HL2" t="inlineStr"/>
+      <c r="HM2" t="inlineStr"/>
+      <c r="HN2" t="inlineStr"/>
+      <c r="HO2" t="inlineStr"/>
+      <c r="HP2" t="inlineStr"/>
+      <c r="HQ2" t="inlineStr"/>
+      <c r="HR2" t="inlineStr"/>
+      <c r="HS2" t="inlineStr"/>
+      <c r="HT2" t="inlineStr"/>
+      <c r="HU2" t="inlineStr"/>
+      <c r="HV2" t="inlineStr"/>
+      <c r="HW2" t="inlineStr"/>
+      <c r="HX2" t="inlineStr"/>
+      <c r="HY2" t="inlineStr"/>
+      <c r="HZ2" t="inlineStr"/>
+      <c r="IA2" t="inlineStr"/>
+      <c r="IB2" t="inlineStr"/>
+      <c r="IC2" t="inlineStr"/>
+      <c r="ID2" t="inlineStr"/>
+      <c r="IE2" t="inlineStr"/>
+      <c r="IF2" t="inlineStr"/>
+      <c r="IG2" t="inlineStr"/>
+      <c r="IH2" t="inlineStr"/>
+      <c r="II2" t="inlineStr"/>
+      <c r="IJ2" t="inlineStr"/>
+      <c r="IK2" t="inlineStr"/>
+      <c r="IL2" t="inlineStr"/>
+      <c r="IM2" t="inlineStr"/>
+      <c r="IN2" t="inlineStr"/>
+      <c r="IO2" t="inlineStr"/>
+      <c r="IP2" t="inlineStr"/>
+      <c r="IQ2" t="inlineStr"/>
+      <c r="IR2" t="inlineStr"/>
+      <c r="IS2" t="inlineStr"/>
+      <c r="IT2" t="inlineStr"/>
+      <c r="IU2" t="inlineStr"/>
+      <c r="IV2" t="inlineStr"/>
+      <c r="IW2" t="inlineStr"/>
+      <c r="IX2" t="inlineStr"/>
+      <c r="IY2" t="inlineStr"/>
+      <c r="IZ2" t="inlineStr"/>
+      <c r="JA2" t="inlineStr"/>
+      <c r="JB2" t="inlineStr"/>
+      <c r="JC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1112,6 +2324,208 @@
       <c r="BI3" t="n">
         <v>0.1212439507557961</v>
       </c>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr"/>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
+      <c r="BO3" t="inlineStr"/>
+      <c r="BP3" t="inlineStr"/>
+      <c r="BQ3" t="inlineStr"/>
+      <c r="BR3" t="inlineStr"/>
+      <c r="BS3" t="inlineStr"/>
+      <c r="BT3" t="inlineStr"/>
+      <c r="BU3" t="inlineStr"/>
+      <c r="BV3" t="inlineStr"/>
+      <c r="BW3" t="inlineStr"/>
+      <c r="BX3" t="inlineStr"/>
+      <c r="BY3" t="inlineStr"/>
+      <c r="BZ3" t="inlineStr"/>
+      <c r="CA3" t="inlineStr"/>
+      <c r="CB3" t="inlineStr"/>
+      <c r="CC3" t="inlineStr"/>
+      <c r="CD3" t="inlineStr"/>
+      <c r="CE3" t="inlineStr"/>
+      <c r="CF3" t="inlineStr"/>
+      <c r="CG3" t="inlineStr"/>
+      <c r="CH3" t="inlineStr"/>
+      <c r="CI3" t="inlineStr"/>
+      <c r="CJ3" t="inlineStr"/>
+      <c r="CK3" t="inlineStr"/>
+      <c r="CL3" t="inlineStr"/>
+      <c r="CM3" t="inlineStr"/>
+      <c r="CN3" t="inlineStr"/>
+      <c r="CO3" t="inlineStr"/>
+      <c r="CP3" t="inlineStr"/>
+      <c r="CQ3" t="inlineStr"/>
+      <c r="CR3" t="inlineStr"/>
+      <c r="CS3" t="inlineStr"/>
+      <c r="CT3" t="inlineStr"/>
+      <c r="CU3" t="inlineStr"/>
+      <c r="CV3" t="inlineStr"/>
+      <c r="CW3" t="inlineStr"/>
+      <c r="CX3" t="inlineStr"/>
+      <c r="CY3" t="inlineStr"/>
+      <c r="CZ3" t="inlineStr"/>
+      <c r="DA3" t="inlineStr"/>
+      <c r="DB3" t="inlineStr"/>
+      <c r="DC3" t="inlineStr"/>
+      <c r="DD3" t="inlineStr"/>
+      <c r="DE3" t="inlineStr"/>
+      <c r="DF3" t="inlineStr"/>
+      <c r="DG3" t="inlineStr"/>
+      <c r="DH3" t="inlineStr"/>
+      <c r="DI3" t="inlineStr"/>
+      <c r="DJ3" t="inlineStr"/>
+      <c r="DK3" t="inlineStr"/>
+      <c r="DL3" t="inlineStr"/>
+      <c r="DM3" t="inlineStr"/>
+      <c r="DN3" t="inlineStr"/>
+      <c r="DO3" t="inlineStr"/>
+      <c r="DP3" t="inlineStr"/>
+      <c r="DQ3" t="inlineStr"/>
+      <c r="DR3" t="inlineStr"/>
+      <c r="DS3" t="inlineStr"/>
+      <c r="DT3" t="inlineStr"/>
+      <c r="DU3" t="inlineStr"/>
+      <c r="DV3" t="inlineStr"/>
+      <c r="DW3" t="inlineStr"/>
+      <c r="DX3" t="inlineStr"/>
+      <c r="DY3" t="inlineStr"/>
+      <c r="DZ3" t="inlineStr"/>
+      <c r="EA3" t="inlineStr"/>
+      <c r="EB3" t="inlineStr"/>
+      <c r="EC3" t="inlineStr"/>
+      <c r="ED3" t="inlineStr"/>
+      <c r="EE3" t="inlineStr"/>
+      <c r="EF3" t="inlineStr"/>
+      <c r="EG3" t="inlineStr"/>
+      <c r="EH3" t="inlineStr"/>
+      <c r="EI3" t="inlineStr"/>
+      <c r="EJ3" t="inlineStr"/>
+      <c r="EK3" t="inlineStr"/>
+      <c r="EL3" t="inlineStr"/>
+      <c r="EM3" t="inlineStr"/>
+      <c r="EN3" t="inlineStr"/>
+      <c r="EO3" t="inlineStr"/>
+      <c r="EP3" t="inlineStr"/>
+      <c r="EQ3" t="inlineStr"/>
+      <c r="ER3" t="inlineStr"/>
+      <c r="ES3" t="inlineStr"/>
+      <c r="ET3" t="inlineStr"/>
+      <c r="EU3" t="inlineStr"/>
+      <c r="EV3" t="inlineStr"/>
+      <c r="EW3" t="inlineStr"/>
+      <c r="EX3" t="inlineStr"/>
+      <c r="EY3" t="inlineStr"/>
+      <c r="EZ3" t="inlineStr"/>
+      <c r="FA3" t="inlineStr"/>
+      <c r="FB3" t="inlineStr"/>
+      <c r="FC3" t="inlineStr"/>
+      <c r="FD3" t="inlineStr"/>
+      <c r="FE3" t="inlineStr"/>
+      <c r="FF3" t="inlineStr"/>
+      <c r="FG3" t="inlineStr"/>
+      <c r="FH3" t="inlineStr"/>
+      <c r="FI3" t="inlineStr"/>
+      <c r="FJ3" t="inlineStr"/>
+      <c r="FK3" t="inlineStr"/>
+      <c r="FL3" t="inlineStr"/>
+      <c r="FM3" t="inlineStr"/>
+      <c r="FN3" t="inlineStr"/>
+      <c r="FO3" t="inlineStr"/>
+      <c r="FP3" t="inlineStr"/>
+      <c r="FQ3" t="inlineStr"/>
+      <c r="FR3" t="inlineStr"/>
+      <c r="FS3" t="inlineStr"/>
+      <c r="FT3" t="inlineStr"/>
+      <c r="FU3" t="inlineStr"/>
+      <c r="FV3" t="inlineStr"/>
+      <c r="FW3" t="inlineStr"/>
+      <c r="FX3" t="inlineStr"/>
+      <c r="FY3" t="inlineStr"/>
+      <c r="FZ3" t="inlineStr"/>
+      <c r="GA3" t="inlineStr"/>
+      <c r="GB3" t="inlineStr"/>
+      <c r="GC3" t="inlineStr"/>
+      <c r="GD3" t="inlineStr"/>
+      <c r="GE3" t="inlineStr"/>
+      <c r="GF3" t="inlineStr"/>
+      <c r="GG3" t="inlineStr"/>
+      <c r="GH3" t="inlineStr"/>
+      <c r="GI3" t="inlineStr"/>
+      <c r="GJ3" t="inlineStr"/>
+      <c r="GK3" t="inlineStr"/>
+      <c r="GL3" t="inlineStr"/>
+      <c r="GM3" t="inlineStr"/>
+      <c r="GN3" t="inlineStr"/>
+      <c r="GO3" t="inlineStr"/>
+      <c r="GP3" t="inlineStr"/>
+      <c r="GQ3" t="inlineStr"/>
+      <c r="GR3" t="inlineStr"/>
+      <c r="GS3" t="inlineStr"/>
+      <c r="GT3" t="inlineStr"/>
+      <c r="GU3" t="inlineStr"/>
+      <c r="GV3" t="inlineStr"/>
+      <c r="GW3" t="inlineStr"/>
+      <c r="GX3" t="inlineStr"/>
+      <c r="GY3" t="inlineStr"/>
+      <c r="GZ3" t="inlineStr"/>
+      <c r="HA3" t="inlineStr"/>
+      <c r="HB3" t="inlineStr"/>
+      <c r="HC3" t="inlineStr"/>
+      <c r="HD3" t="inlineStr"/>
+      <c r="HE3" t="inlineStr"/>
+      <c r="HF3" t="inlineStr"/>
+      <c r="HG3" t="inlineStr"/>
+      <c r="HH3" t="inlineStr"/>
+      <c r="HI3" t="inlineStr"/>
+      <c r="HJ3" t="inlineStr"/>
+      <c r="HK3" t="inlineStr"/>
+      <c r="HL3" t="inlineStr"/>
+      <c r="HM3" t="inlineStr"/>
+      <c r="HN3" t="inlineStr"/>
+      <c r="HO3" t="inlineStr"/>
+      <c r="HP3" t="inlineStr"/>
+      <c r="HQ3" t="inlineStr"/>
+      <c r="HR3" t="inlineStr"/>
+      <c r="HS3" t="inlineStr"/>
+      <c r="HT3" t="inlineStr"/>
+      <c r="HU3" t="inlineStr"/>
+      <c r="HV3" t="inlineStr"/>
+      <c r="HW3" t="inlineStr"/>
+      <c r="HX3" t="inlineStr"/>
+      <c r="HY3" t="inlineStr"/>
+      <c r="HZ3" t="inlineStr"/>
+      <c r="IA3" t="inlineStr"/>
+      <c r="IB3" t="inlineStr"/>
+      <c r="IC3" t="inlineStr"/>
+      <c r="ID3" t="inlineStr"/>
+      <c r="IE3" t="inlineStr"/>
+      <c r="IF3" t="inlineStr"/>
+      <c r="IG3" t="inlineStr"/>
+      <c r="IH3" t="inlineStr"/>
+      <c r="II3" t="inlineStr"/>
+      <c r="IJ3" t="inlineStr"/>
+      <c r="IK3" t="inlineStr"/>
+      <c r="IL3" t="inlineStr"/>
+      <c r="IM3" t="inlineStr"/>
+      <c r="IN3" t="inlineStr"/>
+      <c r="IO3" t="inlineStr"/>
+      <c r="IP3" t="inlineStr"/>
+      <c r="IQ3" t="inlineStr"/>
+      <c r="IR3" t="inlineStr"/>
+      <c r="IS3" t="inlineStr"/>
+      <c r="IT3" t="inlineStr"/>
+      <c r="IU3" t="inlineStr"/>
+      <c r="IV3" t="inlineStr"/>
+      <c r="IW3" t="inlineStr"/>
+      <c r="IX3" t="inlineStr"/>
+      <c r="IY3" t="inlineStr"/>
+      <c r="IZ3" t="inlineStr"/>
+      <c r="JA3" t="inlineStr"/>
+      <c r="JB3" t="inlineStr"/>
+      <c r="JC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1301,6 +2715,208 @@
       <c r="BI4" t="n">
         <v>0.1212439507557961</v>
       </c>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
+      <c r="BO4" t="inlineStr"/>
+      <c r="BP4" t="inlineStr"/>
+      <c r="BQ4" t="inlineStr"/>
+      <c r="BR4" t="inlineStr"/>
+      <c r="BS4" t="inlineStr"/>
+      <c r="BT4" t="inlineStr"/>
+      <c r="BU4" t="inlineStr"/>
+      <c r="BV4" t="inlineStr"/>
+      <c r="BW4" t="inlineStr"/>
+      <c r="BX4" t="inlineStr"/>
+      <c r="BY4" t="inlineStr"/>
+      <c r="BZ4" t="inlineStr"/>
+      <c r="CA4" t="inlineStr"/>
+      <c r="CB4" t="inlineStr"/>
+      <c r="CC4" t="inlineStr"/>
+      <c r="CD4" t="inlineStr"/>
+      <c r="CE4" t="inlineStr"/>
+      <c r="CF4" t="inlineStr"/>
+      <c r="CG4" t="inlineStr"/>
+      <c r="CH4" t="inlineStr"/>
+      <c r="CI4" t="inlineStr"/>
+      <c r="CJ4" t="inlineStr"/>
+      <c r="CK4" t="inlineStr"/>
+      <c r="CL4" t="inlineStr"/>
+      <c r="CM4" t="inlineStr"/>
+      <c r="CN4" t="inlineStr"/>
+      <c r="CO4" t="inlineStr"/>
+      <c r="CP4" t="inlineStr"/>
+      <c r="CQ4" t="inlineStr"/>
+      <c r="CR4" t="inlineStr"/>
+      <c r="CS4" t="inlineStr"/>
+      <c r="CT4" t="inlineStr"/>
+      <c r="CU4" t="inlineStr"/>
+      <c r="CV4" t="inlineStr"/>
+      <c r="CW4" t="inlineStr"/>
+      <c r="CX4" t="inlineStr"/>
+      <c r="CY4" t="inlineStr"/>
+      <c r="CZ4" t="inlineStr"/>
+      <c r="DA4" t="inlineStr"/>
+      <c r="DB4" t="inlineStr"/>
+      <c r="DC4" t="inlineStr"/>
+      <c r="DD4" t="inlineStr"/>
+      <c r="DE4" t="inlineStr"/>
+      <c r="DF4" t="inlineStr"/>
+      <c r="DG4" t="inlineStr"/>
+      <c r="DH4" t="inlineStr"/>
+      <c r="DI4" t="inlineStr"/>
+      <c r="DJ4" t="inlineStr"/>
+      <c r="DK4" t="inlineStr"/>
+      <c r="DL4" t="inlineStr"/>
+      <c r="DM4" t="inlineStr"/>
+      <c r="DN4" t="inlineStr"/>
+      <c r="DO4" t="inlineStr"/>
+      <c r="DP4" t="inlineStr"/>
+      <c r="DQ4" t="inlineStr"/>
+      <c r="DR4" t="inlineStr"/>
+      <c r="DS4" t="inlineStr"/>
+      <c r="DT4" t="inlineStr"/>
+      <c r="DU4" t="inlineStr"/>
+      <c r="DV4" t="inlineStr"/>
+      <c r="DW4" t="inlineStr"/>
+      <c r="DX4" t="inlineStr"/>
+      <c r="DY4" t="inlineStr"/>
+      <c r="DZ4" t="inlineStr"/>
+      <c r="EA4" t="inlineStr"/>
+      <c r="EB4" t="inlineStr"/>
+      <c r="EC4" t="inlineStr"/>
+      <c r="ED4" t="inlineStr"/>
+      <c r="EE4" t="inlineStr"/>
+      <c r="EF4" t="inlineStr"/>
+      <c r="EG4" t="inlineStr"/>
+      <c r="EH4" t="inlineStr"/>
+      <c r="EI4" t="inlineStr"/>
+      <c r="EJ4" t="inlineStr"/>
+      <c r="EK4" t="inlineStr"/>
+      <c r="EL4" t="inlineStr"/>
+      <c r="EM4" t="inlineStr"/>
+      <c r="EN4" t="inlineStr"/>
+      <c r="EO4" t="inlineStr"/>
+      <c r="EP4" t="inlineStr"/>
+      <c r="EQ4" t="inlineStr"/>
+      <c r="ER4" t="inlineStr"/>
+      <c r="ES4" t="inlineStr"/>
+      <c r="ET4" t="inlineStr"/>
+      <c r="EU4" t="inlineStr"/>
+      <c r="EV4" t="inlineStr"/>
+      <c r="EW4" t="inlineStr"/>
+      <c r="EX4" t="inlineStr"/>
+      <c r="EY4" t="inlineStr"/>
+      <c r="EZ4" t="inlineStr"/>
+      <c r="FA4" t="inlineStr"/>
+      <c r="FB4" t="inlineStr"/>
+      <c r="FC4" t="inlineStr"/>
+      <c r="FD4" t="inlineStr"/>
+      <c r="FE4" t="inlineStr"/>
+      <c r="FF4" t="inlineStr"/>
+      <c r="FG4" t="inlineStr"/>
+      <c r="FH4" t="inlineStr"/>
+      <c r="FI4" t="inlineStr"/>
+      <c r="FJ4" t="inlineStr"/>
+      <c r="FK4" t="inlineStr"/>
+      <c r="FL4" t="inlineStr"/>
+      <c r="FM4" t="inlineStr"/>
+      <c r="FN4" t="inlineStr"/>
+      <c r="FO4" t="inlineStr"/>
+      <c r="FP4" t="inlineStr"/>
+      <c r="FQ4" t="inlineStr"/>
+      <c r="FR4" t="inlineStr"/>
+      <c r="FS4" t="inlineStr"/>
+      <c r="FT4" t="inlineStr"/>
+      <c r="FU4" t="inlineStr"/>
+      <c r="FV4" t="inlineStr"/>
+      <c r="FW4" t="inlineStr"/>
+      <c r="FX4" t="inlineStr"/>
+      <c r="FY4" t="inlineStr"/>
+      <c r="FZ4" t="inlineStr"/>
+      <c r="GA4" t="inlineStr"/>
+      <c r="GB4" t="inlineStr"/>
+      <c r="GC4" t="inlineStr"/>
+      <c r="GD4" t="inlineStr"/>
+      <c r="GE4" t="inlineStr"/>
+      <c r="GF4" t="inlineStr"/>
+      <c r="GG4" t="inlineStr"/>
+      <c r="GH4" t="inlineStr"/>
+      <c r="GI4" t="inlineStr"/>
+      <c r="GJ4" t="inlineStr"/>
+      <c r="GK4" t="inlineStr"/>
+      <c r="GL4" t="inlineStr"/>
+      <c r="GM4" t="inlineStr"/>
+      <c r="GN4" t="inlineStr"/>
+      <c r="GO4" t="inlineStr"/>
+      <c r="GP4" t="inlineStr"/>
+      <c r="GQ4" t="inlineStr"/>
+      <c r="GR4" t="inlineStr"/>
+      <c r="GS4" t="inlineStr"/>
+      <c r="GT4" t="inlineStr"/>
+      <c r="GU4" t="inlineStr"/>
+      <c r="GV4" t="inlineStr"/>
+      <c r="GW4" t="inlineStr"/>
+      <c r="GX4" t="inlineStr"/>
+      <c r="GY4" t="inlineStr"/>
+      <c r="GZ4" t="inlineStr"/>
+      <c r="HA4" t="inlineStr"/>
+      <c r="HB4" t="inlineStr"/>
+      <c r="HC4" t="inlineStr"/>
+      <c r="HD4" t="inlineStr"/>
+      <c r="HE4" t="inlineStr"/>
+      <c r="HF4" t="inlineStr"/>
+      <c r="HG4" t="inlineStr"/>
+      <c r="HH4" t="inlineStr"/>
+      <c r="HI4" t="inlineStr"/>
+      <c r="HJ4" t="inlineStr"/>
+      <c r="HK4" t="inlineStr"/>
+      <c r="HL4" t="inlineStr"/>
+      <c r="HM4" t="inlineStr"/>
+      <c r="HN4" t="inlineStr"/>
+      <c r="HO4" t="inlineStr"/>
+      <c r="HP4" t="inlineStr"/>
+      <c r="HQ4" t="inlineStr"/>
+      <c r="HR4" t="inlineStr"/>
+      <c r="HS4" t="inlineStr"/>
+      <c r="HT4" t="inlineStr"/>
+      <c r="HU4" t="inlineStr"/>
+      <c r="HV4" t="inlineStr"/>
+      <c r="HW4" t="inlineStr"/>
+      <c r="HX4" t="inlineStr"/>
+      <c r="HY4" t="inlineStr"/>
+      <c r="HZ4" t="inlineStr"/>
+      <c r="IA4" t="inlineStr"/>
+      <c r="IB4" t="inlineStr"/>
+      <c r="IC4" t="inlineStr"/>
+      <c r="ID4" t="inlineStr"/>
+      <c r="IE4" t="inlineStr"/>
+      <c r="IF4" t="inlineStr"/>
+      <c r="IG4" t="inlineStr"/>
+      <c r="IH4" t="inlineStr"/>
+      <c r="II4" t="inlineStr"/>
+      <c r="IJ4" t="inlineStr"/>
+      <c r="IK4" t="inlineStr"/>
+      <c r="IL4" t="inlineStr"/>
+      <c r="IM4" t="inlineStr"/>
+      <c r="IN4" t="inlineStr"/>
+      <c r="IO4" t="inlineStr"/>
+      <c r="IP4" t="inlineStr"/>
+      <c r="IQ4" t="inlineStr"/>
+      <c r="IR4" t="inlineStr"/>
+      <c r="IS4" t="inlineStr"/>
+      <c r="IT4" t="inlineStr"/>
+      <c r="IU4" t="inlineStr"/>
+      <c r="IV4" t="inlineStr"/>
+      <c r="IW4" t="inlineStr"/>
+      <c r="IX4" t="inlineStr"/>
+      <c r="IY4" t="inlineStr"/>
+      <c r="IZ4" t="inlineStr"/>
+      <c r="JA4" t="inlineStr"/>
+      <c r="JB4" t="inlineStr"/>
+      <c r="JC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1490,6 +3106,208 @@
       <c r="BI5" t="n">
         <v>0.1212439507557961</v>
       </c>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr"/>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr"/>
+      <c r="BO5" t="inlineStr"/>
+      <c r="BP5" t="inlineStr"/>
+      <c r="BQ5" t="inlineStr"/>
+      <c r="BR5" t="inlineStr"/>
+      <c r="BS5" t="inlineStr"/>
+      <c r="BT5" t="inlineStr"/>
+      <c r="BU5" t="inlineStr"/>
+      <c r="BV5" t="inlineStr"/>
+      <c r="BW5" t="inlineStr"/>
+      <c r="BX5" t="inlineStr"/>
+      <c r="BY5" t="inlineStr"/>
+      <c r="BZ5" t="inlineStr"/>
+      <c r="CA5" t="inlineStr"/>
+      <c r="CB5" t="inlineStr"/>
+      <c r="CC5" t="inlineStr"/>
+      <c r="CD5" t="inlineStr"/>
+      <c r="CE5" t="inlineStr"/>
+      <c r="CF5" t="inlineStr"/>
+      <c r="CG5" t="inlineStr"/>
+      <c r="CH5" t="inlineStr"/>
+      <c r="CI5" t="inlineStr"/>
+      <c r="CJ5" t="inlineStr"/>
+      <c r="CK5" t="inlineStr"/>
+      <c r="CL5" t="inlineStr"/>
+      <c r="CM5" t="inlineStr"/>
+      <c r="CN5" t="inlineStr"/>
+      <c r="CO5" t="inlineStr"/>
+      <c r="CP5" t="inlineStr"/>
+      <c r="CQ5" t="inlineStr"/>
+      <c r="CR5" t="inlineStr"/>
+      <c r="CS5" t="inlineStr"/>
+      <c r="CT5" t="inlineStr"/>
+      <c r="CU5" t="inlineStr"/>
+      <c r="CV5" t="inlineStr"/>
+      <c r="CW5" t="inlineStr"/>
+      <c r="CX5" t="inlineStr"/>
+      <c r="CY5" t="inlineStr"/>
+      <c r="CZ5" t="inlineStr"/>
+      <c r="DA5" t="inlineStr"/>
+      <c r="DB5" t="inlineStr"/>
+      <c r="DC5" t="inlineStr"/>
+      <c r="DD5" t="inlineStr"/>
+      <c r="DE5" t="inlineStr"/>
+      <c r="DF5" t="inlineStr"/>
+      <c r="DG5" t="inlineStr"/>
+      <c r="DH5" t="inlineStr"/>
+      <c r="DI5" t="inlineStr"/>
+      <c r="DJ5" t="inlineStr"/>
+      <c r="DK5" t="inlineStr"/>
+      <c r="DL5" t="inlineStr"/>
+      <c r="DM5" t="inlineStr"/>
+      <c r="DN5" t="inlineStr"/>
+      <c r="DO5" t="inlineStr"/>
+      <c r="DP5" t="inlineStr"/>
+      <c r="DQ5" t="inlineStr"/>
+      <c r="DR5" t="inlineStr"/>
+      <c r="DS5" t="inlineStr"/>
+      <c r="DT5" t="inlineStr"/>
+      <c r="DU5" t="inlineStr"/>
+      <c r="DV5" t="inlineStr"/>
+      <c r="DW5" t="inlineStr"/>
+      <c r="DX5" t="inlineStr"/>
+      <c r="DY5" t="inlineStr"/>
+      <c r="DZ5" t="inlineStr"/>
+      <c r="EA5" t="inlineStr"/>
+      <c r="EB5" t="inlineStr"/>
+      <c r="EC5" t="inlineStr"/>
+      <c r="ED5" t="inlineStr"/>
+      <c r="EE5" t="inlineStr"/>
+      <c r="EF5" t="inlineStr"/>
+      <c r="EG5" t="inlineStr"/>
+      <c r="EH5" t="inlineStr"/>
+      <c r="EI5" t="inlineStr"/>
+      <c r="EJ5" t="inlineStr"/>
+      <c r="EK5" t="inlineStr"/>
+      <c r="EL5" t="inlineStr"/>
+      <c r="EM5" t="inlineStr"/>
+      <c r="EN5" t="inlineStr"/>
+      <c r="EO5" t="inlineStr"/>
+      <c r="EP5" t="inlineStr"/>
+      <c r="EQ5" t="inlineStr"/>
+      <c r="ER5" t="inlineStr"/>
+      <c r="ES5" t="inlineStr"/>
+      <c r="ET5" t="inlineStr"/>
+      <c r="EU5" t="inlineStr"/>
+      <c r="EV5" t="inlineStr"/>
+      <c r="EW5" t="inlineStr"/>
+      <c r="EX5" t="inlineStr"/>
+      <c r="EY5" t="inlineStr"/>
+      <c r="EZ5" t="inlineStr"/>
+      <c r="FA5" t="inlineStr"/>
+      <c r="FB5" t="inlineStr"/>
+      <c r="FC5" t="inlineStr"/>
+      <c r="FD5" t="inlineStr"/>
+      <c r="FE5" t="inlineStr"/>
+      <c r="FF5" t="inlineStr"/>
+      <c r="FG5" t="inlineStr"/>
+      <c r="FH5" t="inlineStr"/>
+      <c r="FI5" t="inlineStr"/>
+      <c r="FJ5" t="inlineStr"/>
+      <c r="FK5" t="inlineStr"/>
+      <c r="FL5" t="inlineStr"/>
+      <c r="FM5" t="inlineStr"/>
+      <c r="FN5" t="inlineStr"/>
+      <c r="FO5" t="inlineStr"/>
+      <c r="FP5" t="inlineStr"/>
+      <c r="FQ5" t="inlineStr"/>
+      <c r="FR5" t="inlineStr"/>
+      <c r="FS5" t="inlineStr"/>
+      <c r="FT5" t="inlineStr"/>
+      <c r="FU5" t="inlineStr"/>
+      <c r="FV5" t="inlineStr"/>
+      <c r="FW5" t="inlineStr"/>
+      <c r="FX5" t="inlineStr"/>
+      <c r="FY5" t="inlineStr"/>
+      <c r="FZ5" t="inlineStr"/>
+      <c r="GA5" t="inlineStr"/>
+      <c r="GB5" t="inlineStr"/>
+      <c r="GC5" t="inlineStr"/>
+      <c r="GD5" t="inlineStr"/>
+      <c r="GE5" t="inlineStr"/>
+      <c r="GF5" t="inlineStr"/>
+      <c r="GG5" t="inlineStr"/>
+      <c r="GH5" t="inlineStr"/>
+      <c r="GI5" t="inlineStr"/>
+      <c r="GJ5" t="inlineStr"/>
+      <c r="GK5" t="inlineStr"/>
+      <c r="GL5" t="inlineStr"/>
+      <c r="GM5" t="inlineStr"/>
+      <c r="GN5" t="inlineStr"/>
+      <c r="GO5" t="inlineStr"/>
+      <c r="GP5" t="inlineStr"/>
+      <c r="GQ5" t="inlineStr"/>
+      <c r="GR5" t="inlineStr"/>
+      <c r="GS5" t="inlineStr"/>
+      <c r="GT5" t="inlineStr"/>
+      <c r="GU5" t="inlineStr"/>
+      <c r="GV5" t="inlineStr"/>
+      <c r="GW5" t="inlineStr"/>
+      <c r="GX5" t="inlineStr"/>
+      <c r="GY5" t="inlineStr"/>
+      <c r="GZ5" t="inlineStr"/>
+      <c r="HA5" t="inlineStr"/>
+      <c r="HB5" t="inlineStr"/>
+      <c r="HC5" t="inlineStr"/>
+      <c r="HD5" t="inlineStr"/>
+      <c r="HE5" t="inlineStr"/>
+      <c r="HF5" t="inlineStr"/>
+      <c r="HG5" t="inlineStr"/>
+      <c r="HH5" t="inlineStr"/>
+      <c r="HI5" t="inlineStr"/>
+      <c r="HJ5" t="inlineStr"/>
+      <c r="HK5" t="inlineStr"/>
+      <c r="HL5" t="inlineStr"/>
+      <c r="HM5" t="inlineStr"/>
+      <c r="HN5" t="inlineStr"/>
+      <c r="HO5" t="inlineStr"/>
+      <c r="HP5" t="inlineStr"/>
+      <c r="HQ5" t="inlineStr"/>
+      <c r="HR5" t="inlineStr"/>
+      <c r="HS5" t="inlineStr"/>
+      <c r="HT5" t="inlineStr"/>
+      <c r="HU5" t="inlineStr"/>
+      <c r="HV5" t="inlineStr"/>
+      <c r="HW5" t="inlineStr"/>
+      <c r="HX5" t="inlineStr"/>
+      <c r="HY5" t="inlineStr"/>
+      <c r="HZ5" t="inlineStr"/>
+      <c r="IA5" t="inlineStr"/>
+      <c r="IB5" t="inlineStr"/>
+      <c r="IC5" t="inlineStr"/>
+      <c r="ID5" t="inlineStr"/>
+      <c r="IE5" t="inlineStr"/>
+      <c r="IF5" t="inlineStr"/>
+      <c r="IG5" t="inlineStr"/>
+      <c r="IH5" t="inlineStr"/>
+      <c r="II5" t="inlineStr"/>
+      <c r="IJ5" t="inlineStr"/>
+      <c r="IK5" t="inlineStr"/>
+      <c r="IL5" t="inlineStr"/>
+      <c r="IM5" t="inlineStr"/>
+      <c r="IN5" t="inlineStr"/>
+      <c r="IO5" t="inlineStr"/>
+      <c r="IP5" t="inlineStr"/>
+      <c r="IQ5" t="inlineStr"/>
+      <c r="IR5" t="inlineStr"/>
+      <c r="IS5" t="inlineStr"/>
+      <c r="IT5" t="inlineStr"/>
+      <c r="IU5" t="inlineStr"/>
+      <c r="IV5" t="inlineStr"/>
+      <c r="IW5" t="inlineStr"/>
+      <c r="IX5" t="inlineStr"/>
+      <c r="IY5" t="inlineStr"/>
+      <c r="IZ5" t="inlineStr"/>
+      <c r="JA5" t="inlineStr"/>
+      <c r="JB5" t="inlineStr"/>
+      <c r="JC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1613,6 +3431,208 @@
       <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="inlineStr"/>
+      <c r="BP6" t="inlineStr"/>
+      <c r="BQ6" t="inlineStr"/>
+      <c r="BR6" t="inlineStr"/>
+      <c r="BS6" t="inlineStr"/>
+      <c r="BT6" t="inlineStr"/>
+      <c r="BU6" t="inlineStr"/>
+      <c r="BV6" t="inlineStr"/>
+      <c r="BW6" t="inlineStr"/>
+      <c r="BX6" t="inlineStr"/>
+      <c r="BY6" t="inlineStr"/>
+      <c r="BZ6" t="inlineStr"/>
+      <c r="CA6" t="inlineStr"/>
+      <c r="CB6" t="inlineStr"/>
+      <c r="CC6" t="inlineStr"/>
+      <c r="CD6" t="inlineStr"/>
+      <c r="CE6" t="inlineStr"/>
+      <c r="CF6" t="inlineStr"/>
+      <c r="CG6" t="inlineStr"/>
+      <c r="CH6" t="inlineStr"/>
+      <c r="CI6" t="inlineStr"/>
+      <c r="CJ6" t="inlineStr"/>
+      <c r="CK6" t="inlineStr"/>
+      <c r="CL6" t="inlineStr"/>
+      <c r="CM6" t="inlineStr"/>
+      <c r="CN6" t="inlineStr"/>
+      <c r="CO6" t="inlineStr"/>
+      <c r="CP6" t="inlineStr"/>
+      <c r="CQ6" t="inlineStr"/>
+      <c r="CR6" t="inlineStr"/>
+      <c r="CS6" t="inlineStr"/>
+      <c r="CT6" t="inlineStr"/>
+      <c r="CU6" t="inlineStr"/>
+      <c r="CV6" t="inlineStr"/>
+      <c r="CW6" t="inlineStr"/>
+      <c r="CX6" t="inlineStr"/>
+      <c r="CY6" t="inlineStr"/>
+      <c r="CZ6" t="inlineStr"/>
+      <c r="DA6" t="inlineStr"/>
+      <c r="DB6" t="inlineStr"/>
+      <c r="DC6" t="inlineStr"/>
+      <c r="DD6" t="inlineStr"/>
+      <c r="DE6" t="inlineStr"/>
+      <c r="DF6" t="inlineStr"/>
+      <c r="DG6" t="inlineStr"/>
+      <c r="DH6" t="inlineStr"/>
+      <c r="DI6" t="inlineStr"/>
+      <c r="DJ6" t="inlineStr"/>
+      <c r="DK6" t="inlineStr"/>
+      <c r="DL6" t="inlineStr"/>
+      <c r="DM6" t="inlineStr"/>
+      <c r="DN6" t="inlineStr"/>
+      <c r="DO6" t="inlineStr"/>
+      <c r="DP6" t="inlineStr"/>
+      <c r="DQ6" t="inlineStr"/>
+      <c r="DR6" t="inlineStr"/>
+      <c r="DS6" t="inlineStr"/>
+      <c r="DT6" t="inlineStr"/>
+      <c r="DU6" t="inlineStr"/>
+      <c r="DV6" t="inlineStr"/>
+      <c r="DW6" t="inlineStr"/>
+      <c r="DX6" t="inlineStr"/>
+      <c r="DY6" t="inlineStr"/>
+      <c r="DZ6" t="inlineStr"/>
+      <c r="EA6" t="inlineStr"/>
+      <c r="EB6" t="inlineStr"/>
+      <c r="EC6" t="inlineStr"/>
+      <c r="ED6" t="inlineStr"/>
+      <c r="EE6" t="inlineStr"/>
+      <c r="EF6" t="inlineStr"/>
+      <c r="EG6" t="inlineStr"/>
+      <c r="EH6" t="inlineStr"/>
+      <c r="EI6" t="inlineStr"/>
+      <c r="EJ6" t="inlineStr"/>
+      <c r="EK6" t="inlineStr"/>
+      <c r="EL6" t="inlineStr"/>
+      <c r="EM6" t="inlineStr"/>
+      <c r="EN6" t="inlineStr"/>
+      <c r="EO6" t="inlineStr"/>
+      <c r="EP6" t="inlineStr"/>
+      <c r="EQ6" t="inlineStr"/>
+      <c r="ER6" t="inlineStr"/>
+      <c r="ES6" t="inlineStr"/>
+      <c r="ET6" t="inlineStr"/>
+      <c r="EU6" t="inlineStr"/>
+      <c r="EV6" t="inlineStr"/>
+      <c r="EW6" t="inlineStr"/>
+      <c r="EX6" t="inlineStr"/>
+      <c r="EY6" t="inlineStr"/>
+      <c r="EZ6" t="inlineStr"/>
+      <c r="FA6" t="inlineStr"/>
+      <c r="FB6" t="inlineStr"/>
+      <c r="FC6" t="inlineStr"/>
+      <c r="FD6" t="inlineStr"/>
+      <c r="FE6" t="inlineStr"/>
+      <c r="FF6" t="inlineStr"/>
+      <c r="FG6" t="inlineStr"/>
+      <c r="FH6" t="inlineStr"/>
+      <c r="FI6" t="inlineStr"/>
+      <c r="FJ6" t="inlineStr"/>
+      <c r="FK6" t="inlineStr"/>
+      <c r="FL6" t="inlineStr"/>
+      <c r="FM6" t="inlineStr"/>
+      <c r="FN6" t="inlineStr"/>
+      <c r="FO6" t="inlineStr"/>
+      <c r="FP6" t="inlineStr"/>
+      <c r="FQ6" t="inlineStr"/>
+      <c r="FR6" t="inlineStr"/>
+      <c r="FS6" t="inlineStr"/>
+      <c r="FT6" t="inlineStr"/>
+      <c r="FU6" t="inlineStr"/>
+      <c r="FV6" t="inlineStr"/>
+      <c r="FW6" t="inlineStr"/>
+      <c r="FX6" t="inlineStr"/>
+      <c r="FY6" t="inlineStr"/>
+      <c r="FZ6" t="inlineStr"/>
+      <c r="GA6" t="inlineStr"/>
+      <c r="GB6" t="inlineStr"/>
+      <c r="GC6" t="inlineStr"/>
+      <c r="GD6" t="inlineStr"/>
+      <c r="GE6" t="inlineStr"/>
+      <c r="GF6" t="inlineStr"/>
+      <c r="GG6" t="inlineStr"/>
+      <c r="GH6" t="inlineStr"/>
+      <c r="GI6" t="inlineStr"/>
+      <c r="GJ6" t="inlineStr"/>
+      <c r="GK6" t="inlineStr"/>
+      <c r="GL6" t="inlineStr"/>
+      <c r="GM6" t="inlineStr"/>
+      <c r="GN6" t="inlineStr"/>
+      <c r="GO6" t="inlineStr"/>
+      <c r="GP6" t="inlineStr"/>
+      <c r="GQ6" t="inlineStr"/>
+      <c r="GR6" t="inlineStr"/>
+      <c r="GS6" t="inlineStr"/>
+      <c r="GT6" t="inlineStr"/>
+      <c r="GU6" t="inlineStr"/>
+      <c r="GV6" t="inlineStr"/>
+      <c r="GW6" t="inlineStr"/>
+      <c r="GX6" t="inlineStr"/>
+      <c r="GY6" t="inlineStr"/>
+      <c r="GZ6" t="inlineStr"/>
+      <c r="HA6" t="inlineStr"/>
+      <c r="HB6" t="inlineStr"/>
+      <c r="HC6" t="inlineStr"/>
+      <c r="HD6" t="inlineStr"/>
+      <c r="HE6" t="inlineStr"/>
+      <c r="HF6" t="inlineStr"/>
+      <c r="HG6" t="inlineStr"/>
+      <c r="HH6" t="inlineStr"/>
+      <c r="HI6" t="inlineStr"/>
+      <c r="HJ6" t="inlineStr"/>
+      <c r="HK6" t="inlineStr"/>
+      <c r="HL6" t="inlineStr"/>
+      <c r="HM6" t="inlineStr"/>
+      <c r="HN6" t="inlineStr"/>
+      <c r="HO6" t="inlineStr"/>
+      <c r="HP6" t="inlineStr"/>
+      <c r="HQ6" t="inlineStr"/>
+      <c r="HR6" t="inlineStr"/>
+      <c r="HS6" t="inlineStr"/>
+      <c r="HT6" t="inlineStr"/>
+      <c r="HU6" t="inlineStr"/>
+      <c r="HV6" t="inlineStr"/>
+      <c r="HW6" t="inlineStr"/>
+      <c r="HX6" t="inlineStr"/>
+      <c r="HY6" t="inlineStr"/>
+      <c r="HZ6" t="inlineStr"/>
+      <c r="IA6" t="inlineStr"/>
+      <c r="IB6" t="inlineStr"/>
+      <c r="IC6" t="inlineStr"/>
+      <c r="ID6" t="inlineStr"/>
+      <c r="IE6" t="inlineStr"/>
+      <c r="IF6" t="inlineStr"/>
+      <c r="IG6" t="inlineStr"/>
+      <c r="IH6" t="inlineStr"/>
+      <c r="II6" t="inlineStr"/>
+      <c r="IJ6" t="inlineStr"/>
+      <c r="IK6" t="inlineStr"/>
+      <c r="IL6" t="inlineStr"/>
+      <c r="IM6" t="inlineStr"/>
+      <c r="IN6" t="inlineStr"/>
+      <c r="IO6" t="inlineStr"/>
+      <c r="IP6" t="inlineStr"/>
+      <c r="IQ6" t="inlineStr"/>
+      <c r="IR6" t="inlineStr"/>
+      <c r="IS6" t="inlineStr"/>
+      <c r="IT6" t="inlineStr"/>
+      <c r="IU6" t="inlineStr"/>
+      <c r="IV6" t="inlineStr"/>
+      <c r="IW6" t="inlineStr"/>
+      <c r="IX6" t="inlineStr"/>
+      <c r="IY6" t="inlineStr"/>
+      <c r="IZ6" t="inlineStr"/>
+      <c r="JA6" t="inlineStr"/>
+      <c r="JB6" t="inlineStr"/>
+      <c r="JC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1736,6 +3756,208 @@
       <c r="BG7" t="inlineStr"/>
       <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="inlineStr"/>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="inlineStr"/>
+      <c r="BM7" t="inlineStr"/>
+      <c r="BN7" t="inlineStr"/>
+      <c r="BO7" t="inlineStr"/>
+      <c r="BP7" t="inlineStr"/>
+      <c r="BQ7" t="inlineStr"/>
+      <c r="BR7" t="inlineStr"/>
+      <c r="BS7" t="inlineStr"/>
+      <c r="BT7" t="inlineStr"/>
+      <c r="BU7" t="inlineStr"/>
+      <c r="BV7" t="inlineStr"/>
+      <c r="BW7" t="inlineStr"/>
+      <c r="BX7" t="inlineStr"/>
+      <c r="BY7" t="inlineStr"/>
+      <c r="BZ7" t="inlineStr"/>
+      <c r="CA7" t="inlineStr"/>
+      <c r="CB7" t="inlineStr"/>
+      <c r="CC7" t="inlineStr"/>
+      <c r="CD7" t="inlineStr"/>
+      <c r="CE7" t="inlineStr"/>
+      <c r="CF7" t="inlineStr"/>
+      <c r="CG7" t="inlineStr"/>
+      <c r="CH7" t="inlineStr"/>
+      <c r="CI7" t="inlineStr"/>
+      <c r="CJ7" t="inlineStr"/>
+      <c r="CK7" t="inlineStr"/>
+      <c r="CL7" t="inlineStr"/>
+      <c r="CM7" t="inlineStr"/>
+      <c r="CN7" t="inlineStr"/>
+      <c r="CO7" t="inlineStr"/>
+      <c r="CP7" t="inlineStr"/>
+      <c r="CQ7" t="inlineStr"/>
+      <c r="CR7" t="inlineStr"/>
+      <c r="CS7" t="inlineStr"/>
+      <c r="CT7" t="inlineStr"/>
+      <c r="CU7" t="inlineStr"/>
+      <c r="CV7" t="inlineStr"/>
+      <c r="CW7" t="inlineStr"/>
+      <c r="CX7" t="inlineStr"/>
+      <c r="CY7" t="inlineStr"/>
+      <c r="CZ7" t="inlineStr"/>
+      <c r="DA7" t="inlineStr"/>
+      <c r="DB7" t="inlineStr"/>
+      <c r="DC7" t="inlineStr"/>
+      <c r="DD7" t="inlineStr"/>
+      <c r="DE7" t="inlineStr"/>
+      <c r="DF7" t="inlineStr"/>
+      <c r="DG7" t="inlineStr"/>
+      <c r="DH7" t="inlineStr"/>
+      <c r="DI7" t="inlineStr"/>
+      <c r="DJ7" t="inlineStr"/>
+      <c r="DK7" t="inlineStr"/>
+      <c r="DL7" t="inlineStr"/>
+      <c r="DM7" t="inlineStr"/>
+      <c r="DN7" t="inlineStr"/>
+      <c r="DO7" t="inlineStr"/>
+      <c r="DP7" t="inlineStr"/>
+      <c r="DQ7" t="inlineStr"/>
+      <c r="DR7" t="inlineStr"/>
+      <c r="DS7" t="inlineStr"/>
+      <c r="DT7" t="inlineStr"/>
+      <c r="DU7" t="inlineStr"/>
+      <c r="DV7" t="inlineStr"/>
+      <c r="DW7" t="inlineStr"/>
+      <c r="DX7" t="inlineStr"/>
+      <c r="DY7" t="inlineStr"/>
+      <c r="DZ7" t="inlineStr"/>
+      <c r="EA7" t="inlineStr"/>
+      <c r="EB7" t="inlineStr"/>
+      <c r="EC7" t="inlineStr"/>
+      <c r="ED7" t="inlineStr"/>
+      <c r="EE7" t="inlineStr"/>
+      <c r="EF7" t="inlineStr"/>
+      <c r="EG7" t="inlineStr"/>
+      <c r="EH7" t="inlineStr"/>
+      <c r="EI7" t="inlineStr"/>
+      <c r="EJ7" t="inlineStr"/>
+      <c r="EK7" t="inlineStr"/>
+      <c r="EL7" t="inlineStr"/>
+      <c r="EM7" t="inlineStr"/>
+      <c r="EN7" t="inlineStr"/>
+      <c r="EO7" t="inlineStr"/>
+      <c r="EP7" t="inlineStr"/>
+      <c r="EQ7" t="inlineStr"/>
+      <c r="ER7" t="inlineStr"/>
+      <c r="ES7" t="inlineStr"/>
+      <c r="ET7" t="inlineStr"/>
+      <c r="EU7" t="inlineStr"/>
+      <c r="EV7" t="inlineStr"/>
+      <c r="EW7" t="inlineStr"/>
+      <c r="EX7" t="inlineStr"/>
+      <c r="EY7" t="inlineStr"/>
+      <c r="EZ7" t="inlineStr"/>
+      <c r="FA7" t="inlineStr"/>
+      <c r="FB7" t="inlineStr"/>
+      <c r="FC7" t="inlineStr"/>
+      <c r="FD7" t="inlineStr"/>
+      <c r="FE7" t="inlineStr"/>
+      <c r="FF7" t="inlineStr"/>
+      <c r="FG7" t="inlineStr"/>
+      <c r="FH7" t="inlineStr"/>
+      <c r="FI7" t="inlineStr"/>
+      <c r="FJ7" t="inlineStr"/>
+      <c r="FK7" t="inlineStr"/>
+      <c r="FL7" t="inlineStr"/>
+      <c r="FM7" t="inlineStr"/>
+      <c r="FN7" t="inlineStr"/>
+      <c r="FO7" t="inlineStr"/>
+      <c r="FP7" t="inlineStr"/>
+      <c r="FQ7" t="inlineStr"/>
+      <c r="FR7" t="inlineStr"/>
+      <c r="FS7" t="inlineStr"/>
+      <c r="FT7" t="inlineStr"/>
+      <c r="FU7" t="inlineStr"/>
+      <c r="FV7" t="inlineStr"/>
+      <c r="FW7" t="inlineStr"/>
+      <c r="FX7" t="inlineStr"/>
+      <c r="FY7" t="inlineStr"/>
+      <c r="FZ7" t="inlineStr"/>
+      <c r="GA7" t="inlineStr"/>
+      <c r="GB7" t="inlineStr"/>
+      <c r="GC7" t="inlineStr"/>
+      <c r="GD7" t="inlineStr"/>
+      <c r="GE7" t="inlineStr"/>
+      <c r="GF7" t="inlineStr"/>
+      <c r="GG7" t="inlineStr"/>
+      <c r="GH7" t="inlineStr"/>
+      <c r="GI7" t="inlineStr"/>
+      <c r="GJ7" t="inlineStr"/>
+      <c r="GK7" t="inlineStr"/>
+      <c r="GL7" t="inlineStr"/>
+      <c r="GM7" t="inlineStr"/>
+      <c r="GN7" t="inlineStr"/>
+      <c r="GO7" t="inlineStr"/>
+      <c r="GP7" t="inlineStr"/>
+      <c r="GQ7" t="inlineStr"/>
+      <c r="GR7" t="inlineStr"/>
+      <c r="GS7" t="inlineStr"/>
+      <c r="GT7" t="inlineStr"/>
+      <c r="GU7" t="inlineStr"/>
+      <c r="GV7" t="inlineStr"/>
+      <c r="GW7" t="inlineStr"/>
+      <c r="GX7" t="inlineStr"/>
+      <c r="GY7" t="inlineStr"/>
+      <c r="GZ7" t="inlineStr"/>
+      <c r="HA7" t="inlineStr"/>
+      <c r="HB7" t="inlineStr"/>
+      <c r="HC7" t="inlineStr"/>
+      <c r="HD7" t="inlineStr"/>
+      <c r="HE7" t="inlineStr"/>
+      <c r="HF7" t="inlineStr"/>
+      <c r="HG7" t="inlineStr"/>
+      <c r="HH7" t="inlineStr"/>
+      <c r="HI7" t="inlineStr"/>
+      <c r="HJ7" t="inlineStr"/>
+      <c r="HK7" t="inlineStr"/>
+      <c r="HL7" t="inlineStr"/>
+      <c r="HM7" t="inlineStr"/>
+      <c r="HN7" t="inlineStr"/>
+      <c r="HO7" t="inlineStr"/>
+      <c r="HP7" t="inlineStr"/>
+      <c r="HQ7" t="inlineStr"/>
+      <c r="HR7" t="inlineStr"/>
+      <c r="HS7" t="inlineStr"/>
+      <c r="HT7" t="inlineStr"/>
+      <c r="HU7" t="inlineStr"/>
+      <c r="HV7" t="inlineStr"/>
+      <c r="HW7" t="inlineStr"/>
+      <c r="HX7" t="inlineStr"/>
+      <c r="HY7" t="inlineStr"/>
+      <c r="HZ7" t="inlineStr"/>
+      <c r="IA7" t="inlineStr"/>
+      <c r="IB7" t="inlineStr"/>
+      <c r="IC7" t="inlineStr"/>
+      <c r="ID7" t="inlineStr"/>
+      <c r="IE7" t="inlineStr"/>
+      <c r="IF7" t="inlineStr"/>
+      <c r="IG7" t="inlineStr"/>
+      <c r="IH7" t="inlineStr"/>
+      <c r="II7" t="inlineStr"/>
+      <c r="IJ7" t="inlineStr"/>
+      <c r="IK7" t="inlineStr"/>
+      <c r="IL7" t="inlineStr"/>
+      <c r="IM7" t="inlineStr"/>
+      <c r="IN7" t="inlineStr"/>
+      <c r="IO7" t="inlineStr"/>
+      <c r="IP7" t="inlineStr"/>
+      <c r="IQ7" t="inlineStr"/>
+      <c r="IR7" t="inlineStr"/>
+      <c r="IS7" t="inlineStr"/>
+      <c r="IT7" t="inlineStr"/>
+      <c r="IU7" t="inlineStr"/>
+      <c r="IV7" t="inlineStr"/>
+      <c r="IW7" t="inlineStr"/>
+      <c r="IX7" t="inlineStr"/>
+      <c r="IY7" t="inlineStr"/>
+      <c r="IZ7" t="inlineStr"/>
+      <c r="JA7" t="inlineStr"/>
+      <c r="JB7" t="inlineStr"/>
+      <c r="JC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1869,7 +4091,7 @@
         <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
         <v>0.01269718614916328</v>
@@ -1924,6 +4146,1394 @@
       </c>
       <c r="BI8" t="n">
         <v>0.06162362132781011</v>
+      </c>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="inlineStr"/>
+      <c r="BM8" t="inlineStr"/>
+      <c r="BN8" t="inlineStr"/>
+      <c r="BO8" t="inlineStr"/>
+      <c r="BP8" t="inlineStr"/>
+      <c r="BQ8" t="inlineStr"/>
+      <c r="BR8" t="inlineStr"/>
+      <c r="BS8" t="inlineStr"/>
+      <c r="BT8" t="inlineStr"/>
+      <c r="BU8" t="inlineStr"/>
+      <c r="BV8" t="inlineStr"/>
+      <c r="BW8" t="inlineStr"/>
+      <c r="BX8" t="inlineStr"/>
+      <c r="BY8" t="inlineStr"/>
+      <c r="BZ8" t="inlineStr"/>
+      <c r="CA8" t="inlineStr"/>
+      <c r="CB8" t="inlineStr"/>
+      <c r="CC8" t="inlineStr"/>
+      <c r="CD8" t="inlineStr"/>
+      <c r="CE8" t="inlineStr"/>
+      <c r="CF8" t="inlineStr"/>
+      <c r="CG8" t="inlineStr"/>
+      <c r="CH8" t="inlineStr"/>
+      <c r="CI8" t="inlineStr"/>
+      <c r="CJ8" t="inlineStr"/>
+      <c r="CK8" t="inlineStr"/>
+      <c r="CL8" t="inlineStr"/>
+      <c r="CM8" t="inlineStr"/>
+      <c r="CN8" t="inlineStr"/>
+      <c r="CO8" t="inlineStr"/>
+      <c r="CP8" t="inlineStr"/>
+      <c r="CQ8" t="inlineStr"/>
+      <c r="CR8" t="inlineStr"/>
+      <c r="CS8" t="inlineStr"/>
+      <c r="CT8" t="inlineStr"/>
+      <c r="CU8" t="inlineStr"/>
+      <c r="CV8" t="inlineStr"/>
+      <c r="CW8" t="inlineStr"/>
+      <c r="CX8" t="inlineStr"/>
+      <c r="CY8" t="inlineStr"/>
+      <c r="CZ8" t="inlineStr"/>
+      <c r="DA8" t="inlineStr"/>
+      <c r="DB8" t="inlineStr"/>
+      <c r="DC8" t="inlineStr"/>
+      <c r="DD8" t="inlineStr"/>
+      <c r="DE8" t="inlineStr"/>
+      <c r="DF8" t="inlineStr"/>
+      <c r="DG8" t="inlineStr"/>
+      <c r="DH8" t="inlineStr"/>
+      <c r="DI8" t="inlineStr"/>
+      <c r="DJ8" t="inlineStr"/>
+      <c r="DK8" t="inlineStr"/>
+      <c r="DL8" t="inlineStr"/>
+      <c r="DM8" t="inlineStr"/>
+      <c r="DN8" t="inlineStr"/>
+      <c r="DO8" t="inlineStr"/>
+      <c r="DP8" t="inlineStr"/>
+      <c r="DQ8" t="inlineStr"/>
+      <c r="DR8" t="inlineStr"/>
+      <c r="DS8" t="inlineStr"/>
+      <c r="DT8" t="inlineStr"/>
+      <c r="DU8" t="inlineStr"/>
+      <c r="DV8" t="inlineStr"/>
+      <c r="DW8" t="inlineStr"/>
+      <c r="DX8" t="inlineStr"/>
+      <c r="DY8" t="inlineStr"/>
+      <c r="DZ8" t="inlineStr"/>
+      <c r="EA8" t="inlineStr"/>
+      <c r="EB8" t="inlineStr"/>
+      <c r="EC8" t="inlineStr"/>
+      <c r="ED8" t="inlineStr"/>
+      <c r="EE8" t="inlineStr"/>
+      <c r="EF8" t="inlineStr"/>
+      <c r="EG8" t="inlineStr"/>
+      <c r="EH8" t="inlineStr"/>
+      <c r="EI8" t="inlineStr"/>
+      <c r="EJ8" t="inlineStr"/>
+      <c r="EK8" t="inlineStr"/>
+      <c r="EL8" t="inlineStr"/>
+      <c r="EM8" t="inlineStr"/>
+      <c r="EN8" t="inlineStr"/>
+      <c r="EO8" t="inlineStr"/>
+      <c r="EP8" t="inlineStr"/>
+      <c r="EQ8" t="inlineStr"/>
+      <c r="ER8" t="inlineStr"/>
+      <c r="ES8" t="inlineStr"/>
+      <c r="ET8" t="inlineStr"/>
+      <c r="EU8" t="inlineStr"/>
+      <c r="EV8" t="inlineStr"/>
+      <c r="EW8" t="inlineStr"/>
+      <c r="EX8" t="inlineStr"/>
+      <c r="EY8" t="inlineStr"/>
+      <c r="EZ8" t="inlineStr"/>
+      <c r="FA8" t="inlineStr"/>
+      <c r="FB8" t="inlineStr"/>
+      <c r="FC8" t="inlineStr"/>
+      <c r="FD8" t="inlineStr"/>
+      <c r="FE8" t="inlineStr"/>
+      <c r="FF8" t="inlineStr"/>
+      <c r="FG8" t="inlineStr"/>
+      <c r="FH8" t="inlineStr"/>
+      <c r="FI8" t="inlineStr"/>
+      <c r="FJ8" t="inlineStr"/>
+      <c r="FK8" t="inlineStr"/>
+      <c r="FL8" t="inlineStr"/>
+      <c r="FM8" t="inlineStr"/>
+      <c r="FN8" t="inlineStr"/>
+      <c r="FO8" t="inlineStr"/>
+      <c r="FP8" t="inlineStr"/>
+      <c r="FQ8" t="inlineStr"/>
+      <c r="FR8" t="inlineStr"/>
+      <c r="FS8" t="inlineStr"/>
+      <c r="FT8" t="inlineStr"/>
+      <c r="FU8" t="inlineStr"/>
+      <c r="FV8" t="inlineStr"/>
+      <c r="FW8" t="inlineStr"/>
+      <c r="FX8" t="inlineStr"/>
+      <c r="FY8" t="inlineStr"/>
+      <c r="FZ8" t="inlineStr"/>
+      <c r="GA8" t="inlineStr"/>
+      <c r="GB8" t="inlineStr"/>
+      <c r="GC8" t="inlineStr"/>
+      <c r="GD8" t="inlineStr"/>
+      <c r="GE8" t="inlineStr"/>
+      <c r="GF8" t="inlineStr"/>
+      <c r="GG8" t="inlineStr"/>
+      <c r="GH8" t="inlineStr"/>
+      <c r="GI8" t="inlineStr"/>
+      <c r="GJ8" t="inlineStr"/>
+      <c r="GK8" t="inlineStr"/>
+      <c r="GL8" t="inlineStr"/>
+      <c r="GM8" t="inlineStr"/>
+      <c r="GN8" t="inlineStr"/>
+      <c r="GO8" t="inlineStr"/>
+      <c r="GP8" t="inlineStr"/>
+      <c r="GQ8" t="inlineStr"/>
+      <c r="GR8" t="inlineStr"/>
+      <c r="GS8" t="inlineStr"/>
+      <c r="GT8" t="inlineStr"/>
+      <c r="GU8" t="inlineStr"/>
+      <c r="GV8" t="inlineStr"/>
+      <c r="GW8" t="inlineStr"/>
+      <c r="GX8" t="inlineStr"/>
+      <c r="GY8" t="inlineStr"/>
+      <c r="GZ8" t="inlineStr"/>
+      <c r="HA8" t="inlineStr"/>
+      <c r="HB8" t="inlineStr"/>
+      <c r="HC8" t="inlineStr"/>
+      <c r="HD8" t="inlineStr"/>
+      <c r="HE8" t="inlineStr"/>
+      <c r="HF8" t="inlineStr"/>
+      <c r="HG8" t="inlineStr"/>
+      <c r="HH8" t="inlineStr"/>
+      <c r="HI8" t="inlineStr"/>
+      <c r="HJ8" t="inlineStr"/>
+      <c r="HK8" t="inlineStr"/>
+      <c r="HL8" t="inlineStr"/>
+      <c r="HM8" t="inlineStr"/>
+      <c r="HN8" t="inlineStr"/>
+      <c r="HO8" t="inlineStr"/>
+      <c r="HP8" t="inlineStr"/>
+      <c r="HQ8" t="inlineStr"/>
+      <c r="HR8" t="inlineStr"/>
+      <c r="HS8" t="inlineStr"/>
+      <c r="HT8" t="inlineStr"/>
+      <c r="HU8" t="inlineStr"/>
+      <c r="HV8" t="inlineStr"/>
+      <c r="HW8" t="inlineStr"/>
+      <c r="HX8" t="inlineStr"/>
+      <c r="HY8" t="inlineStr"/>
+      <c r="HZ8" t="inlineStr"/>
+      <c r="IA8" t="inlineStr"/>
+      <c r="IB8" t="inlineStr"/>
+      <c r="IC8" t="inlineStr"/>
+      <c r="ID8" t="inlineStr"/>
+      <c r="IE8" t="inlineStr"/>
+      <c r="IF8" t="inlineStr"/>
+      <c r="IG8" t="inlineStr"/>
+      <c r="IH8" t="inlineStr"/>
+      <c r="II8" t="inlineStr"/>
+      <c r="IJ8" t="inlineStr"/>
+      <c r="IK8" t="inlineStr"/>
+      <c r="IL8" t="inlineStr"/>
+      <c r="IM8" t="inlineStr"/>
+      <c r="IN8" t="inlineStr"/>
+      <c r="IO8" t="inlineStr"/>
+      <c r="IP8" t="inlineStr"/>
+      <c r="IQ8" t="inlineStr"/>
+      <c r="IR8" t="inlineStr"/>
+      <c r="IS8" t="inlineStr"/>
+      <c r="IT8" t="inlineStr"/>
+      <c r="IU8" t="inlineStr"/>
+      <c r="IV8" t="inlineStr"/>
+      <c r="IW8" t="inlineStr"/>
+      <c r="IX8" t="inlineStr"/>
+      <c r="IY8" t="inlineStr"/>
+      <c r="IZ8" t="inlineStr"/>
+      <c r="JA8" t="inlineStr"/>
+      <c r="JB8" t="inlineStr"/>
+      <c r="JC8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-15 19:56:28</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>10</v>
+      </c>
+      <c r="C9" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="n">
+        <v>50</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.2044303924470618</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.2704777759813683</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.2048216012922055</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.2328183299709716</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.4249803482695367</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.3986680104959187</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.4212854927252067</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.4236115578963774</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.3704367657024817</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.3415515886228851</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.3768267838819982</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.3675741906306866</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.4598925759210001</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.4140917151782204</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.4558455495281818</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.4569363138320738</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.4870043257487428</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.4431867587416085</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.4910133034994928</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.4814901592183074</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.4470293253794135</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.414395234732183</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.4441932107907695</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.4448071973146608</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.1485767156532186</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.1766592515118739</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.1409833186875777</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.1607189984478839</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.05025686602566577</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.0868420746711223</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0.05746168108188222</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.0760117042319861</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.04749116049392684</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.07858330124326965</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.06341618410332273</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0.06587518295912001</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0.08247721154412875</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0.1100016128056689</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0.08440093287716685</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.1003719994628212</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0.02051944134920436</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0.002687993818039751</v>
+      </c>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+      <c r="BO9" t="inlineStr"/>
+      <c r="BP9" t="inlineStr"/>
+      <c r="BQ9" t="inlineStr"/>
+      <c r="BR9" t="inlineStr"/>
+      <c r="BS9" t="inlineStr"/>
+      <c r="BT9" t="inlineStr"/>
+      <c r="BU9" t="inlineStr"/>
+      <c r="BV9" t="inlineStr"/>
+      <c r="BW9" t="inlineStr"/>
+      <c r="BX9" t="inlineStr"/>
+      <c r="BY9" t="inlineStr"/>
+      <c r="BZ9" t="inlineStr"/>
+      <c r="CA9" t="inlineStr"/>
+      <c r="CB9" t="inlineStr"/>
+      <c r="CC9" t="inlineStr"/>
+      <c r="CD9" t="inlineStr"/>
+      <c r="CE9" t="inlineStr"/>
+      <c r="CF9" t="inlineStr"/>
+      <c r="CG9" t="inlineStr"/>
+      <c r="CH9" t="inlineStr"/>
+      <c r="CI9" t="inlineStr"/>
+      <c r="CJ9" t="inlineStr"/>
+      <c r="CK9" t="inlineStr"/>
+      <c r="CL9" t="inlineStr"/>
+      <c r="CM9" t="inlineStr"/>
+      <c r="CN9" t="inlineStr"/>
+      <c r="CO9" t="inlineStr"/>
+      <c r="CP9" t="inlineStr"/>
+      <c r="CQ9" t="inlineStr"/>
+      <c r="CR9" t="inlineStr"/>
+      <c r="CS9" t="inlineStr"/>
+      <c r="CT9" t="inlineStr"/>
+      <c r="CU9" t="inlineStr"/>
+      <c r="CV9" t="inlineStr"/>
+      <c r="CW9" t="inlineStr"/>
+      <c r="CX9" t="inlineStr"/>
+      <c r="CY9" t="inlineStr"/>
+      <c r="CZ9" t="inlineStr"/>
+      <c r="DA9" t="inlineStr"/>
+      <c r="DB9" t="inlineStr"/>
+      <c r="DC9" t="inlineStr"/>
+      <c r="DD9" t="inlineStr"/>
+      <c r="DE9" t="inlineStr"/>
+      <c r="DF9" t="inlineStr"/>
+      <c r="DG9" t="inlineStr"/>
+      <c r="DH9" t="inlineStr"/>
+      <c r="DI9" t="inlineStr"/>
+      <c r="DJ9" t="inlineStr"/>
+      <c r="DK9" t="inlineStr"/>
+      <c r="DL9" t="inlineStr"/>
+      <c r="DM9" t="inlineStr"/>
+      <c r="DN9" t="inlineStr"/>
+      <c r="DO9" t="inlineStr"/>
+      <c r="DP9" t="inlineStr"/>
+      <c r="DQ9" t="inlineStr"/>
+      <c r="DR9" t="inlineStr"/>
+      <c r="DS9" t="inlineStr"/>
+      <c r="DT9" t="inlineStr"/>
+      <c r="DU9" t="inlineStr"/>
+      <c r="DV9" t="inlineStr"/>
+      <c r="DW9" t="inlineStr"/>
+      <c r="DX9" t="inlineStr"/>
+      <c r="DY9" t="inlineStr"/>
+      <c r="DZ9" t="inlineStr"/>
+      <c r="EA9" t="inlineStr"/>
+      <c r="EB9" t="inlineStr"/>
+      <c r="EC9" t="inlineStr"/>
+      <c r="ED9" t="inlineStr"/>
+      <c r="EE9" t="inlineStr"/>
+      <c r="EF9" t="inlineStr"/>
+      <c r="EG9" t="inlineStr"/>
+      <c r="EH9" t="inlineStr"/>
+      <c r="EI9" t="inlineStr"/>
+      <c r="EJ9" t="inlineStr"/>
+      <c r="EK9" t="inlineStr"/>
+      <c r="EL9" t="inlineStr"/>
+      <c r="EM9" t="inlineStr"/>
+      <c r="EN9" t="inlineStr"/>
+      <c r="EO9" t="inlineStr"/>
+      <c r="EP9" t="inlineStr"/>
+      <c r="EQ9" t="inlineStr"/>
+      <c r="ER9" t="inlineStr"/>
+      <c r="ES9" t="inlineStr"/>
+      <c r="ET9" t="inlineStr"/>
+      <c r="EU9" t="inlineStr"/>
+      <c r="EV9" t="inlineStr"/>
+      <c r="EW9" t="inlineStr"/>
+      <c r="EX9" t="inlineStr"/>
+      <c r="EY9" t="inlineStr"/>
+      <c r="EZ9" t="inlineStr"/>
+      <c r="FA9" t="inlineStr"/>
+      <c r="FB9" t="inlineStr"/>
+      <c r="FC9" t="inlineStr"/>
+      <c r="FD9" t="inlineStr"/>
+      <c r="FE9" t="inlineStr"/>
+      <c r="FF9" t="inlineStr"/>
+      <c r="FG9" t="inlineStr"/>
+      <c r="FH9" t="inlineStr"/>
+      <c r="FI9" t="inlineStr"/>
+      <c r="FJ9" t="inlineStr"/>
+      <c r="FK9" t="inlineStr"/>
+      <c r="FL9" t="inlineStr"/>
+      <c r="FM9" t="inlineStr"/>
+      <c r="FN9" t="inlineStr"/>
+      <c r="FO9" t="inlineStr"/>
+      <c r="FP9" t="inlineStr"/>
+      <c r="FQ9" t="inlineStr"/>
+      <c r="FR9" t="inlineStr"/>
+      <c r="FS9" t="inlineStr"/>
+      <c r="FT9" t="inlineStr"/>
+      <c r="FU9" t="inlineStr"/>
+      <c r="FV9" t="inlineStr"/>
+      <c r="FW9" t="inlineStr"/>
+      <c r="FX9" t="inlineStr"/>
+      <c r="FY9" t="inlineStr"/>
+      <c r="FZ9" t="inlineStr"/>
+      <c r="GA9" t="inlineStr"/>
+      <c r="GB9" t="inlineStr"/>
+      <c r="GC9" t="inlineStr"/>
+      <c r="GD9" t="inlineStr"/>
+      <c r="GE9" t="inlineStr"/>
+      <c r="GF9" t="inlineStr"/>
+      <c r="GG9" t="inlineStr"/>
+      <c r="GH9" t="inlineStr"/>
+      <c r="GI9" t="inlineStr"/>
+      <c r="GJ9" t="inlineStr"/>
+      <c r="GK9" t="inlineStr"/>
+      <c r="GL9" t="inlineStr"/>
+      <c r="GM9" t="inlineStr"/>
+      <c r="GN9" t="inlineStr"/>
+      <c r="GO9" t="inlineStr"/>
+      <c r="GP9" t="inlineStr"/>
+      <c r="GQ9" t="inlineStr"/>
+      <c r="GR9" t="inlineStr"/>
+      <c r="GS9" t="inlineStr"/>
+      <c r="GT9" t="inlineStr"/>
+      <c r="GU9" t="inlineStr"/>
+      <c r="GV9" t="inlineStr"/>
+      <c r="GW9" t="inlineStr"/>
+      <c r="GX9" t="inlineStr"/>
+      <c r="GY9" t="inlineStr"/>
+      <c r="GZ9" t="inlineStr"/>
+      <c r="HA9" t="inlineStr"/>
+      <c r="HB9" t="inlineStr"/>
+      <c r="HC9" t="inlineStr"/>
+      <c r="HD9" t="inlineStr"/>
+      <c r="HE9" t="inlineStr"/>
+      <c r="HF9" t="inlineStr"/>
+      <c r="HG9" t="inlineStr"/>
+      <c r="HH9" t="inlineStr"/>
+      <c r="HI9" t="inlineStr"/>
+      <c r="HJ9" t="inlineStr"/>
+      <c r="HK9" t="inlineStr"/>
+      <c r="HL9" t="inlineStr"/>
+      <c r="HM9" t="inlineStr"/>
+      <c r="HN9" t="inlineStr"/>
+      <c r="HO9" t="inlineStr"/>
+      <c r="HP9" t="inlineStr"/>
+      <c r="HQ9" t="inlineStr"/>
+      <c r="HR9" t="inlineStr"/>
+      <c r="HS9" t="inlineStr"/>
+      <c r="HT9" t="inlineStr"/>
+      <c r="HU9" t="inlineStr"/>
+      <c r="HV9" t="inlineStr"/>
+      <c r="HW9" t="inlineStr"/>
+      <c r="HX9" t="inlineStr"/>
+      <c r="HY9" t="inlineStr"/>
+      <c r="HZ9" t="inlineStr"/>
+      <c r="IA9" t="inlineStr"/>
+      <c r="IB9" t="inlineStr"/>
+      <c r="IC9" t="inlineStr"/>
+      <c r="ID9" t="inlineStr"/>
+      <c r="IE9" t="inlineStr"/>
+      <c r="IF9" t="inlineStr"/>
+      <c r="IG9" t="inlineStr"/>
+      <c r="IH9" t="inlineStr"/>
+      <c r="II9" t="inlineStr"/>
+      <c r="IJ9" t="inlineStr"/>
+      <c r="IK9" t="inlineStr"/>
+      <c r="IL9" t="inlineStr"/>
+      <c r="IM9" t="inlineStr"/>
+      <c r="IN9" t="inlineStr"/>
+      <c r="IO9" t="inlineStr"/>
+      <c r="IP9" t="inlineStr"/>
+      <c r="IQ9" t="inlineStr"/>
+      <c r="IR9" t="inlineStr"/>
+      <c r="IS9" t="inlineStr"/>
+      <c r="IT9" t="inlineStr"/>
+      <c r="IU9" t="inlineStr"/>
+      <c r="IV9" t="inlineStr"/>
+      <c r="IW9" t="inlineStr"/>
+      <c r="IX9" t="inlineStr"/>
+      <c r="IY9" t="inlineStr"/>
+      <c r="IZ9" t="inlineStr"/>
+      <c r="JA9" t="inlineStr"/>
+      <c r="JB9" t="inlineStr"/>
+      <c r="JC9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-15 20:41:32</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>10</v>
+      </c>
+      <c r="C10" t="n">
+        <v>100</v>
+      </c>
+      <c r="D10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E10" t="n">
+        <v>50</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0.1838516269916657</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.512665407645299</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.1630754666328138</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.3706923598207267</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.5426102878355851</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.3338797321802806</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.5247927382940825</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.4717167956663637</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.4765110931183587</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.2904214012501027</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.4642355707261704</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.4422579284161834</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.4152108564637077</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.256968058618641</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.4391582950457917</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.4051626907151963</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.3704450098461272</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.2315601995760841</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.3830621116547569</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.378742683526372</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.3934995929722896</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.2517793474874719</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.3950867043555272</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.380817398510826</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>3.402980168117167e-05</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.03213758516822962</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.03298242155452278</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0.01269718614916328</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0.0106882844325721</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.04411102269612127</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0.04226166828901452</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0.03638821067383498</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0.01681901334844079</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0.05879325592237104</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0.0008523556492664462</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0.06162362132781011</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.9498778778778779</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0.00174627505960817</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>-0.02880239405345075</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>0.01932549567286986</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>-0.01653855485122683</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>4.222484932484335e-05</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0.03075204775195141</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0.01412941753310348</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0.03871919829033913</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>0.01855925052400355</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0.03835895997683601</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0.01002283617893552</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>0.01447829428012932</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>0.08219233943161922</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>0.004724393950496597</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>0.06141832673640824</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>0.01097820889160808</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>-0.03690601230919455</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>0.02114881452869118</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>-0.002666310391341191</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>1.466399810915956e-05</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>0.04327880803388323</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>0.0312109021986321</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>2.566447998067225e-06</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>0.03990042265394066</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>0.0002769818918783444</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>0.002407430485358878</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>0.06336310452480753</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>0.002445414673552631</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>0.07916985799375562</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>2.000421337456229e-05</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>0.006833387500124431</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>0.002486171611522787</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>4.590091240107541e-06</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>0.0135123323342331</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>0.00807596186700189</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>0.02924195065874801</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>0.01901106571408978</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>0.009427882058312288</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>0.08309402595095965</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>0.07242200518991034</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>-0.02400918976652706</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>-0.07213495670444392</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>2.109216419940168e-05</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>0.01135569381840972</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>-0.02509527946170018</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>9.85218990472901e-06</v>
+      </c>
+      <c r="EU10" t="n">
+        <v>0.04577119432450395</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>0.04235868152814665</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>-0.0002097365405444654</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>-0.06118441210219847</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>0.04716357064125912</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>0.04185667135170823</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>0.06681722639409794</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL10" t="n">
+        <v>0.03999737585137323</v>
+      </c>
+      <c r="FM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN10" t="n">
+        <v>5.878311971236692e-06</v>
+      </c>
+      <c r="FO10" t="n">
+        <v>0.03841304717534481</v>
+      </c>
+      <c r="FP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ10" t="n">
+        <v>0.02155994385208829</v>
+      </c>
+      <c r="FR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>0.02830456116024311</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>0.08972065342534727</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>0.02032707530120384</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>0.09265000316290524</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>1.130904622296478e-05</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>0.02878995476973052</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>0.003462919326619284</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>0.005205481851621524</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>-0.03156361145421006</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH10" t="n">
+        <v>0.09322997473552375</v>
+      </c>
+      <c r="GI10" t="n">
+        <v>0.09924442858974353</v>
+      </c>
+      <c r="GJ10" t="n">
+        <v>0.1020109457116977</v>
+      </c>
+      <c r="GK10" t="n">
+        <v>0.1580575732770333</v>
+      </c>
+      <c r="GL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM10" t="n">
+        <v>0.003546019636902043</v>
+      </c>
+      <c r="GN10" t="n">
+        <v>0.07955937313271948</v>
+      </c>
+      <c r="GO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP10" t="n">
+        <v>0.05762591213102712</v>
+      </c>
+      <c r="GQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR10" t="n">
+        <v>9.810753245881939e-06</v>
+      </c>
+      <c r="GS10" t="n">
+        <v>0.03257200300310992</v>
+      </c>
+      <c r="GT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU10" t="n">
+        <v>-0.005032452471484753</v>
+      </c>
+      <c r="GV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX10" t="n">
+        <v>0.009624252295213968</v>
+      </c>
+      <c r="GY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ10" t="n">
+        <v>-0.004916250253375393</v>
+      </c>
+      <c r="HA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB10" t="n">
+        <v>1.751041721737505e-05</v>
+      </c>
+      <c r="HC10" t="n">
+        <v>0.03352095517755536</v>
+      </c>
+      <c r="HD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="HE10" t="n">
+        <v>0.01844851227270021</v>
+      </c>
+      <c r="HF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG10" t="n">
+        <v>0.03623727805208501</v>
+      </c>
+      <c r="HH10" t="n">
+        <v>0.08212761042941319</v>
+      </c>
+      <c r="HI10" t="n">
+        <v>0.02493666992486772</v>
+      </c>
+      <c r="HJ10" t="n">
+        <v>0.09798305622363936</v>
+      </c>
+      <c r="HK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM10" t="n">
+        <v>0.01238561433255004</v>
+      </c>
+      <c r="HN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="HO10" t="n">
+        <v>0.009751271096852573</v>
+      </c>
+      <c r="HP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ10" t="n">
+        <v>3.063636560625645e-06</v>
+      </c>
+      <c r="HR10" t="n">
+        <v>0.0001049190459050775</v>
+      </c>
+      <c r="HS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="HT10" t="n">
+        <v>-0.03837435582968256</v>
+      </c>
+      <c r="HU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV10" t="n">
+        <v>0.02464531518298731</v>
+      </c>
+      <c r="HW10" t="n">
+        <v>0.08711306121510076</v>
+      </c>
+      <c r="HX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="HY10" t="n">
+        <v>0.08934917130341594</v>
+      </c>
+      <c r="HZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="IB10" t="n">
+        <v>-0.02622461161365992</v>
+      </c>
+      <c r="IC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ID10" t="n">
+        <v>-0.05451751306570535</v>
+      </c>
+      <c r="IE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF10" t="n">
+        <v>2.84317544800809e-06</v>
+      </c>
+      <c r="IG10" t="n">
+        <v>0.01525429230278179</v>
+      </c>
+      <c r="IH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="II10" t="n">
+        <v>-0.01597344351631224</v>
+      </c>
+      <c r="IJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK10" t="n">
+        <v>0.002193485659900803</v>
+      </c>
+      <c r="IL10" t="n">
+        <v>0.06101763468567134</v>
+      </c>
+      <c r="IM10" t="n">
+        <v>0.01796713692626386</v>
+      </c>
+      <c r="IN10" t="n">
+        <v>0.07698585834338659</v>
+      </c>
+      <c r="IO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP10" t="n">
+        <v>0.04800586498262757</v>
+      </c>
+      <c r="IQ10" t="n">
+        <v>0.08737200100479445</v>
+      </c>
+      <c r="IR10" t="n">
+        <v>0.03993392344940688</v>
+      </c>
+      <c r="IS10" t="n">
+        <v>0.1140274349804736</v>
+      </c>
+      <c r="IT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="IV10" t="n">
+        <v>0.05464298669358475</v>
+      </c>
+      <c r="IW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="IX10" t="n">
+        <v>0.04320282427780254</v>
+      </c>
+      <c r="IY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA10" t="n">
+        <v>0.03768344605585518</v>
+      </c>
+      <c r="JB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="JC10" t="n">
+        <v>0.04897292210852509</v>
       </c>
     </row>
   </sheetData>

--- a/ranking/results.xlsx
+++ b/ranking/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JC10"/>
+  <dimension ref="A1:JC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5536,6 +5536,7161 @@
         <v>0.04897292210852509</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-16 10:36:52</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E11" t="n">
+        <v>50</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0.730714735382162</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.84751057632992</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.6037670476628605</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.8943925067318619</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.27372637807708</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.119862502653015</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.246806320006856</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.2355980002151425</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.3440461135549713</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.1370529614200283</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.4460790842761666</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.2997930643916806</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.2068667048107289</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.1325729398187617</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.1847662769991948</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.3440251517627403</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.1430781829861699</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.5367853186919836</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.247501094749392</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.470436061808194</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.1646813204895022</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.5988351281587467</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.3611179545854806</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.1594177559641829</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.1050763873537163</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.1540071740100205</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.06560165649442612</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.03249275071758845</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>-0.009865652579902757</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.01791171584647134</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>-0.07053986580533467</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0.03842682361233148</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.006404363488636597</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0.02110972947111096</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0.08368010897595415</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0.1212439507557961</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.2777777777777777</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.8359595959595961</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0.04255132631051151</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>-0.03267835298260668</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0.1667040048644917</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>0.09704757791195975</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>0.1778133274013021</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>0.08466786627010076</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0.02953910609575506</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>0.07117798982174947</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0.08688263018525529</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0.1063991944656238</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0.05013343875014786</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0.08824714345652947</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0.1080379505486389</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>0.06268915249582746</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>0.03634652541002755</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>0.04092684840530864</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>-0.00636358930424241</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>-0.1941728849960528</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>-0.008634239505344346</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>-0.2191964607252631</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>0.04812747438313928</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>0.06307791463575411</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>0.02292567576473306</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>0.07552060048136344</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0.1026628093620348</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0.05781246908839016</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>0.05847532362766504</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>0.004314979342139319</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>-0.0389412327190528</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>0.0559243726917103</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>-0.04749325969023192</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>-0.09734095150795907</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>0.006162898710737811</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>-0.1363840753125851</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>0.1385743465808548</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>0.1176200113051821</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>0.146261439924052</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>0.10982536977801</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>0.08870210193972414</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>0.1409163605855044</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>0.04371240865546956</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>0.02442182579941316</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>-0.06160349927240403</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>0.1444071953492247</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>0.1051066126687642</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>0.1099196623834666</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>0.1437288703584305</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>0.05639525585140972</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>-0.007958732419819252</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>-0.1643607503751683</v>
+      </c>
+      <c r="FE11" t="n">
+        <v>-0.007859854344684241</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>-0.2095163857656449</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>0.07440001311718719</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>0.07129417756550324</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>0.04857672713292</v>
+      </c>
+      <c r="FL11" t="n">
+        <v>0.145748482237856</v>
+      </c>
+      <c r="FM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN11" t="n">
+        <v>0.156802005227885</v>
+      </c>
+      <c r="FO11" t="n">
+        <v>0.1053019511688177</v>
+      </c>
+      <c r="FP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ11" t="n">
+        <v>0.1962352105315773</v>
+      </c>
+      <c r="FR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS11" t="n">
+        <v>0.07952331651940343</v>
+      </c>
+      <c r="FT11" t="n">
+        <v>0.08456927407640388</v>
+      </c>
+      <c r="FU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV11" t="n">
+        <v>0.1260886747767234</v>
+      </c>
+      <c r="FW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX11" t="n">
+        <v>0.3124329427536303</v>
+      </c>
+      <c r="FY11" t="n">
+        <v>0.1432580583874508</v>
+      </c>
+      <c r="FZ11" t="n">
+        <v>0.251011500322388</v>
+      </c>
+      <c r="GA11" t="n">
+        <v>0.2389815162255411</v>
+      </c>
+      <c r="GB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>-0.07527307098711501</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>0.01279243117137105</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>-0.1175474640857111</v>
+      </c>
+      <c r="GG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH11" t="n">
+        <v>0.02801494211464528</v>
+      </c>
+      <c r="GI11" t="n">
+        <v>0.09186868616087414</v>
+      </c>
+      <c r="GJ11" t="n">
+        <v>0.03329792595922853</v>
+      </c>
+      <c r="GK11" t="n">
+        <v>0.09127393612341352</v>
+      </c>
+      <c r="GL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN11" t="n">
+        <v>0.03195589309958389</v>
+      </c>
+      <c r="GO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP11" t="n">
+        <v>-0.07119092625483572</v>
+      </c>
+      <c r="GQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR11" t="n">
+        <v>0.0124827468258799</v>
+      </c>
+      <c r="GS11" t="n">
+        <v>0.08898481925109601</v>
+      </c>
+      <c r="GT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU11" t="n">
+        <v>0.06809521159868941</v>
+      </c>
+      <c r="GV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW11" t="n">
+        <v>0.06639885666779113</v>
+      </c>
+      <c r="GX11" t="n">
+        <v>0.08963291434578195</v>
+      </c>
+      <c r="GY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ11" t="n">
+        <v>0.1281887525427723</v>
+      </c>
+      <c r="HA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC11" t="n">
+        <v>0.04889376042583849</v>
+      </c>
+      <c r="HD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="HE11" t="n">
+        <v>0.02722939053803746</v>
+      </c>
+      <c r="HF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH11" t="n">
+        <v>0.06161796223441866</v>
+      </c>
+      <c r="HI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ11" t="n">
+        <v>0.06708768052571076</v>
+      </c>
+      <c r="HK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM11" t="n">
+        <v>0.05218202112932081</v>
+      </c>
+      <c r="HN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="HO11" t="n">
+        <v>0.07529798028666135</v>
+      </c>
+      <c r="HP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ11" t="n">
+        <v>-0.008425583632936919</v>
+      </c>
+      <c r="HR11" t="n">
+        <v>0.03234170546698019</v>
+      </c>
+      <c r="HS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="HT11" t="n">
+        <v>-0.09820465444003797</v>
+      </c>
+      <c r="HU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV11" t="n">
+        <v>0.196113691196213</v>
+      </c>
+      <c r="HW11" t="n">
+        <v>0.09436059857020371</v>
+      </c>
+      <c r="HX11" t="n">
+        <v>0.07699475439448568</v>
+      </c>
+      <c r="HY11" t="n">
+        <v>0.2082137643513425</v>
+      </c>
+      <c r="HZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA11" t="n">
+        <v>0.2265518854260207</v>
+      </c>
+      <c r="IB11" t="n">
+        <v>0.1173134552666579</v>
+      </c>
+      <c r="IC11" t="n">
+        <v>0.09097212953143871</v>
+      </c>
+      <c r="ID11" t="n">
+        <v>0.2307210167725286</v>
+      </c>
+      <c r="IE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="IG11" t="n">
+        <v>0.05851085009068032</v>
+      </c>
+      <c r="IH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="II11" t="n">
+        <v>-0.02741921833824066</v>
+      </c>
+      <c r="IJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="IL11" t="n">
+        <v>0.06880013453821573</v>
+      </c>
+      <c r="IM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="IN11" t="n">
+        <v>0.03568623432740499</v>
+      </c>
+      <c r="IO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP11" t="n">
+        <v>-0.03033653660177598</v>
+      </c>
+      <c r="IQ11" t="n">
+        <v>0.04196053905135153</v>
+      </c>
+      <c r="IR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="IS11" t="n">
+        <v>-0.1247809430863335</v>
+      </c>
+      <c r="IT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU11" t="n">
+        <v>0.015233918352284</v>
+      </c>
+      <c r="IV11" t="n">
+        <v>0.1109871202373592</v>
+      </c>
+      <c r="IW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="IX11" t="n">
+        <v>0.02428141250447039</v>
+      </c>
+      <c r="IY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA11" t="n">
+        <v>0.05749787738198585</v>
+      </c>
+      <c r="JB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="JC11" t="n">
+        <v>-0.02120811834379806</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-16 10:38:14</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" t="n">
+        <v>50</v>
+      </c>
+      <c r="E12" t="n">
+        <v>30</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0.7469273696472496</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.8475105689854411</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.6037670476628605</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.8893046914959537</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2831359525330193</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.1198624727010774</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.246806320006856</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.2386568308974071</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.3207141466051388</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.137052990754033</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.4460790842761666</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.2976664753470502</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.2268261835361559</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.1325729634503025</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.187665537697337</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.3435964370255927</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.1430782514380076</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.5367853186919836</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.251630151677902</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.4380435414589925</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.1646812697938488</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.5988351281587467</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.3631671984359213</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.1795695688967079</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.1050764250587832</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.15713384720228</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0.01786066575335016</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0.06560167918746589</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0.03375599849929976</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-0.0237431661775682</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.01791177748242521</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-0.06941883437551764</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0.03842676217773956</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0.006235535828171318</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0.04126125552183125</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0.08368007005816205</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>0.1133963116476752</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0.2380952380952381</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0.8323232323232324</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>-0.003923230846087577</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>0.04255122549799504</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>-0.02977158110100509</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0.1681356471017248</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>0.09704760071089259</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0.1813904679034187</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>0.01057264966986834</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>0.08466792398074716</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>0.03003595442282637</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>0.09126827722392855</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0.08688267514935906</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>0.1050052987439213</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>0.07500830436434518</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>0.08824718836539416</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>0.1083902987793505</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>0.06268914499538278</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>0.03282978907601477</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>0.04092681095066097</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>-0.007412400217513911</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>-0.1753123503520888</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>-0.008634187708973357</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>-0.219280033623838</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>0.04812749049869215</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>0.0600078683289539</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>0.05866058177383753</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>0.07552063873904061</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>0.0998954947634877</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>0.05781244762126967</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>0.05705397036644575</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>-0.02843419765171844</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>0.004314937665263084</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>-0.04748287866574812</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>0.0559242470322255</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>-0.04197960575581251</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>-0.0946501420174938</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>0.00616301512875591</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>-0.1374571090269733</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>0.1601093651471484</v>
+      </c>
+      <c r="EF12" t="n">
+        <v>0.1176199878450087</v>
+      </c>
+      <c r="EG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH12" t="n">
+        <v>0.1484023980440867</v>
+      </c>
+      <c r="EI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ12" t="n">
+        <v>0.1225227001478519</v>
+      </c>
+      <c r="EK12" t="n">
+        <v>0.08870217543218087</v>
+      </c>
+      <c r="EL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM12" t="n">
+        <v>0.1401073895228034</v>
+      </c>
+      <c r="EN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP12" t="n">
+        <v>0.04371243783670821</v>
+      </c>
+      <c r="EQ12" t="n">
+        <v>0.02442182579941316</v>
+      </c>
+      <c r="ER12" t="n">
+        <v>-0.05571292789806119</v>
+      </c>
+      <c r="ES12" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET12" t="n">
+        <v>0.1616482965988809</v>
+      </c>
+      <c r="EU12" t="n">
+        <v>0.1051065488807467</v>
+      </c>
+      <c r="EV12" t="n">
+        <v>0.1099196623834666</v>
+      </c>
+      <c r="EW12" t="n">
+        <v>0.1437601919683886</v>
+      </c>
+      <c r="EX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ12" t="n">
+        <v>0.05639523383855112</v>
+      </c>
+      <c r="FA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB12" t="n">
+        <v>-0.00912541257346353</v>
+      </c>
+      <c r="FC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD12" t="n">
+        <v>-0.1534002081479013</v>
+      </c>
+      <c r="FE12" t="n">
+        <v>-0.007859904204865173</v>
+      </c>
+      <c r="FF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG12" t="n">
+        <v>-0.2120470961682322</v>
+      </c>
+      <c r="FH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI12" t="n">
+        <v>0.06868833917676692</v>
+      </c>
+      <c r="FJ12" t="n">
+        <v>0.07129421173597783</v>
+      </c>
+      <c r="FK12" t="n">
+        <v>0.04857672713292</v>
+      </c>
+      <c r="FL12" t="n">
+        <v>0.1394685716549387</v>
+      </c>
+      <c r="FM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN12" t="n">
+        <v>0.1626127445201082</v>
+      </c>
+      <c r="FO12" t="n">
+        <v>0.1053019412600875</v>
+      </c>
+      <c r="FP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ12" t="n">
+        <v>0.1966494145907554</v>
+      </c>
+      <c r="FR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS12" t="n">
+        <v>0.0910661062384063</v>
+      </c>
+      <c r="FT12" t="n">
+        <v>0.08456942185750502</v>
+      </c>
+      <c r="FU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV12" t="n">
+        <v>0.1240150262758003</v>
+      </c>
+      <c r="FW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX12" t="n">
+        <v>0.3056592503204733</v>
+      </c>
+      <c r="FY12" t="n">
+        <v>0.1432580174989109</v>
+      </c>
+      <c r="FZ12" t="n">
+        <v>0.251011500322388</v>
+      </c>
+      <c r="GA12" t="n">
+        <v>0.2437730890334233</v>
+      </c>
+      <c r="GB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC12" t="n">
+        <v>-0.0693271050620734</v>
+      </c>
+      <c r="GD12" t="n">
+        <v>0.0127924046132001</v>
+      </c>
+      <c r="GE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF12" t="n">
+        <v>-0.1211949173104147</v>
+      </c>
+      <c r="GG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH12" t="n">
+        <v>0.05536797039217147</v>
+      </c>
+      <c r="GI12" t="n">
+        <v>0.09186872449518108</v>
+      </c>
+      <c r="GJ12" t="n">
+        <v>0.03329792595922853</v>
+      </c>
+      <c r="GK12" t="n">
+        <v>0.09359333406481225</v>
+      </c>
+      <c r="GL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM12" t="n">
+        <v>-0.003733713770537982</v>
+      </c>
+      <c r="GN12" t="n">
+        <v>0.03195584031441602</v>
+      </c>
+      <c r="GO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP12" t="n">
+        <v>-0.06609767030385952</v>
+      </c>
+      <c r="GQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR12" t="n">
+        <v>0.04892893400869022</v>
+      </c>
+      <c r="GS12" t="n">
+        <v>0.08898477827627992</v>
+      </c>
+      <c r="GT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU12" t="n">
+        <v>0.07120481310303092</v>
+      </c>
+      <c r="GV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW12" t="n">
+        <v>0.08161478270123683</v>
+      </c>
+      <c r="GX12" t="n">
+        <v>0.08963296670773416</v>
+      </c>
+      <c r="GY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ12" t="n">
+        <v>0.1247267265589643</v>
+      </c>
+      <c r="HA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC12" t="n">
+        <v>0.04889370570813974</v>
+      </c>
+      <c r="HD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="HE12" t="n">
+        <v>0.02585279715685834</v>
+      </c>
+      <c r="HF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG12" t="n">
+        <v>0.003530886488440292</v>
+      </c>
+      <c r="HH12" t="n">
+        <v>0.0616179246959954</v>
+      </c>
+      <c r="HI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ12" t="n">
+        <v>0.06640248468856132</v>
+      </c>
+      <c r="HK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM12" t="n">
+        <v>0.05218210627776888</v>
+      </c>
+      <c r="HN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="HO12" t="n">
+        <v>0.06441074345649195</v>
+      </c>
+      <c r="HP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ12" t="n">
+        <v>-0.01954616563563549</v>
+      </c>
+      <c r="HR12" t="n">
+        <v>0.03234167746393244</v>
+      </c>
+      <c r="HS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="HT12" t="n">
+        <v>-0.0957666669530446</v>
+      </c>
+      <c r="HU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV12" t="n">
+        <v>0.1966921807479711</v>
+      </c>
+      <c r="HW12" t="n">
+        <v>0.09436061613276567</v>
+      </c>
+      <c r="HX12" t="n">
+        <v>0.07699475439448568</v>
+      </c>
+      <c r="HY12" t="n">
+        <v>0.208455046153244</v>
+      </c>
+      <c r="HZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA12" t="n">
+        <v>0.2212343155428003</v>
+      </c>
+      <c r="IB12" t="n">
+        <v>0.1173134104765826</v>
+      </c>
+      <c r="IC12" t="n">
+        <v>0.09097212953143871</v>
+      </c>
+      <c r="ID12" t="n">
+        <v>0.2249887535023649</v>
+      </c>
+      <c r="IE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="IG12" t="n">
+        <v>0.0585107754633449</v>
+      </c>
+      <c r="IH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="II12" t="n">
+        <v>-0.02207905895315086</v>
+      </c>
+      <c r="IJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="IL12" t="n">
+        <v>0.06880013536585292</v>
+      </c>
+      <c r="IM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="IN12" t="n">
+        <v>0.0333166098766345</v>
+      </c>
+      <c r="IO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP12" t="n">
+        <v>-0.03886279847446177</v>
+      </c>
+      <c r="IQ12" t="n">
+        <v>0.04196047403871112</v>
+      </c>
+      <c r="IR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="IS12" t="n">
+        <v>-0.12272090881674</v>
+      </c>
+      <c r="IT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU12" t="n">
+        <v>0.06921975196583302</v>
+      </c>
+      <c r="IV12" t="n">
+        <v>0.1109871790538538</v>
+      </c>
+      <c r="IW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="IX12" t="n">
+        <v>0.03434846024888129</v>
+      </c>
+      <c r="IY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA12" t="n">
+        <v>0.05749786697296082</v>
+      </c>
+      <c r="JB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="JC12" t="n">
+        <v>-0.01390719915076296</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-16 10:50:36</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>50</v>
+      </c>
+      <c r="E13" t="n">
+        <v>50</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0.730714735382162</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.84751057632992</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.6037670476628605</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.8943925067318619</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.27372637807708</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.119862502653015</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.246806320006856</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.2355980002151425</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.3440461135549713</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.1370529614200283</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.4460790842761666</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.2997930643916806</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.2068667048107289</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.1325729398187617</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.1847662769991948</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.3440251517627403</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.1430781829861699</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.5367853186919836</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.247501094749392</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.470436061808194</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.1646813204895022</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.5988351281587467</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.3611179545854806</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.1594177559641829</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.1050763873537163</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.1540071740100205</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0.06560165649442612</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.03249275071758845</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>-0.009865652579902757</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.01791171584647134</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-0.07053986580533467</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0.03842682361233148</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0.006404363488636597</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0.02110972947111096</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0.08368010897595415</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0.1212439507557961</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.2777777777777777</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.8359595959595961</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0.04255132631051151</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>-0.03267835298260668</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0.1667040048644917</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0.09704757791195975</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0.1778133274013021</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0.08466786627010076</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0.02953910609575506</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>0.07117798982174947</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0.08688263018525529</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>0.1063991944656238</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0.05013343875014786</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>0.08824714345652947</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>0.1080379505486389</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>0.06268915249582746</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>0.03634652541002755</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>0.04092684840530864</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>-0.00636358930424241</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>-0.1941728849960528</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>-0.008634239505344346</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>-0.2191964607252631</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>0.04812747438313928</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>0.06307791463575411</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>0.02292567576473306</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>0.07552060048136344</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>0.1026628093620348</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>0.05781246908839016</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>0.05847532362766504</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>0.004314979342139319</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>-0.0389412327190528</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>0.0559243726917103</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>-0.04749325969023192</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>-0.09734095150795907</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>0.006162898710737811</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>-0.1363840753125851</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>0.1385743465808548</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>0.1176200113051821</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH13" t="n">
+        <v>0.146261439924052</v>
+      </c>
+      <c r="EI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ13" t="n">
+        <v>0.10982536977801</v>
+      </c>
+      <c r="EK13" t="n">
+        <v>0.08870210193972414</v>
+      </c>
+      <c r="EL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM13" t="n">
+        <v>0.1409163605855044</v>
+      </c>
+      <c r="EN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP13" t="n">
+        <v>0.04371240865546956</v>
+      </c>
+      <c r="EQ13" t="n">
+        <v>0.02442182579941316</v>
+      </c>
+      <c r="ER13" t="n">
+        <v>-0.06160349927240403</v>
+      </c>
+      <c r="ES13" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET13" t="n">
+        <v>0.1444071953492247</v>
+      </c>
+      <c r="EU13" t="n">
+        <v>0.1051066126687642</v>
+      </c>
+      <c r="EV13" t="n">
+        <v>0.1099196623834666</v>
+      </c>
+      <c r="EW13" t="n">
+        <v>0.1437288703584305</v>
+      </c>
+      <c r="EX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ13" t="n">
+        <v>0.05639525585140972</v>
+      </c>
+      <c r="FA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB13" t="n">
+        <v>-0.007958732419819252</v>
+      </c>
+      <c r="FC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD13" t="n">
+        <v>-0.1643607503751683</v>
+      </c>
+      <c r="FE13" t="n">
+        <v>-0.007859854344684241</v>
+      </c>
+      <c r="FF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG13" t="n">
+        <v>-0.2095163857656449</v>
+      </c>
+      <c r="FH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI13" t="n">
+        <v>0.07440001311718719</v>
+      </c>
+      <c r="FJ13" t="n">
+        <v>0.07129417756550324</v>
+      </c>
+      <c r="FK13" t="n">
+        <v>0.04857672713292</v>
+      </c>
+      <c r="FL13" t="n">
+        <v>0.145748482237856</v>
+      </c>
+      <c r="FM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN13" t="n">
+        <v>0.156802005227885</v>
+      </c>
+      <c r="FO13" t="n">
+        <v>0.1053019511688177</v>
+      </c>
+      <c r="FP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ13" t="n">
+        <v>0.1962352105315773</v>
+      </c>
+      <c r="FR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS13" t="n">
+        <v>0.07952331651940343</v>
+      </c>
+      <c r="FT13" t="n">
+        <v>0.08456927407640388</v>
+      </c>
+      <c r="FU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV13" t="n">
+        <v>0.1260886747767234</v>
+      </c>
+      <c r="FW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX13" t="n">
+        <v>0.3124329427536303</v>
+      </c>
+      <c r="FY13" t="n">
+        <v>0.1432580583874508</v>
+      </c>
+      <c r="FZ13" t="n">
+        <v>0.251011500322388</v>
+      </c>
+      <c r="GA13" t="n">
+        <v>0.2389815162255411</v>
+      </c>
+      <c r="GB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC13" t="n">
+        <v>-0.07527307098711501</v>
+      </c>
+      <c r="GD13" t="n">
+        <v>0.01279243117137105</v>
+      </c>
+      <c r="GE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF13" t="n">
+        <v>-0.1175474640857111</v>
+      </c>
+      <c r="GG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH13" t="n">
+        <v>0.02801494211464528</v>
+      </c>
+      <c r="GI13" t="n">
+        <v>0.09186868616087414</v>
+      </c>
+      <c r="GJ13" t="n">
+        <v>0.03329792595922853</v>
+      </c>
+      <c r="GK13" t="n">
+        <v>0.09127393612341352</v>
+      </c>
+      <c r="GL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN13" t="n">
+        <v>0.03195589309958389</v>
+      </c>
+      <c r="GO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP13" t="n">
+        <v>-0.07119092625483572</v>
+      </c>
+      <c r="GQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR13" t="n">
+        <v>0.0124827468258799</v>
+      </c>
+      <c r="GS13" t="n">
+        <v>0.08898481925109601</v>
+      </c>
+      <c r="GT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU13" t="n">
+        <v>0.06809521159868941</v>
+      </c>
+      <c r="GV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW13" t="n">
+        <v>0.06639885666779113</v>
+      </c>
+      <c r="GX13" t="n">
+        <v>0.08963291434578195</v>
+      </c>
+      <c r="GY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ13" t="n">
+        <v>0.1281887525427723</v>
+      </c>
+      <c r="HA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC13" t="n">
+        <v>0.04889376042583849</v>
+      </c>
+      <c r="HD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="HE13" t="n">
+        <v>0.02722939053803746</v>
+      </c>
+      <c r="HF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH13" t="n">
+        <v>0.06161796223441866</v>
+      </c>
+      <c r="HI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ13" t="n">
+        <v>0.06708768052571076</v>
+      </c>
+      <c r="HK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM13" t="n">
+        <v>0.05218202112932081</v>
+      </c>
+      <c r="HN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="HO13" t="n">
+        <v>0.07529798028666135</v>
+      </c>
+      <c r="HP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ13" t="n">
+        <v>-0.008425583632936919</v>
+      </c>
+      <c r="HR13" t="n">
+        <v>0.03234170546698019</v>
+      </c>
+      <c r="HS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="HT13" t="n">
+        <v>-0.09820465444003797</v>
+      </c>
+      <c r="HU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV13" t="n">
+        <v>0.196113691196213</v>
+      </c>
+      <c r="HW13" t="n">
+        <v>0.09436059857020371</v>
+      </c>
+      <c r="HX13" t="n">
+        <v>0.07699475439448568</v>
+      </c>
+      <c r="HY13" t="n">
+        <v>0.2082137643513425</v>
+      </c>
+      <c r="HZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA13" t="n">
+        <v>0.2265518854260207</v>
+      </c>
+      <c r="IB13" t="n">
+        <v>0.1173134552666579</v>
+      </c>
+      <c r="IC13" t="n">
+        <v>0.09097212953143871</v>
+      </c>
+      <c r="ID13" t="n">
+        <v>0.2307210167725286</v>
+      </c>
+      <c r="IE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="IG13" t="n">
+        <v>0.05851085009068032</v>
+      </c>
+      <c r="IH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="II13" t="n">
+        <v>-0.02741921833824066</v>
+      </c>
+      <c r="IJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="IL13" t="n">
+        <v>0.06880013453821573</v>
+      </c>
+      <c r="IM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="IN13" t="n">
+        <v>0.03568623432740499</v>
+      </c>
+      <c r="IO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP13" t="n">
+        <v>-0.03033653660177598</v>
+      </c>
+      <c r="IQ13" t="n">
+        <v>0.04196053905135153</v>
+      </c>
+      <c r="IR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="IS13" t="n">
+        <v>-0.1247809430863335</v>
+      </c>
+      <c r="IT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU13" t="n">
+        <v>0.015233918352284</v>
+      </c>
+      <c r="IV13" t="n">
+        <v>0.1109871202373592</v>
+      </c>
+      <c r="IW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="IX13" t="n">
+        <v>0.02428141250447039</v>
+      </c>
+      <c r="IY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA13" t="n">
+        <v>0.05749787738198585</v>
+      </c>
+      <c r="JB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="JC13" t="n">
+        <v>-0.02120811834379806</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-16 10:53:57</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" t="n">
+        <v>50</v>
+      </c>
+      <c r="E14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0.730714735382162</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.84751057632992</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.6037670476628605</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.8943925067318619</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.27372637807708</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.119862502653015</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.246806320006856</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.2355980002151425</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.3440461135549713</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.1370529614200283</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.4460790842761666</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.2997930643916806</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.2068667048107289</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.1325729398187617</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.1847662769991948</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.3440251517627403</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.1430781829861699</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.5367853186919836</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.247501094749392</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.470436061808194</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.1646813204895022</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.5988351281587467</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.3611179545854806</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.1594177559641829</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.1050763873537163</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.1540071740100205</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0.06560165649442612</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0.03249275071758845</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>-0.009865652579902757</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.01791171584647134</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>-0.07053986580533467</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0.03842682361233148</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0.006404363488636597</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0.02110972947111096</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0.08368010897595415</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0.1212439507557961</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0.2777777777777777</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0.8359595959595961</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>0.04255132631051151</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>-0.03267835298260668</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0.1667040048644917</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0.09704757791195975</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>0.1778133274013021</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0.08466786627010076</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0.02953910609575506</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>0.07117798982174947</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>0.08688263018525529</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>0.1063991944656238</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>0.05013343875014786</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0.08824714345652947</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0.1080379505486389</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0.06268915249582746</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>0.03634652541002755</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>0.04092684840530864</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>-0.00636358930424241</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>-0.1941728849960528</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>-0.008634239505344346</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>-0.2191964607252631</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>0.04812747438313928</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>0.06307791463575411</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>0.02292567576473306</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>0.07552060048136344</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>0.1026628093620348</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>0.05781246908839016</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>0.05847532362766504</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>0.004314979342139319</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>-0.0389412327190528</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>0.0559243726917103</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>-0.04749325969023192</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>-0.09734095150795907</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>0.006162898710737811</v>
+      </c>
+      <c r="EB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC14" t="n">
+        <v>-0.1363840753125851</v>
+      </c>
+      <c r="ED14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE14" t="n">
+        <v>0.1385743465808548</v>
+      </c>
+      <c r="EF14" t="n">
+        <v>0.1176200113051821</v>
+      </c>
+      <c r="EG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH14" t="n">
+        <v>0.146261439924052</v>
+      </c>
+      <c r="EI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ14" t="n">
+        <v>0.10982536977801</v>
+      </c>
+      <c r="EK14" t="n">
+        <v>0.08870210193972414</v>
+      </c>
+      <c r="EL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM14" t="n">
+        <v>0.1409163605855044</v>
+      </c>
+      <c r="EN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP14" t="n">
+        <v>0.04371240865546956</v>
+      </c>
+      <c r="EQ14" t="n">
+        <v>0.02442182579941316</v>
+      </c>
+      <c r="ER14" t="n">
+        <v>-0.06160349927240403</v>
+      </c>
+      <c r="ES14" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET14" t="n">
+        <v>0.1444071953492247</v>
+      </c>
+      <c r="EU14" t="n">
+        <v>0.1051066126687642</v>
+      </c>
+      <c r="EV14" t="n">
+        <v>0.1099196623834666</v>
+      </c>
+      <c r="EW14" t="n">
+        <v>0.1437288703584305</v>
+      </c>
+      <c r="EX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ14" t="n">
+        <v>0.05639525585140972</v>
+      </c>
+      <c r="FA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB14" t="n">
+        <v>-0.007958732419819252</v>
+      </c>
+      <c r="FC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD14" t="n">
+        <v>-0.1643607503751683</v>
+      </c>
+      <c r="FE14" t="n">
+        <v>-0.007859854344684241</v>
+      </c>
+      <c r="FF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG14" t="n">
+        <v>-0.2095163857656449</v>
+      </c>
+      <c r="FH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI14" t="n">
+        <v>0.07440001311718719</v>
+      </c>
+      <c r="FJ14" t="n">
+        <v>0.07129417756550324</v>
+      </c>
+      <c r="FK14" t="n">
+        <v>0.04857672713292</v>
+      </c>
+      <c r="FL14" t="n">
+        <v>0.145748482237856</v>
+      </c>
+      <c r="FM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN14" t="n">
+        <v>0.156802005227885</v>
+      </c>
+      <c r="FO14" t="n">
+        <v>0.1053019511688177</v>
+      </c>
+      <c r="FP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ14" t="n">
+        <v>0.1962352105315773</v>
+      </c>
+      <c r="FR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS14" t="n">
+        <v>0.07952331651940343</v>
+      </c>
+      <c r="FT14" t="n">
+        <v>0.08456927407640388</v>
+      </c>
+      <c r="FU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV14" t="n">
+        <v>0.1260886747767234</v>
+      </c>
+      <c r="FW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX14" t="n">
+        <v>0.3124329427536303</v>
+      </c>
+      <c r="FY14" t="n">
+        <v>0.1432580583874508</v>
+      </c>
+      <c r="FZ14" t="n">
+        <v>0.251011500322388</v>
+      </c>
+      <c r="GA14" t="n">
+        <v>0.2389815162255411</v>
+      </c>
+      <c r="GB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC14" t="n">
+        <v>-0.07527307098711501</v>
+      </c>
+      <c r="GD14" t="n">
+        <v>0.01279243117137105</v>
+      </c>
+      <c r="GE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF14" t="n">
+        <v>-0.1175474640857111</v>
+      </c>
+      <c r="GG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH14" t="n">
+        <v>0.02801494211464528</v>
+      </c>
+      <c r="GI14" t="n">
+        <v>0.09186868616087414</v>
+      </c>
+      <c r="GJ14" t="n">
+        <v>0.03329792595922853</v>
+      </c>
+      <c r="GK14" t="n">
+        <v>0.09127393612341352</v>
+      </c>
+      <c r="GL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN14" t="n">
+        <v>0.03195589309958389</v>
+      </c>
+      <c r="GO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP14" t="n">
+        <v>-0.07119092625483572</v>
+      </c>
+      <c r="GQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR14" t="n">
+        <v>0.0124827468258799</v>
+      </c>
+      <c r="GS14" t="n">
+        <v>0.08898481925109601</v>
+      </c>
+      <c r="GT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU14" t="n">
+        <v>0.06809521159868941</v>
+      </c>
+      <c r="GV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW14" t="n">
+        <v>0.06639885666779113</v>
+      </c>
+      <c r="GX14" t="n">
+        <v>0.08963291434578195</v>
+      </c>
+      <c r="GY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ14" t="n">
+        <v>0.1281887525427723</v>
+      </c>
+      <c r="HA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC14" t="n">
+        <v>0.04889376042583849</v>
+      </c>
+      <c r="HD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="HE14" t="n">
+        <v>0.02722939053803746</v>
+      </c>
+      <c r="HF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH14" t="n">
+        <v>0.06161796223441866</v>
+      </c>
+      <c r="HI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ14" t="n">
+        <v>0.06708768052571076</v>
+      </c>
+      <c r="HK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM14" t="n">
+        <v>0.05218202112932081</v>
+      </c>
+      <c r="HN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="HO14" t="n">
+        <v>0.07529798028666135</v>
+      </c>
+      <c r="HP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ14" t="n">
+        <v>-0.008425583632936919</v>
+      </c>
+      <c r="HR14" t="n">
+        <v>0.03234170546698019</v>
+      </c>
+      <c r="HS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="HT14" t="n">
+        <v>-0.09820465444003797</v>
+      </c>
+      <c r="HU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV14" t="n">
+        <v>0.196113691196213</v>
+      </c>
+      <c r="HW14" t="n">
+        <v>0.09436059857020371</v>
+      </c>
+      <c r="HX14" t="n">
+        <v>0.07699475439448568</v>
+      </c>
+      <c r="HY14" t="n">
+        <v>0.2082137643513425</v>
+      </c>
+      <c r="HZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA14" t="n">
+        <v>0.2265518854260207</v>
+      </c>
+      <c r="IB14" t="n">
+        <v>0.1173134552666579</v>
+      </c>
+      <c r="IC14" t="n">
+        <v>0.09097212953143871</v>
+      </c>
+      <c r="ID14" t="n">
+        <v>0.2307210167725286</v>
+      </c>
+      <c r="IE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="IG14" t="n">
+        <v>0.05851085009068032</v>
+      </c>
+      <c r="IH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="II14" t="n">
+        <v>-0.02741921833824066</v>
+      </c>
+      <c r="IJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="IL14" t="n">
+        <v>0.06880013453821573</v>
+      </c>
+      <c r="IM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="IN14" t="n">
+        <v>0.03568623432740499</v>
+      </c>
+      <c r="IO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP14" t="n">
+        <v>-0.03033653660177598</v>
+      </c>
+      <c r="IQ14" t="n">
+        <v>0.04196053905135153</v>
+      </c>
+      <c r="IR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="IS14" t="n">
+        <v>-0.1247809430863335</v>
+      </c>
+      <c r="IT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU14" t="n">
+        <v>0.015233918352284</v>
+      </c>
+      <c r="IV14" t="n">
+        <v>0.1109871202373592</v>
+      </c>
+      <c r="IW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="IX14" t="n">
+        <v>0.02428141250447039</v>
+      </c>
+      <c r="IY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA14" t="n">
+        <v>0.05749787738198585</v>
+      </c>
+      <c r="JB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="JC14" t="n">
+        <v>-0.02120811834379806</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-16 10:57:42</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>10</v>
+      </c>
+      <c r="C15" t="n">
+        <v>10</v>
+      </c>
+      <c r="D15" t="n">
+        <v>50</v>
+      </c>
+      <c r="E15" t="n">
+        <v>50</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>0.730714735382162</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.84751057632992</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.6038008511049379</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.8943925067318619</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.27372637807708</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.119862502653015</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.2467050291915034</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.2355980002151425</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.3440461135549713</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.1370529614200283</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.4461018214666534</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.2997930643916806</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.2068667048107289</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.1325729398187617</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.1847662769991948</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.3440251517627403</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.1430781829861699</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.5367986966937877</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.247501094749392</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.470436061808194</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.1646813204895022</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.5988546656885895</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0.3611179545854806</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.1594177559641829</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.1050763873537163</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0.1540071740100205</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0.06560165649442612</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0.03249275071758845</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>-0.009865652579902757</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0.01791171584647134</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>-0.07053986580533467</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0.03842682361233148</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0.006404363488636597</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0.02110972947111096</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0.08368010897595415</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0.1212439507557961</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0.2777777777777777</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0.8359595959595961</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0.04255132631051151</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>-0.03267835298260668</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0.1667040048644917</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0.09704757791195975</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>0.1778133274013021</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>0.08466786627010076</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0.02953910609575506</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>0.07117798982174947</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0.08688263018525529</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>0.1063991944656238</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0.05013343875014786</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>0.08824714345652947</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0.1080379505486389</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>0.06268915249582746</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>0.03634652541002755</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>0.04092684840530864</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>-0.00636358930424241</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>-0.1941728849960528</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>-0.008634239505344346</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>-0.2191964607252631</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>0.04812747438313928</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>0.06307791463575411</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>0.02292567576473306</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>0.07552060048136344</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>0.1026628093620348</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>0.05781246908839016</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>0.05847532362766504</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>0.004314979342139319</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>-0.0389412327190528</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>0.0559243726917103</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>-0.04749325969023192</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>-0.09734095150795907</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>0.006162898710737811</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>-0.1363840753125851</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>0.1385743465808548</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>0.1176200113051821</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH15" t="n">
+        <v>0.146261439924052</v>
+      </c>
+      <c r="EI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ15" t="n">
+        <v>0.10982536977801</v>
+      </c>
+      <c r="EK15" t="n">
+        <v>0.08870210193972414</v>
+      </c>
+      <c r="EL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM15" t="n">
+        <v>0.1409163605855044</v>
+      </c>
+      <c r="EN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP15" t="n">
+        <v>0.04371240865546956</v>
+      </c>
+      <c r="EQ15" t="n">
+        <v>0.0242912807357249</v>
+      </c>
+      <c r="ER15" t="n">
+        <v>-0.06160349927240403</v>
+      </c>
+      <c r="ES15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET15" t="n">
+        <v>0.1444071953492247</v>
+      </c>
+      <c r="EU15" t="n">
+        <v>0.1051066126687642</v>
+      </c>
+      <c r="EV15" t="n">
+        <v>0.1099319588714695</v>
+      </c>
+      <c r="EW15" t="n">
+        <v>0.1437288703584305</v>
+      </c>
+      <c r="EX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ15" t="n">
+        <v>0.05639525585140972</v>
+      </c>
+      <c r="FA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB15" t="n">
+        <v>-0.007958732419819252</v>
+      </c>
+      <c r="FC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD15" t="n">
+        <v>-0.1643607503751683</v>
+      </c>
+      <c r="FE15" t="n">
+        <v>-0.007859854344684241</v>
+      </c>
+      <c r="FF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG15" t="n">
+        <v>-0.2095163857656449</v>
+      </c>
+      <c r="FH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI15" t="n">
+        <v>0.07440001311718719</v>
+      </c>
+      <c r="FJ15" t="n">
+        <v>0.07129417756550324</v>
+      </c>
+      <c r="FK15" t="n">
+        <v>0.0485128583072296</v>
+      </c>
+      <c r="FL15" t="n">
+        <v>0.145748482237856</v>
+      </c>
+      <c r="FM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN15" t="n">
+        <v>0.156802005227885</v>
+      </c>
+      <c r="FO15" t="n">
+        <v>0.1053019511688177</v>
+      </c>
+      <c r="FP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ15" t="n">
+        <v>0.1962352105315773</v>
+      </c>
+      <c r="FR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS15" t="n">
+        <v>0.07952331651940343</v>
+      </c>
+      <c r="FT15" t="n">
+        <v>0.08456927407640388</v>
+      </c>
+      <c r="FU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV15" t="n">
+        <v>0.1260886747767234</v>
+      </c>
+      <c r="FW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX15" t="n">
+        <v>0.3124329427536303</v>
+      </c>
+      <c r="FY15" t="n">
+        <v>0.1432580583874508</v>
+      </c>
+      <c r="FZ15" t="n">
+        <v>0.2510149027833219</v>
+      </c>
+      <c r="GA15" t="n">
+        <v>0.2389815162255411</v>
+      </c>
+      <c r="GB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC15" t="n">
+        <v>-0.07527307098711501</v>
+      </c>
+      <c r="GD15" t="n">
+        <v>0.01279243117137105</v>
+      </c>
+      <c r="GE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF15" t="n">
+        <v>-0.1175474640857111</v>
+      </c>
+      <c r="GG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH15" t="n">
+        <v>0.02801494211464528</v>
+      </c>
+      <c r="GI15" t="n">
+        <v>0.09186868616087414</v>
+      </c>
+      <c r="GJ15" t="n">
+        <v>0.03319471148979803</v>
+      </c>
+      <c r="GK15" t="n">
+        <v>0.09127393612341352</v>
+      </c>
+      <c r="GL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN15" t="n">
+        <v>0.03195589309958389</v>
+      </c>
+      <c r="GO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP15" t="n">
+        <v>-0.07119092625483572</v>
+      </c>
+      <c r="GQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR15" t="n">
+        <v>0.0124827468258799</v>
+      </c>
+      <c r="GS15" t="n">
+        <v>0.08898481925109601</v>
+      </c>
+      <c r="GT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU15" t="n">
+        <v>0.06809521159868941</v>
+      </c>
+      <c r="GV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW15" t="n">
+        <v>0.06639885666779113</v>
+      </c>
+      <c r="GX15" t="n">
+        <v>0.08963291434578195</v>
+      </c>
+      <c r="GY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ15" t="n">
+        <v>0.1281887525427723</v>
+      </c>
+      <c r="HA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC15" t="n">
+        <v>0.04889376042583849</v>
+      </c>
+      <c r="HD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="HE15" t="n">
+        <v>0.02722939053803746</v>
+      </c>
+      <c r="HF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH15" t="n">
+        <v>0.06161796223441866</v>
+      </c>
+      <c r="HI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ15" t="n">
+        <v>0.06708768052571076</v>
+      </c>
+      <c r="HK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM15" t="n">
+        <v>0.05218202112932081</v>
+      </c>
+      <c r="HN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="HO15" t="n">
+        <v>0.07529798028666135</v>
+      </c>
+      <c r="HP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ15" t="n">
+        <v>-0.008425583632936919</v>
+      </c>
+      <c r="HR15" t="n">
+        <v>0.03234170546698019</v>
+      </c>
+      <c r="HS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="HT15" t="n">
+        <v>-0.09820465444003797</v>
+      </c>
+      <c r="HU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV15" t="n">
+        <v>0.196113691196213</v>
+      </c>
+      <c r="HW15" t="n">
+        <v>0.09436059857020371</v>
+      </c>
+      <c r="HX15" t="n">
+        <v>0.07699874034694996</v>
+      </c>
+      <c r="HY15" t="n">
+        <v>0.2082137643513425</v>
+      </c>
+      <c r="HZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA15" t="n">
+        <v>0.2265518854260207</v>
+      </c>
+      <c r="IB15" t="n">
+        <v>0.1173134552666579</v>
+      </c>
+      <c r="IC15" t="n">
+        <v>0.091006958190822</v>
+      </c>
+      <c r="ID15" t="n">
+        <v>0.2307210167725286</v>
+      </c>
+      <c r="IE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="IG15" t="n">
+        <v>0.05851085009068032</v>
+      </c>
+      <c r="IH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="II15" t="n">
+        <v>-0.02741921833824066</v>
+      </c>
+      <c r="IJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="IL15" t="n">
+        <v>0.06880013453821573</v>
+      </c>
+      <c r="IM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="IN15" t="n">
+        <v>0.03568623432740499</v>
+      </c>
+      <c r="IO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP15" t="n">
+        <v>-0.03033653660177598</v>
+      </c>
+      <c r="IQ15" t="n">
+        <v>0.04196053905135153</v>
+      </c>
+      <c r="IR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="IS15" t="n">
+        <v>-0.1247809430863335</v>
+      </c>
+      <c r="IT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU15" t="n">
+        <v>0.015233918352284</v>
+      </c>
+      <c r="IV15" t="n">
+        <v>0.1109871202373592</v>
+      </c>
+      <c r="IW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="IX15" t="n">
+        <v>0.02428141250447039</v>
+      </c>
+      <c r="IY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA15" t="n">
+        <v>0.05749787738198585</v>
+      </c>
+      <c r="JB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="JC15" t="n">
+        <v>-0.02120811834379806</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-16 11:02:44</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>10</v>
+      </c>
+      <c r="C16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D16" t="n">
+        <v>50</v>
+      </c>
+      <c r="E16" t="n">
+        <v>50</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0.4516266767615684</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.7438971340978656</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.3358570563536667</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.6435578232796599</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.4547990410848866</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.1967736432510528</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.485011862525429</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.3942620419297467</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.4616083578468044</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.197246649118916</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.3329162674354369</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.3979774858602876</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.3823643695276336</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.172152472381585</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.502367433714635</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.3310209403516561</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.4526007022352702</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.1959267791074837</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.4251551724689052</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0.4073581815350956</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0.2566538537616691</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0.1497738362575288</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0.3645030495714258</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.2320256696873849</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.00725513071051354</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>-0.07283852732826084</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0.08474653905421552</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0.0697705304158668</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0.03437629374528271</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0.1499565143173955</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.05282719609533702</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0.04288038562631999</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>-0.04843540688391934</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>-0.01813212076066387</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>-0.1003746856226981</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0.03173005239446805</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0.0807622353182755</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0.09564761331910479</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0.8808040201005025</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0.09228250993890633</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>0.02648027203430003</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>0.06414953246848001</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0.03111328699147676</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>0.01090442393550651</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>-0.02760740342064522</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>-0.05704244612001336</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>-0.01659630286594486</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>-0.1183465373208592</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>-0.01193746814567975</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>-0.00860097397479203</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>-0.07104217536119665</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>0.02423458106286523</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>0.003559977901854942</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>-0.07250572728734915</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>-0.03708816873328724</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>-0.1000775872627982</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>0.06066533727596326</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>0.04908090745567292</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>0.04948424025524679</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>0.04343710811487878</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>0.007317444774918589</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>-0.03055464654681397</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>0.02037067364003797</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>0.06556258745395824</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>0.07907092025978119</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>0.03411706275744241</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>0.004272137648543542</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>-0.09090350123735332</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>-0.0312158006752083</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>-0.1338413728586092</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA16" t="n">
+        <v>0.04958029702255527</v>
+      </c>
+      <c r="EB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC16" t="n">
+        <v>0.03767666325355683</v>
+      </c>
+      <c r="ED16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE16" t="n">
+        <v>0.04287805800588372</v>
+      </c>
+      <c r="EF16" t="n">
+        <v>0.08802258122706982</v>
+      </c>
+      <c r="EG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH16" t="n">
+        <v>0.0778557308816603</v>
+      </c>
+      <c r="EI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK16" t="n">
+        <v>0.02352542773313661</v>
+      </c>
+      <c r="EL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM16" t="n">
+        <v>-0.03556224323070836</v>
+      </c>
+      <c r="EN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO16" t="n">
+        <v>-0.002496213095313424</v>
+      </c>
+      <c r="EP16" t="n">
+        <v>0.01917194457277701</v>
+      </c>
+      <c r="EQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER16" t="n">
+        <v>-0.08131260490019475</v>
+      </c>
+      <c r="ES16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET16" t="n">
+        <v>0.09167118246054841</v>
+      </c>
+      <c r="EU16" t="n">
+        <v>0.08513063114718204</v>
+      </c>
+      <c r="EV16" t="n">
+        <v>0.01236717692181848</v>
+      </c>
+      <c r="EW16" t="n">
+        <v>0.1282561726358727</v>
+      </c>
+      <c r="EX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY16" t="n">
+        <v>0.1211309289634797</v>
+      </c>
+      <c r="EZ16" t="n">
+        <v>0.09771730424242649</v>
+      </c>
+      <c r="FA16" t="n">
+        <v>0.08894294937521703</v>
+      </c>
+      <c r="FB16" t="n">
+        <v>0.1565600351077913</v>
+      </c>
+      <c r="FC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE16" t="n">
+        <v>0.03267500788580695</v>
+      </c>
+      <c r="FF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG16" t="n">
+        <v>-0.005074397845294505</v>
+      </c>
+      <c r="FH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ16" t="n">
+        <v>0.03398591961192828</v>
+      </c>
+      <c r="FK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL16" t="n">
+        <v>-0.03014267633282261</v>
+      </c>
+      <c r="FM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN16" t="n">
+        <v>0.04735988797496787</v>
+      </c>
+      <c r="FO16" t="n">
+        <v>0.09311741623931284</v>
+      </c>
+      <c r="FP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ16" t="n">
+        <v>0.07859427683477732</v>
+      </c>
+      <c r="FR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS16" t="n">
+        <v>0.08003427114572602</v>
+      </c>
+      <c r="FT16" t="n">
+        <v>0.1128130272731857</v>
+      </c>
+      <c r="FU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV16" t="n">
+        <v>0.1066310970847022</v>
+      </c>
+      <c r="FW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX16" t="n">
+        <v>0.1144564837036907</v>
+      </c>
+      <c r="FY16" t="n">
+        <v>0.0975725389923783</v>
+      </c>
+      <c r="FZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA16" t="n">
+        <v>0.1383726057069632</v>
+      </c>
+      <c r="GB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC16" t="n">
+        <v>0.04122754927296078</v>
+      </c>
+      <c r="GD16" t="n">
+        <v>0.06583689068846306</v>
+      </c>
+      <c r="GE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF16" t="n">
+        <v>0.09527281562122616</v>
+      </c>
+      <c r="GG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH16" t="n">
+        <v>0.1656224176643271</v>
+      </c>
+      <c r="GI16" t="n">
+        <v>0.1226329664758226</v>
+      </c>
+      <c r="GJ16" t="n">
+        <v>0.1470295826961191</v>
+      </c>
+      <c r="GK16" t="n">
+        <v>0.151852970478912</v>
+      </c>
+      <c r="GL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN16" t="n">
+        <v>0.05635782458923833</v>
+      </c>
+      <c r="GO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP16" t="n">
+        <v>0.04895575471101705</v>
+      </c>
+      <c r="GQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS16" t="n">
+        <v>0.04860359199013247</v>
+      </c>
+      <c r="GT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU16" t="n">
+        <v>-0.005321570561765996</v>
+      </c>
+      <c r="GV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW16" t="n">
+        <v>0.1264398385601631</v>
+      </c>
+      <c r="GX16" t="n">
+        <v>0.1253405018517911</v>
+      </c>
+      <c r="GY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ16" t="n">
+        <v>0.1331207839911026</v>
+      </c>
+      <c r="HA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC16" t="n">
+        <v>0.0506801426312016</v>
+      </c>
+      <c r="HD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="HE16" t="n">
+        <v>0.02307017931008722</v>
+      </c>
+      <c r="HF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG16" t="n">
+        <v>0.1259687172903538</v>
+      </c>
+      <c r="HH16" t="n">
+        <v>0.1171647694115617</v>
+      </c>
+      <c r="HI16" t="n">
+        <v>0.02753817881715973</v>
+      </c>
+      <c r="HJ16" t="n">
+        <v>0.1511921047807538</v>
+      </c>
+      <c r="HK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL16" t="n">
+        <v>0.145452942104615</v>
+      </c>
+      <c r="HM16" t="n">
+        <v>0.09659261142770881</v>
+      </c>
+      <c r="HN16" t="n">
+        <v>0.2350916779849095</v>
+      </c>
+      <c r="HO16" t="n">
+        <v>0.1658264181942425</v>
+      </c>
+      <c r="HP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ16" t="n">
+        <v>-0.005110195092212132</v>
+      </c>
+      <c r="HR16" t="n">
+        <v>0.0097205669984932</v>
+      </c>
+      <c r="HS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="HT16" t="n">
+        <v>-0.08092398025793256</v>
+      </c>
+      <c r="HU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="HW16" t="n">
+        <v>0.02390046392681161</v>
+      </c>
+      <c r="HX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="HY16" t="n">
+        <v>-0.01783028571776434</v>
+      </c>
+      <c r="HZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA16" t="n">
+        <v>0.01394231223596993</v>
+      </c>
+      <c r="IB16" t="n">
+        <v>0.1011969420181187</v>
+      </c>
+      <c r="IC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ID16" t="n">
+        <v>0.05479931999351469</v>
+      </c>
+      <c r="IE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="IG16" t="n">
+        <v>0.07005443435350658</v>
+      </c>
+      <c r="IH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="II16" t="n">
+        <v>0.02022162623288403</v>
+      </c>
+      <c r="IJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="IL16" t="n">
+        <v>0.03672966750137012</v>
+      </c>
+      <c r="IM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="IN16" t="n">
+        <v>0.02177813970409196</v>
+      </c>
+      <c r="IO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP16" t="n">
+        <v>0.02026871633711617</v>
+      </c>
+      <c r="IQ16" t="n">
+        <v>0.07035681016556596</v>
+      </c>
+      <c r="IR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="IS16" t="n">
+        <v>0.09047408662163473</v>
+      </c>
+      <c r="IT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU16" t="n">
+        <v>0.01270668337085064</v>
+      </c>
+      <c r="IV16" t="n">
+        <v>0.09544102067758468</v>
+      </c>
+      <c r="IW16" t="n">
+        <v>0.03237511987851042</v>
+      </c>
+      <c r="IX16" t="n">
+        <v>0.05700279271626237</v>
+      </c>
+      <c r="IY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ16" t="n">
+        <v>-0.07538612817985384</v>
+      </c>
+      <c r="JA16" t="n">
+        <v>-0.01124475812928981</v>
+      </c>
+      <c r="JB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="JC16" t="n">
+        <v>-0.1358554711593053</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-16 11:03:22</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D17" t="n">
+        <v>50</v>
+      </c>
+      <c r="E17" t="n">
+        <v>50</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>0.2562070907440224</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.7438971340978656</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.3358570563536667</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.6435578232796599</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.5105249601387518</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.1967736432510528</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.485011862525429</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.3942620419297467</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.53200204612197</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.197246649118916</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.3329162674354369</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.3979774858602876</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.4115186982678609</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.172152472381585</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.502367433714635</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.3310209403516561</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.4818544475540582</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.1959267791074837</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.4251551724689052</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.4073581815350956</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.2267777563226126</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0.1497738362575288</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0.3645030495714258</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.2320256696873849</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.00725513071051354</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>-0.07283852732826084</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0.0697705304158668</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0.03437629374528271</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0.1499565143173955</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>5.400642901631602e-06</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0.05282719609533702</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0.04288038562631999</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>-0.01813212076066387</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>-0.1003746856226981</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0.0807622353182755</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0.09564761331910479</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0.9355778894472362</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>0.09228250993890633</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>0.02648027203430003</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>0.06414953246848001</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>0.03111328699147676</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>0.01090442393550651</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>-0.02760740342064522</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>-0.01659630286594486</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>-0.1183465373208592</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>3.392653316060199e-06</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>-0.00860097397479203</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>-0.07104217536119665</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>0.02423458106286523</v>
+      </c>
+      <c r="CN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO17" t="n">
+        <v>0.003559977901854942</v>
+      </c>
+      <c r="CP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR17" t="n">
+        <v>-0.03708816873328724</v>
+      </c>
+      <c r="CS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT17" t="n">
+        <v>-0.1000775872627982</v>
+      </c>
+      <c r="CU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW17" t="n">
+        <v>0.06066533727596326</v>
+      </c>
+      <c r="CX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY17" t="n">
+        <v>0.04908090745567292</v>
+      </c>
+      <c r="CZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB17" t="n">
+        <v>0.04948424025524679</v>
+      </c>
+      <c r="DC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD17" t="n">
+        <v>0.04343710811487878</v>
+      </c>
+      <c r="DE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>0.007317444774918589</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI17" t="n">
+        <v>-0.03055464654681397</v>
+      </c>
+      <c r="DJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL17" t="n">
+        <v>0.06556258745395824</v>
+      </c>
+      <c r="DM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN17" t="n">
+        <v>0.07907092025978119</v>
+      </c>
+      <c r="DO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ17" t="n">
+        <v>0.03411706275744241</v>
+      </c>
+      <c r="DR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS17" t="n">
+        <v>0.004272137648543542</v>
+      </c>
+      <c r="DT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV17" t="n">
+        <v>-0.0312158006752083</v>
+      </c>
+      <c r="DW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX17" t="n">
+        <v>-0.1338413728586092</v>
+      </c>
+      <c r="DY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ17" t="n">
+        <v>2.067828567378008e-06</v>
+      </c>
+      <c r="EA17" t="n">
+        <v>0.04958029702255527</v>
+      </c>
+      <c r="EB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC17" t="n">
+        <v>0.03767666325355683</v>
+      </c>
+      <c r="ED17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF17" t="n">
+        <v>0.08802258122706982</v>
+      </c>
+      <c r="EG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH17" t="n">
+        <v>0.0778557308816603</v>
+      </c>
+      <c r="EI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ17" t="n">
+        <v>3.804891450159727e-06</v>
+      </c>
+      <c r="EK17" t="n">
+        <v>0.02352542773313661</v>
+      </c>
+      <c r="EL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM17" t="n">
+        <v>-0.03556224323070836</v>
+      </c>
+      <c r="EN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP17" t="n">
+        <v>0.01917194457277701</v>
+      </c>
+      <c r="EQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER17" t="n">
+        <v>-0.08131260490019475</v>
+      </c>
+      <c r="ES17" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU17" t="n">
+        <v>0.08513063114718204</v>
+      </c>
+      <c r="EV17" t="n">
+        <v>0.01236717692181848</v>
+      </c>
+      <c r="EW17" t="n">
+        <v>0.1282561726358727</v>
+      </c>
+      <c r="EX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ17" t="n">
+        <v>0.09771730424242649</v>
+      </c>
+      <c r="FA17" t="n">
+        <v>0.08894294937521703</v>
+      </c>
+      <c r="FB17" t="n">
+        <v>0.1565600351077913</v>
+      </c>
+      <c r="FC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD17" t="n">
+        <v>1.116136871081418e-05</v>
+      </c>
+      <c r="FE17" t="n">
+        <v>0.03267500788580695</v>
+      </c>
+      <c r="FF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG17" t="n">
+        <v>-0.005074397845294505</v>
+      </c>
+      <c r="FH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ17" t="n">
+        <v>0.03398591961192828</v>
+      </c>
+      <c r="FK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL17" t="n">
+        <v>-0.03014267633282261</v>
+      </c>
+      <c r="FM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO17" t="n">
+        <v>0.09311741623931284</v>
+      </c>
+      <c r="FP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ17" t="n">
+        <v>0.07859427683477732</v>
+      </c>
+      <c r="FR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT17" t="n">
+        <v>0.1128130272731857</v>
+      </c>
+      <c r="FU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV17" t="n">
+        <v>0.1066310970847022</v>
+      </c>
+      <c r="FW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY17" t="n">
+        <v>0.0975725389923783</v>
+      </c>
+      <c r="FZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA17" t="n">
+        <v>0.1383726057069632</v>
+      </c>
+      <c r="GB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC17" t="n">
+        <v>2.527827534669234e-05</v>
+      </c>
+      <c r="GD17" t="n">
+        <v>0.06583689068846306</v>
+      </c>
+      <c r="GE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF17" t="n">
+        <v>0.09527281562122616</v>
+      </c>
+      <c r="GG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH17" t="n">
+        <v>0.05812562259523011</v>
+      </c>
+      <c r="GI17" t="n">
+        <v>0.1226329664758226</v>
+      </c>
+      <c r="GJ17" t="n">
+        <v>0.1470295826961191</v>
+      </c>
+      <c r="GK17" t="n">
+        <v>0.151852970478912</v>
+      </c>
+      <c r="GL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN17" t="n">
+        <v>0.05635782458923833</v>
+      </c>
+      <c r="GO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP17" t="n">
+        <v>0.04895575471101705</v>
+      </c>
+      <c r="GQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS17" t="n">
+        <v>0.04860359199013247</v>
+      </c>
+      <c r="GT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU17" t="n">
+        <v>-0.005321570561765996</v>
+      </c>
+      <c r="GV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX17" t="n">
+        <v>0.1253405018517911</v>
+      </c>
+      <c r="GY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ17" t="n">
+        <v>0.1331207839911026</v>
+      </c>
+      <c r="HA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB17" t="n">
+        <v>2.712009135622742e-05</v>
+      </c>
+      <c r="HC17" t="n">
+        <v>0.0506801426312016</v>
+      </c>
+      <c r="HD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="HE17" t="n">
+        <v>0.02307017931008722</v>
+      </c>
+      <c r="HF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH17" t="n">
+        <v>0.1171647694115617</v>
+      </c>
+      <c r="HI17" t="n">
+        <v>0.02753817881715973</v>
+      </c>
+      <c r="HJ17" t="n">
+        <v>0.1511921047807538</v>
+      </c>
+      <c r="HK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM17" t="n">
+        <v>0.09659261142770881</v>
+      </c>
+      <c r="HN17" t="n">
+        <v>0.2350916779849095</v>
+      </c>
+      <c r="HO17" t="n">
+        <v>0.1658264181942425</v>
+      </c>
+      <c r="HP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR17" t="n">
+        <v>0.0097205669984932</v>
+      </c>
+      <c r="HS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="HT17" t="n">
+        <v>-0.08092398025793256</v>
+      </c>
+      <c r="HU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="HW17" t="n">
+        <v>0.02390046392681161</v>
+      </c>
+      <c r="HX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="HY17" t="n">
+        <v>-0.01783028571776434</v>
+      </c>
+      <c r="HZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="IB17" t="n">
+        <v>0.1011969420181187</v>
+      </c>
+      <c r="IC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="ID17" t="n">
+        <v>0.05479931999351469</v>
+      </c>
+      <c r="IE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF17" t="n">
+        <v>4.72901570569637e-06</v>
+      </c>
+      <c r="IG17" t="n">
+        <v>0.07005443435350658</v>
+      </c>
+      <c r="IH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="II17" t="n">
+        <v>0.02022162623288403</v>
+      </c>
+      <c r="IJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="IL17" t="n">
+        <v>0.03672966750137012</v>
+      </c>
+      <c r="IM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="IN17" t="n">
+        <v>0.02177813970409196</v>
+      </c>
+      <c r="IO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="IQ17" t="n">
+        <v>0.07035681016556596</v>
+      </c>
+      <c r="IR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="IS17" t="n">
+        <v>0.09047408662163473</v>
+      </c>
+      <c r="IT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="IV17" t="n">
+        <v>0.09544102067758468</v>
+      </c>
+      <c r="IW17" t="n">
+        <v>0.03237511987851042</v>
+      </c>
+      <c r="IX17" t="n">
+        <v>0.05700279271626237</v>
+      </c>
+      <c r="IY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA17" t="n">
+        <v>-0.01124475812928981</v>
+      </c>
+      <c r="JB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="JC17" t="n">
+        <v>-0.1358554711593053</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-04-16 11:04:22</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" t="n">
+        <v>100</v>
+      </c>
+      <c r="D18" t="n">
+        <v>50</v>
+      </c>
+      <c r="E18" t="n">
+        <v>50</v>
+      </c>
+      <c r="F18" t="n">
+        <v>5</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>0.2220762988580205</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.512665407645299</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.163039017076092</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.3706923598207267</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.6009180124175695</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.3338797321802806</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.5248107952483532</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.4717167956663637</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.4916022914367599</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.2904214012501027</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.4642354255931951</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.4422579284161834</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.3953917714022094</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.256968058618641</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.4391594474559982</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.4051626907151963</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.3270930766723362</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.2315601995760841</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.3830566024188722</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.378742683526372</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.3659237566665554</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0.2517793474874719</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0.3950864391262446</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.380817398510826</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.051700852724292e-06</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0.03213758516822962</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0.03298242155452278</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0.01269718614916328</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0.0106882844325721</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0.04411102269612127</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0.04226166828901452</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0.03638821067383498</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0.01681901334844079</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0.05879325592237104</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>0.0008141832293096618</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>0.06162362132781011</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>0.9413533533533534</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>0.00174627505960817</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>-0.02880239405345075</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>0.01932549567286986</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>-0.01653855485122683</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>0.03075204775195141</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>0.01412941753310348</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>0.03871919829033913</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>0.01855925052400355</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>0.03835895997683601</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>0.01002283617893552</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>0.08219233943161922</v>
+      </c>
+      <c r="CN18" t="n">
+        <v>0.004698157915060285</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>0.06141832673640824</v>
+      </c>
+      <c r="CP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ18" t="n">
+        <v>8.99505206770642e-07</v>
+      </c>
+      <c r="CR18" t="n">
+        <v>0.01097820889160808</v>
+      </c>
+      <c r="CS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT18" t="n">
+        <v>-0.03690601230919455</v>
+      </c>
+      <c r="CU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW18" t="n">
+        <v>0.02114881452869118</v>
+      </c>
+      <c r="CX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY18" t="n">
+        <v>-0.002666310391341191</v>
+      </c>
+      <c r="CZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB18" t="n">
+        <v>0.04327880803388323</v>
+      </c>
+      <c r="DC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD18" t="n">
+        <v>0.0312109021986321</v>
+      </c>
+      <c r="DE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF18" t="n">
+        <v>9.590233589508524e-07</v>
+      </c>
+      <c r="DG18" t="n">
+        <v>0.03990042265394066</v>
+      </c>
+      <c r="DH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI18" t="n">
+        <v>0.0002769818918783444</v>
+      </c>
+      <c r="DJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL18" t="n">
+        <v>0.06336310452480753</v>
+      </c>
+      <c r="DM18" t="n">
+        <v>0.002399863427747931</v>
+      </c>
+      <c r="DN18" t="n">
+        <v>0.07916985799375562</v>
+      </c>
+      <c r="DO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ18" t="n">
+        <v>0.006833387500124431</v>
+      </c>
+      <c r="DR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS18" t="n">
+        <v>0.002486171611522787</v>
+      </c>
+      <c r="DT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV18" t="n">
+        <v>0.0135123323342331</v>
+      </c>
+      <c r="DW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX18" t="n">
+        <v>0.00807596186700189</v>
+      </c>
+      <c r="DY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA18" t="n">
+        <v>0.02924195065874801</v>
+      </c>
+      <c r="EB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC18" t="n">
+        <v>0.01901106571408978</v>
+      </c>
+      <c r="ED18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF18" t="n">
+        <v>0.08309402595095965</v>
+      </c>
+      <c r="EG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH18" t="n">
+        <v>0.07242200518991034</v>
+      </c>
+      <c r="EI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK18" t="n">
+        <v>-0.02400918976652706</v>
+      </c>
+      <c r="EL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM18" t="n">
+        <v>-0.07213495670444392</v>
+      </c>
+      <c r="EN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP18" t="n">
+        <v>0.01135569381840972</v>
+      </c>
+      <c r="EQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER18" t="n">
+        <v>-0.02509527946170018</v>
+      </c>
+      <c r="ES18" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU18" t="n">
+        <v>0.04577119432450395</v>
+      </c>
+      <c r="EV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW18" t="n">
+        <v>0.04235868152814665</v>
+      </c>
+      <c r="EX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ18" t="n">
+        <v>-0.0002097365405444654</v>
+      </c>
+      <c r="FA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB18" t="n">
+        <v>-0.06118441210219847</v>
+      </c>
+      <c r="FC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE18" t="n">
+        <v>0.04716357064125912</v>
+      </c>
+      <c r="FF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG18" t="n">
+        <v>0.04185667135170823</v>
+      </c>
+      <c r="FH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ18" t="n">
+        <v>0.06681722639409794</v>
+      </c>
+      <c r="FK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL18" t="n">
+        <v>0.03999737585137323</v>
+      </c>
+      <c r="FM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN18" t="n">
+        <v>4.964131722641163e-07</v>
+      </c>
+      <c r="FO18" t="n">
+        <v>0.03841304717534481</v>
+      </c>
+      <c r="FP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ18" t="n">
+        <v>0.02155994385208829</v>
+      </c>
+      <c r="FR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT18" t="n">
+        <v>0.08972065342534727</v>
+      </c>
+      <c r="FU18" t="n">
+        <v>0.02028361243097482</v>
+      </c>
+      <c r="FV18" t="n">
+        <v>0.09265000316290524</v>
+      </c>
+      <c r="FW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY18" t="n">
+        <v>0.02878995476973052</v>
+      </c>
+      <c r="FZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA18" t="n">
+        <v>0.003462919326619284</v>
+      </c>
+      <c r="GB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD18" t="n">
+        <v>0.005205481851621524</v>
+      </c>
+      <c r="GE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF18" t="n">
+        <v>-0.03156361145421006</v>
+      </c>
+      <c r="GG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GI18" t="n">
+        <v>0.09924442858974353</v>
+      </c>
+      <c r="GJ18" t="n">
+        <v>0.1019781185294824</v>
+      </c>
+      <c r="GK18" t="n">
+        <v>0.1580575732770333</v>
+      </c>
+      <c r="GL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN18" t="n">
+        <v>0.07955937313271948</v>
+      </c>
+      <c r="GO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP18" t="n">
+        <v>0.05762591213102712</v>
+      </c>
+      <c r="GQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR18" t="n">
+        <v>1.173394761703718e-06</v>
+      </c>
+      <c r="GS18" t="n">
+        <v>0.03257200300310992</v>
+      </c>
+      <c r="GT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU18" t="n">
+        <v>-0.005032452471484753</v>
+      </c>
+      <c r="GV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW18" t="n">
+        <v>2.392041610870145e-06</v>
+      </c>
+      <c r="GX18" t="n">
+        <v>0.009624252295213968</v>
+      </c>
+      <c r="GY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ18" t="n">
+        <v>-0.004916250253375393</v>
+      </c>
+      <c r="HA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC18" t="n">
+        <v>0.03352095517755536</v>
+      </c>
+      <c r="HD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="HE18" t="n">
+        <v>0.01844851227270021</v>
+      </c>
+      <c r="HF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH18" t="n">
+        <v>0.08212761042941319</v>
+      </c>
+      <c r="HI18" t="n">
+        <v>0.02489655092139507</v>
+      </c>
+      <c r="HJ18" t="n">
+        <v>0.09798305622363936</v>
+      </c>
+      <c r="HK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL18" t="n">
+        <v>6.670874015214593e-07</v>
+      </c>
+      <c r="HM18" t="n">
+        <v>0.01238561433255004</v>
+      </c>
+      <c r="HN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="HO18" t="n">
+        <v>0.009751271096852573</v>
+      </c>
+      <c r="HP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR18" t="n">
+        <v>0.0001049190459050775</v>
+      </c>
+      <c r="HS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="HT18" t="n">
+        <v>-0.03837435582968256</v>
+      </c>
+      <c r="HU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="HW18" t="n">
+        <v>0.08711306121510076</v>
+      </c>
+      <c r="HX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="HY18" t="n">
+        <v>0.08934917130341594</v>
+      </c>
+      <c r="HZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="IB18" t="n">
+        <v>-0.02622461161365992</v>
+      </c>
+      <c r="IC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="ID18" t="n">
+        <v>-0.05451751306570535</v>
+      </c>
+      <c r="IE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="IG18" t="n">
+        <v>0.01525429230278179</v>
+      </c>
+      <c r="IH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="II18" t="n">
+        <v>-0.01597344351631224</v>
+      </c>
+      <c r="IJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="IL18" t="n">
+        <v>0.06101763468567134</v>
+      </c>
+      <c r="IM18" t="n">
+        <v>0.01793462377648873</v>
+      </c>
+      <c r="IN18" t="n">
+        <v>0.07698585834338659</v>
+      </c>
+      <c r="IO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="IQ18" t="n">
+        <v>0.08737200100479445</v>
+      </c>
+      <c r="IR18" t="n">
+        <v>0.03989333265905734</v>
+      </c>
+      <c r="IS18" t="n">
+        <v>0.1140274349804736</v>
+      </c>
+      <c r="IT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="IV18" t="n">
+        <v>0.05464298669358475</v>
+      </c>
+      <c r="IW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="IX18" t="n">
+        <v>0.04320282427780254</v>
+      </c>
+      <c r="IY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA18" t="n">
+        <v>0.03768344605585518</v>
+      </c>
+      <c r="JB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="JC18" t="n">
+        <v>0.04897292210852509</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-04-16 11:08:52</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>20</v>
+      </c>
+      <c r="C19" t="n">
+        <v>100</v>
+      </c>
+      <c r="D19" t="n">
+        <v>50</v>
+      </c>
+      <c r="E19" t="n">
+        <v>50</v>
+      </c>
+      <c r="F19" t="n">
+        <v>5</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>0.0463151545634951</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.4401169485075527</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.07184863879715181</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.2438600315018899</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.4470020335639238</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.2852689404063414</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.4616803100683567</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.435337001466567</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.4097447948970713</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.2708527350560225</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.4230534644716417</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.4166431296931087</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.4481032238452296</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.2868073563848664</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.446391972989987</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.4322623208388844</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.4730390172917288</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.3124246641042563</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.4476622825188341</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0.4518031074076414</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.4557806204125633</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0.2925551106362693</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0.4515084023224811</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0.4320796384007356</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0.04526292078491903</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0.03811020257678774</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0.002936876180084348</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>-0.01035161624950018</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0.02632854241849285</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>-0.005117914631159693</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0.01793161235167599</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0.006960739522292867</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0.01023217420559605</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>-0.006494092389955647</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0.9879719859929964</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>0.04782806044295755</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>0.02640346845109189</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>0.03987094312751173</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>0.02042457629551119</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>0.03417689020218818</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>0.01937958834487259</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>0.04534910087542227</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>0.02938740685628877</v>
+      </c>
+      <c r="CF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH19" t="n">
+        <v>0.03187012199406738</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>0.002536160640824676</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>0.0579534282129473</v>
+      </c>
+      <c r="CN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO19" t="n">
+        <v>0.06292449885256167</v>
+      </c>
+      <c r="CP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR19" t="n">
+        <v>-0.0007330840740396815</v>
+      </c>
+      <c r="CS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT19" t="n">
+        <v>-0.02913829755696832</v>
+      </c>
+      <c r="CU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW19" t="n">
+        <v>0.00846028301040584</v>
+      </c>
+      <c r="CX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY19" t="n">
+        <v>0.01195563116206374</v>
+      </c>
+      <c r="CZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB19" t="n">
+        <v>0.03091972833083469</v>
+      </c>
+      <c r="DC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD19" t="n">
+        <v>0.02598047167906558</v>
+      </c>
+      <c r="DE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG19" t="n">
+        <v>0.04480366859258099</v>
+      </c>
+      <c r="DH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI19" t="n">
+        <v>0.02590363917563379</v>
+      </c>
+      <c r="DJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL19" t="n">
+        <v>0.06698235519426766</v>
+      </c>
+      <c r="DM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN19" t="n">
+        <v>0.06059829889022652</v>
+      </c>
+      <c r="DO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ19" t="n">
+        <v>0.059802986939776</v>
+      </c>
+      <c r="DR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS19" t="n">
+        <v>0.04066047726230888</v>
+      </c>
+      <c r="DT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV19" t="n">
+        <v>0.04376838439353511</v>
+      </c>
+      <c r="DW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX19" t="n">
+        <v>0.038545076904859</v>
+      </c>
+      <c r="DY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA19" t="n">
+        <v>0.01218280903763692</v>
+      </c>
+      <c r="EB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC19" t="n">
+        <v>0.003484361081847578</v>
+      </c>
+      <c r="ED19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF19" t="n">
+        <v>0.06383068491556729</v>
+      </c>
+      <c r="EG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH19" t="n">
+        <v>0.06847854749933903</v>
+      </c>
+      <c r="EI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK19" t="n">
+        <v>0.01682560109940829</v>
+      </c>
+      <c r="EL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM19" t="n">
+        <v>0.00204089528636022</v>
+      </c>
+      <c r="EN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP19" t="n">
+        <v>0.06013545766086364</v>
+      </c>
+      <c r="EQ19" t="n">
+        <v>0.005702944217641651</v>
+      </c>
+      <c r="ER19" t="n">
+        <v>0.06144167202715543</v>
+      </c>
+      <c r="ES19" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU19" t="n">
+        <v>0.03994437093759988</v>
+      </c>
+      <c r="EV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW19" t="n">
+        <v>0.02182653902114921</v>
+      </c>
+      <c r="EX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ19" t="n">
+        <v>0.04211504764480363</v>
+      </c>
+      <c r="FA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB19" t="n">
+        <v>0.01656006953482951</v>
+      </c>
+      <c r="FC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE19" t="n">
+        <v>-0.007585615833203015</v>
+      </c>
+      <c r="FF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG19" t="n">
+        <v>-0.04250544626660348</v>
+      </c>
+      <c r="FH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ19" t="n">
+        <v>0.02859312418394247</v>
+      </c>
+      <c r="FK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL19" t="n">
+        <v>-0.002975651849978012</v>
+      </c>
+      <c r="FM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO19" t="n">
+        <v>0.004523202094763775</v>
+      </c>
+      <c r="FP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ19" t="n">
+        <v>-0.00509440225778542</v>
+      </c>
+      <c r="FR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT19" t="n">
+        <v>0.02360871007382257</v>
+      </c>
+      <c r="FU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV19" t="n">
+        <v>0.002565547579856923</v>
+      </c>
+      <c r="FW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY19" t="n">
+        <v>0.002289283973748414</v>
+      </c>
+      <c r="FZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA19" t="n">
+        <v>-0.0245062108635472</v>
+      </c>
+      <c r="GB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD19" t="n">
+        <v>0.02061220410180786</v>
+      </c>
+      <c r="GE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF19" t="n">
+        <v>-0.02291001275410221</v>
+      </c>
+      <c r="GG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="GI19" t="n">
+        <v>0.07378357664335511</v>
+      </c>
+      <c r="GJ19" t="n">
+        <v>0.03557106377561686</v>
+      </c>
+      <c r="GK19" t="n">
+        <v>0.09114087358290399</v>
+      </c>
+      <c r="GL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN19" t="n">
+        <v>0.01044640859529394</v>
+      </c>
+      <c r="GO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP19" t="n">
+        <v>-0.03082913806688377</v>
+      </c>
+      <c r="GQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS19" t="n">
+        <v>0.006634117435635206</v>
+      </c>
+      <c r="GT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU19" t="n">
+        <v>-0.02515031377379071</v>
+      </c>
+      <c r="GV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX19" t="n">
+        <v>0.03569758737057767</v>
+      </c>
+      <c r="GY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ19" t="n">
+        <v>0.01086406821836385</v>
+      </c>
+      <c r="HA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="HC19" t="n">
+        <v>0.04604340202223885</v>
+      </c>
+      <c r="HD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="HE19" t="n">
+        <v>0.04107110867901612</v>
+      </c>
+      <c r="HF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="HH19" t="n">
+        <v>0.0146455571500069</v>
+      </c>
+      <c r="HI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ19" t="n">
+        <v>-0.01706227686774679</v>
+      </c>
+      <c r="HK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM19" t="n">
+        <v>0.01688872417900352</v>
+      </c>
+      <c r="HN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="HO19" t="n">
+        <v>0.009751898782646425</v>
+      </c>
+      <c r="HP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="HR19" t="n">
+        <v>0.02544783858758252</v>
+      </c>
+      <c r="HS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="HT19" t="n">
+        <v>9.619299009363336e-05</v>
+      </c>
+      <c r="HU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="HW19" t="n">
+        <v>0.02459148834199124</v>
+      </c>
+      <c r="HX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="HY19" t="n">
+        <v>0.02965082644347247</v>
+      </c>
+      <c r="HZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="IB19" t="n">
+        <v>0.05419960613279529</v>
+      </c>
+      <c r="IC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="ID19" t="n">
+        <v>0.05111119736234715</v>
+      </c>
+      <c r="IE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="IG19" t="n">
+        <v>0.03568496699010669</v>
+      </c>
+      <c r="IH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="II19" t="n">
+        <v>0.009035833288616024</v>
+      </c>
+      <c r="IJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="IL19" t="n">
+        <v>0.08723722443652941</v>
+      </c>
+      <c r="IM19" t="n">
+        <v>0.0552456625915875</v>
+      </c>
+      <c r="IN19" t="n">
+        <v>0.1028823251850256</v>
+      </c>
+      <c r="IO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="IQ19" t="n">
+        <v>0.03638898438785349</v>
+      </c>
+      <c r="IR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="IS19" t="n">
+        <v>0.01201361099738081</v>
+      </c>
+      <c r="IT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="IV19" t="n">
+        <v>0.04192062934690717</v>
+      </c>
+      <c r="IW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="IX19" t="n">
+        <v>0.03127851640033308</v>
+      </c>
+      <c r="IY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="JA19" t="n">
+        <v>0.04322407588679886</v>
+      </c>
+      <c r="JB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="JC19" t="n">
+        <v>0.03474728674338361</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ranking/results.xlsx
+++ b/ranking/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JC54"/>
+  <dimension ref="A1:JC69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28196,7 +28196,7 @@
         <v>0</v>
       </c>
       <c r="AX54" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr"/>
@@ -28286,7 +28286,7 @@
         <v>0</v>
       </c>
       <c r="CV54" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW54" t="inlineStr"/>
       <c r="CX54" t="inlineStr"/>
@@ -28304,7 +28304,7 @@
         <v>0</v>
       </c>
       <c r="DF54" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG54" t="inlineStr"/>
       <c r="DH54" t="inlineStr"/>
@@ -28579,6 +28579,8259 @@
       <c r="JA54" t="inlineStr"/>
       <c r="JB54" t="inlineStr"/>
       <c r="JC54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-04-19 09:11:53</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>10</v>
+      </c>
+      <c r="C55" t="n">
+        <v>50</v>
+      </c>
+      <c r="D55" t="n">
+        <v>50</v>
+      </c>
+      <c r="E55" t="n">
+        <v>40</v>
+      </c>
+      <c r="F55" t="n">
+        <v>5</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>0.5475648377671151</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.8554388777555109</v>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.3099633706345113</v>
+      </c>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0.3879172779073495</v>
+      </c>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0.6112793488936589</v>
+      </c>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0.002729237816950692</v>
+      </c>
+      <c r="AE55" t="inlineStr"/>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="inlineStr"/>
+      <c r="AH55" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>0.5889616842509742</v>
+      </c>
+      <c r="AJ55" t="inlineStr"/>
+      <c r="AK55" t="inlineStr"/>
+      <c r="AL55" t="inlineStr"/>
+      <c r="AM55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO55" t="inlineStr"/>
+      <c r="AP55" t="inlineStr"/>
+      <c r="AQ55" t="inlineStr"/>
+      <c r="AR55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>0.004140361641403947</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AU55" t="inlineStr"/>
+      <c r="AV55" t="inlineStr"/>
+      <c r="AW55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr"/>
+      <c r="BA55" t="inlineStr"/>
+      <c r="BB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>0.06771838191177033</v>
+      </c>
+      <c r="BD55" t="inlineStr"/>
+      <c r="BE55" t="inlineStr"/>
+      <c r="BF55" t="inlineStr"/>
+      <c r="BG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI55" t="inlineStr"/>
+      <c r="BJ55" t="inlineStr"/>
+      <c r="BK55" t="inlineStr"/>
+      <c r="BL55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN55" t="inlineStr"/>
+      <c r="BO55" t="inlineStr"/>
+      <c r="BP55" t="inlineStr"/>
+      <c r="BQ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS55" t="inlineStr"/>
+      <c r="BT55" t="inlineStr"/>
+      <c r="BU55" t="inlineStr"/>
+      <c r="BV55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX55" t="inlineStr"/>
+      <c r="BY55" t="inlineStr"/>
+      <c r="BZ55" t="inlineStr"/>
+      <c r="CA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC55" t="inlineStr"/>
+      <c r="CD55" t="inlineStr"/>
+      <c r="CE55" t="inlineStr"/>
+      <c r="CF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH55" t="inlineStr"/>
+      <c r="CI55" t="inlineStr"/>
+      <c r="CJ55" t="inlineStr"/>
+      <c r="CK55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM55" t="inlineStr"/>
+      <c r="CN55" t="inlineStr"/>
+      <c r="CO55" t="inlineStr"/>
+      <c r="CP55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR55" t="inlineStr"/>
+      <c r="CS55" t="inlineStr"/>
+      <c r="CT55" t="inlineStr"/>
+      <c r="CU55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW55" t="inlineStr"/>
+      <c r="CX55" t="inlineStr"/>
+      <c r="CY55" t="inlineStr"/>
+      <c r="CZ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA55" t="n">
+        <v>0.0004652425441040439</v>
+      </c>
+      <c r="DB55" t="inlineStr"/>
+      <c r="DC55" t="inlineStr"/>
+      <c r="DD55" t="inlineStr"/>
+      <c r="DE55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF55" t="n">
+        <v>0.002378210627634981</v>
+      </c>
+      <c r="DG55" t="inlineStr"/>
+      <c r="DH55" t="inlineStr"/>
+      <c r="DI55" t="inlineStr"/>
+      <c r="DJ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL55" t="inlineStr"/>
+      <c r="DM55" t="inlineStr"/>
+      <c r="DN55" t="inlineStr"/>
+      <c r="DO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ55" t="inlineStr"/>
+      <c r="DR55" t="inlineStr"/>
+      <c r="DS55" t="inlineStr"/>
+      <c r="DT55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV55" t="inlineStr"/>
+      <c r="DW55" t="inlineStr"/>
+      <c r="DX55" t="inlineStr"/>
+      <c r="DY55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA55" t="inlineStr"/>
+      <c r="EB55" t="inlineStr"/>
+      <c r="EC55" t="inlineStr"/>
+      <c r="ED55" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE55" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF55" t="inlineStr"/>
+      <c r="EG55" t="inlineStr"/>
+      <c r="EH55" t="inlineStr"/>
+      <c r="EI55" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ55" t="n">
+        <v>0.04929020872496286</v>
+      </c>
+      <c r="EK55" t="inlineStr"/>
+      <c r="EL55" t="inlineStr"/>
+      <c r="EM55" t="inlineStr"/>
+      <c r="EN55" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP55" t="inlineStr"/>
+      <c r="EQ55" t="inlineStr"/>
+      <c r="ER55" t="inlineStr"/>
+      <c r="ES55" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET55" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU55" t="inlineStr"/>
+      <c r="EV55" t="inlineStr"/>
+      <c r="EW55" t="inlineStr"/>
+      <c r="EX55" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY55" t="n">
+        <v>0.07118560336152206</v>
+      </c>
+      <c r="EZ55" t="inlineStr"/>
+      <c r="FA55" t="inlineStr"/>
+      <c r="FB55" t="inlineStr"/>
+      <c r="FC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD55" t="n">
+        <v>0.02956077589783197</v>
+      </c>
+      <c r="FE55" t="inlineStr"/>
+      <c r="FF55" t="inlineStr"/>
+      <c r="FG55" t="inlineStr"/>
+      <c r="FH55" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI55" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ55" t="inlineStr"/>
+      <c r="FK55" t="inlineStr"/>
+      <c r="FL55" t="inlineStr"/>
+      <c r="FM55" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN55" t="n">
+        <v>-0.05265502820501922</v>
+      </c>
+      <c r="FO55" t="inlineStr"/>
+      <c r="FP55" t="inlineStr"/>
+      <c r="FQ55" t="inlineStr"/>
+      <c r="FR55" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS55" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT55" t="inlineStr"/>
+      <c r="FU55" t="inlineStr"/>
+      <c r="FV55" t="inlineStr"/>
+      <c r="FW55" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX55" t="n">
+        <v>0.0007656575063817138</v>
+      </c>
+      <c r="FY55" t="inlineStr"/>
+      <c r="FZ55" t="inlineStr"/>
+      <c r="GA55" t="inlineStr"/>
+      <c r="GB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC55" t="n">
+        <v>0.001281440280566818</v>
+      </c>
+      <c r="GD55" t="inlineStr"/>
+      <c r="GE55" t="inlineStr"/>
+      <c r="GF55" t="inlineStr"/>
+      <c r="GG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH55" t="n">
+        <v>-0.03463245217292477</v>
+      </c>
+      <c r="GI55" t="inlineStr"/>
+      <c r="GJ55" t="inlineStr"/>
+      <c r="GK55" t="inlineStr"/>
+      <c r="GL55" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM55" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN55" t="inlineStr"/>
+      <c r="GO55" t="inlineStr"/>
+      <c r="GP55" t="inlineStr"/>
+      <c r="GQ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR55" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS55" t="inlineStr"/>
+      <c r="GT55" t="inlineStr"/>
+      <c r="GU55" t="inlineStr"/>
+      <c r="GV55" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW55" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX55" t="inlineStr"/>
+      <c r="GY55" t="inlineStr"/>
+      <c r="GZ55" t="inlineStr"/>
+      <c r="HA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC55" t="inlineStr"/>
+      <c r="HD55" t="inlineStr"/>
+      <c r="HE55" t="inlineStr"/>
+      <c r="HF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG55" t="n">
+        <v>0.08855134197779854</v>
+      </c>
+      <c r="HH55" t="inlineStr"/>
+      <c r="HI55" t="inlineStr"/>
+      <c r="HJ55" t="inlineStr"/>
+      <c r="HK55" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL55" t="n">
+        <v>0.07306578187951078</v>
+      </c>
+      <c r="HM55" t="inlineStr"/>
+      <c r="HN55" t="inlineStr"/>
+      <c r="HO55" t="inlineStr"/>
+      <c r="HP55" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR55" t="inlineStr"/>
+      <c r="HS55" t="inlineStr"/>
+      <c r="HT55" t="inlineStr"/>
+      <c r="HU55" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV55" t="n">
+        <v>0</v>
+      </c>
+      <c r="HW55" t="inlineStr"/>
+      <c r="HX55" t="inlineStr"/>
+      <c r="HY55" t="inlineStr"/>
+      <c r="HZ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="IB55" t="inlineStr"/>
+      <c r="IC55" t="inlineStr"/>
+      <c r="ID55" t="inlineStr"/>
+      <c r="IE55" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="IG55" t="inlineStr"/>
+      <c r="IH55" t="inlineStr"/>
+      <c r="II55" t="inlineStr"/>
+      <c r="IJ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK55" t="n">
+        <v>-0.05255075666523811</v>
+      </c>
+      <c r="IL55" t="inlineStr"/>
+      <c r="IM55" t="inlineStr"/>
+      <c r="IN55" t="inlineStr"/>
+      <c r="IO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP55" t="n">
+        <v>0.001368042583380755</v>
+      </c>
+      <c r="IQ55" t="inlineStr"/>
+      <c r="IR55" t="inlineStr"/>
+      <c r="IS55" t="inlineStr"/>
+      <c r="IT55" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU55" t="n">
+        <v>0</v>
+      </c>
+      <c r="IV55" t="inlineStr"/>
+      <c r="IW55" t="inlineStr"/>
+      <c r="IX55" t="inlineStr"/>
+      <c r="IY55" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA55" t="inlineStr"/>
+      <c r="JB55" t="inlineStr"/>
+      <c r="JC55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-04-19 09:12:36</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>10</v>
+      </c>
+      <c r="C56" t="n">
+        <v>50</v>
+      </c>
+      <c r="D56" t="n">
+        <v>50</v>
+      </c>
+      <c r="E56" t="n">
+        <v>40</v>
+      </c>
+      <c r="F56" t="n">
+        <v>5</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>0.5541499977809968</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.852248496993988</v>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.320264710250651</v>
+      </c>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0.3944323489153631</v>
+      </c>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0.6069290177732637</v>
+      </c>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr"/>
+      <c r="AC56" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.01804082382415515</v>
+      </c>
+      <c r="AE56" t="inlineStr"/>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="inlineStr"/>
+      <c r="AH56" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>0.5530727173901038</v>
+      </c>
+      <c r="AJ56" t="inlineStr"/>
+      <c r="AK56" t="inlineStr"/>
+      <c r="AL56" t="inlineStr"/>
+      <c r="AM56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO56" t="inlineStr"/>
+      <c r="AP56" t="inlineStr"/>
+      <c r="AQ56" t="inlineStr"/>
+      <c r="AR56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>0.02101463494262249</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AU56" t="inlineStr"/>
+      <c r="AV56" t="inlineStr"/>
+      <c r="AW56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr"/>
+      <c r="BA56" t="inlineStr"/>
+      <c r="BB56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>0.1006822987367849</v>
+      </c>
+      <c r="BD56" t="inlineStr"/>
+      <c r="BE56" t="inlineStr"/>
+      <c r="BF56" t="inlineStr"/>
+      <c r="BG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI56" t="inlineStr"/>
+      <c r="BJ56" t="inlineStr"/>
+      <c r="BK56" t="inlineStr"/>
+      <c r="BL56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM56" t="n">
+        <v>1.219758118406355e-06</v>
+      </c>
+      <c r="BN56" t="inlineStr"/>
+      <c r="BO56" t="inlineStr"/>
+      <c r="BP56" t="inlineStr"/>
+      <c r="BQ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS56" t="inlineStr"/>
+      <c r="BT56" t="inlineStr"/>
+      <c r="BU56" t="inlineStr"/>
+      <c r="BV56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX56" t="inlineStr"/>
+      <c r="BY56" t="inlineStr"/>
+      <c r="BZ56" t="inlineStr"/>
+      <c r="CA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB56" t="n">
+        <v>2.658613885863182e-06</v>
+      </c>
+      <c r="CC56" t="inlineStr"/>
+      <c r="CD56" t="inlineStr"/>
+      <c r="CE56" t="inlineStr"/>
+      <c r="CF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH56" t="inlineStr"/>
+      <c r="CI56" t="inlineStr"/>
+      <c r="CJ56" t="inlineStr"/>
+      <c r="CK56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM56" t="inlineStr"/>
+      <c r="CN56" t="inlineStr"/>
+      <c r="CO56" t="inlineStr"/>
+      <c r="CP56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR56" t="inlineStr"/>
+      <c r="CS56" t="inlineStr"/>
+      <c r="CT56" t="inlineStr"/>
+      <c r="CU56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW56" t="inlineStr"/>
+      <c r="CX56" t="inlineStr"/>
+      <c r="CY56" t="inlineStr"/>
+      <c r="CZ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB56" t="inlineStr"/>
+      <c r="DC56" t="inlineStr"/>
+      <c r="DD56" t="inlineStr"/>
+      <c r="DE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG56" t="inlineStr"/>
+      <c r="DH56" t="inlineStr"/>
+      <c r="DI56" t="inlineStr"/>
+      <c r="DJ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL56" t="inlineStr"/>
+      <c r="DM56" t="inlineStr"/>
+      <c r="DN56" t="inlineStr"/>
+      <c r="DO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ56" t="inlineStr"/>
+      <c r="DR56" t="inlineStr"/>
+      <c r="DS56" t="inlineStr"/>
+      <c r="DT56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV56" t="inlineStr"/>
+      <c r="DW56" t="inlineStr"/>
+      <c r="DX56" t="inlineStr"/>
+      <c r="DY56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA56" t="inlineStr"/>
+      <c r="EB56" t="inlineStr"/>
+      <c r="EC56" t="inlineStr"/>
+      <c r="ED56" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF56" t="inlineStr"/>
+      <c r="EG56" t="inlineStr"/>
+      <c r="EH56" t="inlineStr"/>
+      <c r="EI56" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ56" t="n">
+        <v>0.0253216063226551</v>
+      </c>
+      <c r="EK56" t="inlineStr"/>
+      <c r="EL56" t="inlineStr"/>
+      <c r="EM56" t="inlineStr"/>
+      <c r="EN56" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP56" t="inlineStr"/>
+      <c r="EQ56" t="inlineStr"/>
+      <c r="ER56" t="inlineStr"/>
+      <c r="ES56" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET56" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU56" t="inlineStr"/>
+      <c r="EV56" t="inlineStr"/>
+      <c r="EW56" t="inlineStr"/>
+      <c r="EX56" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY56" t="n">
+        <v>0.08999570234173948</v>
+      </c>
+      <c r="EZ56" t="inlineStr"/>
+      <c r="FA56" t="inlineStr"/>
+      <c r="FB56" t="inlineStr"/>
+      <c r="FC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD56" t="n">
+        <v>0.05228332081843001</v>
+      </c>
+      <c r="FE56" t="inlineStr"/>
+      <c r="FF56" t="inlineStr"/>
+      <c r="FG56" t="inlineStr"/>
+      <c r="FH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI56" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ56" t="inlineStr"/>
+      <c r="FK56" t="inlineStr"/>
+      <c r="FL56" t="inlineStr"/>
+      <c r="FM56" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN56" t="n">
+        <v>-0.1080935232462268</v>
+      </c>
+      <c r="FO56" t="inlineStr"/>
+      <c r="FP56" t="inlineStr"/>
+      <c r="FQ56" t="inlineStr"/>
+      <c r="FR56" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS56" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT56" t="inlineStr"/>
+      <c r="FU56" t="inlineStr"/>
+      <c r="FV56" t="inlineStr"/>
+      <c r="FW56" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX56" t="n">
+        <v>0.01423871125767598</v>
+      </c>
+      <c r="FY56" t="inlineStr"/>
+      <c r="FZ56" t="inlineStr"/>
+      <c r="GA56" t="inlineStr"/>
+      <c r="GB56" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD56" t="inlineStr"/>
+      <c r="GE56" t="inlineStr"/>
+      <c r="GF56" t="inlineStr"/>
+      <c r="GG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH56" t="n">
+        <v>-0.05961662359081685</v>
+      </c>
+      <c r="GI56" t="inlineStr"/>
+      <c r="GJ56" t="inlineStr"/>
+      <c r="GK56" t="inlineStr"/>
+      <c r="GL56" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM56" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN56" t="inlineStr"/>
+      <c r="GO56" t="inlineStr"/>
+      <c r="GP56" t="inlineStr"/>
+      <c r="GQ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR56" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS56" t="inlineStr"/>
+      <c r="GT56" t="inlineStr"/>
+      <c r="GU56" t="inlineStr"/>
+      <c r="GV56" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW56" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX56" t="inlineStr"/>
+      <c r="GY56" t="inlineStr"/>
+      <c r="GZ56" t="inlineStr"/>
+      <c r="HA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB56" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC56" t="inlineStr"/>
+      <c r="HD56" t="inlineStr"/>
+      <c r="HE56" t="inlineStr"/>
+      <c r="HF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG56" t="n">
+        <v>0.1338168471318732</v>
+      </c>
+      <c r="HH56" t="inlineStr"/>
+      <c r="HI56" t="inlineStr"/>
+      <c r="HJ56" t="inlineStr"/>
+      <c r="HK56" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL56" t="n">
+        <v>0.06347541059390949</v>
+      </c>
+      <c r="HM56" t="inlineStr"/>
+      <c r="HN56" t="inlineStr"/>
+      <c r="HO56" t="inlineStr"/>
+      <c r="HP56" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR56" t="inlineStr"/>
+      <c r="HS56" t="inlineStr"/>
+      <c r="HT56" t="inlineStr"/>
+      <c r="HU56" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV56" t="n">
+        <v>0</v>
+      </c>
+      <c r="HW56" t="inlineStr"/>
+      <c r="HX56" t="inlineStr"/>
+      <c r="HY56" t="inlineStr"/>
+      <c r="HZ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="IB56" t="inlineStr"/>
+      <c r="IC56" t="inlineStr"/>
+      <c r="ID56" t="inlineStr"/>
+      <c r="IE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="IG56" t="inlineStr"/>
+      <c r="IH56" t="inlineStr"/>
+      <c r="II56" t="inlineStr"/>
+      <c r="IJ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK56" t="n">
+        <v>-0.08857899324231086</v>
+      </c>
+      <c r="IL56" t="inlineStr"/>
+      <c r="IM56" t="inlineStr"/>
+      <c r="IN56" t="inlineStr"/>
+      <c r="IO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP56" t="n">
+        <v>0</v>
+      </c>
+      <c r="IQ56" t="inlineStr"/>
+      <c r="IR56" t="inlineStr"/>
+      <c r="IS56" t="inlineStr"/>
+      <c r="IT56" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU56" t="n">
+        <v>0</v>
+      </c>
+      <c r="IV56" t="inlineStr"/>
+      <c r="IW56" t="inlineStr"/>
+      <c r="IX56" t="inlineStr"/>
+      <c r="IY56" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA56" t="inlineStr"/>
+      <c r="JB56" t="inlineStr"/>
+      <c r="JC56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-04-19 09:14:08</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>10</v>
+      </c>
+      <c r="C57" t="n">
+        <v>50</v>
+      </c>
+      <c r="D57" t="n">
+        <v>50</v>
+      </c>
+      <c r="E57" t="n">
+        <v>40</v>
+      </c>
+      <c r="F57" t="n">
+        <v>5</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>0.5475648377671151</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.8554388777555109</v>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.3099633706345113</v>
+      </c>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0.3879172779073495</v>
+      </c>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0.6112793488936589</v>
+      </c>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr"/>
+      <c r="AC57" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.002729237816950692</v>
+      </c>
+      <c r="AE57" t="inlineStr"/>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="inlineStr"/>
+      <c r="AH57" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>0.5889616842509742</v>
+      </c>
+      <c r="AJ57" t="inlineStr"/>
+      <c r="AK57" t="inlineStr"/>
+      <c r="AL57" t="inlineStr"/>
+      <c r="AM57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO57" t="inlineStr"/>
+      <c r="AP57" t="inlineStr"/>
+      <c r="AQ57" t="inlineStr"/>
+      <c r="AR57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>0.004140361641403947</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AU57" t="inlineStr"/>
+      <c r="AV57" t="inlineStr"/>
+      <c r="AW57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr"/>
+      <c r="BA57" t="inlineStr"/>
+      <c r="BB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC57" t="n">
+        <v>0.06771838191177033</v>
+      </c>
+      <c r="BD57" t="inlineStr"/>
+      <c r="BE57" t="inlineStr"/>
+      <c r="BF57" t="inlineStr"/>
+      <c r="BG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI57" t="inlineStr"/>
+      <c r="BJ57" t="inlineStr"/>
+      <c r="BK57" t="inlineStr"/>
+      <c r="BL57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN57" t="inlineStr"/>
+      <c r="BO57" t="inlineStr"/>
+      <c r="BP57" t="inlineStr"/>
+      <c r="BQ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS57" t="inlineStr"/>
+      <c r="BT57" t="inlineStr"/>
+      <c r="BU57" t="inlineStr"/>
+      <c r="BV57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX57" t="inlineStr"/>
+      <c r="BY57" t="inlineStr"/>
+      <c r="BZ57" t="inlineStr"/>
+      <c r="CA57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC57" t="inlineStr"/>
+      <c r="CD57" t="inlineStr"/>
+      <c r="CE57" t="inlineStr"/>
+      <c r="CF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH57" t="inlineStr"/>
+      <c r="CI57" t="inlineStr"/>
+      <c r="CJ57" t="inlineStr"/>
+      <c r="CK57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM57" t="inlineStr"/>
+      <c r="CN57" t="inlineStr"/>
+      <c r="CO57" t="inlineStr"/>
+      <c r="CP57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR57" t="inlineStr"/>
+      <c r="CS57" t="inlineStr"/>
+      <c r="CT57" t="inlineStr"/>
+      <c r="CU57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW57" t="inlineStr"/>
+      <c r="CX57" t="inlineStr"/>
+      <c r="CY57" t="inlineStr"/>
+      <c r="CZ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA57" t="n">
+        <v>0.0004652425441040439</v>
+      </c>
+      <c r="DB57" t="inlineStr"/>
+      <c r="DC57" t="inlineStr"/>
+      <c r="DD57" t="inlineStr"/>
+      <c r="DE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF57" t="n">
+        <v>0.002378210627634981</v>
+      </c>
+      <c r="DG57" t="inlineStr"/>
+      <c r="DH57" t="inlineStr"/>
+      <c r="DI57" t="inlineStr"/>
+      <c r="DJ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL57" t="inlineStr"/>
+      <c r="DM57" t="inlineStr"/>
+      <c r="DN57" t="inlineStr"/>
+      <c r="DO57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ57" t="inlineStr"/>
+      <c r="DR57" t="inlineStr"/>
+      <c r="DS57" t="inlineStr"/>
+      <c r="DT57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV57" t="inlineStr"/>
+      <c r="DW57" t="inlineStr"/>
+      <c r="DX57" t="inlineStr"/>
+      <c r="DY57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA57" t="inlineStr"/>
+      <c r="EB57" t="inlineStr"/>
+      <c r="EC57" t="inlineStr"/>
+      <c r="ED57" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF57" t="inlineStr"/>
+      <c r="EG57" t="inlineStr"/>
+      <c r="EH57" t="inlineStr"/>
+      <c r="EI57" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ57" t="n">
+        <v>0.04929020872496286</v>
+      </c>
+      <c r="EK57" t="inlineStr"/>
+      <c r="EL57" t="inlineStr"/>
+      <c r="EM57" t="inlineStr"/>
+      <c r="EN57" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO57" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP57" t="inlineStr"/>
+      <c r="EQ57" t="inlineStr"/>
+      <c r="ER57" t="inlineStr"/>
+      <c r="ES57" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET57" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU57" t="inlineStr"/>
+      <c r="EV57" t="inlineStr"/>
+      <c r="EW57" t="inlineStr"/>
+      <c r="EX57" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY57" t="n">
+        <v>0.07118560336152206</v>
+      </c>
+      <c r="EZ57" t="inlineStr"/>
+      <c r="FA57" t="inlineStr"/>
+      <c r="FB57" t="inlineStr"/>
+      <c r="FC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD57" t="n">
+        <v>0.02956077589783197</v>
+      </c>
+      <c r="FE57" t="inlineStr"/>
+      <c r="FF57" t="inlineStr"/>
+      <c r="FG57" t="inlineStr"/>
+      <c r="FH57" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI57" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ57" t="inlineStr"/>
+      <c r="FK57" t="inlineStr"/>
+      <c r="FL57" t="inlineStr"/>
+      <c r="FM57" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN57" t="n">
+        <v>-0.05265502820501922</v>
+      </c>
+      <c r="FO57" t="inlineStr"/>
+      <c r="FP57" t="inlineStr"/>
+      <c r="FQ57" t="inlineStr"/>
+      <c r="FR57" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS57" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT57" t="inlineStr"/>
+      <c r="FU57" t="inlineStr"/>
+      <c r="FV57" t="inlineStr"/>
+      <c r="FW57" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX57" t="n">
+        <v>0.0007656575063817138</v>
+      </c>
+      <c r="FY57" t="inlineStr"/>
+      <c r="FZ57" t="inlineStr"/>
+      <c r="GA57" t="inlineStr"/>
+      <c r="GB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC57" t="n">
+        <v>0.001281440280566818</v>
+      </c>
+      <c r="GD57" t="inlineStr"/>
+      <c r="GE57" t="inlineStr"/>
+      <c r="GF57" t="inlineStr"/>
+      <c r="GG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH57" t="n">
+        <v>-0.03463245217292477</v>
+      </c>
+      <c r="GI57" t="inlineStr"/>
+      <c r="GJ57" t="inlineStr"/>
+      <c r="GK57" t="inlineStr"/>
+      <c r="GL57" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM57" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN57" t="inlineStr"/>
+      <c r="GO57" t="inlineStr"/>
+      <c r="GP57" t="inlineStr"/>
+      <c r="GQ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR57" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS57" t="inlineStr"/>
+      <c r="GT57" t="inlineStr"/>
+      <c r="GU57" t="inlineStr"/>
+      <c r="GV57" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW57" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX57" t="inlineStr"/>
+      <c r="GY57" t="inlineStr"/>
+      <c r="GZ57" t="inlineStr"/>
+      <c r="HA57" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC57" t="inlineStr"/>
+      <c r="HD57" t="inlineStr"/>
+      <c r="HE57" t="inlineStr"/>
+      <c r="HF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG57" t="n">
+        <v>0.08855134197779854</v>
+      </c>
+      <c r="HH57" t="inlineStr"/>
+      <c r="HI57" t="inlineStr"/>
+      <c r="HJ57" t="inlineStr"/>
+      <c r="HK57" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL57" t="n">
+        <v>0.07306578187951078</v>
+      </c>
+      <c r="HM57" t="inlineStr"/>
+      <c r="HN57" t="inlineStr"/>
+      <c r="HO57" t="inlineStr"/>
+      <c r="HP57" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR57" t="inlineStr"/>
+      <c r="HS57" t="inlineStr"/>
+      <c r="HT57" t="inlineStr"/>
+      <c r="HU57" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV57" t="n">
+        <v>0</v>
+      </c>
+      <c r="HW57" t="inlineStr"/>
+      <c r="HX57" t="inlineStr"/>
+      <c r="HY57" t="inlineStr"/>
+      <c r="HZ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA57" t="n">
+        <v>0</v>
+      </c>
+      <c r="IB57" t="inlineStr"/>
+      <c r="IC57" t="inlineStr"/>
+      <c r="ID57" t="inlineStr"/>
+      <c r="IE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="IG57" t="inlineStr"/>
+      <c r="IH57" t="inlineStr"/>
+      <c r="II57" t="inlineStr"/>
+      <c r="IJ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK57" t="n">
+        <v>-0.05255075666523811</v>
+      </c>
+      <c r="IL57" t="inlineStr"/>
+      <c r="IM57" t="inlineStr"/>
+      <c r="IN57" t="inlineStr"/>
+      <c r="IO57" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP57" t="n">
+        <v>0.001368042583380755</v>
+      </c>
+      <c r="IQ57" t="inlineStr"/>
+      <c r="IR57" t="inlineStr"/>
+      <c r="IS57" t="inlineStr"/>
+      <c r="IT57" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU57" t="n">
+        <v>0</v>
+      </c>
+      <c r="IV57" t="inlineStr"/>
+      <c r="IW57" t="inlineStr"/>
+      <c r="IX57" t="inlineStr"/>
+      <c r="IY57" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA57" t="inlineStr"/>
+      <c r="JB57" t="inlineStr"/>
+      <c r="JC57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-04-19 09:14:20</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>10</v>
+      </c>
+      <c r="C58" t="n">
+        <v>50</v>
+      </c>
+      <c r="D58" t="n">
+        <v>50</v>
+      </c>
+      <c r="E58" t="n">
+        <v>40</v>
+      </c>
+      <c r="F58" t="n">
+        <v>5</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>0.2808053984803197</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.9210581162324648</v>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.4433777608114526</v>
+      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0.5336743517097566</v>
+      </c>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>0.4473489822203331</v>
+      </c>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr"/>
+      <c r="AC58" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0.365279879472071</v>
+      </c>
+      <c r="AE58" t="inlineStr"/>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="inlineStr"/>
+      <c r="AH58" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>0.3582281541264817</v>
+      </c>
+      <c r="AJ58" t="inlineStr"/>
+      <c r="AK58" t="inlineStr"/>
+      <c r="AL58" t="inlineStr"/>
+      <c r="AM58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO58" t="inlineStr"/>
+      <c r="AP58" t="inlineStr"/>
+      <c r="AQ58" t="inlineStr"/>
+      <c r="AR58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AU58" t="inlineStr"/>
+      <c r="AV58" t="inlineStr"/>
+      <c r="AW58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr"/>
+      <c r="BA58" t="inlineStr"/>
+      <c r="BB58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD58" t="inlineStr"/>
+      <c r="BE58" t="inlineStr"/>
+      <c r="BF58" t="inlineStr"/>
+      <c r="BG58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI58" t="inlineStr"/>
+      <c r="BJ58" t="inlineStr"/>
+      <c r="BK58" t="inlineStr"/>
+      <c r="BL58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN58" t="inlineStr"/>
+      <c r="BO58" t="inlineStr"/>
+      <c r="BP58" t="inlineStr"/>
+      <c r="BQ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS58" t="inlineStr"/>
+      <c r="BT58" t="inlineStr"/>
+      <c r="BU58" t="inlineStr"/>
+      <c r="BV58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW58" t="n">
+        <v>-0.127710326152592</v>
+      </c>
+      <c r="BX58" t="inlineStr"/>
+      <c r="BY58" t="inlineStr"/>
+      <c r="BZ58" t="inlineStr"/>
+      <c r="CA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB58" t="n">
+        <v>0.03411040024502975</v>
+      </c>
+      <c r="CC58" t="inlineStr"/>
+      <c r="CD58" t="inlineStr"/>
+      <c r="CE58" t="inlineStr"/>
+      <c r="CF58" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG58" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH58" t="inlineStr"/>
+      <c r="CI58" t="inlineStr"/>
+      <c r="CJ58" t="inlineStr"/>
+      <c r="CK58" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL58" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM58" t="inlineStr"/>
+      <c r="CN58" t="inlineStr"/>
+      <c r="CO58" t="inlineStr"/>
+      <c r="CP58" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR58" t="inlineStr"/>
+      <c r="CS58" t="inlineStr"/>
+      <c r="CT58" t="inlineStr"/>
+      <c r="CU58" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV58" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW58" t="inlineStr"/>
+      <c r="CX58" t="inlineStr"/>
+      <c r="CY58" t="inlineStr"/>
+      <c r="CZ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB58" t="inlineStr"/>
+      <c r="DC58" t="inlineStr"/>
+      <c r="DD58" t="inlineStr"/>
+      <c r="DE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF58" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG58" t="inlineStr"/>
+      <c r="DH58" t="inlineStr"/>
+      <c r="DI58" t="inlineStr"/>
+      <c r="DJ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK58" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL58" t="inlineStr"/>
+      <c r="DM58" t="inlineStr"/>
+      <c r="DN58" t="inlineStr"/>
+      <c r="DO58" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP58" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ58" t="inlineStr"/>
+      <c r="DR58" t="inlineStr"/>
+      <c r="DS58" t="inlineStr"/>
+      <c r="DT58" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU58" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV58" t="inlineStr"/>
+      <c r="DW58" t="inlineStr"/>
+      <c r="DX58" t="inlineStr"/>
+      <c r="DY58" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA58" t="inlineStr"/>
+      <c r="EB58" t="inlineStr"/>
+      <c r="EC58" t="inlineStr"/>
+      <c r="ED58" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF58" t="inlineStr"/>
+      <c r="EG58" t="inlineStr"/>
+      <c r="EH58" t="inlineStr"/>
+      <c r="EI58" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK58" t="inlineStr"/>
+      <c r="EL58" t="inlineStr"/>
+      <c r="EM58" t="inlineStr"/>
+      <c r="EN58" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO58" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP58" t="inlineStr"/>
+      <c r="EQ58" t="inlineStr"/>
+      <c r="ER58" t="inlineStr"/>
+      <c r="ES58" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET58" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU58" t="inlineStr"/>
+      <c r="EV58" t="inlineStr"/>
+      <c r="EW58" t="inlineStr"/>
+      <c r="EX58" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY58" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ58" t="inlineStr"/>
+      <c r="FA58" t="inlineStr"/>
+      <c r="FB58" t="inlineStr"/>
+      <c r="FC58" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD58" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE58" t="inlineStr"/>
+      <c r="FF58" t="inlineStr"/>
+      <c r="FG58" t="inlineStr"/>
+      <c r="FH58" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI58" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ58" t="inlineStr"/>
+      <c r="FK58" t="inlineStr"/>
+      <c r="FL58" t="inlineStr"/>
+      <c r="FM58" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN58" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO58" t="inlineStr"/>
+      <c r="FP58" t="inlineStr"/>
+      <c r="FQ58" t="inlineStr"/>
+      <c r="FR58" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS58" t="n">
+        <v>0.06800048870454665</v>
+      </c>
+      <c r="FT58" t="inlineStr"/>
+      <c r="FU58" t="inlineStr"/>
+      <c r="FV58" t="inlineStr"/>
+      <c r="FW58" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX58" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY58" t="inlineStr"/>
+      <c r="FZ58" t="inlineStr"/>
+      <c r="GA58" t="inlineStr"/>
+      <c r="GB58" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC58" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD58" t="inlineStr"/>
+      <c r="GE58" t="inlineStr"/>
+      <c r="GF58" t="inlineStr"/>
+      <c r="GG58" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH58" t="n">
+        <v>0</v>
+      </c>
+      <c r="GI58" t="inlineStr"/>
+      <c r="GJ58" t="inlineStr"/>
+      <c r="GK58" t="inlineStr"/>
+      <c r="GL58" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM58" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN58" t="inlineStr"/>
+      <c r="GO58" t="inlineStr"/>
+      <c r="GP58" t="inlineStr"/>
+      <c r="GQ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR58" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS58" t="inlineStr"/>
+      <c r="GT58" t="inlineStr"/>
+      <c r="GU58" t="inlineStr"/>
+      <c r="GV58" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW58" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX58" t="inlineStr"/>
+      <c r="GY58" t="inlineStr"/>
+      <c r="GZ58" t="inlineStr"/>
+      <c r="HA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB58" t="n">
+        <v>-0.162255509969591</v>
+      </c>
+      <c r="HC58" t="inlineStr"/>
+      <c r="HD58" t="inlineStr"/>
+      <c r="HE58" t="inlineStr"/>
+      <c r="HF58" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG58" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH58" t="inlineStr"/>
+      <c r="HI58" t="inlineStr"/>
+      <c r="HJ58" t="inlineStr"/>
+      <c r="HK58" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL58" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM58" t="inlineStr"/>
+      <c r="HN58" t="inlineStr"/>
+      <c r="HO58" t="inlineStr"/>
+      <c r="HP58" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR58" t="inlineStr"/>
+      <c r="HS58" t="inlineStr"/>
+      <c r="HT58" t="inlineStr"/>
+      <c r="HU58" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV58" t="n">
+        <v>0</v>
+      </c>
+      <c r="HW58" t="inlineStr"/>
+      <c r="HX58" t="inlineStr"/>
+      <c r="HY58" t="inlineStr"/>
+      <c r="HZ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="IB58" t="inlineStr"/>
+      <c r="IC58" t="inlineStr"/>
+      <c r="ID58" t="inlineStr"/>
+      <c r="IE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF58" t="n">
+        <v>0.09113490607336841</v>
+      </c>
+      <c r="IG58" t="inlineStr"/>
+      <c r="IH58" t="inlineStr"/>
+      <c r="II58" t="inlineStr"/>
+      <c r="IJ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK58" t="n">
+        <v>0</v>
+      </c>
+      <c r="IL58" t="inlineStr"/>
+      <c r="IM58" t="inlineStr"/>
+      <c r="IN58" t="inlineStr"/>
+      <c r="IO58" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP58" t="n">
+        <v>0</v>
+      </c>
+      <c r="IQ58" t="inlineStr"/>
+      <c r="IR58" t="inlineStr"/>
+      <c r="IS58" t="inlineStr"/>
+      <c r="IT58" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU58" t="n">
+        <v>0</v>
+      </c>
+      <c r="IV58" t="inlineStr"/>
+      <c r="IW58" t="inlineStr"/>
+      <c r="IX58" t="inlineStr"/>
+      <c r="IY58" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA58" t="inlineStr"/>
+      <c r="JB58" t="inlineStr"/>
+      <c r="JC58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-04-19 09:14:39</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>10</v>
+      </c>
+      <c r="C59" t="n">
+        <v>50</v>
+      </c>
+      <c r="D59" t="n">
+        <v>50</v>
+      </c>
+      <c r="E59" t="n">
+        <v>40</v>
+      </c>
+      <c r="F59" t="n">
+        <v>5</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>0.3065307550484289</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.9163286573146291</v>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.4447776122041258</v>
+      </c>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0.4789040870493141</v>
+      </c>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
+      <c r="X59" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>0.4680044632650313</v>
+      </c>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr"/>
+      <c r="AB59" t="inlineStr"/>
+      <c r="AC59" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0.3727815772458776</v>
+      </c>
+      <c r="AE59" t="inlineStr"/>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="inlineStr"/>
+      <c r="AH59" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>0.3665485300771387</v>
+      </c>
+      <c r="AJ59" t="inlineStr"/>
+      <c r="AK59" t="inlineStr"/>
+      <c r="AL59" t="inlineStr"/>
+      <c r="AM59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO59" t="inlineStr"/>
+      <c r="AP59" t="inlineStr"/>
+      <c r="AQ59" t="inlineStr"/>
+      <c r="AR59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AU59" t="inlineStr"/>
+      <c r="AV59" t="inlineStr"/>
+      <c r="AW59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr"/>
+      <c r="BA59" t="inlineStr"/>
+      <c r="BB59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD59" t="inlineStr"/>
+      <c r="BE59" t="inlineStr"/>
+      <c r="BF59" t="inlineStr"/>
+      <c r="BG59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI59" t="inlineStr"/>
+      <c r="BJ59" t="inlineStr"/>
+      <c r="BK59" t="inlineStr"/>
+      <c r="BL59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN59" t="inlineStr"/>
+      <c r="BO59" t="inlineStr"/>
+      <c r="BP59" t="inlineStr"/>
+      <c r="BQ59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS59" t="inlineStr"/>
+      <c r="BT59" t="inlineStr"/>
+      <c r="BU59" t="inlineStr"/>
+      <c r="BV59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW59" t="n">
+        <v>0.1536557567808414</v>
+      </c>
+      <c r="BX59" t="inlineStr"/>
+      <c r="BY59" t="inlineStr"/>
+      <c r="BZ59" t="inlineStr"/>
+      <c r="CA59" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB59" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC59" t="inlineStr"/>
+      <c r="CD59" t="inlineStr"/>
+      <c r="CE59" t="inlineStr"/>
+      <c r="CF59" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG59" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH59" t="inlineStr"/>
+      <c r="CI59" t="inlineStr"/>
+      <c r="CJ59" t="inlineStr"/>
+      <c r="CK59" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL59" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM59" t="inlineStr"/>
+      <c r="CN59" t="inlineStr"/>
+      <c r="CO59" t="inlineStr"/>
+      <c r="CP59" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ59" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR59" t="inlineStr"/>
+      <c r="CS59" t="inlineStr"/>
+      <c r="CT59" t="inlineStr"/>
+      <c r="CU59" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV59" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW59" t="inlineStr"/>
+      <c r="CX59" t="inlineStr"/>
+      <c r="CY59" t="inlineStr"/>
+      <c r="CZ59" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA59" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB59" t="inlineStr"/>
+      <c r="DC59" t="inlineStr"/>
+      <c r="DD59" t="inlineStr"/>
+      <c r="DE59" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF59" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG59" t="inlineStr"/>
+      <c r="DH59" t="inlineStr"/>
+      <c r="DI59" t="inlineStr"/>
+      <c r="DJ59" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK59" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL59" t="inlineStr"/>
+      <c r="DM59" t="inlineStr"/>
+      <c r="DN59" t="inlineStr"/>
+      <c r="DO59" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP59" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ59" t="inlineStr"/>
+      <c r="DR59" t="inlineStr"/>
+      <c r="DS59" t="inlineStr"/>
+      <c r="DT59" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU59" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV59" t="inlineStr"/>
+      <c r="DW59" t="inlineStr"/>
+      <c r="DX59" t="inlineStr"/>
+      <c r="DY59" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ59" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA59" t="inlineStr"/>
+      <c r="EB59" t="inlineStr"/>
+      <c r="EC59" t="inlineStr"/>
+      <c r="ED59" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE59" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF59" t="inlineStr"/>
+      <c r="EG59" t="inlineStr"/>
+      <c r="EH59" t="inlineStr"/>
+      <c r="EI59" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ59" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK59" t="inlineStr"/>
+      <c r="EL59" t="inlineStr"/>
+      <c r="EM59" t="inlineStr"/>
+      <c r="EN59" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO59" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP59" t="inlineStr"/>
+      <c r="EQ59" t="inlineStr"/>
+      <c r="ER59" t="inlineStr"/>
+      <c r="ES59" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET59" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU59" t="inlineStr"/>
+      <c r="EV59" t="inlineStr"/>
+      <c r="EW59" t="inlineStr"/>
+      <c r="EX59" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY59" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ59" t="inlineStr"/>
+      <c r="FA59" t="inlineStr"/>
+      <c r="FB59" t="inlineStr"/>
+      <c r="FC59" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD59" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE59" t="inlineStr"/>
+      <c r="FF59" t="inlineStr"/>
+      <c r="FG59" t="inlineStr"/>
+      <c r="FH59" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI59" t="n">
+        <v>0.07231644195032315</v>
+      </c>
+      <c r="FJ59" t="inlineStr"/>
+      <c r="FK59" t="inlineStr"/>
+      <c r="FL59" t="inlineStr"/>
+      <c r="FM59" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN59" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO59" t="inlineStr"/>
+      <c r="FP59" t="inlineStr"/>
+      <c r="FQ59" t="inlineStr"/>
+      <c r="FR59" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS59" t="n">
+        <v>0.1789526372099746</v>
+      </c>
+      <c r="FT59" t="inlineStr"/>
+      <c r="FU59" t="inlineStr"/>
+      <c r="FV59" t="inlineStr"/>
+      <c r="FW59" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX59" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY59" t="inlineStr"/>
+      <c r="FZ59" t="inlineStr"/>
+      <c r="GA59" t="inlineStr"/>
+      <c r="GB59" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC59" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD59" t="inlineStr"/>
+      <c r="GE59" t="inlineStr"/>
+      <c r="GF59" t="inlineStr"/>
+      <c r="GG59" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH59" t="n">
+        <v>0</v>
+      </c>
+      <c r="GI59" t="inlineStr"/>
+      <c r="GJ59" t="inlineStr"/>
+      <c r="GK59" t="inlineStr"/>
+      <c r="GL59" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM59" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN59" t="inlineStr"/>
+      <c r="GO59" t="inlineStr"/>
+      <c r="GP59" t="inlineStr"/>
+      <c r="GQ59" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR59" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS59" t="inlineStr"/>
+      <c r="GT59" t="inlineStr"/>
+      <c r="GU59" t="inlineStr"/>
+      <c r="GV59" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW59" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX59" t="inlineStr"/>
+      <c r="GY59" t="inlineStr"/>
+      <c r="GZ59" t="inlineStr"/>
+      <c r="HA59" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB59" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC59" t="inlineStr"/>
+      <c r="HD59" t="inlineStr"/>
+      <c r="HE59" t="inlineStr"/>
+      <c r="HF59" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG59" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH59" t="inlineStr"/>
+      <c r="HI59" t="inlineStr"/>
+      <c r="HJ59" t="inlineStr"/>
+      <c r="HK59" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL59" t="n">
+        <v>-0.1017174899944962</v>
+      </c>
+      <c r="HM59" t="inlineStr"/>
+      <c r="HN59" t="inlineStr"/>
+      <c r="HO59" t="inlineStr"/>
+      <c r="HP59" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ59" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR59" t="inlineStr"/>
+      <c r="HS59" t="inlineStr"/>
+      <c r="HT59" t="inlineStr"/>
+      <c r="HU59" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV59" t="n">
+        <v>0</v>
+      </c>
+      <c r="HW59" t="inlineStr"/>
+      <c r="HX59" t="inlineStr"/>
+      <c r="HY59" t="inlineStr"/>
+      <c r="HZ59" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA59" t="n">
+        <v>0</v>
+      </c>
+      <c r="IB59" t="inlineStr"/>
+      <c r="IC59" t="inlineStr"/>
+      <c r="ID59" t="inlineStr"/>
+      <c r="IE59" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF59" t="n">
+        <v>0</v>
+      </c>
+      <c r="IG59" t="inlineStr"/>
+      <c r="IH59" t="inlineStr"/>
+      <c r="II59" t="inlineStr"/>
+      <c r="IJ59" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK59" t="n">
+        <v>0</v>
+      </c>
+      <c r="IL59" t="inlineStr"/>
+      <c r="IM59" t="inlineStr"/>
+      <c r="IN59" t="inlineStr"/>
+      <c r="IO59" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP59" t="n">
+        <v>0</v>
+      </c>
+      <c r="IQ59" t="inlineStr"/>
+      <c r="IR59" t="inlineStr"/>
+      <c r="IS59" t="inlineStr"/>
+      <c r="IT59" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU59" t="n">
+        <v>-0.09623611959343314</v>
+      </c>
+      <c r="IV59" t="inlineStr"/>
+      <c r="IW59" t="inlineStr"/>
+      <c r="IX59" t="inlineStr"/>
+      <c r="IY59" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ59" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA59" t="inlineStr"/>
+      <c r="JB59" t="inlineStr"/>
+      <c r="JC59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-04-19 09:15:03</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>10</v>
+      </c>
+      <c r="C60" t="n">
+        <v>50</v>
+      </c>
+      <c r="D60" t="n">
+        <v>50</v>
+      </c>
+      <c r="E60" t="n">
+        <v>40</v>
+      </c>
+      <c r="F60" t="n">
+        <v>5</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>0.36534595470912</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.9034549098196391</v>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.486272315389377</v>
+      </c>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0.1555217911199288</v>
+      </c>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
+      <c r="X60" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>0.4053563478676919</v>
+      </c>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr"/>
+      <c r="AC60" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0.4666015070708024</v>
+      </c>
+      <c r="AE60" t="inlineStr"/>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="inlineStr"/>
+      <c r="AH60" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AI60" t="n">
+        <v>0.5730834480292102</v>
+      </c>
+      <c r="AJ60" t="inlineStr"/>
+      <c r="AK60" t="inlineStr"/>
+      <c r="AL60" t="inlineStr"/>
+      <c r="AM60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO60" t="inlineStr"/>
+      <c r="AP60" t="inlineStr"/>
+      <c r="AQ60" t="inlineStr"/>
+      <c r="AR60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AU60" t="inlineStr"/>
+      <c r="AV60" t="inlineStr"/>
+      <c r="AW60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr"/>
+      <c r="BA60" t="inlineStr"/>
+      <c r="BB60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD60" t="inlineStr"/>
+      <c r="BE60" t="inlineStr"/>
+      <c r="BF60" t="inlineStr"/>
+      <c r="BG60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI60" t="inlineStr"/>
+      <c r="BJ60" t="inlineStr"/>
+      <c r="BK60" t="inlineStr"/>
+      <c r="BL60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM60" t="n">
+        <v>0.09395262440875378</v>
+      </c>
+      <c r="BN60" t="inlineStr"/>
+      <c r="BO60" t="inlineStr"/>
+      <c r="BP60" t="inlineStr"/>
+      <c r="BQ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR60" t="n">
+        <v>0.03927917671614394</v>
+      </c>
+      <c r="BS60" t="inlineStr"/>
+      <c r="BT60" t="inlineStr"/>
+      <c r="BU60" t="inlineStr"/>
+      <c r="BV60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW60" t="n">
+        <v>0.09691993100990175</v>
+      </c>
+      <c r="BX60" t="inlineStr"/>
+      <c r="BY60" t="inlineStr"/>
+      <c r="BZ60" t="inlineStr"/>
+      <c r="CA60" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB60" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC60" t="inlineStr"/>
+      <c r="CD60" t="inlineStr"/>
+      <c r="CE60" t="inlineStr"/>
+      <c r="CF60" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG60" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH60" t="inlineStr"/>
+      <c r="CI60" t="inlineStr"/>
+      <c r="CJ60" t="inlineStr"/>
+      <c r="CK60" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL60" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM60" t="inlineStr"/>
+      <c r="CN60" t="inlineStr"/>
+      <c r="CO60" t="inlineStr"/>
+      <c r="CP60" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR60" t="inlineStr"/>
+      <c r="CS60" t="inlineStr"/>
+      <c r="CT60" t="inlineStr"/>
+      <c r="CU60" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV60" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW60" t="inlineStr"/>
+      <c r="CX60" t="inlineStr"/>
+      <c r="CY60" t="inlineStr"/>
+      <c r="CZ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA60" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB60" t="inlineStr"/>
+      <c r="DC60" t="inlineStr"/>
+      <c r="DD60" t="inlineStr"/>
+      <c r="DE60" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF60" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG60" t="inlineStr"/>
+      <c r="DH60" t="inlineStr"/>
+      <c r="DI60" t="inlineStr"/>
+      <c r="DJ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK60" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL60" t="inlineStr"/>
+      <c r="DM60" t="inlineStr"/>
+      <c r="DN60" t="inlineStr"/>
+      <c r="DO60" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP60" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ60" t="inlineStr"/>
+      <c r="DR60" t="inlineStr"/>
+      <c r="DS60" t="inlineStr"/>
+      <c r="DT60" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU60" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV60" t="inlineStr"/>
+      <c r="DW60" t="inlineStr"/>
+      <c r="DX60" t="inlineStr"/>
+      <c r="DY60" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ60" t="n">
+        <v>-0.08153662532223538</v>
+      </c>
+      <c r="EA60" t="inlineStr"/>
+      <c r="EB60" t="inlineStr"/>
+      <c r="EC60" t="inlineStr"/>
+      <c r="ED60" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE60" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF60" t="inlineStr"/>
+      <c r="EG60" t="inlineStr"/>
+      <c r="EH60" t="inlineStr"/>
+      <c r="EI60" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK60" t="inlineStr"/>
+      <c r="EL60" t="inlineStr"/>
+      <c r="EM60" t="inlineStr"/>
+      <c r="EN60" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO60" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP60" t="inlineStr"/>
+      <c r="EQ60" t="inlineStr"/>
+      <c r="ER60" t="inlineStr"/>
+      <c r="ES60" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET60" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU60" t="inlineStr"/>
+      <c r="EV60" t="inlineStr"/>
+      <c r="EW60" t="inlineStr"/>
+      <c r="EX60" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY60" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ60" t="inlineStr"/>
+      <c r="FA60" t="inlineStr"/>
+      <c r="FB60" t="inlineStr"/>
+      <c r="FC60" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD60" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE60" t="inlineStr"/>
+      <c r="FF60" t="inlineStr"/>
+      <c r="FG60" t="inlineStr"/>
+      <c r="FH60" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI60" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ60" t="inlineStr"/>
+      <c r="FK60" t="inlineStr"/>
+      <c r="FL60" t="inlineStr"/>
+      <c r="FM60" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN60" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO60" t="inlineStr"/>
+      <c r="FP60" t="inlineStr"/>
+      <c r="FQ60" t="inlineStr"/>
+      <c r="FR60" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS60" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT60" t="inlineStr"/>
+      <c r="FU60" t="inlineStr"/>
+      <c r="FV60" t="inlineStr"/>
+      <c r="FW60" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX60" t="n">
+        <v>0.0498516856042459</v>
+      </c>
+      <c r="FY60" t="inlineStr"/>
+      <c r="FZ60" t="inlineStr"/>
+      <c r="GA60" t="inlineStr"/>
+      <c r="GB60" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC60" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD60" t="inlineStr"/>
+      <c r="GE60" t="inlineStr"/>
+      <c r="GF60" t="inlineStr"/>
+      <c r="GG60" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH60" t="n">
+        <v>0</v>
+      </c>
+      <c r="GI60" t="inlineStr"/>
+      <c r="GJ60" t="inlineStr"/>
+      <c r="GK60" t="inlineStr"/>
+      <c r="GL60" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM60" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN60" t="inlineStr"/>
+      <c r="GO60" t="inlineStr"/>
+      <c r="GP60" t="inlineStr"/>
+      <c r="GQ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR60" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS60" t="inlineStr"/>
+      <c r="GT60" t="inlineStr"/>
+      <c r="GU60" t="inlineStr"/>
+      <c r="GV60" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW60" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX60" t="inlineStr"/>
+      <c r="GY60" t="inlineStr"/>
+      <c r="GZ60" t="inlineStr"/>
+      <c r="HA60" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB60" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC60" t="inlineStr"/>
+      <c r="HD60" t="inlineStr"/>
+      <c r="HE60" t="inlineStr"/>
+      <c r="HF60" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG60" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH60" t="inlineStr"/>
+      <c r="HI60" t="inlineStr"/>
+      <c r="HJ60" t="inlineStr"/>
+      <c r="HK60" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL60" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM60" t="inlineStr"/>
+      <c r="HN60" t="inlineStr"/>
+      <c r="HO60" t="inlineStr"/>
+      <c r="HP60" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR60" t="inlineStr"/>
+      <c r="HS60" t="inlineStr"/>
+      <c r="HT60" t="inlineStr"/>
+      <c r="HU60" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV60" t="n">
+        <v>0</v>
+      </c>
+      <c r="HW60" t="inlineStr"/>
+      <c r="HX60" t="inlineStr"/>
+      <c r="HY60" t="inlineStr"/>
+      <c r="HZ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA60" t="n">
+        <v>0</v>
+      </c>
+      <c r="IB60" t="inlineStr"/>
+      <c r="IC60" t="inlineStr"/>
+      <c r="ID60" t="inlineStr"/>
+      <c r="IE60" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF60" t="n">
+        <v>0</v>
+      </c>
+      <c r="IG60" t="inlineStr"/>
+      <c r="IH60" t="inlineStr"/>
+      <c r="II60" t="inlineStr"/>
+      <c r="IJ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK60" t="n">
+        <v>0</v>
+      </c>
+      <c r="IL60" t="inlineStr"/>
+      <c r="IM60" t="inlineStr"/>
+      <c r="IN60" t="inlineStr"/>
+      <c r="IO60" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP60" t="n">
+        <v>0</v>
+      </c>
+      <c r="IQ60" t="inlineStr"/>
+      <c r="IR60" t="inlineStr"/>
+      <c r="IS60" t="inlineStr"/>
+      <c r="IT60" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU60" t="n">
+        <v>0</v>
+      </c>
+      <c r="IV60" t="inlineStr"/>
+      <c r="IW60" t="inlineStr"/>
+      <c r="IX60" t="inlineStr"/>
+      <c r="IY60" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA60" t="inlineStr"/>
+      <c r="JB60" t="inlineStr"/>
+      <c r="JC60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-04-19 09:15:18</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>10</v>
+      </c>
+      <c r="C61" t="n">
+        <v>50</v>
+      </c>
+      <c r="D61" t="n">
+        <v>50</v>
+      </c>
+      <c r="E61" t="n">
+        <v>40</v>
+      </c>
+      <c r="F61" t="n">
+        <v>5</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>0.2459427191038222</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.9333386773547092</v>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.4238538456128129</v>
+      </c>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0.4949233285792539</v>
+      </c>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>0.5778865000952824</v>
+      </c>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr"/>
+      <c r="AC61" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0.2897401457513914</v>
+      </c>
+      <c r="AE61" t="inlineStr"/>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
+      <c r="AH61" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>0.3820367175879837</v>
+      </c>
+      <c r="AJ61" t="inlineStr"/>
+      <c r="AK61" t="inlineStr"/>
+      <c r="AL61" t="inlineStr"/>
+      <c r="AM61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO61" t="inlineStr"/>
+      <c r="AP61" t="inlineStr"/>
+      <c r="AQ61" t="inlineStr"/>
+      <c r="AR61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AU61" t="inlineStr"/>
+      <c r="AV61" t="inlineStr"/>
+      <c r="AW61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr"/>
+      <c r="BA61" t="inlineStr"/>
+      <c r="BB61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD61" t="inlineStr"/>
+      <c r="BE61" t="inlineStr"/>
+      <c r="BF61" t="inlineStr"/>
+      <c r="BG61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI61" t="inlineStr"/>
+      <c r="BJ61" t="inlineStr"/>
+      <c r="BK61" t="inlineStr"/>
+      <c r="BL61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN61" t="inlineStr"/>
+      <c r="BO61" t="inlineStr"/>
+      <c r="BP61" t="inlineStr"/>
+      <c r="BQ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR61" t="n">
+        <v>0.02526680892272552</v>
+      </c>
+      <c r="BS61" t="inlineStr"/>
+      <c r="BT61" t="inlineStr"/>
+      <c r="BU61" t="inlineStr"/>
+      <c r="BV61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX61" t="inlineStr"/>
+      <c r="BY61" t="inlineStr"/>
+      <c r="BZ61" t="inlineStr"/>
+      <c r="CA61" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB61" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC61" t="inlineStr"/>
+      <c r="CD61" t="inlineStr"/>
+      <c r="CE61" t="inlineStr"/>
+      <c r="CF61" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG61" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH61" t="inlineStr"/>
+      <c r="CI61" t="inlineStr"/>
+      <c r="CJ61" t="inlineStr"/>
+      <c r="CK61" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL61" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM61" t="inlineStr"/>
+      <c r="CN61" t="inlineStr"/>
+      <c r="CO61" t="inlineStr"/>
+      <c r="CP61" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR61" t="inlineStr"/>
+      <c r="CS61" t="inlineStr"/>
+      <c r="CT61" t="inlineStr"/>
+      <c r="CU61" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV61" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW61" t="inlineStr"/>
+      <c r="CX61" t="inlineStr"/>
+      <c r="CY61" t="inlineStr"/>
+      <c r="CZ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA61" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB61" t="inlineStr"/>
+      <c r="DC61" t="inlineStr"/>
+      <c r="DD61" t="inlineStr"/>
+      <c r="DE61" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF61" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG61" t="inlineStr"/>
+      <c r="DH61" t="inlineStr"/>
+      <c r="DI61" t="inlineStr"/>
+      <c r="DJ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK61" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL61" t="inlineStr"/>
+      <c r="DM61" t="inlineStr"/>
+      <c r="DN61" t="inlineStr"/>
+      <c r="DO61" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP61" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ61" t="inlineStr"/>
+      <c r="DR61" t="inlineStr"/>
+      <c r="DS61" t="inlineStr"/>
+      <c r="DT61" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU61" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV61" t="inlineStr"/>
+      <c r="DW61" t="inlineStr"/>
+      <c r="DX61" t="inlineStr"/>
+      <c r="DY61" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA61" t="inlineStr"/>
+      <c r="EB61" t="inlineStr"/>
+      <c r="EC61" t="inlineStr"/>
+      <c r="ED61" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE61" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF61" t="inlineStr"/>
+      <c r="EG61" t="inlineStr"/>
+      <c r="EH61" t="inlineStr"/>
+      <c r="EI61" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK61" t="inlineStr"/>
+      <c r="EL61" t="inlineStr"/>
+      <c r="EM61" t="inlineStr"/>
+      <c r="EN61" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO61" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP61" t="inlineStr"/>
+      <c r="EQ61" t="inlineStr"/>
+      <c r="ER61" t="inlineStr"/>
+      <c r="ES61" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET61" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU61" t="inlineStr"/>
+      <c r="EV61" t="inlineStr"/>
+      <c r="EW61" t="inlineStr"/>
+      <c r="EX61" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY61" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ61" t="inlineStr"/>
+      <c r="FA61" t="inlineStr"/>
+      <c r="FB61" t="inlineStr"/>
+      <c r="FC61" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD61" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE61" t="inlineStr"/>
+      <c r="FF61" t="inlineStr"/>
+      <c r="FG61" t="inlineStr"/>
+      <c r="FH61" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI61" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ61" t="inlineStr"/>
+      <c r="FK61" t="inlineStr"/>
+      <c r="FL61" t="inlineStr"/>
+      <c r="FM61" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN61" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO61" t="inlineStr"/>
+      <c r="FP61" t="inlineStr"/>
+      <c r="FQ61" t="inlineStr"/>
+      <c r="FR61" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS61" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT61" t="inlineStr"/>
+      <c r="FU61" t="inlineStr"/>
+      <c r="FV61" t="inlineStr"/>
+      <c r="FW61" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX61" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY61" t="inlineStr"/>
+      <c r="FZ61" t="inlineStr"/>
+      <c r="GA61" t="inlineStr"/>
+      <c r="GB61" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC61" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD61" t="inlineStr"/>
+      <c r="GE61" t="inlineStr"/>
+      <c r="GF61" t="inlineStr"/>
+      <c r="GG61" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH61" t="n">
+        <v>0</v>
+      </c>
+      <c r="GI61" t="inlineStr"/>
+      <c r="GJ61" t="inlineStr"/>
+      <c r="GK61" t="inlineStr"/>
+      <c r="GL61" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM61" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN61" t="inlineStr"/>
+      <c r="GO61" t="inlineStr"/>
+      <c r="GP61" t="inlineStr"/>
+      <c r="GQ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR61" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS61" t="inlineStr"/>
+      <c r="GT61" t="inlineStr"/>
+      <c r="GU61" t="inlineStr"/>
+      <c r="GV61" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW61" t="n">
+        <v>-0.1031233533220247</v>
+      </c>
+      <c r="GX61" t="inlineStr"/>
+      <c r="GY61" t="inlineStr"/>
+      <c r="GZ61" t="inlineStr"/>
+      <c r="HA61" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB61" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC61" t="inlineStr"/>
+      <c r="HD61" t="inlineStr"/>
+      <c r="HE61" t="inlineStr"/>
+      <c r="HF61" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG61" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH61" t="inlineStr"/>
+      <c r="HI61" t="inlineStr"/>
+      <c r="HJ61" t="inlineStr"/>
+      <c r="HK61" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL61" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM61" t="inlineStr"/>
+      <c r="HN61" t="inlineStr"/>
+      <c r="HO61" t="inlineStr"/>
+      <c r="HP61" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR61" t="inlineStr"/>
+      <c r="HS61" t="inlineStr"/>
+      <c r="HT61" t="inlineStr"/>
+      <c r="HU61" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV61" t="n">
+        <v>0</v>
+      </c>
+      <c r="HW61" t="inlineStr"/>
+      <c r="HX61" t="inlineStr"/>
+      <c r="HY61" t="inlineStr"/>
+      <c r="HZ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA61" t="n">
+        <v>0</v>
+      </c>
+      <c r="IB61" t="inlineStr"/>
+      <c r="IC61" t="inlineStr"/>
+      <c r="ID61" t="inlineStr"/>
+      <c r="IE61" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF61" t="n">
+        <v>0.0164853303252253</v>
+      </c>
+      <c r="IG61" t="inlineStr"/>
+      <c r="IH61" t="inlineStr"/>
+      <c r="II61" t="inlineStr"/>
+      <c r="IJ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK61" t="n">
+        <v>0</v>
+      </c>
+      <c r="IL61" t="inlineStr"/>
+      <c r="IM61" t="inlineStr"/>
+      <c r="IN61" t="inlineStr"/>
+      <c r="IO61" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP61" t="n">
+        <v>0</v>
+      </c>
+      <c r="IQ61" t="inlineStr"/>
+      <c r="IR61" t="inlineStr"/>
+      <c r="IS61" t="inlineStr"/>
+      <c r="IT61" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU61" t="n">
+        <v>0</v>
+      </c>
+      <c r="IV61" t="inlineStr"/>
+      <c r="IW61" t="inlineStr"/>
+      <c r="IX61" t="inlineStr"/>
+      <c r="IY61" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA61" t="inlineStr"/>
+      <c r="JB61" t="inlineStr"/>
+      <c r="JC61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-04-19 09:15:38</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>10</v>
+      </c>
+      <c r="C62" t="n">
+        <v>50</v>
+      </c>
+      <c r="D62" t="n">
+        <v>50</v>
+      </c>
+      <c r="E62" t="n">
+        <v>40</v>
+      </c>
+      <c r="F62" t="n">
+        <v>5</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>0.248528934924149</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.930132264529058</v>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.4368969219567061</v>
+      </c>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0.5883803594976738</v>
+      </c>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>0.3756526856934376</v>
+      </c>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr"/>
+      <c r="AB62" t="inlineStr"/>
+      <c r="AC62" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0.2724845549875576</v>
+      </c>
+      <c r="AE62" t="inlineStr"/>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
+      <c r="AH62" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AI62" t="n">
+        <v>0.4935962619829384</v>
+      </c>
+      <c r="AJ62" t="inlineStr"/>
+      <c r="AK62" t="inlineStr"/>
+      <c r="AL62" t="inlineStr"/>
+      <c r="AM62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO62" t="inlineStr"/>
+      <c r="AP62" t="inlineStr"/>
+      <c r="AQ62" t="inlineStr"/>
+      <c r="AR62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AU62" t="inlineStr"/>
+      <c r="AV62" t="inlineStr"/>
+      <c r="AW62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr"/>
+      <c r="BA62" t="inlineStr"/>
+      <c r="BB62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD62" t="inlineStr"/>
+      <c r="BE62" t="inlineStr"/>
+      <c r="BF62" t="inlineStr"/>
+      <c r="BG62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI62" t="inlineStr"/>
+      <c r="BJ62" t="inlineStr"/>
+      <c r="BK62" t="inlineStr"/>
+      <c r="BL62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN62" t="inlineStr"/>
+      <c r="BO62" t="inlineStr"/>
+      <c r="BP62" t="inlineStr"/>
+      <c r="BQ62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS62" t="inlineStr"/>
+      <c r="BT62" t="inlineStr"/>
+      <c r="BU62" t="inlineStr"/>
+      <c r="BV62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW62" t="n">
+        <v>-0.01556487154650775</v>
+      </c>
+      <c r="BX62" t="inlineStr"/>
+      <c r="BY62" t="inlineStr"/>
+      <c r="BZ62" t="inlineStr"/>
+      <c r="CA62" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB62" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC62" t="inlineStr"/>
+      <c r="CD62" t="inlineStr"/>
+      <c r="CE62" t="inlineStr"/>
+      <c r="CF62" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG62" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH62" t="inlineStr"/>
+      <c r="CI62" t="inlineStr"/>
+      <c r="CJ62" t="inlineStr"/>
+      <c r="CK62" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL62" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM62" t="inlineStr"/>
+      <c r="CN62" t="inlineStr"/>
+      <c r="CO62" t="inlineStr"/>
+      <c r="CP62" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ62" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR62" t="inlineStr"/>
+      <c r="CS62" t="inlineStr"/>
+      <c r="CT62" t="inlineStr"/>
+      <c r="CU62" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV62" t="n">
+        <v>0.05411500601473089</v>
+      </c>
+      <c r="CW62" t="inlineStr"/>
+      <c r="CX62" t="inlineStr"/>
+      <c r="CY62" t="inlineStr"/>
+      <c r="CZ62" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA62" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB62" t="inlineStr"/>
+      <c r="DC62" t="inlineStr"/>
+      <c r="DD62" t="inlineStr"/>
+      <c r="DE62" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF62" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG62" t="inlineStr"/>
+      <c r="DH62" t="inlineStr"/>
+      <c r="DI62" t="inlineStr"/>
+      <c r="DJ62" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK62" t="n">
+        <v>1.852155759466e-06</v>
+      </c>
+      <c r="DL62" t="inlineStr"/>
+      <c r="DM62" t="inlineStr"/>
+      <c r="DN62" t="inlineStr"/>
+      <c r="DO62" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP62" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ62" t="inlineStr"/>
+      <c r="DR62" t="inlineStr"/>
+      <c r="DS62" t="inlineStr"/>
+      <c r="DT62" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU62" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV62" t="inlineStr"/>
+      <c r="DW62" t="inlineStr"/>
+      <c r="DX62" t="inlineStr"/>
+      <c r="DY62" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ62" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA62" t="inlineStr"/>
+      <c r="EB62" t="inlineStr"/>
+      <c r="EC62" t="inlineStr"/>
+      <c r="ED62" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE62" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF62" t="inlineStr"/>
+      <c r="EG62" t="inlineStr"/>
+      <c r="EH62" t="inlineStr"/>
+      <c r="EI62" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ62" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK62" t="inlineStr"/>
+      <c r="EL62" t="inlineStr"/>
+      <c r="EM62" t="inlineStr"/>
+      <c r="EN62" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO62" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP62" t="inlineStr"/>
+      <c r="EQ62" t="inlineStr"/>
+      <c r="ER62" t="inlineStr"/>
+      <c r="ES62" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET62" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU62" t="inlineStr"/>
+      <c r="EV62" t="inlineStr"/>
+      <c r="EW62" t="inlineStr"/>
+      <c r="EX62" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY62" t="n">
+        <v>-0.02585483617119348</v>
+      </c>
+      <c r="EZ62" t="inlineStr"/>
+      <c r="FA62" t="inlineStr"/>
+      <c r="FB62" t="inlineStr"/>
+      <c r="FC62" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD62" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE62" t="inlineStr"/>
+      <c r="FF62" t="inlineStr"/>
+      <c r="FG62" t="inlineStr"/>
+      <c r="FH62" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI62" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ62" t="inlineStr"/>
+      <c r="FK62" t="inlineStr"/>
+      <c r="FL62" t="inlineStr"/>
+      <c r="FM62" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN62" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO62" t="inlineStr"/>
+      <c r="FP62" t="inlineStr"/>
+      <c r="FQ62" t="inlineStr"/>
+      <c r="FR62" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS62" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT62" t="inlineStr"/>
+      <c r="FU62" t="inlineStr"/>
+      <c r="FV62" t="inlineStr"/>
+      <c r="FW62" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX62" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY62" t="inlineStr"/>
+      <c r="FZ62" t="inlineStr"/>
+      <c r="GA62" t="inlineStr"/>
+      <c r="GB62" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC62" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD62" t="inlineStr"/>
+      <c r="GE62" t="inlineStr"/>
+      <c r="GF62" t="inlineStr"/>
+      <c r="GG62" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH62" t="n">
+        <v>0</v>
+      </c>
+      <c r="GI62" t="inlineStr"/>
+      <c r="GJ62" t="inlineStr"/>
+      <c r="GK62" t="inlineStr"/>
+      <c r="GL62" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM62" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN62" t="inlineStr"/>
+      <c r="GO62" t="inlineStr"/>
+      <c r="GP62" t="inlineStr"/>
+      <c r="GQ62" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR62" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS62" t="inlineStr"/>
+      <c r="GT62" t="inlineStr"/>
+      <c r="GU62" t="inlineStr"/>
+      <c r="GV62" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW62" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX62" t="inlineStr"/>
+      <c r="GY62" t="inlineStr"/>
+      <c r="GZ62" t="inlineStr"/>
+      <c r="HA62" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB62" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC62" t="inlineStr"/>
+      <c r="HD62" t="inlineStr"/>
+      <c r="HE62" t="inlineStr"/>
+      <c r="HF62" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG62" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH62" t="inlineStr"/>
+      <c r="HI62" t="inlineStr"/>
+      <c r="HJ62" t="inlineStr"/>
+      <c r="HK62" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL62" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM62" t="inlineStr"/>
+      <c r="HN62" t="inlineStr"/>
+      <c r="HO62" t="inlineStr"/>
+      <c r="HP62" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ62" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR62" t="inlineStr"/>
+      <c r="HS62" t="inlineStr"/>
+      <c r="HT62" t="inlineStr"/>
+      <c r="HU62" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV62" t="n">
+        <v>0</v>
+      </c>
+      <c r="HW62" t="inlineStr"/>
+      <c r="HX62" t="inlineStr"/>
+      <c r="HY62" t="inlineStr"/>
+      <c r="HZ62" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA62" t="n">
+        <v>0</v>
+      </c>
+      <c r="IB62" t="inlineStr"/>
+      <c r="IC62" t="inlineStr"/>
+      <c r="ID62" t="inlineStr"/>
+      <c r="IE62" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF62" t="n">
+        <v>0</v>
+      </c>
+      <c r="IG62" t="inlineStr"/>
+      <c r="IH62" t="inlineStr"/>
+      <c r="II62" t="inlineStr"/>
+      <c r="IJ62" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK62" t="n">
+        <v>0</v>
+      </c>
+      <c r="IL62" t="inlineStr"/>
+      <c r="IM62" t="inlineStr"/>
+      <c r="IN62" t="inlineStr"/>
+      <c r="IO62" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP62" t="n">
+        <v>0</v>
+      </c>
+      <c r="IQ62" t="inlineStr"/>
+      <c r="IR62" t="inlineStr"/>
+      <c r="IS62" t="inlineStr"/>
+      <c r="IT62" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU62" t="n">
+        <v>-0.00950882032910904</v>
+      </c>
+      <c r="IV62" t="inlineStr"/>
+      <c r="IW62" t="inlineStr"/>
+      <c r="IX62" t="inlineStr"/>
+      <c r="IY62" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ62" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA62" t="inlineStr"/>
+      <c r="JB62" t="inlineStr"/>
+      <c r="JC62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-04-19 09:17:35</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>10</v>
+      </c>
+      <c r="C63" t="n">
+        <v>50</v>
+      </c>
+      <c r="D63" t="n">
+        <v>50</v>
+      </c>
+      <c r="E63" t="n">
+        <v>40</v>
+      </c>
+      <c r="F63" t="n">
+        <v>5</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>0.2521304229265615</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.8333333333333333</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.9311262525050099</v>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.5017072862609468</v>
+      </c>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0.2273505352380405</v>
+      </c>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
+      <c r="X63" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>0.4882689433596512</v>
+      </c>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr"/>
+      <c r="AB63" t="inlineStr"/>
+      <c r="AC63" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0.5389638204818585</v>
+      </c>
+      <c r="AE63" t="inlineStr"/>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="inlineStr"/>
+      <c r="AH63" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AI63" t="n">
+        <v>0.4087042508183417</v>
+      </c>
+      <c r="AJ63" t="inlineStr"/>
+      <c r="AK63" t="inlineStr"/>
+      <c r="AL63" t="inlineStr"/>
+      <c r="AM63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO63" t="inlineStr"/>
+      <c r="AP63" t="inlineStr"/>
+      <c r="AQ63" t="inlineStr"/>
+      <c r="AR63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AU63" t="inlineStr"/>
+      <c r="AV63" t="inlineStr"/>
+      <c r="AW63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr"/>
+      <c r="BA63" t="inlineStr"/>
+      <c r="BB63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD63" t="inlineStr"/>
+      <c r="BE63" t="inlineStr"/>
+      <c r="BF63" t="inlineStr"/>
+      <c r="BG63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI63" t="inlineStr"/>
+      <c r="BJ63" t="inlineStr"/>
+      <c r="BK63" t="inlineStr"/>
+      <c r="BL63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN63" t="inlineStr"/>
+      <c r="BO63" t="inlineStr"/>
+      <c r="BP63" t="inlineStr"/>
+      <c r="BQ63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS63" t="inlineStr"/>
+      <c r="BT63" t="inlineStr"/>
+      <c r="BU63" t="inlineStr"/>
+      <c r="BV63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX63" t="inlineStr"/>
+      <c r="BY63" t="inlineStr"/>
+      <c r="BZ63" t="inlineStr"/>
+      <c r="CA63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC63" t="inlineStr"/>
+      <c r="CD63" t="inlineStr"/>
+      <c r="CE63" t="inlineStr"/>
+      <c r="CF63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH63" t="inlineStr"/>
+      <c r="CI63" t="inlineStr"/>
+      <c r="CJ63" t="inlineStr"/>
+      <c r="CK63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL63" t="n">
+        <v>6.428547529269804e-07</v>
+      </c>
+      <c r="CM63" t="inlineStr"/>
+      <c r="CN63" t="inlineStr"/>
+      <c r="CO63" t="inlineStr"/>
+      <c r="CP63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ63" t="n">
+        <v>0.02478648531219113</v>
+      </c>
+      <c r="CR63" t="inlineStr"/>
+      <c r="CS63" t="inlineStr"/>
+      <c r="CT63" t="inlineStr"/>
+      <c r="CU63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW63" t="inlineStr"/>
+      <c r="CX63" t="inlineStr"/>
+      <c r="CY63" t="inlineStr"/>
+      <c r="CZ63" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA63" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB63" t="inlineStr"/>
+      <c r="DC63" t="inlineStr"/>
+      <c r="DD63" t="inlineStr"/>
+      <c r="DE63" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF63" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG63" t="inlineStr"/>
+      <c r="DH63" t="inlineStr"/>
+      <c r="DI63" t="inlineStr"/>
+      <c r="DJ63" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK63" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL63" t="inlineStr"/>
+      <c r="DM63" t="inlineStr"/>
+      <c r="DN63" t="inlineStr"/>
+      <c r="DO63" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP63" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ63" t="inlineStr"/>
+      <c r="DR63" t="inlineStr"/>
+      <c r="DS63" t="inlineStr"/>
+      <c r="DT63" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU63" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV63" t="inlineStr"/>
+      <c r="DW63" t="inlineStr"/>
+      <c r="DX63" t="inlineStr"/>
+      <c r="DY63" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ63" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA63" t="inlineStr"/>
+      <c r="EB63" t="inlineStr"/>
+      <c r="EC63" t="inlineStr"/>
+      <c r="ED63" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE63" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF63" t="inlineStr"/>
+      <c r="EG63" t="inlineStr"/>
+      <c r="EH63" t="inlineStr"/>
+      <c r="EI63" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ63" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK63" t="inlineStr"/>
+      <c r="EL63" t="inlineStr"/>
+      <c r="EM63" t="inlineStr"/>
+      <c r="EN63" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO63" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP63" t="inlineStr"/>
+      <c r="EQ63" t="inlineStr"/>
+      <c r="ER63" t="inlineStr"/>
+      <c r="ES63" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET63" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU63" t="inlineStr"/>
+      <c r="EV63" t="inlineStr"/>
+      <c r="EW63" t="inlineStr"/>
+      <c r="EX63" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY63" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ63" t="inlineStr"/>
+      <c r="FA63" t="inlineStr"/>
+      <c r="FB63" t="inlineStr"/>
+      <c r="FC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE63" t="inlineStr"/>
+      <c r="FF63" t="inlineStr"/>
+      <c r="FG63" t="inlineStr"/>
+      <c r="FH63" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI63" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ63" t="inlineStr"/>
+      <c r="FK63" t="inlineStr"/>
+      <c r="FL63" t="inlineStr"/>
+      <c r="FM63" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN63" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO63" t="inlineStr"/>
+      <c r="FP63" t="inlineStr"/>
+      <c r="FQ63" t="inlineStr"/>
+      <c r="FR63" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS63" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT63" t="inlineStr"/>
+      <c r="FU63" t="inlineStr"/>
+      <c r="FV63" t="inlineStr"/>
+      <c r="FW63" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX63" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY63" t="inlineStr"/>
+      <c r="FZ63" t="inlineStr"/>
+      <c r="GA63" t="inlineStr"/>
+      <c r="GB63" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD63" t="inlineStr"/>
+      <c r="GE63" t="inlineStr"/>
+      <c r="GF63" t="inlineStr"/>
+      <c r="GG63" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH63" t="n">
+        <v>0</v>
+      </c>
+      <c r="GI63" t="inlineStr"/>
+      <c r="GJ63" t="inlineStr"/>
+      <c r="GK63" t="inlineStr"/>
+      <c r="GL63" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM63" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN63" t="inlineStr"/>
+      <c r="GO63" t="inlineStr"/>
+      <c r="GP63" t="inlineStr"/>
+      <c r="GQ63" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR63" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS63" t="inlineStr"/>
+      <c r="GT63" t="inlineStr"/>
+      <c r="GU63" t="inlineStr"/>
+      <c r="GV63" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW63" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX63" t="inlineStr"/>
+      <c r="GY63" t="inlineStr"/>
+      <c r="GZ63" t="inlineStr"/>
+      <c r="HA63" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB63" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC63" t="inlineStr"/>
+      <c r="HD63" t="inlineStr"/>
+      <c r="HE63" t="inlineStr"/>
+      <c r="HF63" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG63" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH63" t="inlineStr"/>
+      <c r="HI63" t="inlineStr"/>
+      <c r="HJ63" t="inlineStr"/>
+      <c r="HK63" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL63" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM63" t="inlineStr"/>
+      <c r="HN63" t="inlineStr"/>
+      <c r="HO63" t="inlineStr"/>
+      <c r="HP63" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ63" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR63" t="inlineStr"/>
+      <c r="HS63" t="inlineStr"/>
+      <c r="HT63" t="inlineStr"/>
+      <c r="HU63" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV63" t="n">
+        <v>0</v>
+      </c>
+      <c r="HW63" t="inlineStr"/>
+      <c r="HX63" t="inlineStr"/>
+      <c r="HY63" t="inlineStr"/>
+      <c r="HZ63" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA63" t="n">
+        <v>0.007709298897757804</v>
+      </c>
+      <c r="IB63" t="inlineStr"/>
+      <c r="IC63" t="inlineStr"/>
+      <c r="ID63" t="inlineStr"/>
+      <c r="IE63" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF63" t="n">
+        <v>6.648819389115068e-05</v>
+      </c>
+      <c r="IG63" t="inlineStr"/>
+      <c r="IH63" t="inlineStr"/>
+      <c r="II63" t="inlineStr"/>
+      <c r="IJ63" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK63" t="n">
+        <v>0</v>
+      </c>
+      <c r="IL63" t="inlineStr"/>
+      <c r="IM63" t="inlineStr"/>
+      <c r="IN63" t="inlineStr"/>
+      <c r="IO63" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP63" t="n">
+        <v>0</v>
+      </c>
+      <c r="IQ63" t="inlineStr"/>
+      <c r="IR63" t="inlineStr"/>
+      <c r="IS63" t="inlineStr"/>
+      <c r="IT63" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU63" t="n">
+        <v>0</v>
+      </c>
+      <c r="IV63" t="inlineStr"/>
+      <c r="IW63" t="inlineStr"/>
+      <c r="IX63" t="inlineStr"/>
+      <c r="IY63" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ63" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA63" t="inlineStr"/>
+      <c r="JB63" t="inlineStr"/>
+      <c r="JC63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-04-19 09:18:59</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>10</v>
+      </c>
+      <c r="C64" t="n">
+        <v>100</v>
+      </c>
+      <c r="D64" t="n">
+        <v>50</v>
+      </c>
+      <c r="E64" t="n">
+        <v>40</v>
+      </c>
+      <c r="F64" t="n">
+        <v>5</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>0.1144700578737745</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.9671391391391392</v>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.4434884738573872</v>
+      </c>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0.4174104555192489</v>
+      </c>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
+      <c r="X64" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>0.4872694529702189</v>
+      </c>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="inlineStr"/>
+      <c r="AC64" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0.4750650011365475</v>
+      </c>
+      <c r="AE64" t="inlineStr"/>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="inlineStr"/>
+      <c r="AH64" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>0.3981845539891197</v>
+      </c>
+      <c r="AJ64" t="inlineStr"/>
+      <c r="AK64" t="inlineStr"/>
+      <c r="AL64" t="inlineStr"/>
+      <c r="AM64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO64" t="inlineStr"/>
+      <c r="AP64" t="inlineStr"/>
+      <c r="AQ64" t="inlineStr"/>
+      <c r="AR64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AU64" t="inlineStr"/>
+      <c r="AV64" t="inlineStr"/>
+      <c r="AW64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX64" t="n">
+        <v>1.041188548275008e-06</v>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr"/>
+      <c r="BA64" t="inlineStr"/>
+      <c r="BB64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD64" t="inlineStr"/>
+      <c r="BE64" t="inlineStr"/>
+      <c r="BF64" t="inlineStr"/>
+      <c r="BG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI64" t="inlineStr"/>
+      <c r="BJ64" t="inlineStr"/>
+      <c r="BK64" t="inlineStr"/>
+      <c r="BL64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM64" t="n">
+        <v>1.970979857083514e-06</v>
+      </c>
+      <c r="BN64" t="inlineStr"/>
+      <c r="BO64" t="inlineStr"/>
+      <c r="BP64" t="inlineStr"/>
+      <c r="BQ64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS64" t="inlineStr"/>
+      <c r="BT64" t="inlineStr"/>
+      <c r="BU64" t="inlineStr"/>
+      <c r="BV64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX64" t="inlineStr"/>
+      <c r="BY64" t="inlineStr"/>
+      <c r="BZ64" t="inlineStr"/>
+      <c r="CA64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC64" t="inlineStr"/>
+      <c r="CD64" t="inlineStr"/>
+      <c r="CE64" t="inlineStr"/>
+      <c r="CF64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH64" t="inlineStr"/>
+      <c r="CI64" t="inlineStr"/>
+      <c r="CJ64" t="inlineStr"/>
+      <c r="CK64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM64" t="inlineStr"/>
+      <c r="CN64" t="inlineStr"/>
+      <c r="CO64" t="inlineStr"/>
+      <c r="CP64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR64" t="inlineStr"/>
+      <c r="CS64" t="inlineStr"/>
+      <c r="CT64" t="inlineStr"/>
+      <c r="CU64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW64" t="inlineStr"/>
+      <c r="CX64" t="inlineStr"/>
+      <c r="CY64" t="inlineStr"/>
+      <c r="CZ64" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA64" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB64" t="inlineStr"/>
+      <c r="DC64" t="inlineStr"/>
+      <c r="DD64" t="inlineStr"/>
+      <c r="DE64" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF64" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG64" t="inlineStr"/>
+      <c r="DH64" t="inlineStr"/>
+      <c r="DI64" t="inlineStr"/>
+      <c r="DJ64" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK64" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL64" t="inlineStr"/>
+      <c r="DM64" t="inlineStr"/>
+      <c r="DN64" t="inlineStr"/>
+      <c r="DO64" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP64" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ64" t="inlineStr"/>
+      <c r="DR64" t="inlineStr"/>
+      <c r="DS64" t="inlineStr"/>
+      <c r="DT64" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU64" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV64" t="inlineStr"/>
+      <c r="DW64" t="inlineStr"/>
+      <c r="DX64" t="inlineStr"/>
+      <c r="DY64" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ64" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA64" t="inlineStr"/>
+      <c r="EB64" t="inlineStr"/>
+      <c r="EC64" t="inlineStr"/>
+      <c r="ED64" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE64" t="n">
+        <v>1.839428513195483e-06</v>
+      </c>
+      <c r="EF64" t="inlineStr"/>
+      <c r="EG64" t="inlineStr"/>
+      <c r="EH64" t="inlineStr"/>
+      <c r="EI64" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ64" t="n">
+        <v>9.59088566010885e-06</v>
+      </c>
+      <c r="EK64" t="inlineStr"/>
+      <c r="EL64" t="inlineStr"/>
+      <c r="EM64" t="inlineStr"/>
+      <c r="EN64" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO64" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP64" t="inlineStr"/>
+      <c r="EQ64" t="inlineStr"/>
+      <c r="ER64" t="inlineStr"/>
+      <c r="ES64" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET64" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU64" t="inlineStr"/>
+      <c r="EV64" t="inlineStr"/>
+      <c r="EW64" t="inlineStr"/>
+      <c r="EX64" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY64" t="n">
+        <v>0.01722250671086057</v>
+      </c>
+      <c r="EZ64" t="inlineStr"/>
+      <c r="FA64" t="inlineStr"/>
+      <c r="FB64" t="inlineStr"/>
+      <c r="FC64" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD64" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE64" t="inlineStr"/>
+      <c r="FF64" t="inlineStr"/>
+      <c r="FG64" t="inlineStr"/>
+      <c r="FH64" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI64" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ64" t="inlineStr"/>
+      <c r="FK64" t="inlineStr"/>
+      <c r="FL64" t="inlineStr"/>
+      <c r="FM64" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN64" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO64" t="inlineStr"/>
+      <c r="FP64" t="inlineStr"/>
+      <c r="FQ64" t="inlineStr"/>
+      <c r="FR64" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS64" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT64" t="inlineStr"/>
+      <c r="FU64" t="inlineStr"/>
+      <c r="FV64" t="inlineStr"/>
+      <c r="FW64" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX64" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY64" t="inlineStr"/>
+      <c r="FZ64" t="inlineStr"/>
+      <c r="GA64" t="inlineStr"/>
+      <c r="GB64" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC64" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD64" t="inlineStr"/>
+      <c r="GE64" t="inlineStr"/>
+      <c r="GF64" t="inlineStr"/>
+      <c r="GG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH64" t="n">
+        <v>1.498451460801574e-06</v>
+      </c>
+      <c r="GI64" t="inlineStr"/>
+      <c r="GJ64" t="inlineStr"/>
+      <c r="GK64" t="inlineStr"/>
+      <c r="GL64" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM64" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN64" t="inlineStr"/>
+      <c r="GO64" t="inlineStr"/>
+      <c r="GP64" t="inlineStr"/>
+      <c r="GQ64" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR64" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS64" t="inlineStr"/>
+      <c r="GT64" t="inlineStr"/>
+      <c r="GU64" t="inlineStr"/>
+      <c r="GV64" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW64" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX64" t="inlineStr"/>
+      <c r="GY64" t="inlineStr"/>
+      <c r="GZ64" t="inlineStr"/>
+      <c r="HA64" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB64" t="n">
+        <v>2.702187217464209e-06</v>
+      </c>
+      <c r="HC64" t="inlineStr"/>
+      <c r="HD64" t="inlineStr"/>
+      <c r="HE64" t="inlineStr"/>
+      <c r="HF64" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH64" t="inlineStr"/>
+      <c r="HI64" t="inlineStr"/>
+      <c r="HJ64" t="inlineStr"/>
+      <c r="HK64" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL64" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM64" t="inlineStr"/>
+      <c r="HN64" t="inlineStr"/>
+      <c r="HO64" t="inlineStr"/>
+      <c r="HP64" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ64" t="n">
+        <v>0.02392159497712448</v>
+      </c>
+      <c r="HR64" t="inlineStr"/>
+      <c r="HS64" t="inlineStr"/>
+      <c r="HT64" t="inlineStr"/>
+      <c r="HU64" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV64" t="n">
+        <v>0</v>
+      </c>
+      <c r="HW64" t="inlineStr"/>
+      <c r="HX64" t="inlineStr"/>
+      <c r="HY64" t="inlineStr"/>
+      <c r="HZ64" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA64" t="n">
+        <v>0</v>
+      </c>
+      <c r="IB64" t="inlineStr"/>
+      <c r="IC64" t="inlineStr"/>
+      <c r="ID64" t="inlineStr"/>
+      <c r="IE64" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF64" t="n">
+        <v>0</v>
+      </c>
+      <c r="IG64" t="inlineStr"/>
+      <c r="IH64" t="inlineStr"/>
+      <c r="II64" t="inlineStr"/>
+      <c r="IJ64" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK64" t="n">
+        <v>0.05034652752026628</v>
+      </c>
+      <c r="IL64" t="inlineStr"/>
+      <c r="IM64" t="inlineStr"/>
+      <c r="IN64" t="inlineStr"/>
+      <c r="IO64" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP64" t="n">
+        <v>0</v>
+      </c>
+      <c r="IQ64" t="inlineStr"/>
+      <c r="IR64" t="inlineStr"/>
+      <c r="IS64" t="inlineStr"/>
+      <c r="IT64" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU64" t="n">
+        <v>0</v>
+      </c>
+      <c r="IV64" t="inlineStr"/>
+      <c r="IW64" t="inlineStr"/>
+      <c r="IX64" t="inlineStr"/>
+      <c r="IY64" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ64" t="n">
+        <v>0.06335330025887873</v>
+      </c>
+      <c r="JA64" t="inlineStr"/>
+      <c r="JB64" t="inlineStr"/>
+      <c r="JC64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-04-19 09:58:25</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>10</v>
+      </c>
+      <c r="C65" t="n">
+        <v>100</v>
+      </c>
+      <c r="D65" t="n">
+        <v>50</v>
+      </c>
+      <c r="E65" t="n">
+        <v>40</v>
+      </c>
+      <c r="F65" t="n">
+        <v>5</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>0.4831035811448697</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.1851851851851852</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.8177577577577578</v>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0.3279344289697239</v>
+      </c>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0.3949718068494437</v>
+      </c>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>0.3964433469952495</v>
+      </c>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr"/>
+      <c r="AB65" t="inlineStr"/>
+      <c r="AC65" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>0.4812918663691341</v>
+      </c>
+      <c r="AE65" t="inlineStr"/>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="inlineStr"/>
+      <c r="AH65" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>0.3744896153249389</v>
+      </c>
+      <c r="AJ65" t="inlineStr"/>
+      <c r="AK65" t="inlineStr"/>
+      <c r="AL65" t="inlineStr"/>
+      <c r="AM65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>0.03084332201370652</v>
+      </c>
+      <c r="AO65" t="inlineStr"/>
+      <c r="AP65" t="inlineStr"/>
+      <c r="AQ65" t="inlineStr"/>
+      <c r="AR65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS65" t="n">
+        <v>-0.1659155544020997</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AU65" t="inlineStr"/>
+      <c r="AV65" t="inlineStr"/>
+      <c r="AW65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX65" t="n">
+        <v>-0.04794706331862943</v>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr"/>
+      <c r="BA65" t="inlineStr"/>
+      <c r="BB65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD65" t="inlineStr"/>
+      <c r="BE65" t="inlineStr"/>
+      <c r="BF65" t="inlineStr"/>
+      <c r="BG65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH65" t="n">
+        <v>-0.007593907615303447</v>
+      </c>
+      <c r="BI65" t="inlineStr"/>
+      <c r="BJ65" t="inlineStr"/>
+      <c r="BK65" t="inlineStr"/>
+      <c r="BL65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM65" t="n">
+        <v>-0.06936119600890803</v>
+      </c>
+      <c r="BN65" t="inlineStr"/>
+      <c r="BO65" t="inlineStr"/>
+      <c r="BP65" t="inlineStr"/>
+      <c r="BQ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR65" t="n">
+        <v>-0.02280283459618119</v>
+      </c>
+      <c r="BS65" t="inlineStr"/>
+      <c r="BT65" t="inlineStr"/>
+      <c r="BU65" t="inlineStr"/>
+      <c r="BV65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW65" t="n">
+        <v>-0.01934443054896103</v>
+      </c>
+      <c r="BX65" t="inlineStr"/>
+      <c r="BY65" t="inlineStr"/>
+      <c r="BZ65" t="inlineStr"/>
+      <c r="CA65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB65" t="n">
+        <v>0.004138740926344591</v>
+      </c>
+      <c r="CC65" t="inlineStr"/>
+      <c r="CD65" t="inlineStr"/>
+      <c r="CE65" t="inlineStr"/>
+      <c r="CF65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG65" t="n">
+        <v>-0.1106600662663222</v>
+      </c>
+      <c r="CH65" t="inlineStr"/>
+      <c r="CI65" t="inlineStr"/>
+      <c r="CJ65" t="inlineStr"/>
+      <c r="CK65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL65" t="n">
+        <v>-0.03969262922156318</v>
+      </c>
+      <c r="CM65" t="inlineStr"/>
+      <c r="CN65" t="inlineStr"/>
+      <c r="CO65" t="inlineStr"/>
+      <c r="CP65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ65" t="n">
+        <v>-0.06059235753291883</v>
+      </c>
+      <c r="CR65" t="inlineStr"/>
+      <c r="CS65" t="inlineStr"/>
+      <c r="CT65" t="inlineStr"/>
+      <c r="CU65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV65" t="n">
+        <v>-0.04859791486134369</v>
+      </c>
+      <c r="CW65" t="inlineStr"/>
+      <c r="CX65" t="inlineStr"/>
+      <c r="CY65" t="inlineStr"/>
+      <c r="CZ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA65" t="n">
+        <v>-0.03661444889889332</v>
+      </c>
+      <c r="DB65" t="inlineStr"/>
+      <c r="DC65" t="inlineStr"/>
+      <c r="DD65" t="inlineStr"/>
+      <c r="DE65" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF65" t="n">
+        <v>0.09121282959612292</v>
+      </c>
+      <c r="DG65" t="inlineStr"/>
+      <c r="DH65" t="inlineStr"/>
+      <c r="DI65" t="inlineStr"/>
+      <c r="DJ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK65" t="n">
+        <v>-0.01598591689774067</v>
+      </c>
+      <c r="DL65" t="inlineStr"/>
+      <c r="DM65" t="inlineStr"/>
+      <c r="DN65" t="inlineStr"/>
+      <c r="DO65" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP65" t="n">
+        <v>-0.02747859909048908</v>
+      </c>
+      <c r="DQ65" t="inlineStr"/>
+      <c r="DR65" t="inlineStr"/>
+      <c r="DS65" t="inlineStr"/>
+      <c r="DT65" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU65" t="n">
+        <v>0.07629118412384939</v>
+      </c>
+      <c r="DV65" t="inlineStr"/>
+      <c r="DW65" t="inlineStr"/>
+      <c r="DX65" t="inlineStr"/>
+      <c r="DY65" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ65" t="n">
+        <v>0.03801729947994618</v>
+      </c>
+      <c r="EA65" t="inlineStr"/>
+      <c r="EB65" t="inlineStr"/>
+      <c r="EC65" t="inlineStr"/>
+      <c r="ED65" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE65" t="n">
+        <v>-0.006736554074943837</v>
+      </c>
+      <c r="EF65" t="inlineStr"/>
+      <c r="EG65" t="inlineStr"/>
+      <c r="EH65" t="inlineStr"/>
+      <c r="EI65" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ65" t="n">
+        <v>0.008356500574431002</v>
+      </c>
+      <c r="EK65" t="inlineStr"/>
+      <c r="EL65" t="inlineStr"/>
+      <c r="EM65" t="inlineStr"/>
+      <c r="EN65" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO65" t="n">
+        <v>-0.04124636363750642</v>
+      </c>
+      <c r="EP65" t="inlineStr"/>
+      <c r="EQ65" t="inlineStr"/>
+      <c r="ER65" t="inlineStr"/>
+      <c r="ES65" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET65" t="n">
+        <v>-0.1073908013893629</v>
+      </c>
+      <c r="EU65" t="inlineStr"/>
+      <c r="EV65" t="inlineStr"/>
+      <c r="EW65" t="inlineStr"/>
+      <c r="EX65" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY65" t="n">
+        <v>0.09308088683637127</v>
+      </c>
+      <c r="EZ65" t="inlineStr"/>
+      <c r="FA65" t="inlineStr"/>
+      <c r="FB65" t="inlineStr"/>
+      <c r="FC65" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD65" t="n">
+        <v>-0.09216035491398088</v>
+      </c>
+      <c r="FE65" t="inlineStr"/>
+      <c r="FF65" t="inlineStr"/>
+      <c r="FG65" t="inlineStr"/>
+      <c r="FH65" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI65" t="n">
+        <v>-0.02140406967320335</v>
+      </c>
+      <c r="FJ65" t="inlineStr"/>
+      <c r="FK65" t="inlineStr"/>
+      <c r="FL65" t="inlineStr"/>
+      <c r="FM65" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN65" t="n">
+        <v>-0.01700431969190362</v>
+      </c>
+      <c r="FO65" t="inlineStr"/>
+      <c r="FP65" t="inlineStr"/>
+      <c r="FQ65" t="inlineStr"/>
+      <c r="FR65" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS65" t="n">
+        <v>-0.02800816379414055</v>
+      </c>
+      <c r="FT65" t="inlineStr"/>
+      <c r="FU65" t="inlineStr"/>
+      <c r="FV65" t="inlineStr"/>
+      <c r="FW65" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX65" t="n">
+        <v>-0.02106933931447036</v>
+      </c>
+      <c r="FY65" t="inlineStr"/>
+      <c r="FZ65" t="inlineStr"/>
+      <c r="GA65" t="inlineStr"/>
+      <c r="GB65" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC65" t="n">
+        <v>-0.0003449318078145503</v>
+      </c>
+      <c r="GD65" t="inlineStr"/>
+      <c r="GE65" t="inlineStr"/>
+      <c r="GF65" t="inlineStr"/>
+      <c r="GG65" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH65" t="n">
+        <v>-0.004824912086817503</v>
+      </c>
+      <c r="GI65" t="inlineStr"/>
+      <c r="GJ65" t="inlineStr"/>
+      <c r="GK65" t="inlineStr"/>
+      <c r="GL65" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM65" t="n">
+        <v>-0.03309383286988677</v>
+      </c>
+      <c r="GN65" t="inlineStr"/>
+      <c r="GO65" t="inlineStr"/>
+      <c r="GP65" t="inlineStr"/>
+      <c r="GQ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR65" t="n">
+        <v>-0.01381561764511086</v>
+      </c>
+      <c r="GS65" t="inlineStr"/>
+      <c r="GT65" t="inlineStr"/>
+      <c r="GU65" t="inlineStr"/>
+      <c r="GV65" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW65" t="n">
+        <v>0.01841899247913761</v>
+      </c>
+      <c r="GX65" t="inlineStr"/>
+      <c r="GY65" t="inlineStr"/>
+      <c r="GZ65" t="inlineStr"/>
+      <c r="HA65" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB65" t="n">
+        <v>0.02868353409091725</v>
+      </c>
+      <c r="HC65" t="inlineStr"/>
+      <c r="HD65" t="inlineStr"/>
+      <c r="HE65" t="inlineStr"/>
+      <c r="HF65" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG65" t="n">
+        <v>-0.1611963716388611</v>
+      </c>
+      <c r="HH65" t="inlineStr"/>
+      <c r="HI65" t="inlineStr"/>
+      <c r="HJ65" t="inlineStr"/>
+      <c r="HK65" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL65" t="n">
+        <v>-0.01897883353641791</v>
+      </c>
+      <c r="HM65" t="inlineStr"/>
+      <c r="HN65" t="inlineStr"/>
+      <c r="HO65" t="inlineStr"/>
+      <c r="HP65" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ65" t="n">
+        <v>0.1652201359996768</v>
+      </c>
+      <c r="HR65" t="inlineStr"/>
+      <c r="HS65" t="inlineStr"/>
+      <c r="HT65" t="inlineStr"/>
+      <c r="HU65" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV65" t="n">
+        <v>-0.04272081179417655</v>
+      </c>
+      <c r="HW65" t="inlineStr"/>
+      <c r="HX65" t="inlineStr"/>
+      <c r="HY65" t="inlineStr"/>
+      <c r="HZ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA65" t="n">
+        <v>-0.02697211817188683</v>
+      </c>
+      <c r="IB65" t="inlineStr"/>
+      <c r="IC65" t="inlineStr"/>
+      <c r="ID65" t="inlineStr"/>
+      <c r="IE65" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF65" t="n">
+        <v>-0.02805970181604089</v>
+      </c>
+      <c r="IG65" t="inlineStr"/>
+      <c r="IH65" t="inlineStr"/>
+      <c r="II65" t="inlineStr"/>
+      <c r="IJ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK65" t="n">
+        <v>0.1836143970915837</v>
+      </c>
+      <c r="IL65" t="inlineStr"/>
+      <c r="IM65" t="inlineStr"/>
+      <c r="IN65" t="inlineStr"/>
+      <c r="IO65" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP65" t="n">
+        <v>0.05454139191207134</v>
+      </c>
+      <c r="IQ65" t="inlineStr"/>
+      <c r="IR65" t="inlineStr"/>
+      <c r="IS65" t="inlineStr"/>
+      <c r="IT65" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU65" t="n">
+        <v>0.06031187720463912</v>
+      </c>
+      <c r="IV65" t="inlineStr"/>
+      <c r="IW65" t="inlineStr"/>
+      <c r="IX65" t="inlineStr"/>
+      <c r="IY65" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ65" t="n">
+        <v>0.02815792263248174</v>
+      </c>
+      <c r="JA65" t="inlineStr"/>
+      <c r="JB65" t="inlineStr"/>
+      <c r="JC65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-04-19 09:59:08</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>10</v>
+      </c>
+      <c r="C66" t="n">
+        <v>100</v>
+      </c>
+      <c r="D66" t="n">
+        <v>50</v>
+      </c>
+      <c r="E66" t="n">
+        <v>40</v>
+      </c>
+      <c r="F66" t="n">
+        <v>5</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>0.2812723806035833</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.9003243243243244</v>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.3673802433949679</v>
+      </c>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0.4166759665394049</v>
+      </c>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>0.4352354067812034</v>
+      </c>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr"/>
+      <c r="AC66" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>0.5448362717472991</v>
+      </c>
+      <c r="AE66" t="inlineStr"/>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="inlineStr"/>
+      <c r="AH66" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>0.3834877780087107</v>
+      </c>
+      <c r="AJ66" t="inlineStr"/>
+      <c r="AK66" t="inlineStr"/>
+      <c r="AL66" t="inlineStr"/>
+      <c r="AM66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO66" t="inlineStr"/>
+      <c r="AP66" t="inlineStr"/>
+      <c r="AQ66" t="inlineStr"/>
+      <c r="AR66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS66" t="n">
+        <v>-0.1438037733676138</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AU66" t="inlineStr"/>
+      <c r="AV66" t="inlineStr"/>
+      <c r="AW66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr"/>
+      <c r="BA66" t="inlineStr"/>
+      <c r="BB66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD66" t="inlineStr"/>
+      <c r="BE66" t="inlineStr"/>
+      <c r="BF66" t="inlineStr"/>
+      <c r="BG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI66" t="inlineStr"/>
+      <c r="BJ66" t="inlineStr"/>
+      <c r="BK66" t="inlineStr"/>
+      <c r="BL66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN66" t="inlineStr"/>
+      <c r="BO66" t="inlineStr"/>
+      <c r="BP66" t="inlineStr"/>
+      <c r="BQ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS66" t="inlineStr"/>
+      <c r="BT66" t="inlineStr"/>
+      <c r="BU66" t="inlineStr"/>
+      <c r="BV66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX66" t="inlineStr"/>
+      <c r="BY66" t="inlineStr"/>
+      <c r="BZ66" t="inlineStr"/>
+      <c r="CA66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC66" t="inlineStr"/>
+      <c r="CD66" t="inlineStr"/>
+      <c r="CE66" t="inlineStr"/>
+      <c r="CF66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG66" t="n">
+        <v>-0.03556553355210895</v>
+      </c>
+      <c r="CH66" t="inlineStr"/>
+      <c r="CI66" t="inlineStr"/>
+      <c r="CJ66" t="inlineStr"/>
+      <c r="CK66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM66" t="inlineStr"/>
+      <c r="CN66" t="inlineStr"/>
+      <c r="CO66" t="inlineStr"/>
+      <c r="CP66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR66" t="inlineStr"/>
+      <c r="CS66" t="inlineStr"/>
+      <c r="CT66" t="inlineStr"/>
+      <c r="CU66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW66" t="inlineStr"/>
+      <c r="CX66" t="inlineStr"/>
+      <c r="CY66" t="inlineStr"/>
+      <c r="CZ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA66" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB66" t="inlineStr"/>
+      <c r="DC66" t="inlineStr"/>
+      <c r="DD66" t="inlineStr"/>
+      <c r="DE66" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF66" t="n">
+        <v>9.2260104659308e-05</v>
+      </c>
+      <c r="DG66" t="inlineStr"/>
+      <c r="DH66" t="inlineStr"/>
+      <c r="DI66" t="inlineStr"/>
+      <c r="DJ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK66" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL66" t="inlineStr"/>
+      <c r="DM66" t="inlineStr"/>
+      <c r="DN66" t="inlineStr"/>
+      <c r="DO66" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP66" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ66" t="inlineStr"/>
+      <c r="DR66" t="inlineStr"/>
+      <c r="DS66" t="inlineStr"/>
+      <c r="DT66" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU66" t="n">
+        <v>0.0001885679861460831</v>
+      </c>
+      <c r="DV66" t="inlineStr"/>
+      <c r="DW66" t="inlineStr"/>
+      <c r="DX66" t="inlineStr"/>
+      <c r="DY66" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA66" t="inlineStr"/>
+      <c r="EB66" t="inlineStr"/>
+      <c r="EC66" t="inlineStr"/>
+      <c r="ED66" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE66" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF66" t="inlineStr"/>
+      <c r="EG66" t="inlineStr"/>
+      <c r="EH66" t="inlineStr"/>
+      <c r="EI66" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK66" t="inlineStr"/>
+      <c r="EL66" t="inlineStr"/>
+      <c r="EM66" t="inlineStr"/>
+      <c r="EN66" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO66" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP66" t="inlineStr"/>
+      <c r="EQ66" t="inlineStr"/>
+      <c r="ER66" t="inlineStr"/>
+      <c r="ES66" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET66" t="n">
+        <v>-0.04674635875622263</v>
+      </c>
+      <c r="EU66" t="inlineStr"/>
+      <c r="EV66" t="inlineStr"/>
+      <c r="EW66" t="inlineStr"/>
+      <c r="EX66" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY66" t="n">
+        <v>7.023943644048388e-05</v>
+      </c>
+      <c r="EZ66" t="inlineStr"/>
+      <c r="FA66" t="inlineStr"/>
+      <c r="FB66" t="inlineStr"/>
+      <c r="FC66" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD66" t="n">
+        <v>-0.008975754135200241</v>
+      </c>
+      <c r="FE66" t="inlineStr"/>
+      <c r="FF66" t="inlineStr"/>
+      <c r="FG66" t="inlineStr"/>
+      <c r="FH66" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI66" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ66" t="inlineStr"/>
+      <c r="FK66" t="inlineStr"/>
+      <c r="FL66" t="inlineStr"/>
+      <c r="FM66" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN66" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO66" t="inlineStr"/>
+      <c r="FP66" t="inlineStr"/>
+      <c r="FQ66" t="inlineStr"/>
+      <c r="FR66" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS66" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT66" t="inlineStr"/>
+      <c r="FU66" t="inlineStr"/>
+      <c r="FV66" t="inlineStr"/>
+      <c r="FW66" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX66" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY66" t="inlineStr"/>
+      <c r="FZ66" t="inlineStr"/>
+      <c r="GA66" t="inlineStr"/>
+      <c r="GB66" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC66" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD66" t="inlineStr"/>
+      <c r="GE66" t="inlineStr"/>
+      <c r="GF66" t="inlineStr"/>
+      <c r="GG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH66" t="n">
+        <v>0</v>
+      </c>
+      <c r="GI66" t="inlineStr"/>
+      <c r="GJ66" t="inlineStr"/>
+      <c r="GK66" t="inlineStr"/>
+      <c r="GL66" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM66" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN66" t="inlineStr"/>
+      <c r="GO66" t="inlineStr"/>
+      <c r="GP66" t="inlineStr"/>
+      <c r="GQ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR66" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS66" t="inlineStr"/>
+      <c r="GT66" t="inlineStr"/>
+      <c r="GU66" t="inlineStr"/>
+      <c r="GV66" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW66" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX66" t="inlineStr"/>
+      <c r="GY66" t="inlineStr"/>
+      <c r="GZ66" t="inlineStr"/>
+      <c r="HA66" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB66" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC66" t="inlineStr"/>
+      <c r="HD66" t="inlineStr"/>
+      <c r="HE66" t="inlineStr"/>
+      <c r="HF66" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG66" t="n">
+        <v>-0.1783966929373731</v>
+      </c>
+      <c r="HH66" t="inlineStr"/>
+      <c r="HI66" t="inlineStr"/>
+      <c r="HJ66" t="inlineStr"/>
+      <c r="HK66" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL66" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM66" t="inlineStr"/>
+      <c r="HN66" t="inlineStr"/>
+      <c r="HO66" t="inlineStr"/>
+      <c r="HP66" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR66" t="inlineStr"/>
+      <c r="HS66" t="inlineStr"/>
+      <c r="HT66" t="inlineStr"/>
+      <c r="HU66" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV66" t="n">
+        <v>0</v>
+      </c>
+      <c r="HW66" t="inlineStr"/>
+      <c r="HX66" t="inlineStr"/>
+      <c r="HY66" t="inlineStr"/>
+      <c r="HZ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA66" t="n">
+        <v>0</v>
+      </c>
+      <c r="IB66" t="inlineStr"/>
+      <c r="IC66" t="inlineStr"/>
+      <c r="ID66" t="inlineStr"/>
+      <c r="IE66" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF66" t="n">
+        <v>0</v>
+      </c>
+      <c r="IG66" t="inlineStr"/>
+      <c r="IH66" t="inlineStr"/>
+      <c r="II66" t="inlineStr"/>
+      <c r="IJ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK66" t="n">
+        <v>0.04514280754915855</v>
+      </c>
+      <c r="IL66" t="inlineStr"/>
+      <c r="IM66" t="inlineStr"/>
+      <c r="IN66" t="inlineStr"/>
+      <c r="IO66" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP66" t="n">
+        <v>0</v>
+      </c>
+      <c r="IQ66" t="inlineStr"/>
+      <c r="IR66" t="inlineStr"/>
+      <c r="IS66" t="inlineStr"/>
+      <c r="IT66" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU66" t="n">
+        <v>0.0002769535674588896</v>
+      </c>
+      <c r="IV66" t="inlineStr"/>
+      <c r="IW66" t="inlineStr"/>
+      <c r="IX66" t="inlineStr"/>
+      <c r="IY66" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA66" t="inlineStr"/>
+      <c r="JB66" t="inlineStr"/>
+      <c r="JC66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-04-19 10:17:22</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>10</v>
+      </c>
+      <c r="C67" t="n">
+        <v>100</v>
+      </c>
+      <c r="D67" t="n">
+        <v>50</v>
+      </c>
+      <c r="E67" t="n">
+        <v>40</v>
+      </c>
+      <c r="F67" t="n">
+        <v>5</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>0.1144700578737745</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.9671391391391392</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0.9536448617695518</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.08884061472152738</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.3318408741304625</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0.4434884738573872</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0.3854677638705822</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0.4313321584119694</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0.4307758656269129</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0.4174104555192489</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0.3526805830474796</v>
+      </c>
+      <c r="V67" t="n">
+        <v>0.4321142758209725</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0.3797615250809367</v>
+      </c>
+      <c r="X67" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>0.4872694529702189</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>0.3941914308645739</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>0.4855890552014349</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>0.4599040751087692</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>0.4750650011365475</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>0.4101076392537971</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>0.4675406283098794</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>0.4698447696336012</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>0.3981845539891197</v>
+      </c>
+      <c r="AJ67" t="n">
+        <v>0.3405714609394642</v>
+      </c>
+      <c r="AK67" t="n">
+        <v>0.4106676034007202</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>0.3726146971621438</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>0.07479144020591809</v>
+      </c>
+      <c r="AP67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ67" t="n">
+        <v>0.01101860371676124</v>
+      </c>
+      <c r="AR67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="n">
+        <v>-0.07836456325900948</v>
+      </c>
+      <c r="AU67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV67" t="n">
+        <v>-0.08445205520083648</v>
+      </c>
+      <c r="AW67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX67" t="n">
+        <v>1.041188548275008e-06</v>
+      </c>
+      <c r="AY67" t="n">
+        <v>0.02341283716262564</v>
+      </c>
+      <c r="AZ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA67" t="n">
+        <v>0.0003300607311461253</v>
+      </c>
+      <c r="BB67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD67" t="n">
+        <v>0.08744369702862911</v>
+      </c>
+      <c r="BE67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF67" t="n">
+        <v>0.02858127669441826</v>
+      </c>
+      <c r="BG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI67" t="n">
+        <v>0.08459954769170611</v>
+      </c>
+      <c r="BJ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK67" t="n">
+        <v>0.00876260427316034</v>
+      </c>
+      <c r="BL67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM67" t="n">
+        <v>1.970979857083514e-06</v>
+      </c>
+      <c r="BN67" t="n">
+        <v>0.003192039761784742</v>
+      </c>
+      <c r="BO67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP67" t="n">
+        <v>-3.929199850935201e-05</v>
+      </c>
+      <c r="BQ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS67" t="n">
+        <v>0.01363705202697191</v>
+      </c>
+      <c r="BT67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU67" t="n">
+        <v>-7.943859523498892e-05</v>
+      </c>
+      <c r="BV67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX67" t="n">
+        <v>0.02472965002079261</v>
+      </c>
+      <c r="BY67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ67" t="n">
+        <v>3.447283706093494e-05</v>
+      </c>
+      <c r="CA67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC67" t="n">
+        <v>0.1253646445668714</v>
+      </c>
+      <c r="CD67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE67" t="n">
+        <v>0.06204229890530044</v>
+      </c>
+      <c r="CF67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH67" t="n">
+        <v>-0.0388198955366289</v>
+      </c>
+      <c r="CI67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ67" t="n">
+        <v>-0.03304622982005279</v>
+      </c>
+      <c r="CK67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM67" t="n">
+        <v>-0.07174322422537287</v>
+      </c>
+      <c r="CN67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO67" t="n">
+        <v>-0.07246574752398248</v>
+      </c>
+      <c r="CP67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR67" t="n">
+        <v>-0.03796031626880576</v>
+      </c>
+      <c r="CS67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT67" t="n">
+        <v>-0.02698037371975968</v>
+      </c>
+      <c r="CU67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW67" t="n">
+        <v>-0.002455911848001288</v>
+      </c>
+      <c r="CX67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY67" t="n">
+        <v>-0.001364762020180563</v>
+      </c>
+      <c r="CZ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA67" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB67" t="n">
+        <v>-0.0005902032453384893</v>
+      </c>
+      <c r="DC67" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD67" t="n">
+        <v>-8.226961034979953e-05</v>
+      </c>
+      <c r="DE67" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF67" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG67" t="n">
+        <v>0.1071574837812121</v>
+      </c>
+      <c r="DH67" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI67" t="n">
+        <v>0.03397342203330817</v>
+      </c>
+      <c r="DJ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK67" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL67" t="n">
+        <v>0.08343069216612654</v>
+      </c>
+      <c r="DM67" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN67" t="n">
+        <v>0.006419580131760759</v>
+      </c>
+      <c r="DO67" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP67" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ67" t="n">
+        <v>0.04442929991794951</v>
+      </c>
+      <c r="DR67" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS67" t="n">
+        <v>4.528973073649779e-05</v>
+      </c>
+      <c r="DT67" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU67" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV67" t="n">
+        <v>0.1028242575413772</v>
+      </c>
+      <c r="DW67" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX67" t="n">
+        <v>0.05439059417626117</v>
+      </c>
+      <c r="DY67" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA67" t="n">
+        <v>0.1204355133070613</v>
+      </c>
+      <c r="EB67" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC67" t="n">
+        <v>0.05953480458184204</v>
+      </c>
+      <c r="ED67" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE67" t="n">
+        <v>1.839428513195483e-06</v>
+      </c>
+      <c r="EF67" t="n">
+        <v>0.06065931476633235</v>
+      </c>
+      <c r="EG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH67" t="n">
+        <v>-1.584930031051402e-05</v>
+      </c>
+      <c r="EI67" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ67" t="n">
+        <v>9.59088566010885e-06</v>
+      </c>
+      <c r="EK67" t="n">
+        <v>0.06071534343913072</v>
+      </c>
+      <c r="EL67" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM67" t="n">
+        <v>5.165902839215153e-05</v>
+      </c>
+      <c r="EN67" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO67" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP67" t="n">
+        <v>-0.007712768743300042</v>
+      </c>
+      <c r="EQ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER67" t="n">
+        <v>-0.0001980238601578312</v>
+      </c>
+      <c r="ES67" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET67" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU67" t="n">
+        <v>-0.04136777772735881</v>
+      </c>
+      <c r="EV67" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW67" t="n">
+        <v>-0.03813603117535663</v>
+      </c>
+      <c r="EX67" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY67" t="n">
+        <v>0.01722250671086057</v>
+      </c>
+      <c r="EZ67" t="n">
+        <v>0.1535797390528636</v>
+      </c>
+      <c r="FA67" t="n">
+        <v>0.02094578635952471</v>
+      </c>
+      <c r="FB67" t="n">
+        <v>0.0989154997557431</v>
+      </c>
+      <c r="FC67" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD67" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE67" t="n">
+        <v>0.01741573582728647</v>
+      </c>
+      <c r="FF67" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG67" t="n">
+        <v>-1.2043111276479e-05</v>
+      </c>
+      <c r="FH67" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI67" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ67" t="n">
+        <v>0.07855743012843544</v>
+      </c>
+      <c r="FK67" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL67" t="n">
+        <v>0.0001492084364225081</v>
+      </c>
+      <c r="FM67" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN67" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO67" t="n">
+        <v>0.004342657884880234</v>
+      </c>
+      <c r="FP67" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ67" t="n">
+        <v>-0.0002994527831435119</v>
+      </c>
+      <c r="FR67" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS67" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT67" t="n">
+        <v>0.02961566521290366</v>
+      </c>
+      <c r="FU67" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV67" t="n">
+        <v>-9.060927827574611e-05</v>
+      </c>
+      <c r="FW67" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX67" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY67" t="n">
+        <v>0.07146312216195172</v>
+      </c>
+      <c r="FZ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA67" t="n">
+        <v>1.713054973840784e-05</v>
+      </c>
+      <c r="GB67" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC67" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD67" t="n">
+        <v>0.03522784999870992</v>
+      </c>
+      <c r="GE67" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF67" t="n">
+        <v>-6.314334100076582e-05</v>
+      </c>
+      <c r="GG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH67" t="n">
+        <v>1.498451460801574e-06</v>
+      </c>
+      <c r="GI67" t="n">
+        <v>0.07666997620940813</v>
+      </c>
+      <c r="GJ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="GK67" t="n">
+        <v>0.003876837424522122</v>
+      </c>
+      <c r="GL67" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM67" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN67" t="n">
+        <v>0.04909753880277341</v>
+      </c>
+      <c r="GO67" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP67" t="n">
+        <v>1.20648362262278e-05</v>
+      </c>
+      <c r="GQ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR67" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS67" t="n">
+        <v>0.01597529772903446</v>
+      </c>
+      <c r="GT67" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU67" t="n">
+        <v>-6.845376985212492e-05</v>
+      </c>
+      <c r="GV67" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW67" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX67" t="n">
+        <v>0.1010790015630298</v>
+      </c>
+      <c r="GY67" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ67" t="n">
+        <v>0.04273639980626311</v>
+      </c>
+      <c r="HA67" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB67" t="n">
+        <v>2.702187217464209e-06</v>
+      </c>
+      <c r="HC67" t="n">
+        <v>0.08807845757843991</v>
+      </c>
+      <c r="HD67" t="n">
+        <v>0</v>
+      </c>
+      <c r="HE67" t="n">
+        <v>0.01902559534953149</v>
+      </c>
+      <c r="HF67" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH67" t="n">
+        <v>-0.1244363176523562</v>
+      </c>
+      <c r="HI67" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ67" t="n">
+        <v>-0.1580848920257515</v>
+      </c>
+      <c r="HK67" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL67" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM67" t="n">
+        <v>0.05982672122168067</v>
+      </c>
+      <c r="HN67" t="n">
+        <v>0</v>
+      </c>
+      <c r="HO67" t="n">
+        <v>-3.063965641358511e-05</v>
+      </c>
+      <c r="HP67" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ67" t="n">
+        <v>0.02392159497712448</v>
+      </c>
+      <c r="HR67" t="n">
+        <v>0.1393212308728277</v>
+      </c>
+      <c r="HS67" t="n">
+        <v>0.00290178930882881</v>
+      </c>
+      <c r="HT67" t="n">
+        <v>0.08739869813431114</v>
+      </c>
+      <c r="HU67" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV67" t="n">
+        <v>0</v>
+      </c>
+      <c r="HW67" t="n">
+        <v>0.04493115251276569</v>
+      </c>
+      <c r="HX67" t="n">
+        <v>0</v>
+      </c>
+      <c r="HY67" t="n">
+        <v>-0.0001274327158495288</v>
+      </c>
+      <c r="HZ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA67" t="n">
+        <v>0</v>
+      </c>
+      <c r="IB67" t="n">
+        <v>-0.007384217988625954</v>
+      </c>
+      <c r="IC67" t="n">
+        <v>0</v>
+      </c>
+      <c r="ID67" t="n">
+        <v>-7.971199397387853e-05</v>
+      </c>
+      <c r="IE67" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF67" t="n">
+        <v>0</v>
+      </c>
+      <c r="IG67" t="n">
+        <v>0.04804429491159838</v>
+      </c>
+      <c r="IH67" t="n">
+        <v>0</v>
+      </c>
+      <c r="II67" t="n">
+        <v>-0.0002799596348532607</v>
+      </c>
+      <c r="IJ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK67" t="n">
+        <v>0.05034652752026628</v>
+      </c>
+      <c r="IL67" t="n">
+        <v>0.1393284862359434</v>
+      </c>
+      <c r="IM67" t="n">
+        <v>0.02109309685444662</v>
+      </c>
+      <c r="IN67" t="n">
+        <v>0.09255249816650898</v>
+      </c>
+      <c r="IO67" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP67" t="n">
+        <v>0</v>
+      </c>
+      <c r="IQ67" t="n">
+        <v>0.1208670329170033</v>
+      </c>
+      <c r="IR67" t="n">
+        <v>0</v>
+      </c>
+      <c r="IS67" t="n">
+        <v>0.04411671550273647</v>
+      </c>
+      <c r="IT67" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU67" t="n">
+        <v>0</v>
+      </c>
+      <c r="IV67" t="n">
+        <v>0.1102593689710699</v>
+      </c>
+      <c r="IW67" t="n">
+        <v>0</v>
+      </c>
+      <c r="IX67" t="n">
+        <v>0.03577412682831958</v>
+      </c>
+      <c r="IY67" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ67" t="n">
+        <v>0.06335330025887873</v>
+      </c>
+      <c r="JA67" t="n">
+        <v>0.1681230829207597</v>
+      </c>
+      <c r="JB67" t="n">
+        <v>0.05743610828003</v>
+      </c>
+      <c r="JC67" t="n">
+        <v>0.1201190150947564</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-04-19 10:25:14</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>10</v>
+      </c>
+      <c r="C68" t="n">
+        <v>100</v>
+      </c>
+      <c r="D68" t="n">
+        <v>50</v>
+      </c>
+      <c r="E68" t="n">
+        <v>40</v>
+      </c>
+      <c r="F68" t="n">
+        <v>5</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>0.1482969174677192</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.9596956956956958</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0.9629130882846779</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.1509138080277019</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.2588041968315969</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0.4253246212929515</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0.3631989533648214</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0.4420851994763379</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0.4009589376695143</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0.4137688247786359</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0.3727893422914855</v>
+      </c>
+      <c r="V68" t="n">
+        <v>0.4059681803076974</v>
+      </c>
+      <c r="W68" t="n">
+        <v>0.408711519363026</v>
+      </c>
+      <c r="X68" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>0.4848872380502073</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>0.4428523380273526</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>0.4663287352087873</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>0.4807399119844509</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>0.5410919286520878</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>0.4506576168140828</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>0.5497983327157687</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>0.5035108372459687</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>0.3464075883795265</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>0.3529636884047206</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>0.3464243309052601</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>0.3672347406833776</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>0.03274553505200609</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ68" t="n">
+        <v>0.0001828963124230574</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="n">
+        <v>0.08989347990703102</v>
+      </c>
+      <c r="AU68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV68" t="n">
+        <v>0.0116163062283624</v>
+      </c>
+      <c r="AW68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY68" t="n">
+        <v>-0.001066349099301714</v>
+      </c>
+      <c r="AZ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA68" t="n">
+        <v>-6.360726232915184e-05</v>
+      </c>
+      <c r="BB68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD68" t="n">
+        <v>0.003724115605215337</v>
+      </c>
+      <c r="BE68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF68" t="n">
+        <v>-0.0001748260180410296</v>
+      </c>
+      <c r="BG68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI68" t="n">
+        <v>0.1123178125501612</v>
+      </c>
+      <c r="BJ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK68" t="n">
+        <v>0.03884066531852289</v>
+      </c>
+      <c r="BL68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN68" t="n">
+        <v>0.09617491420839436</v>
+      </c>
+      <c r="BO68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP68" t="n">
+        <v>0.01860167106521679</v>
+      </c>
+      <c r="BQ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS68" t="n">
+        <v>0.02178726416297033</v>
+      </c>
+      <c r="BT68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU68" t="n">
+        <v>0.0001700975430781801</v>
+      </c>
+      <c r="BV68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX68" t="n">
+        <v>0.1092321448721939</v>
+      </c>
+      <c r="BY68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ68" t="n">
+        <v>0.03972525103197174</v>
+      </c>
+      <c r="CA68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC68" t="n">
+        <v>0.03145742493396329</v>
+      </c>
+      <c r="CD68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE68" t="n">
+        <v>-5.270207727307044e-06</v>
+      </c>
+      <c r="CF68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH68" t="n">
+        <v>0.04800172339669577</v>
+      </c>
+      <c r="CI68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ68" t="n">
+        <v>8.926464268951919e-05</v>
+      </c>
+      <c r="CK68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM68" t="n">
+        <v>0.06772401197518638</v>
+      </c>
+      <c r="CN68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO68" t="n">
+        <v>2.661839594418709e-05</v>
+      </c>
+      <c r="CP68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR68" t="n">
+        <v>0.1040200513524011</v>
+      </c>
+      <c r="CS68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT68" t="n">
+        <v>0.03801918006919982</v>
+      </c>
+      <c r="CU68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW68" t="n">
+        <v>0.00129071713135928</v>
+      </c>
+      <c r="CX68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY68" t="n">
+        <v>1.84574634241717e-05</v>
+      </c>
+      <c r="CZ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA68" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB68" t="n">
+        <v>0.07865404522322589</v>
+      </c>
+      <c r="DC68" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD68" t="n">
+        <v>0.0008021141432952774</v>
+      </c>
+      <c r="DE68" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF68" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG68" t="n">
+        <v>0.05939931194710104</v>
+      </c>
+      <c r="DH68" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI68" t="n">
+        <v>4.230816551865404e-05</v>
+      </c>
+      <c r="DJ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK68" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL68" t="n">
+        <v>0.008143156435312434</v>
+      </c>
+      <c r="DM68" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN68" t="n">
+        <v>1.633635811222673e-05</v>
+      </c>
+      <c r="DO68" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP68" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ68" t="n">
+        <v>0.07308643878290462</v>
+      </c>
+      <c r="DR68" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS68" t="n">
+        <v>5.224987575115724e-06</v>
+      </c>
+      <c r="DT68" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU68" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV68" t="n">
+        <v>0.06738589146081003</v>
+      </c>
+      <c r="DW68" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX68" t="n">
+        <v>-4.011745576309612e-05</v>
+      </c>
+      <c r="DY68" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA68" t="n">
+        <v>0.04867778281533248</v>
+      </c>
+      <c r="EB68" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC68" t="n">
+        <v>-5.432527011667156e-05</v>
+      </c>
+      <c r="ED68" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE68" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF68" t="n">
+        <v>0.01226679541426947</v>
+      </c>
+      <c r="EG68" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH68" t="n">
+        <v>-3.799904447652476e-05</v>
+      </c>
+      <c r="EI68" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK68" t="n">
+        <v>-0.004253397733579068</v>
+      </c>
+      <c r="EL68" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM68" t="n">
+        <v>2.618762100447967e-05</v>
+      </c>
+      <c r="EN68" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO68" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP68" t="n">
+        <v>-0.0214507982942831</v>
+      </c>
+      <c r="EQ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER68" t="n">
+        <v>-0.006526510643062107</v>
+      </c>
+      <c r="ES68" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET68" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU68" t="n">
+        <v>0.01464063127144998</v>
+      </c>
+      <c r="EV68" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW68" t="n">
+        <v>-2.098778645534208e-05</v>
+      </c>
+      <c r="EX68" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY68" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ68" t="n">
+        <v>-0.0606187468156335</v>
+      </c>
+      <c r="FA68" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB68" t="n">
+        <v>-0.06319191230359124</v>
+      </c>
+      <c r="FC68" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD68" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE68" t="n">
+        <v>0.04289344924151425</v>
+      </c>
+      <c r="FF68" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG68" t="n">
+        <v>3.250866154013847e-05</v>
+      </c>
+      <c r="FH68" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI68" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ68" t="n">
+        <v>-0.1289927253317418</v>
+      </c>
+      <c r="FK68" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL68" t="n">
+        <v>-0.1389224037978428</v>
+      </c>
+      <c r="FM68" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN68" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO68" t="n">
+        <v>-0.01463331012582409</v>
+      </c>
+      <c r="FP68" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ68" t="n">
+        <v>-0.009499737557939158</v>
+      </c>
+      <c r="FR68" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS68" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT68" t="n">
+        <v>0.04123041033009264</v>
+      </c>
+      <c r="FU68" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV68" t="n">
+        <v>-8.013845277178172e-05</v>
+      </c>
+      <c r="FW68" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX68" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY68" t="n">
+        <v>0.05486375645114731</v>
+      </c>
+      <c r="FZ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA68" t="n">
+        <v>1.073675655924594e-05</v>
+      </c>
+      <c r="GB68" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC68" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD68" t="n">
+        <v>0.005877218271296521</v>
+      </c>
+      <c r="GE68" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF68" t="n">
+        <v>-9.528746559871079e-05</v>
+      </c>
+      <c r="GG68" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH68" t="n">
+        <v>0</v>
+      </c>
+      <c r="GI68" t="n">
+        <v>0.08709083663904106</v>
+      </c>
+      <c r="GJ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="GK68" t="n">
+        <v>0.00837805963903907</v>
+      </c>
+      <c r="GL68" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM68" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN68" t="n">
+        <v>-0.02188938483799282</v>
+      </c>
+      <c r="GO68" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP68" t="n">
+        <v>-0.01261204034709579</v>
+      </c>
+      <c r="GQ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR68" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS68" t="n">
+        <v>0.1614059374398114</v>
+      </c>
+      <c r="GT68" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU68" t="n">
+        <v>0.11924108276781</v>
+      </c>
+      <c r="GV68" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW68" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX68" t="n">
+        <v>-0.05949964923978149</v>
+      </c>
+      <c r="GY68" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ68" t="n">
+        <v>-0.06794766096089778</v>
+      </c>
+      <c r="HA68" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB68" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC68" t="n">
+        <v>0.03472636803484254</v>
+      </c>
+      <c r="HD68" t="n">
+        <v>0</v>
+      </c>
+      <c r="HE68" t="n">
+        <v>0.0002567464447288758</v>
+      </c>
+      <c r="HF68" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG68" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH68" t="n">
+        <v>-0.02395521864642743</v>
+      </c>
+      <c r="HI68" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ68" t="n">
+        <v>-0.0008842991680324257</v>
+      </c>
+      <c r="HK68" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL68" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM68" t="n">
+        <v>0.06622564460675992</v>
+      </c>
+      <c r="HN68" t="n">
+        <v>0</v>
+      </c>
+      <c r="HO68" t="n">
+        <v>1.923848794140434e-05</v>
+      </c>
+      <c r="HP68" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR68" t="n">
+        <v>-0.03327358386716624</v>
+      </c>
+      <c r="HS68" t="n">
+        <v>0</v>
+      </c>
+      <c r="HT68" t="n">
+        <v>-0.02936102298166333</v>
+      </c>
+      <c r="HU68" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV68" t="n">
+        <v>0</v>
+      </c>
+      <c r="HW68" t="n">
+        <v>0.07269636195991007</v>
+      </c>
+      <c r="HX68" t="n">
+        <v>0</v>
+      </c>
+      <c r="HY68" t="n">
+        <v>1.603012680683574e-05</v>
+      </c>
+      <c r="HZ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA68" t="n">
+        <v>0</v>
+      </c>
+      <c r="IB68" t="n">
+        <v>0.02590808995200147</v>
+      </c>
+      <c r="IC68" t="n">
+        <v>0</v>
+      </c>
+      <c r="ID68" t="n">
+        <v>0.0005437636156452633</v>
+      </c>
+      <c r="IE68" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF68" t="n">
+        <v>0</v>
+      </c>
+      <c r="IG68" t="n">
+        <v>0.07780634056129608</v>
+      </c>
+      <c r="IH68" t="n">
+        <v>0</v>
+      </c>
+      <c r="II68" t="n">
+        <v>-9.304177792006006e-06</v>
+      </c>
+      <c r="IJ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK68" t="n">
+        <v>0</v>
+      </c>
+      <c r="IL68" t="n">
+        <v>0.1300971904710841</v>
+      </c>
+      <c r="IM68" t="n">
+        <v>0</v>
+      </c>
+      <c r="IN68" t="n">
+        <v>0.0634232896674146</v>
+      </c>
+      <c r="IO68" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP68" t="n">
+        <v>0</v>
+      </c>
+      <c r="IQ68" t="n">
+        <v>0.05745171897626637</v>
+      </c>
+      <c r="IR68" t="n">
+        <v>0</v>
+      </c>
+      <c r="IS68" t="n">
+        <v>0.0001951696921460128</v>
+      </c>
+      <c r="IT68" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU68" t="n">
+        <v>0</v>
+      </c>
+      <c r="IV68" t="n">
+        <v>0.08407539107462275</v>
+      </c>
+      <c r="IW68" t="n">
+        <v>0</v>
+      </c>
+      <c r="IX68" t="n">
+        <v>0.0004739608035766706</v>
+      </c>
+      <c r="IY68" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA68" t="n">
+        <v>0.09464502534016593</v>
+      </c>
+      <c r="JB68" t="n">
+        <v>0</v>
+      </c>
+      <c r="JC68" t="n">
+        <v>0.01666591981202987</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:43:03</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>10</v>
+      </c>
+      <c r="C69" t="n">
+        <v>100</v>
+      </c>
+      <c r="D69" t="n">
+        <v>50</v>
+      </c>
+      <c r="E69" t="n">
+        <v>400</v>
+      </c>
+      <c r="F69" t="n">
+        <v>5</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>0.1487463411476649</v>
+      </c>
+      <c r="I69" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.9596156156156157</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0.9629130882846779</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.1509138080277019</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.1638410526596532</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0.4264346755836849</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0.3631989533648214</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0.4420851994763379</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0.4172119141707926</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0.4135526033873967</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0.3727893422914855</v>
+      </c>
+      <c r="V69" t="n">
+        <v>0.4059681803076974</v>
+      </c>
+      <c r="W69" t="n">
+        <v>0.416452325212114</v>
+      </c>
+      <c r="X69" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>0.4840755319824488</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>0.4428523380273526</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>0.4663287352087873</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>0.484945010338912</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>0.5415529615307106</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>0.4506576168140828</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>0.5497983327157687</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>0.5229523376160061</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>0.3457151730609604</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>0.3529636884047206</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>0.3464243309052601</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>0.3644928121179202</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>0.03274553505200609</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ69" t="n">
+        <v>1.416037333045412e-05</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>0.08989347990703102</v>
+      </c>
+      <c r="AU69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV69" t="n">
+        <v>-5.118921100548514e-06</v>
+      </c>
+      <c r="AW69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY69" t="n">
+        <v>-0.001066349099301714</v>
+      </c>
+      <c r="AZ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA69" t="n">
+        <v>-3.513428236009097e-05</v>
+      </c>
+      <c r="BB69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD69" t="n">
+        <v>0.003724115605215337</v>
+      </c>
+      <c r="BE69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF69" t="n">
+        <v>-6.451094961079803e-05</v>
+      </c>
+      <c r="BG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI69" t="n">
+        <v>0.1123178125501612</v>
+      </c>
+      <c r="BJ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK69" t="n">
+        <v>0.0002063766842205601</v>
+      </c>
+      <c r="BL69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN69" t="n">
+        <v>0.09617491420839436</v>
+      </c>
+      <c r="BO69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP69" t="n">
+        <v>2.086258693117533e-05</v>
+      </c>
+      <c r="BQ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS69" t="n">
+        <v>0.02178726416297033</v>
+      </c>
+      <c r="BT69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU69" t="n">
+        <v>5.796804744927903e-05</v>
+      </c>
+      <c r="BV69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX69" t="n">
+        <v>0.1092321448721939</v>
+      </c>
+      <c r="BY69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ69" t="n">
+        <v>8.60714630240543e-05</v>
+      </c>
+      <c r="CA69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC69" t="n">
+        <v>0.03145742493396329</v>
+      </c>
+      <c r="CD69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE69" t="n">
+        <v>-7.551243701340494e-06</v>
+      </c>
+      <c r="CF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH69" t="n">
+        <v>0.04800172339669577</v>
+      </c>
+      <c r="CI69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ69" t="n">
+        <v>1.196470430210083e-05</v>
+      </c>
+      <c r="CK69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM69" t="n">
+        <v>0.06772401197518638</v>
+      </c>
+      <c r="CN69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO69" t="n">
+        <v>7.224393113178503e-06</v>
+      </c>
+      <c r="CP69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR69" t="n">
+        <v>0.1040200513524011</v>
+      </c>
+      <c r="CS69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT69" t="n">
+        <v>3.135902548343794e-05</v>
+      </c>
+      <c r="CU69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW69" t="n">
+        <v>0.00129071713135928</v>
+      </c>
+      <c r="CX69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY69" t="n">
+        <v>5.807104493624104e-06</v>
+      </c>
+      <c r="CZ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA69" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB69" t="n">
+        <v>0.07865404522322589</v>
+      </c>
+      <c r="DC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD69" t="n">
+        <v>0.0001526681403661669</v>
+      </c>
+      <c r="DE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG69" t="n">
+        <v>0.05939931194710104</v>
+      </c>
+      <c r="DH69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI69" t="n">
+        <v>1.226238473389266e-05</v>
+      </c>
+      <c r="DJ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL69" t="n">
+        <v>0.008143156435312434</v>
+      </c>
+      <c r="DM69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN69" t="n">
+        <v>3.961425224824349e-06</v>
+      </c>
+      <c r="DO69" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP69" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ69" t="n">
+        <v>0.07308643878290462</v>
+      </c>
+      <c r="DR69" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS69" t="n">
+        <v>1.03267778421697e-06</v>
+      </c>
+      <c r="DT69" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV69" t="n">
+        <v>0.06738589146081003</v>
+      </c>
+      <c r="DW69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX69" t="n">
+        <v>-1.464848124137013e-05</v>
+      </c>
+      <c r="DY69" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA69" t="n">
+        <v>0.04867778281533248</v>
+      </c>
+      <c r="EB69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EC69" t="n">
+        <v>-1.721245648697206e-05</v>
+      </c>
+      <c r="ED69" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF69" t="n">
+        <v>0.01226679541426947</v>
+      </c>
+      <c r="EG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH69" t="n">
+        <v>-2.822467664184084e-05</v>
+      </c>
+      <c r="EI69" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK69" t="n">
+        <v>-0.004253397733579068</v>
+      </c>
+      <c r="EL69" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM69" t="n">
+        <v>4.130640677779554e-06</v>
+      </c>
+      <c r="EN69" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO69" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP69" t="n">
+        <v>-0.0214507982942831</v>
+      </c>
+      <c r="EQ69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER69" t="n">
+        <v>-4.275784188696047e-05</v>
+      </c>
+      <c r="ES69" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU69" t="n">
+        <v>0.01464063127144998</v>
+      </c>
+      <c r="EV69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW69" t="n">
+        <v>-8.28241280239517e-06</v>
+      </c>
+      <c r="EX69" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ69" t="n">
+        <v>-0.0606187468156335</v>
+      </c>
+      <c r="FA69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB69" t="n">
+        <v>-6.668065581172057e-05</v>
+      </c>
+      <c r="FC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE69" t="n">
+        <v>0.04289344924151425</v>
+      </c>
+      <c r="FF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG69" t="n">
+        <v>6.785097207052384e-06</v>
+      </c>
+      <c r="FH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ69" t="n">
+        <v>-0.1289927253317418</v>
+      </c>
+      <c r="FK69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL69" t="n">
+        <v>-0.06763325675082377</v>
+      </c>
+      <c r="FM69" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO69" t="n">
+        <v>-0.01463331012582409</v>
+      </c>
+      <c r="FP69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ69" t="n">
+        <v>-6.878839833613235e-05</v>
+      </c>
+      <c r="FR69" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT69" t="n">
+        <v>0.04123041033009264</v>
+      </c>
+      <c r="FU69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FV69" t="n">
+        <v>-2.757026067083453e-05</v>
+      </c>
+      <c r="FW69" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY69" t="n">
+        <v>0.05486375645114731</v>
+      </c>
+      <c r="FZ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA69" t="n">
+        <v>6.396150952936333e-06</v>
+      </c>
+      <c r="GB69" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD69" t="n">
+        <v>0.005877218271296521</v>
+      </c>
+      <c r="GE69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF69" t="n">
+        <v>-2.735722718354725e-05</v>
+      </c>
+      <c r="GG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="GI69" t="n">
+        <v>0.08709083663904106</v>
+      </c>
+      <c r="GJ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="GK69" t="n">
+        <v>3.942389606518657e-05</v>
+      </c>
+      <c r="GL69" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GN69" t="n">
+        <v>-0.02188938483799282</v>
+      </c>
+      <c r="GO69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GP69" t="n">
+        <v>-7.302568026417882e-06</v>
+      </c>
+      <c r="GQ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR69" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS69" t="n">
+        <v>0.1614059374398114</v>
+      </c>
+      <c r="GT69" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU69" t="n">
+        <v>0.07964333006014741</v>
+      </c>
+      <c r="GV69" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GX69" t="n">
+        <v>-0.05949964923978149</v>
+      </c>
+      <c r="GY69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GZ69" t="n">
+        <v>-0.008789671037433821</v>
+      </c>
+      <c r="HA69" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB69" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC69" t="n">
+        <v>0.03472636803484254</v>
+      </c>
+      <c r="HD69" t="n">
+        <v>0</v>
+      </c>
+      <c r="HE69" t="n">
+        <v>7.382408540549761e-05</v>
+      </c>
+      <c r="HF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="HH69" t="n">
+        <v>-0.02395521864642743</v>
+      </c>
+      <c r="HI69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="HJ69" t="n">
+        <v>-6.799683141396897e-05</v>
+      </c>
+      <c r="HK69" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="HM69" t="n">
+        <v>0.06622564460675992</v>
+      </c>
+      <c r="HN69" t="n">
+        <v>0</v>
+      </c>
+      <c r="HO69" t="n">
+        <v>1.307383288728478e-06</v>
+      </c>
+      <c r="HP69" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="HR69" t="n">
+        <v>-0.03327358386716624</v>
+      </c>
+      <c r="HS69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="HT69" t="n">
+        <v>-0.0002485886090894331</v>
+      </c>
+      <c r="HU69" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV69" t="n">
+        <v>0</v>
+      </c>
+      <c r="HW69" t="n">
+        <v>0.07269636195991007</v>
+      </c>
+      <c r="HX69" t="n">
+        <v>0</v>
+      </c>
+      <c r="HY69" t="n">
+        <v>4.394735648404702e-06</v>
+      </c>
+      <c r="HZ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA69" t="n">
+        <v>0</v>
+      </c>
+      <c r="IB69" t="n">
+        <v>0.02590808995200147</v>
+      </c>
+      <c r="IC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="ID69" t="n">
+        <v>0.0001681958147648326</v>
+      </c>
+      <c r="IE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="IG69" t="n">
+        <v>0.07780634056129608</v>
+      </c>
+      <c r="IH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="II69" t="n">
+        <v>-2.188994579808497e-06</v>
+      </c>
+      <c r="IJ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK69" t="n">
+        <v>0</v>
+      </c>
+      <c r="IL69" t="n">
+        <v>0.1300971904710841</v>
+      </c>
+      <c r="IM69" t="n">
+        <v>0</v>
+      </c>
+      <c r="IN69" t="n">
+        <v>7.793038195774311e-05</v>
+      </c>
+      <c r="IO69" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP69" t="n">
+        <v>0</v>
+      </c>
+      <c r="IQ69" t="n">
+        <v>0.05745171897626637</v>
+      </c>
+      <c r="IR69" t="n">
+        <v>0</v>
+      </c>
+      <c r="IS69" t="n">
+        <v>6.057500708343093e-05</v>
+      </c>
+      <c r="IT69" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU69" t="n">
+        <v>0</v>
+      </c>
+      <c r="IV69" t="n">
+        <v>0.08407539107462275</v>
+      </c>
+      <c r="IW69" t="n">
+        <v>0</v>
+      </c>
+      <c r="IX69" t="n">
+        <v>1.911361494070111e-06</v>
+      </c>
+      <c r="IY69" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="JA69" t="n">
+        <v>0.09464502534016593</v>
+      </c>
+      <c r="JB69" t="n">
+        <v>0</v>
+      </c>
+      <c r="JC69" t="n">
+        <v>6.101490173532565e-05</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ranking/results.xlsx
+++ b/ranking/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JC69"/>
+  <dimension ref="A1:JD72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1744,6 +1744,11 @@
           <t>theta_49_dgd</t>
         </is>
       </c>
+      <c r="JD1" s="1" t="inlineStr">
+        <is>
+          <t>W_inner</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2539,6 +2544,7 @@
       <c r="JC2" t="n">
         <v>0.09899675505170645</v>
       </c>
+      <c r="JD2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3028,6 +3034,7 @@
       <c r="JA3" t="inlineStr"/>
       <c r="JB3" t="inlineStr"/>
       <c r="JC3" t="inlineStr"/>
+      <c r="JD3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3517,6 +3524,7 @@
       <c r="JA4" t="inlineStr"/>
       <c r="JB4" t="inlineStr"/>
       <c r="JC4" t="inlineStr"/>
+      <c r="JD4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4006,6 +4014,7 @@
       <c r="JA5" t="inlineStr"/>
       <c r="JB5" t="inlineStr"/>
       <c r="JC5" t="inlineStr"/>
+      <c r="JD5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4495,6 +4504,7 @@
       <c r="JA6" t="inlineStr"/>
       <c r="JB6" t="inlineStr"/>
       <c r="JC6" t="inlineStr"/>
+      <c r="JD6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4984,6 +4994,7 @@
       <c r="JA7" t="inlineStr"/>
       <c r="JB7" t="inlineStr"/>
       <c r="JC7" t="inlineStr"/>
+      <c r="JD7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5473,6 +5484,7 @@
       <c r="JA8" t="inlineStr"/>
       <c r="JB8" t="inlineStr"/>
       <c r="JC8" t="inlineStr"/>
+      <c r="JD8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5962,6 +5974,7 @@
       <c r="JA9" t="inlineStr"/>
       <c r="JB9" t="inlineStr"/>
       <c r="JC9" t="inlineStr"/>
+      <c r="JD9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6451,6 +6464,7 @@
       <c r="JA10" t="inlineStr"/>
       <c r="JB10" t="inlineStr"/>
       <c r="JC10" t="inlineStr"/>
+      <c r="JD10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6940,6 +6954,7 @@
       <c r="JA11" t="inlineStr"/>
       <c r="JB11" t="inlineStr"/>
       <c r="JC11" t="inlineStr"/>
+      <c r="JD11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7429,6 +7444,7 @@
       <c r="JA12" t="inlineStr"/>
       <c r="JB12" t="inlineStr"/>
       <c r="JC12" t="inlineStr"/>
+      <c r="JD12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7918,6 +7934,7 @@
       <c r="JA13" t="inlineStr"/>
       <c r="JB13" t="inlineStr"/>
       <c r="JC13" t="inlineStr"/>
+      <c r="JD13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8407,6 +8424,7 @@
       <c r="JA14" t="inlineStr"/>
       <c r="JB14" t="inlineStr"/>
       <c r="JC14" t="inlineStr"/>
+      <c r="JD14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8896,6 +8914,7 @@
       <c r="JA15" t="inlineStr"/>
       <c r="JB15" t="inlineStr"/>
       <c r="JC15" t="inlineStr"/>
+      <c r="JD15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9385,6 +9404,7 @@
       <c r="JA16" t="inlineStr"/>
       <c r="JB16" t="inlineStr"/>
       <c r="JC16" t="inlineStr"/>
+      <c r="JD16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9874,6 +9894,7 @@
       <c r="JA17" t="inlineStr"/>
       <c r="JB17" t="inlineStr"/>
       <c r="JC17" t="inlineStr"/>
+      <c r="JD17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -10363,6 +10384,7 @@
       <c r="JA18" t="inlineStr"/>
       <c r="JB18" t="inlineStr"/>
       <c r="JC18" t="inlineStr"/>
+      <c r="JD18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10852,6 +10874,7 @@
       <c r="JA19" t="inlineStr"/>
       <c r="JB19" t="inlineStr"/>
       <c r="JC19" t="inlineStr"/>
+      <c r="JD19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -11341,6 +11364,7 @@
       <c r="JA20" t="inlineStr"/>
       <c r="JB20" t="inlineStr"/>
       <c r="JC20" t="inlineStr"/>
+      <c r="JD20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -11830,6 +11854,7 @@
       <c r="JA21" t="inlineStr"/>
       <c r="JB21" t="inlineStr"/>
       <c r="JC21" t="inlineStr"/>
+      <c r="JD21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -12319,6 +12344,7 @@
       <c r="JA22" t="inlineStr"/>
       <c r="JB22" t="inlineStr"/>
       <c r="JC22" t="inlineStr"/>
+      <c r="JD22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -12808,6 +12834,7 @@
       <c r="JA23" t="inlineStr"/>
       <c r="JB23" t="inlineStr"/>
       <c r="JC23" t="inlineStr"/>
+      <c r="JD23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -13297,6 +13324,7 @@
       <c r="JA24" t="inlineStr"/>
       <c r="JB24" t="inlineStr"/>
       <c r="JC24" t="inlineStr"/>
+      <c r="JD24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -13786,6 +13814,7 @@
       <c r="JA25" t="inlineStr"/>
       <c r="JB25" t="inlineStr"/>
       <c r="JC25" t="inlineStr"/>
+      <c r="JD25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -14275,6 +14304,7 @@
       <c r="JA26" t="inlineStr"/>
       <c r="JB26" t="inlineStr"/>
       <c r="JC26" t="inlineStr"/>
+      <c r="JD26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -14764,6 +14794,7 @@
       <c r="JA27" t="inlineStr"/>
       <c r="JB27" t="inlineStr"/>
       <c r="JC27" t="inlineStr"/>
+      <c r="JD27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -15253,6 +15284,7 @@
       <c r="JA28" t="inlineStr"/>
       <c r="JB28" t="inlineStr"/>
       <c r="JC28" t="inlineStr"/>
+      <c r="JD28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -15742,6 +15774,7 @@
       <c r="JA29" t="inlineStr"/>
       <c r="JB29" t="inlineStr"/>
       <c r="JC29" t="inlineStr"/>
+      <c r="JD29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -16231,6 +16264,7 @@
       <c r="JA30" t="inlineStr"/>
       <c r="JB30" t="inlineStr"/>
       <c r="JC30" t="inlineStr"/>
+      <c r="JD30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -16720,6 +16754,7 @@
       <c r="JA31" t="inlineStr"/>
       <c r="JB31" t="inlineStr"/>
       <c r="JC31" t="inlineStr"/>
+      <c r="JD31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -17209,6 +17244,7 @@
       <c r="JA32" t="inlineStr"/>
       <c r="JB32" t="inlineStr"/>
       <c r="JC32" t="inlineStr"/>
+      <c r="JD32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -17698,6 +17734,7 @@
       <c r="JA33" t="inlineStr"/>
       <c r="JB33" t="inlineStr"/>
       <c r="JC33" t="inlineStr"/>
+      <c r="JD33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -18187,6 +18224,7 @@
       <c r="JA34" t="inlineStr"/>
       <c r="JB34" t="inlineStr"/>
       <c r="JC34" t="inlineStr"/>
+      <c r="JD34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -18676,6 +18714,7 @@
       <c r="JA35" t="inlineStr"/>
       <c r="JB35" t="inlineStr"/>
       <c r="JC35" t="inlineStr"/>
+      <c r="JD35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -19165,6 +19204,7 @@
       <c r="JA36" t="inlineStr"/>
       <c r="JB36" t="inlineStr"/>
       <c r="JC36" t="inlineStr"/>
+      <c r="JD36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -19654,6 +19694,7 @@
       <c r="JA37" t="inlineStr"/>
       <c r="JB37" t="inlineStr"/>
       <c r="JC37" t="inlineStr"/>
+      <c r="JD37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -20143,6 +20184,7 @@
       <c r="JA38" t="inlineStr"/>
       <c r="JB38" t="inlineStr"/>
       <c r="JC38" t="inlineStr"/>
+      <c r="JD38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -20632,6 +20674,7 @@
       <c r="JA39" t="inlineStr"/>
       <c r="JB39" t="inlineStr"/>
       <c r="JC39" t="inlineStr"/>
+      <c r="JD39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -21121,6 +21164,7 @@
       <c r="JA40" t="inlineStr"/>
       <c r="JB40" t="inlineStr"/>
       <c r="JC40" t="inlineStr"/>
+      <c r="JD40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -21916,6 +21960,7 @@
       <c r="JC41" t="n">
         <v>0</v>
       </c>
+      <c r="JD41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -22711,6 +22756,7 @@
       <c r="JC42" t="n">
         <v>1.521290203721152e-05</v>
       </c>
+      <c r="JD42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -23200,6 +23246,7 @@
       <c r="JA43" t="inlineStr"/>
       <c r="JB43" t="inlineStr"/>
       <c r="JC43" t="inlineStr"/>
+      <c r="JD43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -23689,6 +23736,7 @@
       <c r="JA44" t="inlineStr"/>
       <c r="JB44" t="inlineStr"/>
       <c r="JC44" t="inlineStr"/>
+      <c r="JD44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -24178,6 +24226,7 @@
       <c r="JA45" t="inlineStr"/>
       <c r="JB45" t="inlineStr"/>
       <c r="JC45" t="inlineStr"/>
+      <c r="JD45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -24667,6 +24716,7 @@
       <c r="JA46" t="inlineStr"/>
       <c r="JB46" t="inlineStr"/>
       <c r="JC46" t="inlineStr"/>
+      <c r="JD46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -25156,6 +25206,7 @@
       <c r="JA47" t="inlineStr"/>
       <c r="JB47" t="inlineStr"/>
       <c r="JC47" t="inlineStr"/>
+      <c r="JD47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -25645,6 +25696,7 @@
       <c r="JA48" t="inlineStr"/>
       <c r="JB48" t="inlineStr"/>
       <c r="JC48" t="inlineStr"/>
+      <c r="JD48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -26134,6 +26186,7 @@
       <c r="JA49" t="inlineStr"/>
       <c r="JB49" t="inlineStr"/>
       <c r="JC49" t="inlineStr"/>
+      <c r="JD49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -26623,6 +26676,7 @@
       <c r="JA50" t="inlineStr"/>
       <c r="JB50" t="inlineStr"/>
       <c r="JC50" t="inlineStr"/>
+      <c r="JD50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -27112,6 +27166,7 @@
       <c r="JA51" t="inlineStr"/>
       <c r="JB51" t="inlineStr"/>
       <c r="JC51" t="inlineStr"/>
+      <c r="JD51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -27601,6 +27656,7 @@
       <c r="JA52" t="inlineStr"/>
       <c r="JB52" t="inlineStr"/>
       <c r="JC52" t="inlineStr"/>
+      <c r="JD52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -28090,6 +28146,7 @@
       <c r="JA53" t="inlineStr"/>
       <c r="JB53" t="inlineStr"/>
       <c r="JC53" t="inlineStr"/>
+      <c r="JD53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -28579,6 +28636,7 @@
       <c r="JA54" t="inlineStr"/>
       <c r="JB54" t="inlineStr"/>
       <c r="JC54" t="inlineStr"/>
+      <c r="JD54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -29068,6 +29126,7 @@
       <c r="JA55" t="inlineStr"/>
       <c r="JB55" t="inlineStr"/>
       <c r="JC55" t="inlineStr"/>
+      <c r="JD55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -29557,6 +29616,7 @@
       <c r="JA56" t="inlineStr"/>
       <c r="JB56" t="inlineStr"/>
       <c r="JC56" t="inlineStr"/>
+      <c r="JD56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -30046,6 +30106,7 @@
       <c r="JA57" t="inlineStr"/>
       <c r="JB57" t="inlineStr"/>
       <c r="JC57" t="inlineStr"/>
+      <c r="JD57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -30535,6 +30596,7 @@
       <c r="JA58" t="inlineStr"/>
       <c r="JB58" t="inlineStr"/>
       <c r="JC58" t="inlineStr"/>
+      <c r="JD58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -31024,6 +31086,7 @@
       <c r="JA59" t="inlineStr"/>
       <c r="JB59" t="inlineStr"/>
       <c r="JC59" t="inlineStr"/>
+      <c r="JD59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -31513,6 +31576,7 @@
       <c r="JA60" t="inlineStr"/>
       <c r="JB60" t="inlineStr"/>
       <c r="JC60" t="inlineStr"/>
+      <c r="JD60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -32002,6 +32066,7 @@
       <c r="JA61" t="inlineStr"/>
       <c r="JB61" t="inlineStr"/>
       <c r="JC61" t="inlineStr"/>
+      <c r="JD61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -32491,6 +32556,7 @@
       <c r="JA62" t="inlineStr"/>
       <c r="JB62" t="inlineStr"/>
       <c r="JC62" t="inlineStr"/>
+      <c r="JD62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -32980,6 +33046,7 @@
       <c r="JA63" t="inlineStr"/>
       <c r="JB63" t="inlineStr"/>
       <c r="JC63" t="inlineStr"/>
+      <c r="JD63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -33469,6 +33536,7 @@
       <c r="JA64" t="inlineStr"/>
       <c r="JB64" t="inlineStr"/>
       <c r="JC64" t="inlineStr"/>
+      <c r="JD64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -33958,6 +34026,7 @@
       <c r="JA65" t="inlineStr"/>
       <c r="JB65" t="inlineStr"/>
       <c r="JC65" t="inlineStr"/>
+      <c r="JD65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -34447,6 +34516,7 @@
       <c r="JA66" t="inlineStr"/>
       <c r="JB66" t="inlineStr"/>
       <c r="JC66" t="inlineStr"/>
+      <c r="JD66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -35242,6 +35312,7 @@
       <c r="JC67" t="n">
         <v>0.1201190150947564</v>
       </c>
+      <c r="JD67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -36037,6 +36108,7 @@
       <c r="JC68" t="n">
         <v>0.01666591981202987</v>
       </c>
+      <c r="JD68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -36212,7 +36284,7 @@
         <v>0.003724115605215337</v>
       </c>
       <c r="BE69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF69" t="n">
         <v>-6.451094961079803e-05</v>
@@ -36236,7 +36308,7 @@
         <v>0</v>
       </c>
       <c r="BM69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN69" t="n">
         <v>0.09617491420839436</v>
@@ -36251,7 +36323,7 @@
         <v>0</v>
       </c>
       <c r="BR69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS69" t="n">
         <v>0.02178726416297033</v>
@@ -36266,7 +36338,7 @@
         <v>0</v>
       </c>
       <c r="BW69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX69" t="n">
         <v>0.1092321448721939</v>
@@ -36281,7 +36353,7 @@
         <v>0</v>
       </c>
       <c r="CB69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC69" t="n">
         <v>0.03145742493396329</v>
@@ -36296,7 +36368,7 @@
         <v>0</v>
       </c>
       <c r="CG69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH69" t="n">
         <v>0.04800172339669577</v>
@@ -36311,7 +36383,7 @@
         <v>0</v>
       </c>
       <c r="CL69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM69" t="n">
         <v>0.06772401197518638</v>
@@ -36371,13 +36443,13 @@
         <v>0</v>
       </c>
       <c r="DF69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG69" t="n">
         <v>0.05939931194710104</v>
       </c>
       <c r="DH69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI69" t="n">
         <v>1.226238473389266e-05</v>
@@ -36386,13 +36458,13 @@
         <v>0</v>
       </c>
       <c r="DK69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL69" t="n">
         <v>0.008143156435312434</v>
       </c>
       <c r="DM69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN69" t="n">
         <v>3.961425224824349e-06</v>
@@ -36416,13 +36488,13 @@
         <v>0</v>
       </c>
       <c r="DU69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV69" t="n">
         <v>0.06738589146081003</v>
       </c>
       <c r="DW69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX69" t="n">
         <v>-1.464848124137013e-05</v>
@@ -36437,7 +36509,7 @@
         <v>0.04867778281533248</v>
       </c>
       <c r="EB69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC69" t="n">
         <v>-1.721245648697206e-05</v>
@@ -36446,7 +36518,7 @@
         <v>0</v>
       </c>
       <c r="EE69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF69" t="n">
         <v>0.01226679541426947</v>
@@ -36461,7 +36533,7 @@
         <v>0</v>
       </c>
       <c r="EJ69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EK69" t="n">
         <v>-0.004253397733579068</v>
@@ -36482,7 +36554,7 @@
         <v>-0.0214507982942831</v>
       </c>
       <c r="EQ69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER69" t="n">
         <v>-4.275784188696047e-05</v>
@@ -36491,13 +36563,13 @@
         <v>0</v>
       </c>
       <c r="ET69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU69" t="n">
         <v>0.01464063127144998</v>
       </c>
       <c r="EV69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW69" t="n">
         <v>-8.28241280239517e-06</v>
@@ -36506,13 +36578,13 @@
         <v>0</v>
       </c>
       <c r="EY69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EZ69" t="n">
         <v>-0.0606187468156335</v>
       </c>
       <c r="FA69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB69" t="n">
         <v>-6.668065581172057e-05</v>
@@ -36521,7 +36593,7 @@
         <v>0</v>
       </c>
       <c r="FD69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE69" t="n">
         <v>0.04289344924151425</v>
@@ -36536,13 +36608,13 @@
         <v>0</v>
       </c>
       <c r="FI69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ69" t="n">
         <v>-0.1289927253317418</v>
       </c>
       <c r="FK69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FL69" t="n">
         <v>-0.06763325675082377</v>
@@ -36551,13 +36623,13 @@
         <v>0</v>
       </c>
       <c r="FN69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO69" t="n">
         <v>-0.01463331012582409</v>
       </c>
       <c r="FP69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ69" t="n">
         <v>-6.878839833613235e-05</v>
@@ -36566,13 +36638,13 @@
         <v>0</v>
       </c>
       <c r="FS69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT69" t="n">
         <v>0.04123041033009264</v>
       </c>
       <c r="FU69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV69" t="n">
         <v>-2.757026067083453e-05</v>
@@ -36581,7 +36653,7 @@
         <v>0</v>
       </c>
       <c r="FX69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY69" t="n">
         <v>0.05486375645114731</v>
@@ -36602,7 +36674,7 @@
         <v>0.005877218271296521</v>
       </c>
       <c r="GE69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF69" t="n">
         <v>-2.735722718354725e-05</v>
@@ -36626,13 +36698,13 @@
         <v>0</v>
       </c>
       <c r="GM69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GN69" t="n">
         <v>-0.02188938483799282</v>
       </c>
       <c r="GO69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GP69" t="n">
         <v>-7.302568026417882e-06</v>
@@ -36656,13 +36728,13 @@
         <v>0</v>
       </c>
       <c r="GW69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GX69" t="n">
         <v>-0.05949964923978149</v>
       </c>
       <c r="GY69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GZ69" t="n">
         <v>-0.008789671037433821</v>
@@ -36686,13 +36758,13 @@
         <v>0</v>
       </c>
       <c r="HG69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="HH69" t="n">
         <v>-0.02395521864642743</v>
       </c>
       <c r="HI69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="HJ69" t="n">
         <v>-6.799683141396897e-05</v>
@@ -36701,7 +36773,7 @@
         <v>0</v>
       </c>
       <c r="HL69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="HM69" t="n">
         <v>0.06622564460675992</v>
@@ -36716,13 +36788,13 @@
         <v>0</v>
       </c>
       <c r="HQ69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="HR69" t="n">
         <v>-0.03327358386716624</v>
       </c>
       <c r="HS69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="HT69" t="n">
         <v>-0.0002485886090894331</v>
@@ -36821,7 +36893,7 @@
         <v>0</v>
       </c>
       <c r="IZ69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="JA69" t="n">
         <v>0.09464502534016593</v>
@@ -36831,6 +36903,1783 @@
       </c>
       <c r="JC69" t="n">
         <v>6.101490173532565e-05</v>
+      </c>
+      <c r="JD69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-04-20 20:28:39</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>10</v>
+      </c>
+      <c r="C70" t="n">
+        <v>100</v>
+      </c>
+      <c r="D70" t="n">
+        <v>50</v>
+      </c>
+      <c r="E70" t="n">
+        <v>40</v>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>exp</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>0.1251436123068011</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.9587027027027027</v>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="n">
+        <v>0.1643965840185594</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0.4227645714217698</v>
+      </c>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="n">
+        <v>0.4536182413498976</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0.4476057660138444</v>
+      </c>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="n">
+        <v>0.4682029914119304</v>
+      </c>
+      <c r="X70" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>0.3903109310406991</v>
+      </c>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr"/>
+      <c r="AB70" t="n">
+        <v>0.3013370522744404</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>0.4628547114227459</v>
+      </c>
+      <c r="AE70" t="inlineStr"/>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="n">
+        <v>0.4651808420767356</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>0.4950225526075757</v>
+      </c>
+      <c r="AJ70" t="inlineStr"/>
+      <c r="AK70" t="inlineStr"/>
+      <c r="AL70" t="n">
+        <v>0.5175120648629646</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO70" t="inlineStr"/>
+      <c r="AP70" t="inlineStr"/>
+      <c r="AQ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AU70" t="inlineStr"/>
+      <c r="AV70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr"/>
+      <c r="BA70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD70" t="inlineStr"/>
+      <c r="BE70" t="inlineStr"/>
+      <c r="BF70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI70" t="inlineStr"/>
+      <c r="BJ70" t="inlineStr"/>
+      <c r="BK70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM70" t="n">
+        <v>0.01142490100407152</v>
+      </c>
+      <c r="BN70" t="inlineStr"/>
+      <c r="BO70" t="inlineStr"/>
+      <c r="BP70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR70" t="n">
+        <v>0.04335391656419746</v>
+      </c>
+      <c r="BS70" t="inlineStr"/>
+      <c r="BT70" t="inlineStr"/>
+      <c r="BU70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX70" t="inlineStr"/>
+      <c r="BY70" t="inlineStr"/>
+      <c r="BZ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC70" t="inlineStr"/>
+      <c r="CD70" t="inlineStr"/>
+      <c r="CE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH70" t="inlineStr"/>
+      <c r="CI70" t="inlineStr"/>
+      <c r="CJ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL70" t="n">
+        <v>0.009399380166522486</v>
+      </c>
+      <c r="CM70" t="inlineStr"/>
+      <c r="CN70" t="inlineStr"/>
+      <c r="CO70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ70" t="n">
+        <v>0.009784119489788528</v>
+      </c>
+      <c r="CR70" t="inlineStr"/>
+      <c r="CS70" t="inlineStr"/>
+      <c r="CT70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW70" t="inlineStr"/>
+      <c r="CX70" t="inlineStr"/>
+      <c r="CY70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA70" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB70" t="inlineStr"/>
+      <c r="DC70" t="inlineStr"/>
+      <c r="DD70" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF70" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG70" t="inlineStr"/>
+      <c r="DH70" t="inlineStr"/>
+      <c r="DI70" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK70" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL70" t="inlineStr"/>
+      <c r="DM70" t="inlineStr"/>
+      <c r="DN70" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO70" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP70" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ70" t="inlineStr"/>
+      <c r="DR70" t="inlineStr"/>
+      <c r="DS70" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT70" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU70" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV70" t="inlineStr"/>
+      <c r="DW70" t="inlineStr"/>
+      <c r="DX70" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY70" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ70" t="n">
+        <v>0.0145829241280647</v>
+      </c>
+      <c r="EA70" t="inlineStr"/>
+      <c r="EB70" t="inlineStr"/>
+      <c r="EC70" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED70" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF70" t="inlineStr"/>
+      <c r="EG70" t="inlineStr"/>
+      <c r="EH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI70" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK70" t="inlineStr"/>
+      <c r="EL70" t="inlineStr"/>
+      <c r="EM70" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN70" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO70" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP70" t="inlineStr"/>
+      <c r="EQ70" t="inlineStr"/>
+      <c r="ER70" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES70" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET70" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU70" t="inlineStr"/>
+      <c r="EV70" t="inlineStr"/>
+      <c r="EW70" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX70" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY70" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ70" t="inlineStr"/>
+      <c r="FA70" t="inlineStr"/>
+      <c r="FB70" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC70" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD70" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE70" t="inlineStr"/>
+      <c r="FF70" t="inlineStr"/>
+      <c r="FG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI70" t="n">
+        <v>0.0152037483177902</v>
+      </c>
+      <c r="FJ70" t="inlineStr"/>
+      <c r="FK70" t="inlineStr"/>
+      <c r="FL70" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM70" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN70" t="n">
+        <v>0.01223262848496849</v>
+      </c>
+      <c r="FO70" t="inlineStr"/>
+      <c r="FP70" t="inlineStr"/>
+      <c r="FQ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR70" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS70" t="n">
+        <v>0.02996838538756586</v>
+      </c>
+      <c r="FT70" t="inlineStr"/>
+      <c r="FU70" t="inlineStr"/>
+      <c r="FV70" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW70" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX70" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY70" t="inlineStr"/>
+      <c r="FZ70" t="inlineStr"/>
+      <c r="GA70" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB70" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC70" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD70" t="inlineStr"/>
+      <c r="GE70" t="inlineStr"/>
+      <c r="GF70" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH70" t="n">
+        <v>0.05091715384987692</v>
+      </c>
+      <c r="GI70" t="inlineStr"/>
+      <c r="GJ70" t="inlineStr"/>
+      <c r="GK70" t="n">
+        <v>0</v>
+      </c>
+      <c r="GL70" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM70" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN70" t="inlineStr"/>
+      <c r="GO70" t="inlineStr"/>
+      <c r="GP70" t="n">
+        <v>0</v>
+      </c>
+      <c r="GQ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR70" t="n">
+        <v>0.03854382673323793</v>
+      </c>
+      <c r="GS70" t="inlineStr"/>
+      <c r="GT70" t="inlineStr"/>
+      <c r="GU70" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV70" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW70" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX70" t="inlineStr"/>
+      <c r="GY70" t="inlineStr"/>
+      <c r="GZ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="HA70" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB70" t="n">
+        <v>0.02629735766088426</v>
+      </c>
+      <c r="HC70" t="inlineStr"/>
+      <c r="HD70" t="inlineStr"/>
+      <c r="HE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="HF70" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG70" t="n">
+        <v>0.01676969468782597</v>
+      </c>
+      <c r="HH70" t="inlineStr"/>
+      <c r="HI70" t="inlineStr"/>
+      <c r="HJ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK70" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL70" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM70" t="inlineStr"/>
+      <c r="HN70" t="inlineStr"/>
+      <c r="HO70" t="n">
+        <v>0</v>
+      </c>
+      <c r="HP70" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ70" t="n">
+        <v>0.01569740142883769</v>
+      </c>
+      <c r="HR70" t="inlineStr"/>
+      <c r="HS70" t="inlineStr"/>
+      <c r="HT70" t="n">
+        <v>0</v>
+      </c>
+      <c r="HU70" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV70" t="n">
+        <v>0</v>
+      </c>
+      <c r="HW70" t="inlineStr"/>
+      <c r="HX70" t="inlineStr"/>
+      <c r="HY70" t="n">
+        <v>0</v>
+      </c>
+      <c r="HZ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA70" t="n">
+        <v>0</v>
+      </c>
+      <c r="IB70" t="inlineStr"/>
+      <c r="IC70" t="inlineStr"/>
+      <c r="ID70" t="n">
+        <v>0</v>
+      </c>
+      <c r="IE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF70" t="n">
+        <v>0</v>
+      </c>
+      <c r="IG70" t="inlineStr"/>
+      <c r="IH70" t="inlineStr"/>
+      <c r="II70" t="n">
+        <v>0</v>
+      </c>
+      <c r="IJ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK70" t="n">
+        <v>0.01765420746107408</v>
+      </c>
+      <c r="IL70" t="inlineStr"/>
+      <c r="IM70" t="inlineStr"/>
+      <c r="IN70" t="n">
+        <v>0</v>
+      </c>
+      <c r="IO70" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP70" t="n">
+        <v>0</v>
+      </c>
+      <c r="IQ70" t="inlineStr"/>
+      <c r="IR70" t="inlineStr"/>
+      <c r="IS70" t="n">
+        <v>0</v>
+      </c>
+      <c r="IT70" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU70" t="n">
+        <v>0</v>
+      </c>
+      <c r="IV70" t="inlineStr"/>
+      <c r="IW70" t="inlineStr"/>
+      <c r="IX70" t="n">
+        <v>0</v>
+      </c>
+      <c r="IY70" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA70" t="inlineStr"/>
+      <c r="JB70" t="inlineStr"/>
+      <c r="JC70" t="n">
+        <v>0</v>
+      </c>
+      <c r="JD70" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-04-20 20:30:41</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>10</v>
+      </c>
+      <c r="C71" t="n">
+        <v>100</v>
+      </c>
+      <c r="D71" t="n">
+        <v>50</v>
+      </c>
+      <c r="E71" t="n">
+        <v>40</v>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>0.3370658791072577</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.9160920920920921</v>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="n">
+        <v>0.3357806908995257</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0.2116385658378677</v>
+      </c>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="n">
+        <v>0.1401070282539275</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0.4483099162127231</v>
+      </c>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="n">
+        <v>0.5138408309950322</v>
+      </c>
+      <c r="X71" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>0.4582588207412475</v>
+      </c>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr"/>
+      <c r="AB71" t="n">
+        <v>0.445665023598454</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>0.3320980017148263</v>
+      </c>
+      <c r="AE71" t="inlineStr"/>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="n">
+        <v>0.444911147462784</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>0.6587390225478212</v>
+      </c>
+      <c r="AJ71" t="inlineStr"/>
+      <c r="AK71" t="inlineStr"/>
+      <c r="AL71" t="n">
+        <v>0.5654816845337634</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO71" t="inlineStr"/>
+      <c r="AP71" t="inlineStr"/>
+      <c r="AQ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS71" t="n">
+        <v>1.273591312310204e-05</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AU71" t="inlineStr"/>
+      <c r="AV71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr"/>
+      <c r="BA71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD71" t="inlineStr"/>
+      <c r="BE71" t="inlineStr"/>
+      <c r="BF71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI71" t="inlineStr"/>
+      <c r="BJ71" t="inlineStr"/>
+      <c r="BK71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN71" t="inlineStr"/>
+      <c r="BO71" t="inlineStr"/>
+      <c r="BP71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS71" t="inlineStr"/>
+      <c r="BT71" t="inlineStr"/>
+      <c r="BU71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW71" t="n">
+        <v>8.335421681426141e-05</v>
+      </c>
+      <c r="BX71" t="inlineStr"/>
+      <c r="BY71" t="inlineStr"/>
+      <c r="BZ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC71" t="inlineStr"/>
+      <c r="CD71" t="inlineStr"/>
+      <c r="CE71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH71" t="inlineStr"/>
+      <c r="CI71" t="inlineStr"/>
+      <c r="CJ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM71" t="inlineStr"/>
+      <c r="CN71" t="inlineStr"/>
+      <c r="CO71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR71" t="inlineStr"/>
+      <c r="CS71" t="inlineStr"/>
+      <c r="CT71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW71" t="inlineStr"/>
+      <c r="CX71" t="inlineStr"/>
+      <c r="CY71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA71" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB71" t="inlineStr"/>
+      <c r="DC71" t="inlineStr"/>
+      <c r="DD71" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE71" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF71" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG71" t="inlineStr"/>
+      <c r="DH71" t="inlineStr"/>
+      <c r="DI71" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK71" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL71" t="inlineStr"/>
+      <c r="DM71" t="inlineStr"/>
+      <c r="DN71" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO71" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP71" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ71" t="inlineStr"/>
+      <c r="DR71" t="inlineStr"/>
+      <c r="DS71" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT71" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU71" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV71" t="inlineStr"/>
+      <c r="DW71" t="inlineStr"/>
+      <c r="DX71" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY71" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA71" t="inlineStr"/>
+      <c r="EB71" t="inlineStr"/>
+      <c r="EC71" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED71" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE71" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF71" t="inlineStr"/>
+      <c r="EG71" t="inlineStr"/>
+      <c r="EH71" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI71" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK71" t="inlineStr"/>
+      <c r="EL71" t="inlineStr"/>
+      <c r="EM71" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN71" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO71" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP71" t="inlineStr"/>
+      <c r="EQ71" t="inlineStr"/>
+      <c r="ER71" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES71" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET71" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU71" t="inlineStr"/>
+      <c r="EV71" t="inlineStr"/>
+      <c r="EW71" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX71" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY71" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ71" t="inlineStr"/>
+      <c r="FA71" t="inlineStr"/>
+      <c r="FB71" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC71" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD71" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE71" t="inlineStr"/>
+      <c r="FF71" t="inlineStr"/>
+      <c r="FG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH71" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI71" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ71" t="inlineStr"/>
+      <c r="FK71" t="inlineStr"/>
+      <c r="FL71" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM71" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN71" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO71" t="inlineStr"/>
+      <c r="FP71" t="inlineStr"/>
+      <c r="FQ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR71" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS71" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT71" t="inlineStr"/>
+      <c r="FU71" t="inlineStr"/>
+      <c r="FV71" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW71" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX71" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY71" t="inlineStr"/>
+      <c r="FZ71" t="inlineStr"/>
+      <c r="GA71" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB71" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC71" t="n">
+        <v>2.475974687393181e-06</v>
+      </c>
+      <c r="GD71" t="inlineStr"/>
+      <c r="GE71" t="inlineStr"/>
+      <c r="GF71" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH71" t="n">
+        <v>0</v>
+      </c>
+      <c r="GI71" t="inlineStr"/>
+      <c r="GJ71" t="inlineStr"/>
+      <c r="GK71" t="n">
+        <v>0</v>
+      </c>
+      <c r="GL71" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM71" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN71" t="inlineStr"/>
+      <c r="GO71" t="inlineStr"/>
+      <c r="GP71" t="n">
+        <v>0</v>
+      </c>
+      <c r="GQ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR71" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS71" t="inlineStr"/>
+      <c r="GT71" t="inlineStr"/>
+      <c r="GU71" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV71" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW71" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX71" t="inlineStr"/>
+      <c r="GY71" t="inlineStr"/>
+      <c r="GZ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="HA71" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB71" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC71" t="inlineStr"/>
+      <c r="HD71" t="inlineStr"/>
+      <c r="HE71" t="n">
+        <v>0</v>
+      </c>
+      <c r="HF71" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH71" t="inlineStr"/>
+      <c r="HI71" t="inlineStr"/>
+      <c r="HJ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK71" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL71" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM71" t="inlineStr"/>
+      <c r="HN71" t="inlineStr"/>
+      <c r="HO71" t="n">
+        <v>0</v>
+      </c>
+      <c r="HP71" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR71" t="inlineStr"/>
+      <c r="HS71" t="inlineStr"/>
+      <c r="HT71" t="n">
+        <v>0</v>
+      </c>
+      <c r="HU71" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV71" t="n">
+        <v>0</v>
+      </c>
+      <c r="HW71" t="inlineStr"/>
+      <c r="HX71" t="inlineStr"/>
+      <c r="HY71" t="n">
+        <v>0</v>
+      </c>
+      <c r="HZ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA71" t="n">
+        <v>0</v>
+      </c>
+      <c r="IB71" t="inlineStr"/>
+      <c r="IC71" t="inlineStr"/>
+      <c r="ID71" t="n">
+        <v>0</v>
+      </c>
+      <c r="IE71" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF71" t="n">
+        <v>0</v>
+      </c>
+      <c r="IG71" t="inlineStr"/>
+      <c r="IH71" t="inlineStr"/>
+      <c r="II71" t="n">
+        <v>0</v>
+      </c>
+      <c r="IJ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK71" t="n">
+        <v>0</v>
+      </c>
+      <c r="IL71" t="inlineStr"/>
+      <c r="IM71" t="inlineStr"/>
+      <c r="IN71" t="n">
+        <v>0</v>
+      </c>
+      <c r="IO71" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP71" t="n">
+        <v>1.331896293025564e-06</v>
+      </c>
+      <c r="IQ71" t="inlineStr"/>
+      <c r="IR71" t="inlineStr"/>
+      <c r="IS71" t="n">
+        <v>0</v>
+      </c>
+      <c r="IT71" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU71" t="n">
+        <v>0</v>
+      </c>
+      <c r="IV71" t="inlineStr"/>
+      <c r="IW71" t="inlineStr"/>
+      <c r="IX71" t="n">
+        <v>0</v>
+      </c>
+      <c r="IY71" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA71" t="inlineStr"/>
+      <c r="JB71" t="inlineStr"/>
+      <c r="JC71" t="n">
+        <v>0</v>
+      </c>
+      <c r="JD71" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-04-20 20:32:38</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>10</v>
+      </c>
+      <c r="C72" t="n">
+        <v>100</v>
+      </c>
+      <c r="D72" t="n">
+        <v>50</v>
+      </c>
+      <c r="E72" t="n">
+        <v>40</v>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>0.2212412936712705</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.9484164164164164</v>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="n">
+        <v>0.2094488497938567</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0.345213720537687</v>
+      </c>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="n">
+        <v>0.2621197160845905</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0.4497934977411436</v>
+      </c>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="n">
+        <v>0.4933906744900063</v>
+      </c>
+      <c r="X72" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>0.4481342723497151</v>
+      </c>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr"/>
+      <c r="AB72" t="n">
+        <v>0.4510745601421027</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>0.3912981498055055</v>
+      </c>
+      <c r="AE72" t="inlineStr"/>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="n">
+        <v>0.4468367471272708</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>0.5469031335859372</v>
+      </c>
+      <c r="AJ72" t="inlineStr"/>
+      <c r="AK72" t="inlineStr"/>
+      <c r="AL72" t="n">
+        <v>0.5335947554610392</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO72" t="inlineStr"/>
+      <c r="AP72" t="inlineStr"/>
+      <c r="AQ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AU72" t="inlineStr"/>
+      <c r="AV72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr"/>
+      <c r="BA72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD72" t="inlineStr"/>
+      <c r="BE72" t="inlineStr"/>
+      <c r="BF72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH72" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI72" t="inlineStr"/>
+      <c r="BJ72" t="inlineStr"/>
+      <c r="BK72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN72" t="inlineStr"/>
+      <c r="BO72" t="inlineStr"/>
+      <c r="BP72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS72" t="inlineStr"/>
+      <c r="BT72" t="inlineStr"/>
+      <c r="BU72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX72" t="inlineStr"/>
+      <c r="BY72" t="inlineStr"/>
+      <c r="BZ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB72" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC72" t="inlineStr"/>
+      <c r="CD72" t="inlineStr"/>
+      <c r="CE72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH72" t="inlineStr"/>
+      <c r="CI72" t="inlineStr"/>
+      <c r="CJ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL72" t="n">
+        <v>-0.03265120641357604</v>
+      </c>
+      <c r="CM72" t="inlineStr"/>
+      <c r="CN72" t="inlineStr"/>
+      <c r="CO72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR72" t="inlineStr"/>
+      <c r="CS72" t="inlineStr"/>
+      <c r="CT72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV72" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW72" t="inlineStr"/>
+      <c r="CX72" t="inlineStr"/>
+      <c r="CY72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA72" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB72" t="inlineStr"/>
+      <c r="DC72" t="inlineStr"/>
+      <c r="DD72" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE72" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF72" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG72" t="inlineStr"/>
+      <c r="DH72" t="inlineStr"/>
+      <c r="DI72" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK72" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL72" t="inlineStr"/>
+      <c r="DM72" t="inlineStr"/>
+      <c r="DN72" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO72" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP72" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ72" t="inlineStr"/>
+      <c r="DR72" t="inlineStr"/>
+      <c r="DS72" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT72" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU72" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV72" t="inlineStr"/>
+      <c r="DW72" t="inlineStr"/>
+      <c r="DX72" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY72" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA72" t="inlineStr"/>
+      <c r="EB72" t="inlineStr"/>
+      <c r="EC72" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED72" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE72" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF72" t="inlineStr"/>
+      <c r="EG72" t="inlineStr"/>
+      <c r="EH72" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI72" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK72" t="inlineStr"/>
+      <c r="EL72" t="inlineStr"/>
+      <c r="EM72" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN72" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO72" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP72" t="inlineStr"/>
+      <c r="EQ72" t="inlineStr"/>
+      <c r="ER72" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES72" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET72" t="n">
+        <v>-0.09037031430505783</v>
+      </c>
+      <c r="EU72" t="inlineStr"/>
+      <c r="EV72" t="inlineStr"/>
+      <c r="EW72" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX72" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY72" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ72" t="inlineStr"/>
+      <c r="FA72" t="inlineStr"/>
+      <c r="FB72" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC72" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD72" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE72" t="inlineStr"/>
+      <c r="FF72" t="inlineStr"/>
+      <c r="FG72" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH72" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI72" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ72" t="inlineStr"/>
+      <c r="FK72" t="inlineStr"/>
+      <c r="FL72" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM72" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN72" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO72" t="inlineStr"/>
+      <c r="FP72" t="inlineStr"/>
+      <c r="FQ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR72" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS72" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT72" t="inlineStr"/>
+      <c r="FU72" t="inlineStr"/>
+      <c r="FV72" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW72" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX72" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY72" t="inlineStr"/>
+      <c r="FZ72" t="inlineStr"/>
+      <c r="GA72" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB72" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC72" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD72" t="inlineStr"/>
+      <c r="GE72" t="inlineStr"/>
+      <c r="GF72" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG72" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH72" t="n">
+        <v>0</v>
+      </c>
+      <c r="GI72" t="inlineStr"/>
+      <c r="GJ72" t="inlineStr"/>
+      <c r="GK72" t="n">
+        <v>0</v>
+      </c>
+      <c r="GL72" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM72" t="n">
+        <v>0.1274315342470725</v>
+      </c>
+      <c r="GN72" t="inlineStr"/>
+      <c r="GO72" t="inlineStr"/>
+      <c r="GP72" t="n">
+        <v>0</v>
+      </c>
+      <c r="GQ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR72" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GS72" t="inlineStr"/>
+      <c r="GT72" t="inlineStr"/>
+      <c r="GU72" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV72" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW72" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GX72" t="inlineStr"/>
+      <c r="GY72" t="inlineStr"/>
+      <c r="GZ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="HA72" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB72" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC72" t="inlineStr"/>
+      <c r="HD72" t="inlineStr"/>
+      <c r="HE72" t="n">
+        <v>0</v>
+      </c>
+      <c r="HF72" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG72" t="n">
+        <v>-0</v>
+      </c>
+      <c r="HH72" t="inlineStr"/>
+      <c r="HI72" t="inlineStr"/>
+      <c r="HJ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK72" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL72" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM72" t="inlineStr"/>
+      <c r="HN72" t="inlineStr"/>
+      <c r="HO72" t="n">
+        <v>0</v>
+      </c>
+      <c r="HP72" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR72" t="inlineStr"/>
+      <c r="HS72" t="inlineStr"/>
+      <c r="HT72" t="n">
+        <v>0</v>
+      </c>
+      <c r="HU72" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV72" t="n">
+        <v>-0</v>
+      </c>
+      <c r="HW72" t="inlineStr"/>
+      <c r="HX72" t="inlineStr"/>
+      <c r="HY72" t="n">
+        <v>0</v>
+      </c>
+      <c r="HZ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA72" t="n">
+        <v>0</v>
+      </c>
+      <c r="IB72" t="inlineStr"/>
+      <c r="IC72" t="inlineStr"/>
+      <c r="ID72" t="n">
+        <v>0</v>
+      </c>
+      <c r="IE72" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF72" t="n">
+        <v>0</v>
+      </c>
+      <c r="IG72" t="inlineStr"/>
+      <c r="IH72" t="inlineStr"/>
+      <c r="II72" t="n">
+        <v>0</v>
+      </c>
+      <c r="IJ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK72" t="n">
+        <v>0</v>
+      </c>
+      <c r="IL72" t="inlineStr"/>
+      <c r="IM72" t="inlineStr"/>
+      <c r="IN72" t="n">
+        <v>0</v>
+      </c>
+      <c r="IO72" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP72" t="n">
+        <v>-3.486811104169365e-06</v>
+      </c>
+      <c r="IQ72" t="inlineStr"/>
+      <c r="IR72" t="inlineStr"/>
+      <c r="IS72" t="n">
+        <v>0</v>
+      </c>
+      <c r="IT72" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU72" t="n">
+        <v>-0</v>
+      </c>
+      <c r="IV72" t="inlineStr"/>
+      <c r="IW72" t="inlineStr"/>
+      <c r="IX72" t="n">
+        <v>0</v>
+      </c>
+      <c r="IY72" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA72" t="inlineStr"/>
+      <c r="JB72" t="inlineStr"/>
+      <c r="JC72" t="n">
+        <v>0</v>
+      </c>
+      <c r="JD72" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/ranking/results.xlsx
+++ b/ranking/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:LC97"/>
+  <dimension ref="A1:LC109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58495,7 +58495,7 @@
         <v>0</v>
       </c>
       <c r="AN97" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO97" t="inlineStr"/>
       <c r="AP97" t="inlineStr"/>
@@ -58531,7 +58531,7 @@
         <v>0</v>
       </c>
       <c r="BH97" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI97" t="inlineStr"/>
       <c r="BJ97" t="inlineStr"/>
@@ -58540,7 +58540,7 @@
         <v>0</v>
       </c>
       <c r="BM97" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN97" t="inlineStr"/>
       <c r="BO97" t="inlineStr"/>
@@ -58549,7 +58549,7 @@
         <v>0</v>
       </c>
       <c r="BR97" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS97" t="inlineStr"/>
       <c r="BT97" t="inlineStr"/>
@@ -58558,7 +58558,7 @@
         <v>0</v>
       </c>
       <c r="BW97" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX97" t="inlineStr"/>
       <c r="BY97" t="inlineStr"/>
@@ -58567,7 +58567,7 @@
         <v>0</v>
       </c>
       <c r="CB97" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC97" t="inlineStr"/>
       <c r="CD97" t="inlineStr"/>
@@ -58585,7 +58585,7 @@
         <v>0</v>
       </c>
       <c r="CL97" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM97" t="inlineStr"/>
       <c r="CN97" t="inlineStr"/>
@@ -58603,7 +58603,7 @@
         <v>0</v>
       </c>
       <c r="CV97" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW97" t="inlineStr"/>
       <c r="CX97" t="inlineStr"/>
@@ -58621,7 +58621,7 @@
         <v>0</v>
       </c>
       <c r="DF97" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG97" t="inlineStr"/>
       <c r="DH97" t="inlineStr"/>
@@ -58630,7 +58630,7 @@
         <v>0</v>
       </c>
       <c r="DK97" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL97" t="inlineStr"/>
       <c r="DM97" t="inlineStr"/>
@@ -58639,7 +58639,7 @@
         <v>0</v>
       </c>
       <c r="DP97" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ97" t="inlineStr"/>
       <c r="DR97" t="inlineStr"/>
@@ -58648,7 +58648,7 @@
         <v>0</v>
       </c>
       <c r="DU97" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV97" t="inlineStr"/>
       <c r="DW97" t="inlineStr"/>
@@ -58657,7 +58657,7 @@
         <v>0</v>
       </c>
       <c r="DZ97" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA97" t="inlineStr"/>
       <c r="EB97" t="inlineStr"/>
@@ -58666,7 +58666,7 @@
         <v>0</v>
       </c>
       <c r="EE97" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF97" t="inlineStr"/>
       <c r="EG97" t="inlineStr"/>
@@ -58675,7 +58675,7 @@
         <v>0</v>
       </c>
       <c r="EJ97" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EK97" t="inlineStr"/>
       <c r="EL97" t="inlineStr"/>
@@ -58684,7 +58684,7 @@
         <v>0</v>
       </c>
       <c r="EO97" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP97" t="inlineStr"/>
       <c r="EQ97" t="inlineStr"/>
@@ -58693,7 +58693,7 @@
         <v>0</v>
       </c>
       <c r="ET97" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU97" t="inlineStr"/>
       <c r="EV97" t="inlineStr"/>
@@ -58711,7 +58711,7 @@
         <v>0</v>
       </c>
       <c r="FD97" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE97" t="inlineStr"/>
       <c r="FF97" t="inlineStr"/>
@@ -58720,7 +58720,7 @@
         <v>0</v>
       </c>
       <c r="FI97" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ97" t="inlineStr"/>
       <c r="FK97" t="inlineStr"/>
@@ -58729,7 +58729,7 @@
         <v>0</v>
       </c>
       <c r="FN97" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO97" t="inlineStr"/>
       <c r="FP97" t="inlineStr"/>
@@ -58738,7 +58738,7 @@
         <v>0</v>
       </c>
       <c r="FS97" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT97" t="inlineStr"/>
       <c r="FU97" t="inlineStr"/>
@@ -58765,7 +58765,7 @@
         <v>0</v>
       </c>
       <c r="GH97" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GI97" t="inlineStr"/>
       <c r="GJ97" t="inlineStr"/>
@@ -58774,7 +58774,7 @@
         <v>0</v>
       </c>
       <c r="GM97" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GN97" t="inlineStr"/>
       <c r="GO97" t="inlineStr"/>
@@ -58783,7 +58783,7 @@
         <v>0</v>
       </c>
       <c r="GR97" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GS97" t="inlineStr"/>
       <c r="GT97" t="inlineStr"/>
@@ -58792,7 +58792,7 @@
         <v>0</v>
       </c>
       <c r="GW97" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GX97" t="inlineStr"/>
       <c r="GY97" t="inlineStr"/>
@@ -58801,7 +58801,7 @@
         <v>0</v>
       </c>
       <c r="HB97" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="HC97" t="inlineStr"/>
       <c r="HD97" t="inlineStr"/>
@@ -58810,7 +58810,7 @@
         <v>0</v>
       </c>
       <c r="HG97" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="HH97" t="inlineStr"/>
       <c r="HI97" t="inlineStr"/>
@@ -58819,7 +58819,7 @@
         <v>0</v>
       </c>
       <c r="HL97" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="HM97" t="inlineStr"/>
       <c r="HN97" t="inlineStr"/>
@@ -58837,7 +58837,7 @@
         <v>0</v>
       </c>
       <c r="HV97" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="HW97" t="inlineStr"/>
       <c r="HX97" t="inlineStr"/>
@@ -58846,7 +58846,7 @@
         <v>0</v>
       </c>
       <c r="IA97" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="IB97" t="inlineStr"/>
       <c r="IC97" t="inlineStr"/>
@@ -58855,7 +58855,7 @@
         <v>0</v>
       </c>
       <c r="IF97" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="IG97" t="inlineStr"/>
       <c r="IH97" t="inlineStr"/>
@@ -58864,7 +58864,7 @@
         <v>0</v>
       </c>
       <c r="IK97" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="IL97" t="inlineStr"/>
       <c r="IM97" t="inlineStr"/>
@@ -58873,7 +58873,7 @@
         <v>0</v>
       </c>
       <c r="IP97" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="IQ97" t="inlineStr"/>
       <c r="IR97" t="inlineStr"/>
@@ -58882,7 +58882,7 @@
         <v>0</v>
       </c>
       <c r="IU97" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="IV97" t="inlineStr"/>
       <c r="IW97" t="inlineStr"/>
@@ -58891,7 +58891,7 @@
         <v>0</v>
       </c>
       <c r="IZ97" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="JA97" t="inlineStr"/>
       <c r="JB97" t="inlineStr"/>
@@ -59053,6 +59053,7746 @@
         <v>-2.73199692528353e-05</v>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:10:28</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>10</v>
+      </c>
+      <c r="C98" t="n">
+        <v>100</v>
+      </c>
+      <c r="D98" t="n">
+        <v>50</v>
+      </c>
+      <c r="E98" t="n">
+        <v>200</v>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>0.1309674614782952</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0.9662902902902903</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0.9684243501793534</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0.5128266921273362</v>
+      </c>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
+      <c r="S98" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="T98" t="n">
+        <v>0.3522046053287754</v>
+      </c>
+      <c r="U98" t="inlineStr"/>
+      <c r="V98" t="inlineStr"/>
+      <c r="W98" t="inlineStr"/>
+      <c r="X98" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>0.497798503723377</v>
+      </c>
+      <c r="Z98" t="inlineStr"/>
+      <c r="AA98" t="inlineStr"/>
+      <c r="AB98" t="inlineStr"/>
+      <c r="AC98" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AD98" t="n">
+        <v>0.4256935492390026</v>
+      </c>
+      <c r="AE98" t="inlineStr"/>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="inlineStr"/>
+      <c r="AH98" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AI98" t="n">
+        <v>0.4283675759600179</v>
+      </c>
+      <c r="AJ98" t="inlineStr"/>
+      <c r="AK98" t="inlineStr"/>
+      <c r="AL98" t="inlineStr"/>
+      <c r="AM98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO98" t="inlineStr"/>
+      <c r="AP98" t="inlineStr"/>
+      <c r="AQ98" t="inlineStr"/>
+      <c r="AR98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AU98" t="inlineStr"/>
+      <c r="AV98" t="inlineStr"/>
+      <c r="AW98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr"/>
+      <c r="BA98" t="inlineStr"/>
+      <c r="BB98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD98" t="inlineStr"/>
+      <c r="BE98" t="inlineStr"/>
+      <c r="BF98" t="inlineStr"/>
+      <c r="BG98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI98" t="inlineStr"/>
+      <c r="BJ98" t="inlineStr"/>
+      <c r="BK98" t="inlineStr"/>
+      <c r="BL98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN98" t="inlineStr"/>
+      <c r="BO98" t="inlineStr"/>
+      <c r="BP98" t="inlineStr"/>
+      <c r="BQ98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS98" t="inlineStr"/>
+      <c r="BT98" t="inlineStr"/>
+      <c r="BU98" t="inlineStr"/>
+      <c r="BV98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX98" t="inlineStr"/>
+      <c r="BY98" t="inlineStr"/>
+      <c r="BZ98" t="inlineStr"/>
+      <c r="CA98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC98" t="inlineStr"/>
+      <c r="CD98" t="inlineStr"/>
+      <c r="CE98" t="inlineStr"/>
+      <c r="CF98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG98" t="n">
+        <v>-0.02106113767444692</v>
+      </c>
+      <c r="CH98" t="inlineStr"/>
+      <c r="CI98" t="inlineStr"/>
+      <c r="CJ98" t="inlineStr"/>
+      <c r="CK98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM98" t="inlineStr"/>
+      <c r="CN98" t="inlineStr"/>
+      <c r="CO98" t="inlineStr"/>
+      <c r="CP98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR98" t="inlineStr"/>
+      <c r="CS98" t="inlineStr"/>
+      <c r="CT98" t="inlineStr"/>
+      <c r="CU98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW98" t="inlineStr"/>
+      <c r="CX98" t="inlineStr"/>
+      <c r="CY98" t="inlineStr"/>
+      <c r="CZ98" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA98" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB98" t="inlineStr"/>
+      <c r="DC98" t="inlineStr"/>
+      <c r="DD98" t="inlineStr"/>
+      <c r="DE98" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF98" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG98" t="inlineStr"/>
+      <c r="DH98" t="inlineStr"/>
+      <c r="DI98" t="inlineStr"/>
+      <c r="DJ98" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK98" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL98" t="inlineStr"/>
+      <c r="DM98" t="inlineStr"/>
+      <c r="DN98" t="inlineStr"/>
+      <c r="DO98" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP98" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ98" t="inlineStr"/>
+      <c r="DR98" t="inlineStr"/>
+      <c r="DS98" t="inlineStr"/>
+      <c r="DT98" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU98" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV98" t="inlineStr"/>
+      <c r="DW98" t="inlineStr"/>
+      <c r="DX98" t="inlineStr"/>
+      <c r="DY98" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ98" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA98" t="inlineStr"/>
+      <c r="EB98" t="inlineStr"/>
+      <c r="EC98" t="inlineStr"/>
+      <c r="ED98" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE98" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF98" t="inlineStr"/>
+      <c r="EG98" t="inlineStr"/>
+      <c r="EH98" t="inlineStr"/>
+      <c r="EI98" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ98" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK98" t="inlineStr"/>
+      <c r="EL98" t="inlineStr"/>
+      <c r="EM98" t="inlineStr"/>
+      <c r="EN98" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO98" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP98" t="inlineStr"/>
+      <c r="EQ98" t="inlineStr"/>
+      <c r="ER98" t="inlineStr"/>
+      <c r="ES98" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET98" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU98" t="inlineStr"/>
+      <c r="EV98" t="inlineStr"/>
+      <c r="EW98" t="inlineStr"/>
+      <c r="EX98" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY98" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ98" t="inlineStr"/>
+      <c r="FA98" t="inlineStr"/>
+      <c r="FB98" t="inlineStr"/>
+      <c r="FC98" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD98" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE98" t="inlineStr"/>
+      <c r="FF98" t="inlineStr"/>
+      <c r="FG98" t="inlineStr"/>
+      <c r="FH98" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI98" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ98" t="inlineStr"/>
+      <c r="FK98" t="inlineStr"/>
+      <c r="FL98" t="inlineStr"/>
+      <c r="FM98" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN98" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO98" t="inlineStr"/>
+      <c r="FP98" t="inlineStr"/>
+      <c r="FQ98" t="inlineStr"/>
+      <c r="FR98" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS98" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT98" t="inlineStr"/>
+      <c r="FU98" t="inlineStr"/>
+      <c r="FV98" t="inlineStr"/>
+      <c r="FW98" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX98" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY98" t="inlineStr"/>
+      <c r="FZ98" t="inlineStr"/>
+      <c r="GA98" t="inlineStr"/>
+      <c r="GB98" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC98" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD98" t="inlineStr"/>
+      <c r="GE98" t="inlineStr"/>
+      <c r="GF98" t="inlineStr"/>
+      <c r="GG98" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH98" t="n">
+        <v>0</v>
+      </c>
+      <c r="GI98" t="inlineStr"/>
+      <c r="GJ98" t="inlineStr"/>
+      <c r="GK98" t="inlineStr"/>
+      <c r="GL98" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM98" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN98" t="inlineStr"/>
+      <c r="GO98" t="inlineStr"/>
+      <c r="GP98" t="inlineStr"/>
+      <c r="GQ98" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR98" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS98" t="inlineStr"/>
+      <c r="GT98" t="inlineStr"/>
+      <c r="GU98" t="inlineStr"/>
+      <c r="GV98" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW98" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX98" t="inlineStr"/>
+      <c r="GY98" t="inlineStr"/>
+      <c r="GZ98" t="inlineStr"/>
+      <c r="HA98" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB98" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC98" t="inlineStr"/>
+      <c r="HD98" t="inlineStr"/>
+      <c r="HE98" t="inlineStr"/>
+      <c r="HF98" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG98" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH98" t="inlineStr"/>
+      <c r="HI98" t="inlineStr"/>
+      <c r="HJ98" t="inlineStr"/>
+      <c r="HK98" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL98" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM98" t="inlineStr"/>
+      <c r="HN98" t="inlineStr"/>
+      <c r="HO98" t="inlineStr"/>
+      <c r="HP98" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ98" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR98" t="inlineStr"/>
+      <c r="HS98" t="inlineStr"/>
+      <c r="HT98" t="inlineStr"/>
+      <c r="HU98" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV98" t="n">
+        <v>0</v>
+      </c>
+      <c r="HW98" t="inlineStr"/>
+      <c r="HX98" t="inlineStr"/>
+      <c r="HY98" t="inlineStr"/>
+      <c r="HZ98" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA98" t="n">
+        <v>0</v>
+      </c>
+      <c r="IB98" t="inlineStr"/>
+      <c r="IC98" t="inlineStr"/>
+      <c r="ID98" t="inlineStr"/>
+      <c r="IE98" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF98" t="n">
+        <v>0</v>
+      </c>
+      <c r="IG98" t="inlineStr"/>
+      <c r="IH98" t="inlineStr"/>
+      <c r="II98" t="inlineStr"/>
+      <c r="IJ98" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK98" t="n">
+        <v>0</v>
+      </c>
+      <c r="IL98" t="inlineStr"/>
+      <c r="IM98" t="inlineStr"/>
+      <c r="IN98" t="inlineStr"/>
+      <c r="IO98" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP98" t="n">
+        <v>0</v>
+      </c>
+      <c r="IQ98" t="inlineStr"/>
+      <c r="IR98" t="inlineStr"/>
+      <c r="IS98" t="inlineStr"/>
+      <c r="IT98" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU98" t="n">
+        <v>0</v>
+      </c>
+      <c r="IV98" t="inlineStr"/>
+      <c r="IW98" t="inlineStr"/>
+      <c r="IX98" t="inlineStr"/>
+      <c r="IY98" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ98" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA98" t="inlineStr"/>
+      <c r="JB98" t="inlineStr"/>
+      <c r="JC98" t="inlineStr"/>
+      <c r="JD98" t="n">
+        <v>5</v>
+      </c>
+      <c r="JE98" t="n">
+        <v>0.1621459801602033</v>
+      </c>
+      <c r="JF98" t="n">
+        <v>0.5153151675456151</v>
+      </c>
+      <c r="JG98" t="n">
+        <v>0.3203091520336468</v>
+      </c>
+      <c r="JH98" t="n">
+        <v>0.5162094342964226</v>
+      </c>
+      <c r="JI98" t="n">
+        <v>0.4283301844824338</v>
+      </c>
+      <c r="JJ98" t="n">
+        <v>0.4264936413347523</v>
+      </c>
+      <c r="JK98" t="n">
+        <v>5.293829985016243e-05</v>
+      </c>
+      <c r="JL98" t="n">
+        <v>1.549419369156263e-05</v>
+      </c>
+      <c r="JM98" t="n">
+        <v>0.0001212078710404407</v>
+      </c>
+      <c r="JN98" t="n">
+        <v>0.0001721180389439467</v>
+      </c>
+      <c r="JO98" t="n">
+        <v>-0.0001189556640747227</v>
+      </c>
+      <c r="JP98" t="n">
+        <v>-0.0002249381364017046</v>
+      </c>
+      <c r="JQ98" t="n">
+        <v>0</v>
+      </c>
+      <c r="JR98" t="n">
+        <v>-4.733603085629367e-05</v>
+      </c>
+      <c r="JS98" t="n">
+        <v>0</v>
+      </c>
+      <c r="JT98" t="n">
+        <v>-0.0005492400386304608</v>
+      </c>
+      <c r="JU98" t="n">
+        <v>-7.884982200148769e-05</v>
+      </c>
+      <c r="JV98" t="n">
+        <v>6.865050501672477e-05</v>
+      </c>
+      <c r="JW98" t="n">
+        <v>-3.014464951629469e-05</v>
+      </c>
+      <c r="JX98" t="n">
+        <v>1.694784303279466e-05</v>
+      </c>
+      <c r="JY98" t="n">
+        <v>-0.0002098215090159466</v>
+      </c>
+      <c r="JZ98" t="n">
+        <v>-1.267424769364759e-05</v>
+      </c>
+      <c r="KA98" t="n">
+        <v>-3.390266721908227e-05</v>
+      </c>
+      <c r="KB98" t="n">
+        <v>-0.000323687457741617</v>
+      </c>
+      <c r="KC98" t="n">
+        <v>7.000970231148708e-06</v>
+      </c>
+      <c r="KD98" t="n">
+        <v>-0.0004807174259225122</v>
+      </c>
+      <c r="KE98" t="n">
+        <v>-4.439184511577743e-05</v>
+      </c>
+      <c r="KF98" t="n">
+        <v>-0.0006696637666401958</v>
+      </c>
+      <c r="KG98" t="n">
+        <v>-0.0001082974352733832</v>
+      </c>
+      <c r="KH98" t="n">
+        <v>-3.5549660284195e-05</v>
+      </c>
+      <c r="KI98" t="n">
+        <v>-0.0001065433200567963</v>
+      </c>
+      <c r="KJ98" t="n">
+        <v>-4.832700401073146e-05</v>
+      </c>
+      <c r="KK98" t="n">
+        <v>-0.0001585452582810646</v>
+      </c>
+      <c r="KL98" t="n">
+        <v>-0.0002371593455373042</v>
+      </c>
+      <c r="KM98" t="n">
+        <v>2.307368066164126e-05</v>
+      </c>
+      <c r="KN98" t="n">
+        <v>0.0001262915255371631</v>
+      </c>
+      <c r="KO98" t="n">
+        <v>6.972885894597983e-05</v>
+      </c>
+      <c r="KP98" t="n">
+        <v>-0.0003398371993758527</v>
+      </c>
+      <c r="KQ98" t="n">
+        <v>1.971471296882563e-05</v>
+      </c>
+      <c r="KR98" t="n">
+        <v>0</v>
+      </c>
+      <c r="KS98" t="n">
+        <v>-0.0001554514795408999</v>
+      </c>
+      <c r="KT98" t="n">
+        <v>-5.170900984144686e-05</v>
+      </c>
+      <c r="KU98" t="n">
+        <v>-0.0009092423429055575</v>
+      </c>
+      <c r="KV98" t="n">
+        <v>-2.158705195892355e-05</v>
+      </c>
+      <c r="KW98" t="n">
+        <v>-2.883060163298075e-05</v>
+      </c>
+      <c r="KX98" t="n">
+        <v>-0.0001190742422977265</v>
+      </c>
+      <c r="KY98" t="n">
+        <v>-8.315689119544047e-05</v>
+      </c>
+      <c r="KZ98" t="n">
+        <v>-1.890383526875511e-06</v>
+      </c>
+      <c r="LA98" t="n">
+        <v>-0.0002226157266408184</v>
+      </c>
+      <c r="LB98" t="n">
+        <v>1.497779191334733e-05</v>
+      </c>
+      <c r="LC98" t="n">
+        <v>-2.622656590701506e-05</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:44</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>10</v>
+      </c>
+      <c r="C99" t="n">
+        <v>100</v>
+      </c>
+      <c r="D99" t="n">
+        <v>50</v>
+      </c>
+      <c r="E99" t="n">
+        <v>200</v>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>0.1309674614782952</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0.9662902902902903</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0.9684243501793534</v>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0.5128266921273362</v>
+      </c>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="T99" t="n">
+        <v>0.3522046053287754</v>
+      </c>
+      <c r="U99" t="inlineStr"/>
+      <c r="V99" t="inlineStr"/>
+      <c r="W99" t="inlineStr"/>
+      <c r="X99" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>0.497798503723377</v>
+      </c>
+      <c r="Z99" t="inlineStr"/>
+      <c r="AA99" t="inlineStr"/>
+      <c r="AB99" t="inlineStr"/>
+      <c r="AC99" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AD99" t="n">
+        <v>0.4256935492390026</v>
+      </c>
+      <c r="AE99" t="inlineStr"/>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="inlineStr"/>
+      <c r="AH99" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AI99" t="n">
+        <v>0.4283675759600179</v>
+      </c>
+      <c r="AJ99" t="inlineStr"/>
+      <c r="AK99" t="inlineStr"/>
+      <c r="AL99" t="inlineStr"/>
+      <c r="AM99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO99" t="inlineStr"/>
+      <c r="AP99" t="inlineStr"/>
+      <c r="AQ99" t="inlineStr"/>
+      <c r="AR99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AU99" t="inlineStr"/>
+      <c r="AV99" t="inlineStr"/>
+      <c r="AW99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr"/>
+      <c r="BA99" t="inlineStr"/>
+      <c r="BB99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD99" t="inlineStr"/>
+      <c r="BE99" t="inlineStr"/>
+      <c r="BF99" t="inlineStr"/>
+      <c r="BG99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI99" t="inlineStr"/>
+      <c r="BJ99" t="inlineStr"/>
+      <c r="BK99" t="inlineStr"/>
+      <c r="BL99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN99" t="inlineStr"/>
+      <c r="BO99" t="inlineStr"/>
+      <c r="BP99" t="inlineStr"/>
+      <c r="BQ99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS99" t="inlineStr"/>
+      <c r="BT99" t="inlineStr"/>
+      <c r="BU99" t="inlineStr"/>
+      <c r="BV99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX99" t="inlineStr"/>
+      <c r="BY99" t="inlineStr"/>
+      <c r="BZ99" t="inlineStr"/>
+      <c r="CA99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC99" t="inlineStr"/>
+      <c r="CD99" t="inlineStr"/>
+      <c r="CE99" t="inlineStr"/>
+      <c r="CF99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG99" t="n">
+        <v>-0.02106113767444692</v>
+      </c>
+      <c r="CH99" t="inlineStr"/>
+      <c r="CI99" t="inlineStr"/>
+      <c r="CJ99" t="inlineStr"/>
+      <c r="CK99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM99" t="inlineStr"/>
+      <c r="CN99" t="inlineStr"/>
+      <c r="CO99" t="inlineStr"/>
+      <c r="CP99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR99" t="inlineStr"/>
+      <c r="CS99" t="inlineStr"/>
+      <c r="CT99" t="inlineStr"/>
+      <c r="CU99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW99" t="inlineStr"/>
+      <c r="CX99" t="inlineStr"/>
+      <c r="CY99" t="inlineStr"/>
+      <c r="CZ99" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA99" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB99" t="inlineStr"/>
+      <c r="DC99" t="inlineStr"/>
+      <c r="DD99" t="inlineStr"/>
+      <c r="DE99" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF99" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG99" t="inlineStr"/>
+      <c r="DH99" t="inlineStr"/>
+      <c r="DI99" t="inlineStr"/>
+      <c r="DJ99" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK99" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL99" t="inlineStr"/>
+      <c r="DM99" t="inlineStr"/>
+      <c r="DN99" t="inlineStr"/>
+      <c r="DO99" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP99" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ99" t="inlineStr"/>
+      <c r="DR99" t="inlineStr"/>
+      <c r="DS99" t="inlineStr"/>
+      <c r="DT99" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU99" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV99" t="inlineStr"/>
+      <c r="DW99" t="inlineStr"/>
+      <c r="DX99" t="inlineStr"/>
+      <c r="DY99" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ99" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA99" t="inlineStr"/>
+      <c r="EB99" t="inlineStr"/>
+      <c r="EC99" t="inlineStr"/>
+      <c r="ED99" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE99" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF99" t="inlineStr"/>
+      <c r="EG99" t="inlineStr"/>
+      <c r="EH99" t="inlineStr"/>
+      <c r="EI99" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ99" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK99" t="inlineStr"/>
+      <c r="EL99" t="inlineStr"/>
+      <c r="EM99" t="inlineStr"/>
+      <c r="EN99" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO99" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP99" t="inlineStr"/>
+      <c r="EQ99" t="inlineStr"/>
+      <c r="ER99" t="inlineStr"/>
+      <c r="ES99" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET99" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU99" t="inlineStr"/>
+      <c r="EV99" t="inlineStr"/>
+      <c r="EW99" t="inlineStr"/>
+      <c r="EX99" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY99" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ99" t="inlineStr"/>
+      <c r="FA99" t="inlineStr"/>
+      <c r="FB99" t="inlineStr"/>
+      <c r="FC99" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD99" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE99" t="inlineStr"/>
+      <c r="FF99" t="inlineStr"/>
+      <c r="FG99" t="inlineStr"/>
+      <c r="FH99" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI99" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ99" t="inlineStr"/>
+      <c r="FK99" t="inlineStr"/>
+      <c r="FL99" t="inlineStr"/>
+      <c r="FM99" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN99" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO99" t="inlineStr"/>
+      <c r="FP99" t="inlineStr"/>
+      <c r="FQ99" t="inlineStr"/>
+      <c r="FR99" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS99" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT99" t="inlineStr"/>
+      <c r="FU99" t="inlineStr"/>
+      <c r="FV99" t="inlineStr"/>
+      <c r="FW99" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX99" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY99" t="inlineStr"/>
+      <c r="FZ99" t="inlineStr"/>
+      <c r="GA99" t="inlineStr"/>
+      <c r="GB99" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC99" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD99" t="inlineStr"/>
+      <c r="GE99" t="inlineStr"/>
+      <c r="GF99" t="inlineStr"/>
+      <c r="GG99" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH99" t="n">
+        <v>0</v>
+      </c>
+      <c r="GI99" t="inlineStr"/>
+      <c r="GJ99" t="inlineStr"/>
+      <c r="GK99" t="inlineStr"/>
+      <c r="GL99" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM99" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN99" t="inlineStr"/>
+      <c r="GO99" t="inlineStr"/>
+      <c r="GP99" t="inlineStr"/>
+      <c r="GQ99" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR99" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS99" t="inlineStr"/>
+      <c r="GT99" t="inlineStr"/>
+      <c r="GU99" t="inlineStr"/>
+      <c r="GV99" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW99" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX99" t="inlineStr"/>
+      <c r="GY99" t="inlineStr"/>
+      <c r="GZ99" t="inlineStr"/>
+      <c r="HA99" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB99" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC99" t="inlineStr"/>
+      <c r="HD99" t="inlineStr"/>
+      <c r="HE99" t="inlineStr"/>
+      <c r="HF99" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG99" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH99" t="inlineStr"/>
+      <c r="HI99" t="inlineStr"/>
+      <c r="HJ99" t="inlineStr"/>
+      <c r="HK99" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL99" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM99" t="inlineStr"/>
+      <c r="HN99" t="inlineStr"/>
+      <c r="HO99" t="inlineStr"/>
+      <c r="HP99" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ99" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR99" t="inlineStr"/>
+      <c r="HS99" t="inlineStr"/>
+      <c r="HT99" t="inlineStr"/>
+      <c r="HU99" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV99" t="n">
+        <v>0</v>
+      </c>
+      <c r="HW99" t="inlineStr"/>
+      <c r="HX99" t="inlineStr"/>
+      <c r="HY99" t="inlineStr"/>
+      <c r="HZ99" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA99" t="n">
+        <v>0</v>
+      </c>
+      <c r="IB99" t="inlineStr"/>
+      <c r="IC99" t="inlineStr"/>
+      <c r="ID99" t="inlineStr"/>
+      <c r="IE99" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF99" t="n">
+        <v>0</v>
+      </c>
+      <c r="IG99" t="inlineStr"/>
+      <c r="IH99" t="inlineStr"/>
+      <c r="II99" t="inlineStr"/>
+      <c r="IJ99" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK99" t="n">
+        <v>0</v>
+      </c>
+      <c r="IL99" t="inlineStr"/>
+      <c r="IM99" t="inlineStr"/>
+      <c r="IN99" t="inlineStr"/>
+      <c r="IO99" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP99" t="n">
+        <v>0</v>
+      </c>
+      <c r="IQ99" t="inlineStr"/>
+      <c r="IR99" t="inlineStr"/>
+      <c r="IS99" t="inlineStr"/>
+      <c r="IT99" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU99" t="n">
+        <v>0</v>
+      </c>
+      <c r="IV99" t="inlineStr"/>
+      <c r="IW99" t="inlineStr"/>
+      <c r="IX99" t="inlineStr"/>
+      <c r="IY99" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ99" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA99" t="inlineStr"/>
+      <c r="JB99" t="inlineStr"/>
+      <c r="JC99" t="inlineStr"/>
+      <c r="JD99" t="n">
+        <v>5</v>
+      </c>
+      <c r="JE99" t="n">
+        <v>0.3224637531216099</v>
+      </c>
+      <c r="JF99" t="n">
+        <v>0.4266901350615616</v>
+      </c>
+      <c r="JG99" t="n">
+        <v>0.3770437594690611</v>
+      </c>
+      <c r="JH99" t="n">
+        <v>0.4558408396793848</v>
+      </c>
+      <c r="JI99" t="n">
+        <v>0.4316679220751515</v>
+      </c>
+      <c r="JJ99" t="n">
+        <v>0.4285688893854727</v>
+      </c>
+      <c r="JK99" t="n">
+        <v>0</v>
+      </c>
+      <c r="JL99" t="n">
+        <v>0.03796205622597679</v>
+      </c>
+      <c r="JM99" t="n">
+        <v>0.05569965784697495</v>
+      </c>
+      <c r="JN99" t="n">
+        <v>0.1634563460518387</v>
+      </c>
+      <c r="JO99" t="n">
+        <v>-2.241440768043446e-06</v>
+      </c>
+      <c r="JP99" t="n">
+        <v>-0.1334137828875155</v>
+      </c>
+      <c r="JQ99" t="n">
+        <v>0</v>
+      </c>
+      <c r="JR99" t="n">
+        <v>-1.188959303100426e-06</v>
+      </c>
+      <c r="JS99" t="n">
+        <v>0</v>
+      </c>
+      <c r="JT99" t="n">
+        <v>-0.07823780758803325</v>
+      </c>
+      <c r="JU99" t="n">
+        <v>-9.854966419205452e-07</v>
+      </c>
+      <c r="JV99" t="n">
+        <v>0.04650226951968136</v>
+      </c>
+      <c r="JW99" t="n">
+        <v>0</v>
+      </c>
+      <c r="JX99" t="n">
+        <v>0.0550550185634199</v>
+      </c>
+      <c r="JY99" t="n">
+        <v>-6.362326339417647e-06</v>
+      </c>
+      <c r="JZ99" t="n">
+        <v>0</v>
+      </c>
+      <c r="KA99" t="n">
+        <v>-1.329203508961383e-06</v>
+      </c>
+      <c r="KB99" t="n">
+        <v>-4.159704179714098e-06</v>
+      </c>
+      <c r="KC99" t="n">
+        <v>0</v>
+      </c>
+      <c r="KD99" t="n">
+        <v>-0.009559852763716912</v>
+      </c>
+      <c r="KE99" t="n">
+        <v>-1.431121628106347e-06</v>
+      </c>
+      <c r="KF99" t="n">
+        <v>-0.124724532213412</v>
+      </c>
+      <c r="KG99" t="n">
+        <v>0</v>
+      </c>
+      <c r="KH99" t="n">
+        <v>0.01697745926489905</v>
+      </c>
+      <c r="KI99" t="n">
+        <v>-1.521582149080149e-06</v>
+      </c>
+      <c r="KJ99" t="n">
+        <v>0</v>
+      </c>
+      <c r="KK99" t="n">
+        <v>-3.417822723801456e-06</v>
+      </c>
+      <c r="KL99" t="n">
+        <v>-0.03737869730290295</v>
+      </c>
+      <c r="KM99" t="n">
+        <v>0.07948859779542994</v>
+      </c>
+      <c r="KN99" t="n">
+        <v>0.06752925075036717</v>
+      </c>
+      <c r="KO99" t="n">
+        <v>1.556277885632516e-06</v>
+      </c>
+      <c r="KP99" t="n">
+        <v>-8.751825459602366e-06</v>
+      </c>
+      <c r="KQ99" t="n">
+        <v>0</v>
+      </c>
+      <c r="KR99" t="n">
+        <v>0</v>
+      </c>
+      <c r="KS99" t="n">
+        <v>-3.564568955871743e-06</v>
+      </c>
+      <c r="KT99" t="n">
+        <v>0</v>
+      </c>
+      <c r="KU99" t="n">
+        <v>-0.04711529266741422</v>
+      </c>
+      <c r="KV99" t="n">
+        <v>0.02106325368030601</v>
+      </c>
+      <c r="KW99" t="n">
+        <v>3.286054265501857e-09</v>
+      </c>
+      <c r="KX99" t="n">
+        <v>-4.138587931335711e-06</v>
+      </c>
+      <c r="KY99" t="n">
+        <v>-1.529635587527855e-06</v>
+      </c>
+      <c r="KZ99" t="n">
+        <v>0</v>
+      </c>
+      <c r="LA99" t="n">
+        <v>-0.08199711697873506</v>
+      </c>
+      <c r="LB99" t="n">
+        <v>0</v>
+      </c>
+      <c r="LC99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:38:54</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>10</v>
+      </c>
+      <c r="C100" t="n">
+        <v>100</v>
+      </c>
+      <c r="D100" t="n">
+        <v>50</v>
+      </c>
+      <c r="E100" t="n">
+        <v>200</v>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>0.1309674614782952</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0.9662902902902903</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0.9684243501793534</v>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0.5128266921273362</v>
+      </c>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr"/>
+      <c r="S100" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="T100" t="n">
+        <v>0.3522046053287754</v>
+      </c>
+      <c r="U100" t="inlineStr"/>
+      <c r="V100" t="inlineStr"/>
+      <c r="W100" t="inlineStr"/>
+      <c r="X100" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>0.497798503723377</v>
+      </c>
+      <c r="Z100" t="inlineStr"/>
+      <c r="AA100" t="inlineStr"/>
+      <c r="AB100" t="inlineStr"/>
+      <c r="AC100" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AD100" t="n">
+        <v>0.4256935492390026</v>
+      </c>
+      <c r="AE100" t="inlineStr"/>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="inlineStr"/>
+      <c r="AH100" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AI100" t="n">
+        <v>0.4283675759600179</v>
+      </c>
+      <c r="AJ100" t="inlineStr"/>
+      <c r="AK100" t="inlineStr"/>
+      <c r="AL100" t="inlineStr"/>
+      <c r="AM100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO100" t="inlineStr"/>
+      <c r="AP100" t="inlineStr"/>
+      <c r="AQ100" t="inlineStr"/>
+      <c r="AR100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AU100" t="inlineStr"/>
+      <c r="AV100" t="inlineStr"/>
+      <c r="AW100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr"/>
+      <c r="BA100" t="inlineStr"/>
+      <c r="BB100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD100" t="inlineStr"/>
+      <c r="BE100" t="inlineStr"/>
+      <c r="BF100" t="inlineStr"/>
+      <c r="BG100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI100" t="inlineStr"/>
+      <c r="BJ100" t="inlineStr"/>
+      <c r="BK100" t="inlineStr"/>
+      <c r="BL100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN100" t="inlineStr"/>
+      <c r="BO100" t="inlineStr"/>
+      <c r="BP100" t="inlineStr"/>
+      <c r="BQ100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS100" t="inlineStr"/>
+      <c r="BT100" t="inlineStr"/>
+      <c r="BU100" t="inlineStr"/>
+      <c r="BV100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX100" t="inlineStr"/>
+      <c r="BY100" t="inlineStr"/>
+      <c r="BZ100" t="inlineStr"/>
+      <c r="CA100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC100" t="inlineStr"/>
+      <c r="CD100" t="inlineStr"/>
+      <c r="CE100" t="inlineStr"/>
+      <c r="CF100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG100" t="n">
+        <v>-0.02106113767444692</v>
+      </c>
+      <c r="CH100" t="inlineStr"/>
+      <c r="CI100" t="inlineStr"/>
+      <c r="CJ100" t="inlineStr"/>
+      <c r="CK100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM100" t="inlineStr"/>
+      <c r="CN100" t="inlineStr"/>
+      <c r="CO100" t="inlineStr"/>
+      <c r="CP100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR100" t="inlineStr"/>
+      <c r="CS100" t="inlineStr"/>
+      <c r="CT100" t="inlineStr"/>
+      <c r="CU100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW100" t="inlineStr"/>
+      <c r="CX100" t="inlineStr"/>
+      <c r="CY100" t="inlineStr"/>
+      <c r="CZ100" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA100" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB100" t="inlineStr"/>
+      <c r="DC100" t="inlineStr"/>
+      <c r="DD100" t="inlineStr"/>
+      <c r="DE100" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF100" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG100" t="inlineStr"/>
+      <c r="DH100" t="inlineStr"/>
+      <c r="DI100" t="inlineStr"/>
+      <c r="DJ100" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK100" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL100" t="inlineStr"/>
+      <c r="DM100" t="inlineStr"/>
+      <c r="DN100" t="inlineStr"/>
+      <c r="DO100" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP100" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ100" t="inlineStr"/>
+      <c r="DR100" t="inlineStr"/>
+      <c r="DS100" t="inlineStr"/>
+      <c r="DT100" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU100" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV100" t="inlineStr"/>
+      <c r="DW100" t="inlineStr"/>
+      <c r="DX100" t="inlineStr"/>
+      <c r="DY100" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ100" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA100" t="inlineStr"/>
+      <c r="EB100" t="inlineStr"/>
+      <c r="EC100" t="inlineStr"/>
+      <c r="ED100" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE100" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF100" t="inlineStr"/>
+      <c r="EG100" t="inlineStr"/>
+      <c r="EH100" t="inlineStr"/>
+      <c r="EI100" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ100" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK100" t="inlineStr"/>
+      <c r="EL100" t="inlineStr"/>
+      <c r="EM100" t="inlineStr"/>
+      <c r="EN100" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO100" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP100" t="inlineStr"/>
+      <c r="EQ100" t="inlineStr"/>
+      <c r="ER100" t="inlineStr"/>
+      <c r="ES100" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET100" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU100" t="inlineStr"/>
+      <c r="EV100" t="inlineStr"/>
+      <c r="EW100" t="inlineStr"/>
+      <c r="EX100" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY100" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ100" t="inlineStr"/>
+      <c r="FA100" t="inlineStr"/>
+      <c r="FB100" t="inlineStr"/>
+      <c r="FC100" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD100" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE100" t="inlineStr"/>
+      <c r="FF100" t="inlineStr"/>
+      <c r="FG100" t="inlineStr"/>
+      <c r="FH100" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI100" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ100" t="inlineStr"/>
+      <c r="FK100" t="inlineStr"/>
+      <c r="FL100" t="inlineStr"/>
+      <c r="FM100" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN100" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO100" t="inlineStr"/>
+      <c r="FP100" t="inlineStr"/>
+      <c r="FQ100" t="inlineStr"/>
+      <c r="FR100" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS100" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT100" t="inlineStr"/>
+      <c r="FU100" t="inlineStr"/>
+      <c r="FV100" t="inlineStr"/>
+      <c r="FW100" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX100" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY100" t="inlineStr"/>
+      <c r="FZ100" t="inlineStr"/>
+      <c r="GA100" t="inlineStr"/>
+      <c r="GB100" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC100" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD100" t="inlineStr"/>
+      <c r="GE100" t="inlineStr"/>
+      <c r="GF100" t="inlineStr"/>
+      <c r="GG100" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH100" t="n">
+        <v>0</v>
+      </c>
+      <c r="GI100" t="inlineStr"/>
+      <c r="GJ100" t="inlineStr"/>
+      <c r="GK100" t="inlineStr"/>
+      <c r="GL100" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM100" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN100" t="inlineStr"/>
+      <c r="GO100" t="inlineStr"/>
+      <c r="GP100" t="inlineStr"/>
+      <c r="GQ100" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR100" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS100" t="inlineStr"/>
+      <c r="GT100" t="inlineStr"/>
+      <c r="GU100" t="inlineStr"/>
+      <c r="GV100" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW100" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX100" t="inlineStr"/>
+      <c r="GY100" t="inlineStr"/>
+      <c r="GZ100" t="inlineStr"/>
+      <c r="HA100" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB100" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC100" t="inlineStr"/>
+      <c r="HD100" t="inlineStr"/>
+      <c r="HE100" t="inlineStr"/>
+      <c r="HF100" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG100" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH100" t="inlineStr"/>
+      <c r="HI100" t="inlineStr"/>
+      <c r="HJ100" t="inlineStr"/>
+      <c r="HK100" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL100" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM100" t="inlineStr"/>
+      <c r="HN100" t="inlineStr"/>
+      <c r="HO100" t="inlineStr"/>
+      <c r="HP100" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ100" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR100" t="inlineStr"/>
+      <c r="HS100" t="inlineStr"/>
+      <c r="HT100" t="inlineStr"/>
+      <c r="HU100" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV100" t="n">
+        <v>0</v>
+      </c>
+      <c r="HW100" t="inlineStr"/>
+      <c r="HX100" t="inlineStr"/>
+      <c r="HY100" t="inlineStr"/>
+      <c r="HZ100" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA100" t="n">
+        <v>0</v>
+      </c>
+      <c r="IB100" t="inlineStr"/>
+      <c r="IC100" t="inlineStr"/>
+      <c r="ID100" t="inlineStr"/>
+      <c r="IE100" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF100" t="n">
+        <v>0</v>
+      </c>
+      <c r="IG100" t="inlineStr"/>
+      <c r="IH100" t="inlineStr"/>
+      <c r="II100" t="inlineStr"/>
+      <c r="IJ100" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK100" t="n">
+        <v>0</v>
+      </c>
+      <c r="IL100" t="inlineStr"/>
+      <c r="IM100" t="inlineStr"/>
+      <c r="IN100" t="inlineStr"/>
+      <c r="IO100" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP100" t="n">
+        <v>0</v>
+      </c>
+      <c r="IQ100" t="inlineStr"/>
+      <c r="IR100" t="inlineStr"/>
+      <c r="IS100" t="inlineStr"/>
+      <c r="IT100" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU100" t="n">
+        <v>0</v>
+      </c>
+      <c r="IV100" t="inlineStr"/>
+      <c r="IW100" t="inlineStr"/>
+      <c r="IX100" t="inlineStr"/>
+      <c r="IY100" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ100" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA100" t="inlineStr"/>
+      <c r="JB100" t="inlineStr"/>
+      <c r="JC100" t="inlineStr"/>
+      <c r="JD100" t="n">
+        <v>5</v>
+      </c>
+      <c r="JE100" t="n">
+        <v>0.5047576938856736</v>
+      </c>
+      <c r="JF100" t="n">
+        <v>0.3522077125010333</v>
+      </c>
+      <c r="JG100" t="n">
+        <v>0.3631337712018164</v>
+      </c>
+      <c r="JH100" t="n">
+        <v>0.4191596409696104</v>
+      </c>
+      <c r="JI100" t="n">
+        <v>0.2429500984764665</v>
+      </c>
+      <c r="JJ100" t="n">
+        <v>0.306314793000073</v>
+      </c>
+      <c r="JK100" t="n">
+        <v>-0.05088368660113516</v>
+      </c>
+      <c r="JL100" t="n">
+        <v>0.04088516011591245</v>
+      </c>
+      <c r="JM100" t="n">
+        <v>0.0255769494096454</v>
+      </c>
+      <c r="JN100" t="n">
+        <v>0.07381328920070677</v>
+      </c>
+      <c r="JO100" t="n">
+        <v>-0.009999669450996574</v>
+      </c>
+      <c r="JP100" t="n">
+        <v>-0.09317433503250305</v>
+      </c>
+      <c r="JQ100" t="n">
+        <v>0.02584089441312678</v>
+      </c>
+      <c r="JR100" t="n">
+        <v>0.05444288001363257</v>
+      </c>
+      <c r="JS100" t="n">
+        <v>-0.06948947290315236</v>
+      </c>
+      <c r="JT100" t="n">
+        <v>-0.1561467903602244</v>
+      </c>
+      <c r="JU100" t="n">
+        <v>0.05308234308571387</v>
+      </c>
+      <c r="JV100" t="n">
+        <v>0.05091589562273591</v>
+      </c>
+      <c r="JW100" t="n">
+        <v>0.03947610759987309</v>
+      </c>
+      <c r="JX100" t="n">
+        <v>0.09571750744132015</v>
+      </c>
+      <c r="JY100" t="n">
+        <v>-0.04061091627097972</v>
+      </c>
+      <c r="JZ100" t="n">
+        <v>0.07744341815821257</v>
+      </c>
+      <c r="KA100" t="n">
+        <v>0.04481050283827236</v>
+      </c>
+      <c r="KB100" t="n">
+        <v>-0.06502709367754243</v>
+      </c>
+      <c r="KC100" t="n">
+        <v>0.0102469303519359</v>
+      </c>
+      <c r="KD100" t="n">
+        <v>0.03281297804843818</v>
+      </c>
+      <c r="KE100" t="n">
+        <v>0.07153954079144202</v>
+      </c>
+      <c r="KF100" t="n">
+        <v>-0.05768965164333863</v>
+      </c>
+      <c r="KG100" t="n">
+        <v>0.07330208361200566</v>
+      </c>
+      <c r="KH100" t="n">
+        <v>0.1015313654266961</v>
+      </c>
+      <c r="KI100" t="n">
+        <v>-0.0380717111152486</v>
+      </c>
+      <c r="KJ100" t="n">
+        <v>-0.02547986105145224</v>
+      </c>
+      <c r="KK100" t="n">
+        <v>-0.05718294700442099</v>
+      </c>
+      <c r="KL100" t="n">
+        <v>-0.01141059133351519</v>
+      </c>
+      <c r="KM100" t="n">
+        <v>0.1132249416883519</v>
+      </c>
+      <c r="KN100" t="n">
+        <v>0.089531127158931</v>
+      </c>
+      <c r="KO100" t="n">
+        <v>-0.009611050935489727</v>
+      </c>
+      <c r="KP100" t="n">
+        <v>-0.01968043750206132</v>
+      </c>
+      <c r="KQ100" t="n">
+        <v>-0.04113257426077518</v>
+      </c>
+      <c r="KR100" t="n">
+        <v>0.008588537690217033</v>
+      </c>
+      <c r="KS100" t="n">
+        <v>-3.399937922840546e-05</v>
+      </c>
+      <c r="KT100" t="n">
+        <v>0.06177887441234855</v>
+      </c>
+      <c r="KU100" t="n">
+        <v>-0.02518092624815984</v>
+      </c>
+      <c r="KV100" t="n">
+        <v>0.1081780525182884</v>
+      </c>
+      <c r="KW100" t="n">
+        <v>0.05347228334089715</v>
+      </c>
+      <c r="KX100" t="n">
+        <v>0.02279550522285011</v>
+      </c>
+      <c r="KY100" t="n">
+        <v>0.0221609939426596</v>
+      </c>
+      <c r="KZ100" t="n">
+        <v>-0.05978564804449835</v>
+      </c>
+      <c r="LA100" t="n">
+        <v>-0.1136199619395583</v>
+      </c>
+      <c r="LB100" t="n">
+        <v>0.01090908314155258</v>
+      </c>
+      <c r="LC100" t="n">
+        <v>-0.06168929059584678</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-04-22 08:46:56</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>10</v>
+      </c>
+      <c r="C101" t="n">
+        <v>100</v>
+      </c>
+      <c r="D101" t="n">
+        <v>50</v>
+      </c>
+      <c r="E101" t="n">
+        <v>200</v>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>0.1309674614782952</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0.9662902902902903</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0.9684243501793534</v>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0.5128266921273362</v>
+      </c>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr"/>
+      <c r="S101" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="T101" t="n">
+        <v>0.3522046053287754</v>
+      </c>
+      <c r="U101" t="inlineStr"/>
+      <c r="V101" t="inlineStr"/>
+      <c r="W101" t="inlineStr"/>
+      <c r="X101" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>0.497798503723377</v>
+      </c>
+      <c r="Z101" t="inlineStr"/>
+      <c r="AA101" t="inlineStr"/>
+      <c r="AB101" t="inlineStr"/>
+      <c r="AC101" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AD101" t="n">
+        <v>0.4256935492390026</v>
+      </c>
+      <c r="AE101" t="inlineStr"/>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="inlineStr"/>
+      <c r="AH101" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AI101" t="n">
+        <v>0.4283675759600179</v>
+      </c>
+      <c r="AJ101" t="inlineStr"/>
+      <c r="AK101" t="inlineStr"/>
+      <c r="AL101" t="inlineStr"/>
+      <c r="AM101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO101" t="inlineStr"/>
+      <c r="AP101" t="inlineStr"/>
+      <c r="AQ101" t="inlineStr"/>
+      <c r="AR101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AU101" t="inlineStr"/>
+      <c r="AV101" t="inlineStr"/>
+      <c r="AW101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr"/>
+      <c r="BA101" t="inlineStr"/>
+      <c r="BB101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD101" t="inlineStr"/>
+      <c r="BE101" t="inlineStr"/>
+      <c r="BF101" t="inlineStr"/>
+      <c r="BG101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI101" t="inlineStr"/>
+      <c r="BJ101" t="inlineStr"/>
+      <c r="BK101" t="inlineStr"/>
+      <c r="BL101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN101" t="inlineStr"/>
+      <c r="BO101" t="inlineStr"/>
+      <c r="BP101" t="inlineStr"/>
+      <c r="BQ101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS101" t="inlineStr"/>
+      <c r="BT101" t="inlineStr"/>
+      <c r="BU101" t="inlineStr"/>
+      <c r="BV101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX101" t="inlineStr"/>
+      <c r="BY101" t="inlineStr"/>
+      <c r="BZ101" t="inlineStr"/>
+      <c r="CA101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC101" t="inlineStr"/>
+      <c r="CD101" t="inlineStr"/>
+      <c r="CE101" t="inlineStr"/>
+      <c r="CF101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG101" t="n">
+        <v>-0.02106113767444692</v>
+      </c>
+      <c r="CH101" t="inlineStr"/>
+      <c r="CI101" t="inlineStr"/>
+      <c r="CJ101" t="inlineStr"/>
+      <c r="CK101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM101" t="inlineStr"/>
+      <c r="CN101" t="inlineStr"/>
+      <c r="CO101" t="inlineStr"/>
+      <c r="CP101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR101" t="inlineStr"/>
+      <c r="CS101" t="inlineStr"/>
+      <c r="CT101" t="inlineStr"/>
+      <c r="CU101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW101" t="inlineStr"/>
+      <c r="CX101" t="inlineStr"/>
+      <c r="CY101" t="inlineStr"/>
+      <c r="CZ101" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA101" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB101" t="inlineStr"/>
+      <c r="DC101" t="inlineStr"/>
+      <c r="DD101" t="inlineStr"/>
+      <c r="DE101" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF101" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG101" t="inlineStr"/>
+      <c r="DH101" t="inlineStr"/>
+      <c r="DI101" t="inlineStr"/>
+      <c r="DJ101" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK101" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL101" t="inlineStr"/>
+      <c r="DM101" t="inlineStr"/>
+      <c r="DN101" t="inlineStr"/>
+      <c r="DO101" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP101" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ101" t="inlineStr"/>
+      <c r="DR101" t="inlineStr"/>
+      <c r="DS101" t="inlineStr"/>
+      <c r="DT101" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU101" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV101" t="inlineStr"/>
+      <c r="DW101" t="inlineStr"/>
+      <c r="DX101" t="inlineStr"/>
+      <c r="DY101" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ101" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA101" t="inlineStr"/>
+      <c r="EB101" t="inlineStr"/>
+      <c r="EC101" t="inlineStr"/>
+      <c r="ED101" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE101" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF101" t="inlineStr"/>
+      <c r="EG101" t="inlineStr"/>
+      <c r="EH101" t="inlineStr"/>
+      <c r="EI101" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ101" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK101" t="inlineStr"/>
+      <c r="EL101" t="inlineStr"/>
+      <c r="EM101" t="inlineStr"/>
+      <c r="EN101" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO101" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP101" t="inlineStr"/>
+      <c r="EQ101" t="inlineStr"/>
+      <c r="ER101" t="inlineStr"/>
+      <c r="ES101" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET101" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU101" t="inlineStr"/>
+      <c r="EV101" t="inlineStr"/>
+      <c r="EW101" t="inlineStr"/>
+      <c r="EX101" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY101" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ101" t="inlineStr"/>
+      <c r="FA101" t="inlineStr"/>
+      <c r="FB101" t="inlineStr"/>
+      <c r="FC101" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD101" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE101" t="inlineStr"/>
+      <c r="FF101" t="inlineStr"/>
+      <c r="FG101" t="inlineStr"/>
+      <c r="FH101" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI101" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ101" t="inlineStr"/>
+      <c r="FK101" t="inlineStr"/>
+      <c r="FL101" t="inlineStr"/>
+      <c r="FM101" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN101" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO101" t="inlineStr"/>
+      <c r="FP101" t="inlineStr"/>
+      <c r="FQ101" t="inlineStr"/>
+      <c r="FR101" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS101" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT101" t="inlineStr"/>
+      <c r="FU101" t="inlineStr"/>
+      <c r="FV101" t="inlineStr"/>
+      <c r="FW101" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX101" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY101" t="inlineStr"/>
+      <c r="FZ101" t="inlineStr"/>
+      <c r="GA101" t="inlineStr"/>
+      <c r="GB101" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC101" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD101" t="inlineStr"/>
+      <c r="GE101" t="inlineStr"/>
+      <c r="GF101" t="inlineStr"/>
+      <c r="GG101" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH101" t="n">
+        <v>0</v>
+      </c>
+      <c r="GI101" t="inlineStr"/>
+      <c r="GJ101" t="inlineStr"/>
+      <c r="GK101" t="inlineStr"/>
+      <c r="GL101" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM101" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN101" t="inlineStr"/>
+      <c r="GO101" t="inlineStr"/>
+      <c r="GP101" t="inlineStr"/>
+      <c r="GQ101" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR101" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS101" t="inlineStr"/>
+      <c r="GT101" t="inlineStr"/>
+      <c r="GU101" t="inlineStr"/>
+      <c r="GV101" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW101" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX101" t="inlineStr"/>
+      <c r="GY101" t="inlineStr"/>
+      <c r="GZ101" t="inlineStr"/>
+      <c r="HA101" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB101" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC101" t="inlineStr"/>
+      <c r="HD101" t="inlineStr"/>
+      <c r="HE101" t="inlineStr"/>
+      <c r="HF101" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG101" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH101" t="inlineStr"/>
+      <c r="HI101" t="inlineStr"/>
+      <c r="HJ101" t="inlineStr"/>
+      <c r="HK101" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL101" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM101" t="inlineStr"/>
+      <c r="HN101" t="inlineStr"/>
+      <c r="HO101" t="inlineStr"/>
+      <c r="HP101" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ101" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR101" t="inlineStr"/>
+      <c r="HS101" t="inlineStr"/>
+      <c r="HT101" t="inlineStr"/>
+      <c r="HU101" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV101" t="n">
+        <v>0</v>
+      </c>
+      <c r="HW101" t="inlineStr"/>
+      <c r="HX101" t="inlineStr"/>
+      <c r="HY101" t="inlineStr"/>
+      <c r="HZ101" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA101" t="n">
+        <v>0</v>
+      </c>
+      <c r="IB101" t="inlineStr"/>
+      <c r="IC101" t="inlineStr"/>
+      <c r="ID101" t="inlineStr"/>
+      <c r="IE101" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF101" t="n">
+        <v>0</v>
+      </c>
+      <c r="IG101" t="inlineStr"/>
+      <c r="IH101" t="inlineStr"/>
+      <c r="II101" t="inlineStr"/>
+      <c r="IJ101" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK101" t="n">
+        <v>0</v>
+      </c>
+      <c r="IL101" t="inlineStr"/>
+      <c r="IM101" t="inlineStr"/>
+      <c r="IN101" t="inlineStr"/>
+      <c r="IO101" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP101" t="n">
+        <v>0</v>
+      </c>
+      <c r="IQ101" t="inlineStr"/>
+      <c r="IR101" t="inlineStr"/>
+      <c r="IS101" t="inlineStr"/>
+      <c r="IT101" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU101" t="n">
+        <v>0</v>
+      </c>
+      <c r="IV101" t="inlineStr"/>
+      <c r="IW101" t="inlineStr"/>
+      <c r="IX101" t="inlineStr"/>
+      <c r="IY101" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ101" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA101" t="inlineStr"/>
+      <c r="JB101" t="inlineStr"/>
+      <c r="JC101" t="inlineStr"/>
+      <c r="JD101" t="n">
+        <v>5</v>
+      </c>
+      <c r="JE101" t="n">
+        <v>0.4765708233996739</v>
+      </c>
+      <c r="JF101" t="n">
+        <v>0.3687459533762987</v>
+      </c>
+      <c r="JG101" t="n">
+        <v>0.3745617155484849</v>
+      </c>
+      <c r="JH101" t="n">
+        <v>0.4291585151319878</v>
+      </c>
+      <c r="JI101" t="n">
+        <v>0.2426560619898996</v>
+      </c>
+      <c r="JJ101" t="n">
+        <v>0.3130948284771345</v>
+      </c>
+      <c r="JK101" t="n">
+        <v>-0.04847769674798549</v>
+      </c>
+      <c r="JL101" t="n">
+        <v>0.03463113002667773</v>
+      </c>
+      <c r="JM101" t="n">
+        <v>0.02218466323675842</v>
+      </c>
+      <c r="JN101" t="n">
+        <v>0.06497359680983064</v>
+      </c>
+      <c r="JO101" t="n">
+        <v>-0.008291238544682491</v>
+      </c>
+      <c r="JP101" t="n">
+        <v>-0.08694698945672466</v>
+      </c>
+      <c r="JQ101" t="n">
+        <v>0.02179867049616483</v>
+      </c>
+      <c r="JR101" t="n">
+        <v>0.04989606786092601</v>
+      </c>
+      <c r="JS101" t="n">
+        <v>-0.05841632014100836</v>
+      </c>
+      <c r="JT101" t="n">
+        <v>-0.159261835277191</v>
+      </c>
+      <c r="JU101" t="n">
+        <v>0.05315992519856143</v>
+      </c>
+      <c r="JV101" t="n">
+        <v>0.05002918184148167</v>
+      </c>
+      <c r="JW101" t="n">
+        <v>0.03840989900294938</v>
+      </c>
+      <c r="JX101" t="n">
+        <v>0.0873117743269978</v>
+      </c>
+      <c r="JY101" t="n">
+        <v>-0.03270084967588075</v>
+      </c>
+      <c r="JZ101" t="n">
+        <v>0.07272640144395918</v>
+      </c>
+      <c r="KA101" t="n">
+        <v>0.04509768643802805</v>
+      </c>
+      <c r="KB101" t="n">
+        <v>-0.06129056111554758</v>
+      </c>
+      <c r="KC101" t="n">
+        <v>0.005334033260095591</v>
+      </c>
+      <c r="KD101" t="n">
+        <v>0.03462779074461565</v>
+      </c>
+      <c r="KE101" t="n">
+        <v>0.0702631563886302</v>
+      </c>
+      <c r="KF101" t="n">
+        <v>-0.05032674155122147</v>
+      </c>
+      <c r="KG101" t="n">
+        <v>0.06876957546758375</v>
+      </c>
+      <c r="KH101" t="n">
+        <v>0.09451568087352677</v>
+      </c>
+      <c r="KI101" t="n">
+        <v>-0.03620739311909284</v>
+      </c>
+      <c r="KJ101" t="n">
+        <v>-0.02869754936805313</v>
+      </c>
+      <c r="KK101" t="n">
+        <v>-0.05672960634737587</v>
+      </c>
+      <c r="KL101" t="n">
+        <v>-0.009359960152783259</v>
+      </c>
+      <c r="KM101" t="n">
+        <v>0.104703213323389</v>
+      </c>
+      <c r="KN101" t="n">
+        <v>0.08360664032717455</v>
+      </c>
+      <c r="KO101" t="n">
+        <v>-0.01139085925357891</v>
+      </c>
+      <c r="KP101" t="n">
+        <v>-0.02122119885402438</v>
+      </c>
+      <c r="KQ101" t="n">
+        <v>-0.03493698014040063</v>
+      </c>
+      <c r="KR101" t="n">
+        <v>0.002617934267453781</v>
+      </c>
+      <c r="KS101" t="n">
+        <v>0.0005710934137708971</v>
+      </c>
+      <c r="KT101" t="n">
+        <v>0.05860057111578948</v>
+      </c>
+      <c r="KU101" t="n">
+        <v>-0.02597125552723759</v>
+      </c>
+      <c r="KV101" t="n">
+        <v>0.1023742967992988</v>
+      </c>
+      <c r="KW101" t="n">
+        <v>0.0523477239950247</v>
+      </c>
+      <c r="KX101" t="n">
+        <v>0.01536392429464333</v>
+      </c>
+      <c r="KY101" t="n">
+        <v>0.01696913709016393</v>
+      </c>
+      <c r="KZ101" t="n">
+        <v>-0.05206690412279889</v>
+      </c>
+      <c r="LA101" t="n">
+        <v>-0.1000786508214971</v>
+      </c>
+      <c r="LB101" t="n">
+        <v>0.005370216414202744</v>
+      </c>
+      <c r="LC101" t="n">
+        <v>-0.0561018442880184</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-04-22 08:53:58</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>10</v>
+      </c>
+      <c r="C102" t="n">
+        <v>100</v>
+      </c>
+      <c r="D102" t="n">
+        <v>50</v>
+      </c>
+      <c r="E102" t="n">
+        <v>200</v>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>0.1309674614782952</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0.9662902902902903</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0.9684243501793534</v>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0.5128266921273362</v>
+      </c>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr"/>
+      <c r="S102" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="T102" t="n">
+        <v>0.3522046053287754</v>
+      </c>
+      <c r="U102" t="inlineStr"/>
+      <c r="V102" t="inlineStr"/>
+      <c r="W102" t="inlineStr"/>
+      <c r="X102" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>0.497798503723377</v>
+      </c>
+      <c r="Z102" t="inlineStr"/>
+      <c r="AA102" t="inlineStr"/>
+      <c r="AB102" t="inlineStr"/>
+      <c r="AC102" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AD102" t="n">
+        <v>0.4256935492390026</v>
+      </c>
+      <c r="AE102" t="inlineStr"/>
+      <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="inlineStr"/>
+      <c r="AH102" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AI102" t="n">
+        <v>0.4283675759600179</v>
+      </c>
+      <c r="AJ102" t="inlineStr"/>
+      <c r="AK102" t="inlineStr"/>
+      <c r="AL102" t="inlineStr"/>
+      <c r="AM102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO102" t="inlineStr"/>
+      <c r="AP102" t="inlineStr"/>
+      <c r="AQ102" t="inlineStr"/>
+      <c r="AR102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AU102" t="inlineStr"/>
+      <c r="AV102" t="inlineStr"/>
+      <c r="AW102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr"/>
+      <c r="BA102" t="inlineStr"/>
+      <c r="BB102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD102" t="inlineStr"/>
+      <c r="BE102" t="inlineStr"/>
+      <c r="BF102" t="inlineStr"/>
+      <c r="BG102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI102" t="inlineStr"/>
+      <c r="BJ102" t="inlineStr"/>
+      <c r="BK102" t="inlineStr"/>
+      <c r="BL102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN102" t="inlineStr"/>
+      <c r="BO102" t="inlineStr"/>
+      <c r="BP102" t="inlineStr"/>
+      <c r="BQ102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS102" t="inlineStr"/>
+      <c r="BT102" t="inlineStr"/>
+      <c r="BU102" t="inlineStr"/>
+      <c r="BV102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX102" t="inlineStr"/>
+      <c r="BY102" t="inlineStr"/>
+      <c r="BZ102" t="inlineStr"/>
+      <c r="CA102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC102" t="inlineStr"/>
+      <c r="CD102" t="inlineStr"/>
+      <c r="CE102" t="inlineStr"/>
+      <c r="CF102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG102" t="n">
+        <v>-0.02106113767444692</v>
+      </c>
+      <c r="CH102" t="inlineStr"/>
+      <c r="CI102" t="inlineStr"/>
+      <c r="CJ102" t="inlineStr"/>
+      <c r="CK102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM102" t="inlineStr"/>
+      <c r="CN102" t="inlineStr"/>
+      <c r="CO102" t="inlineStr"/>
+      <c r="CP102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR102" t="inlineStr"/>
+      <c r="CS102" t="inlineStr"/>
+      <c r="CT102" t="inlineStr"/>
+      <c r="CU102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW102" t="inlineStr"/>
+      <c r="CX102" t="inlineStr"/>
+      <c r="CY102" t="inlineStr"/>
+      <c r="CZ102" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA102" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB102" t="inlineStr"/>
+      <c r="DC102" t="inlineStr"/>
+      <c r="DD102" t="inlineStr"/>
+      <c r="DE102" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF102" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG102" t="inlineStr"/>
+      <c r="DH102" t="inlineStr"/>
+      <c r="DI102" t="inlineStr"/>
+      <c r="DJ102" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK102" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL102" t="inlineStr"/>
+      <c r="DM102" t="inlineStr"/>
+      <c r="DN102" t="inlineStr"/>
+      <c r="DO102" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP102" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ102" t="inlineStr"/>
+      <c r="DR102" t="inlineStr"/>
+      <c r="DS102" t="inlineStr"/>
+      <c r="DT102" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU102" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV102" t="inlineStr"/>
+      <c r="DW102" t="inlineStr"/>
+      <c r="DX102" t="inlineStr"/>
+      <c r="DY102" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ102" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA102" t="inlineStr"/>
+      <c r="EB102" t="inlineStr"/>
+      <c r="EC102" t="inlineStr"/>
+      <c r="ED102" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE102" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF102" t="inlineStr"/>
+      <c r="EG102" t="inlineStr"/>
+      <c r="EH102" t="inlineStr"/>
+      <c r="EI102" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ102" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK102" t="inlineStr"/>
+      <c r="EL102" t="inlineStr"/>
+      <c r="EM102" t="inlineStr"/>
+      <c r="EN102" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO102" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP102" t="inlineStr"/>
+      <c r="EQ102" t="inlineStr"/>
+      <c r="ER102" t="inlineStr"/>
+      <c r="ES102" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET102" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU102" t="inlineStr"/>
+      <c r="EV102" t="inlineStr"/>
+      <c r="EW102" t="inlineStr"/>
+      <c r="EX102" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY102" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ102" t="inlineStr"/>
+      <c r="FA102" t="inlineStr"/>
+      <c r="FB102" t="inlineStr"/>
+      <c r="FC102" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD102" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE102" t="inlineStr"/>
+      <c r="FF102" t="inlineStr"/>
+      <c r="FG102" t="inlineStr"/>
+      <c r="FH102" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI102" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ102" t="inlineStr"/>
+      <c r="FK102" t="inlineStr"/>
+      <c r="FL102" t="inlineStr"/>
+      <c r="FM102" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN102" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO102" t="inlineStr"/>
+      <c r="FP102" t="inlineStr"/>
+      <c r="FQ102" t="inlineStr"/>
+      <c r="FR102" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS102" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT102" t="inlineStr"/>
+      <c r="FU102" t="inlineStr"/>
+      <c r="FV102" t="inlineStr"/>
+      <c r="FW102" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX102" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY102" t="inlineStr"/>
+      <c r="FZ102" t="inlineStr"/>
+      <c r="GA102" t="inlineStr"/>
+      <c r="GB102" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC102" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD102" t="inlineStr"/>
+      <c r="GE102" t="inlineStr"/>
+      <c r="GF102" t="inlineStr"/>
+      <c r="GG102" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH102" t="n">
+        <v>0</v>
+      </c>
+      <c r="GI102" t="inlineStr"/>
+      <c r="GJ102" t="inlineStr"/>
+      <c r="GK102" t="inlineStr"/>
+      <c r="GL102" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM102" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN102" t="inlineStr"/>
+      <c r="GO102" t="inlineStr"/>
+      <c r="GP102" t="inlineStr"/>
+      <c r="GQ102" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR102" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS102" t="inlineStr"/>
+      <c r="GT102" t="inlineStr"/>
+      <c r="GU102" t="inlineStr"/>
+      <c r="GV102" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW102" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX102" t="inlineStr"/>
+      <c r="GY102" t="inlineStr"/>
+      <c r="GZ102" t="inlineStr"/>
+      <c r="HA102" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB102" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC102" t="inlineStr"/>
+      <c r="HD102" t="inlineStr"/>
+      <c r="HE102" t="inlineStr"/>
+      <c r="HF102" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG102" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH102" t="inlineStr"/>
+      <c r="HI102" t="inlineStr"/>
+      <c r="HJ102" t="inlineStr"/>
+      <c r="HK102" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL102" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM102" t="inlineStr"/>
+      <c r="HN102" t="inlineStr"/>
+      <c r="HO102" t="inlineStr"/>
+      <c r="HP102" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ102" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR102" t="inlineStr"/>
+      <c r="HS102" t="inlineStr"/>
+      <c r="HT102" t="inlineStr"/>
+      <c r="HU102" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV102" t="n">
+        <v>0</v>
+      </c>
+      <c r="HW102" t="inlineStr"/>
+      <c r="HX102" t="inlineStr"/>
+      <c r="HY102" t="inlineStr"/>
+      <c r="HZ102" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA102" t="n">
+        <v>0</v>
+      </c>
+      <c r="IB102" t="inlineStr"/>
+      <c r="IC102" t="inlineStr"/>
+      <c r="ID102" t="inlineStr"/>
+      <c r="IE102" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF102" t="n">
+        <v>0</v>
+      </c>
+      <c r="IG102" t="inlineStr"/>
+      <c r="IH102" t="inlineStr"/>
+      <c r="II102" t="inlineStr"/>
+      <c r="IJ102" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK102" t="n">
+        <v>0</v>
+      </c>
+      <c r="IL102" t="inlineStr"/>
+      <c r="IM102" t="inlineStr"/>
+      <c r="IN102" t="inlineStr"/>
+      <c r="IO102" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP102" t="n">
+        <v>0</v>
+      </c>
+      <c r="IQ102" t="inlineStr"/>
+      <c r="IR102" t="inlineStr"/>
+      <c r="IS102" t="inlineStr"/>
+      <c r="IT102" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU102" t="n">
+        <v>0</v>
+      </c>
+      <c r="IV102" t="inlineStr"/>
+      <c r="IW102" t="inlineStr"/>
+      <c r="IX102" t="inlineStr"/>
+      <c r="IY102" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ102" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA102" t="inlineStr"/>
+      <c r="JB102" t="inlineStr"/>
+      <c r="JC102" t="inlineStr"/>
+      <c r="JD102" t="n">
+        <v>5</v>
+      </c>
+      <c r="JE102" t="n">
+        <v>0.3992034940468153</v>
+      </c>
+      <c r="JF102" t="n">
+        <v>0.430363640808083</v>
+      </c>
+      <c r="JG102" t="n">
+        <v>0.3846200124482571</v>
+      </c>
+      <c r="JH102" t="n">
+        <v>0.429472207856074</v>
+      </c>
+      <c r="JI102" t="n">
+        <v>0.2898340803334979</v>
+      </c>
+      <c r="JJ102" t="n">
+        <v>0.3439472315500453</v>
+      </c>
+      <c r="JK102" t="n">
+        <v>-0.01862046202520664</v>
+      </c>
+      <c r="JL102" t="n">
+        <v>0.03014161648734489</v>
+      </c>
+      <c r="JM102" t="n">
+        <v>0.02819087425422303</v>
+      </c>
+      <c r="JN102" t="n">
+        <v>0.07049000134502494</v>
+      </c>
+      <c r="JO102" t="n">
+        <v>0.001773803326497191</v>
+      </c>
+      <c r="JP102" t="n">
+        <v>-0.08988959528904787</v>
+      </c>
+      <c r="JQ102" t="n">
+        <v>0.0435143655040675</v>
+      </c>
+      <c r="JR102" t="n">
+        <v>-0.03680248691389947</v>
+      </c>
+      <c r="JS102" t="n">
+        <v>-0.03119852023465694</v>
+      </c>
+      <c r="JT102" t="n">
+        <v>-0.1731352198605281</v>
+      </c>
+      <c r="JU102" t="n">
+        <v>0.03221115921369284</v>
+      </c>
+      <c r="JV102" t="n">
+        <v>0.05236603398685587</v>
+      </c>
+      <c r="JW102" t="n">
+        <v>0.02903335545576102</v>
+      </c>
+      <c r="JX102" t="n">
+        <v>0.04853819531585646</v>
+      </c>
+      <c r="JY102" t="n">
+        <v>-0.02277067824723757</v>
+      </c>
+      <c r="JZ102" t="n">
+        <v>0.06269244668711824</v>
+      </c>
+      <c r="KA102" t="n">
+        <v>0.04232548000609161</v>
+      </c>
+      <c r="KB102" t="n">
+        <v>-0.04483448072257958</v>
+      </c>
+      <c r="KC102" t="n">
+        <v>0.009145849451468267</v>
+      </c>
+      <c r="KD102" t="n">
+        <v>0.043584387614716</v>
+      </c>
+      <c r="KE102" t="n">
+        <v>0.0379350527999994</v>
+      </c>
+      <c r="KF102" t="n">
+        <v>-0.06357466920589563</v>
+      </c>
+      <c r="KG102" t="n">
+        <v>0.03364354073343383</v>
+      </c>
+      <c r="KH102" t="n">
+        <v>0.08648236254784104</v>
+      </c>
+      <c r="KI102" t="n">
+        <v>0.001212015845481017</v>
+      </c>
+      <c r="KJ102" t="n">
+        <v>-0.04129060613946224</v>
+      </c>
+      <c r="KK102" t="n">
+        <v>-0.0326665390449225</v>
+      </c>
+      <c r="KL102" t="n">
+        <v>-0.02011706011319318</v>
+      </c>
+      <c r="KM102" t="n">
+        <v>0.07826797623567354</v>
+      </c>
+      <c r="KN102" t="n">
+        <v>0.06623879841646474</v>
+      </c>
+      <c r="KO102" t="n">
+        <v>-0.01478963001539312</v>
+      </c>
+      <c r="KP102" t="n">
+        <v>-0.04488918605486022</v>
+      </c>
+      <c r="KQ102" t="n">
+        <v>-0.007226292730089097</v>
+      </c>
+      <c r="KR102" t="n">
+        <v>0.008823872501672544</v>
+      </c>
+      <c r="KS102" t="n">
+        <v>-0.03800596575854533</v>
+      </c>
+      <c r="KT102" t="n">
+        <v>0.08046869076403648</v>
+      </c>
+      <c r="KU102" t="n">
+        <v>-0.02405789447086921</v>
+      </c>
+      <c r="KV102" t="n">
+        <v>0.08754688423592444</v>
+      </c>
+      <c r="KW102" t="n">
+        <v>0.05249997800227161</v>
+      </c>
+      <c r="KX102" t="n">
+        <v>0.01231550458692005</v>
+      </c>
+      <c r="KY102" t="n">
+        <v>-0.02097889293127191</v>
+      </c>
+      <c r="KZ102" t="n">
+        <v>-0.03183087219685558</v>
+      </c>
+      <c r="LA102" t="n">
+        <v>-0.04324301631268364</v>
+      </c>
+      <c r="LB102" t="n">
+        <v>0.01332143839560011</v>
+      </c>
+      <c r="LC102" t="n">
+        <v>-0.01356881719588433</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-04-22 09:04:28</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>10</v>
+      </c>
+      <c r="C103" t="n">
+        <v>100</v>
+      </c>
+      <c r="D103" t="n">
+        <v>50</v>
+      </c>
+      <c r="E103" t="n">
+        <v>200</v>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>0.1309674614782952</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0.9662902902902903</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0.9684243501793534</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0.5128266921273362</v>
+      </c>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr"/>
+      <c r="S103" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="T103" t="n">
+        <v>0.3522046053287754</v>
+      </c>
+      <c r="U103" t="inlineStr"/>
+      <c r="V103" t="inlineStr"/>
+      <c r="W103" t="inlineStr"/>
+      <c r="X103" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>0.497798503723377</v>
+      </c>
+      <c r="Z103" t="inlineStr"/>
+      <c r="AA103" t="inlineStr"/>
+      <c r="AB103" t="inlineStr"/>
+      <c r="AC103" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AD103" t="n">
+        <v>0.4256935492390026</v>
+      </c>
+      <c r="AE103" t="inlineStr"/>
+      <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="inlineStr"/>
+      <c r="AH103" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AI103" t="n">
+        <v>0.4283675759600179</v>
+      </c>
+      <c r="AJ103" t="inlineStr"/>
+      <c r="AK103" t="inlineStr"/>
+      <c r="AL103" t="inlineStr"/>
+      <c r="AM103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO103" t="inlineStr"/>
+      <c r="AP103" t="inlineStr"/>
+      <c r="AQ103" t="inlineStr"/>
+      <c r="AR103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AU103" t="inlineStr"/>
+      <c r="AV103" t="inlineStr"/>
+      <c r="AW103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr"/>
+      <c r="BA103" t="inlineStr"/>
+      <c r="BB103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD103" t="inlineStr"/>
+      <c r="BE103" t="inlineStr"/>
+      <c r="BF103" t="inlineStr"/>
+      <c r="BG103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI103" t="inlineStr"/>
+      <c r="BJ103" t="inlineStr"/>
+      <c r="BK103" t="inlineStr"/>
+      <c r="BL103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN103" t="inlineStr"/>
+      <c r="BO103" t="inlineStr"/>
+      <c r="BP103" t="inlineStr"/>
+      <c r="BQ103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS103" t="inlineStr"/>
+      <c r="BT103" t="inlineStr"/>
+      <c r="BU103" t="inlineStr"/>
+      <c r="BV103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX103" t="inlineStr"/>
+      <c r="BY103" t="inlineStr"/>
+      <c r="BZ103" t="inlineStr"/>
+      <c r="CA103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC103" t="inlineStr"/>
+      <c r="CD103" t="inlineStr"/>
+      <c r="CE103" t="inlineStr"/>
+      <c r="CF103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG103" t="n">
+        <v>-0.02106113767444692</v>
+      </c>
+      <c r="CH103" t="inlineStr"/>
+      <c r="CI103" t="inlineStr"/>
+      <c r="CJ103" t="inlineStr"/>
+      <c r="CK103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM103" t="inlineStr"/>
+      <c r="CN103" t="inlineStr"/>
+      <c r="CO103" t="inlineStr"/>
+      <c r="CP103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR103" t="inlineStr"/>
+      <c r="CS103" t="inlineStr"/>
+      <c r="CT103" t="inlineStr"/>
+      <c r="CU103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW103" t="inlineStr"/>
+      <c r="CX103" t="inlineStr"/>
+      <c r="CY103" t="inlineStr"/>
+      <c r="CZ103" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA103" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB103" t="inlineStr"/>
+      <c r="DC103" t="inlineStr"/>
+      <c r="DD103" t="inlineStr"/>
+      <c r="DE103" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF103" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG103" t="inlineStr"/>
+      <c r="DH103" t="inlineStr"/>
+      <c r="DI103" t="inlineStr"/>
+      <c r="DJ103" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK103" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL103" t="inlineStr"/>
+      <c r="DM103" t="inlineStr"/>
+      <c r="DN103" t="inlineStr"/>
+      <c r="DO103" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP103" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ103" t="inlineStr"/>
+      <c r="DR103" t="inlineStr"/>
+      <c r="DS103" t="inlineStr"/>
+      <c r="DT103" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU103" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV103" t="inlineStr"/>
+      <c r="DW103" t="inlineStr"/>
+      <c r="DX103" t="inlineStr"/>
+      <c r="DY103" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ103" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA103" t="inlineStr"/>
+      <c r="EB103" t="inlineStr"/>
+      <c r="EC103" t="inlineStr"/>
+      <c r="ED103" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE103" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF103" t="inlineStr"/>
+      <c r="EG103" t="inlineStr"/>
+      <c r="EH103" t="inlineStr"/>
+      <c r="EI103" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ103" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK103" t="inlineStr"/>
+      <c r="EL103" t="inlineStr"/>
+      <c r="EM103" t="inlineStr"/>
+      <c r="EN103" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO103" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP103" t="inlineStr"/>
+      <c r="EQ103" t="inlineStr"/>
+      <c r="ER103" t="inlineStr"/>
+      <c r="ES103" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET103" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU103" t="inlineStr"/>
+      <c r="EV103" t="inlineStr"/>
+      <c r="EW103" t="inlineStr"/>
+      <c r="EX103" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY103" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ103" t="inlineStr"/>
+      <c r="FA103" t="inlineStr"/>
+      <c r="FB103" t="inlineStr"/>
+      <c r="FC103" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD103" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE103" t="inlineStr"/>
+      <c r="FF103" t="inlineStr"/>
+      <c r="FG103" t="inlineStr"/>
+      <c r="FH103" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI103" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ103" t="inlineStr"/>
+      <c r="FK103" t="inlineStr"/>
+      <c r="FL103" t="inlineStr"/>
+      <c r="FM103" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN103" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO103" t="inlineStr"/>
+      <c r="FP103" t="inlineStr"/>
+      <c r="FQ103" t="inlineStr"/>
+      <c r="FR103" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS103" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT103" t="inlineStr"/>
+      <c r="FU103" t="inlineStr"/>
+      <c r="FV103" t="inlineStr"/>
+      <c r="FW103" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX103" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY103" t="inlineStr"/>
+      <c r="FZ103" t="inlineStr"/>
+      <c r="GA103" t="inlineStr"/>
+      <c r="GB103" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC103" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD103" t="inlineStr"/>
+      <c r="GE103" t="inlineStr"/>
+      <c r="GF103" t="inlineStr"/>
+      <c r="GG103" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH103" t="n">
+        <v>0</v>
+      </c>
+      <c r="GI103" t="inlineStr"/>
+      <c r="GJ103" t="inlineStr"/>
+      <c r="GK103" t="inlineStr"/>
+      <c r="GL103" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM103" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN103" t="inlineStr"/>
+      <c r="GO103" t="inlineStr"/>
+      <c r="GP103" t="inlineStr"/>
+      <c r="GQ103" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR103" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS103" t="inlineStr"/>
+      <c r="GT103" t="inlineStr"/>
+      <c r="GU103" t="inlineStr"/>
+      <c r="GV103" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW103" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX103" t="inlineStr"/>
+      <c r="GY103" t="inlineStr"/>
+      <c r="GZ103" t="inlineStr"/>
+      <c r="HA103" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB103" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC103" t="inlineStr"/>
+      <c r="HD103" t="inlineStr"/>
+      <c r="HE103" t="inlineStr"/>
+      <c r="HF103" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG103" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH103" t="inlineStr"/>
+      <c r="HI103" t="inlineStr"/>
+      <c r="HJ103" t="inlineStr"/>
+      <c r="HK103" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL103" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM103" t="inlineStr"/>
+      <c r="HN103" t="inlineStr"/>
+      <c r="HO103" t="inlineStr"/>
+      <c r="HP103" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ103" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR103" t="inlineStr"/>
+      <c r="HS103" t="inlineStr"/>
+      <c r="HT103" t="inlineStr"/>
+      <c r="HU103" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV103" t="n">
+        <v>0</v>
+      </c>
+      <c r="HW103" t="inlineStr"/>
+      <c r="HX103" t="inlineStr"/>
+      <c r="HY103" t="inlineStr"/>
+      <c r="HZ103" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA103" t="n">
+        <v>0</v>
+      </c>
+      <c r="IB103" t="inlineStr"/>
+      <c r="IC103" t="inlineStr"/>
+      <c r="ID103" t="inlineStr"/>
+      <c r="IE103" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF103" t="n">
+        <v>0</v>
+      </c>
+      <c r="IG103" t="inlineStr"/>
+      <c r="IH103" t="inlineStr"/>
+      <c r="II103" t="inlineStr"/>
+      <c r="IJ103" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK103" t="n">
+        <v>0</v>
+      </c>
+      <c r="IL103" t="inlineStr"/>
+      <c r="IM103" t="inlineStr"/>
+      <c r="IN103" t="inlineStr"/>
+      <c r="IO103" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP103" t="n">
+        <v>0</v>
+      </c>
+      <c r="IQ103" t="inlineStr"/>
+      <c r="IR103" t="inlineStr"/>
+      <c r="IS103" t="inlineStr"/>
+      <c r="IT103" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU103" t="n">
+        <v>0</v>
+      </c>
+      <c r="IV103" t="inlineStr"/>
+      <c r="IW103" t="inlineStr"/>
+      <c r="IX103" t="inlineStr"/>
+      <c r="IY103" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ103" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA103" t="inlineStr"/>
+      <c r="JB103" t="inlineStr"/>
+      <c r="JC103" t="inlineStr"/>
+      <c r="JD103" t="n">
+        <v>5</v>
+      </c>
+      <c r="JE103" t="n">
+        <v>1.051462224238267</v>
+      </c>
+      <c r="JF103" t="n">
+        <v>0</v>
+      </c>
+      <c r="JG103" t="n">
+        <v>0</v>
+      </c>
+      <c r="JH103" t="n">
+        <v>1</v>
+      </c>
+      <c r="JI103" t="n">
+        <v>0</v>
+      </c>
+      <c r="JJ103" t="n">
+        <v>0</v>
+      </c>
+      <c r="JK103" t="n">
+        <v>0</v>
+      </c>
+      <c r="JL103" t="n">
+        <v>0</v>
+      </c>
+      <c r="JM103" t="n">
+        <v>0</v>
+      </c>
+      <c r="JN103" t="n">
+        <v>0</v>
+      </c>
+      <c r="JO103" t="n">
+        <v>0</v>
+      </c>
+      <c r="JP103" t="n">
+        <v>0</v>
+      </c>
+      <c r="JQ103" t="n">
+        <v>0</v>
+      </c>
+      <c r="JR103" t="n">
+        <v>0</v>
+      </c>
+      <c r="JS103" t="n">
+        <v>0</v>
+      </c>
+      <c r="JT103" t="n">
+        <v>0</v>
+      </c>
+      <c r="JU103" t="n">
+        <v>0</v>
+      </c>
+      <c r="JV103" t="n">
+        <v>0</v>
+      </c>
+      <c r="JW103" t="n">
+        <v>0</v>
+      </c>
+      <c r="JX103" t="n">
+        <v>0</v>
+      </c>
+      <c r="JY103" t="n">
+        <v>0</v>
+      </c>
+      <c r="JZ103" t="n">
+        <v>0</v>
+      </c>
+      <c r="KA103" t="n">
+        <v>0</v>
+      </c>
+      <c r="KB103" t="n">
+        <v>0</v>
+      </c>
+      <c r="KC103" t="n">
+        <v>0</v>
+      </c>
+      <c r="KD103" t="n">
+        <v>0</v>
+      </c>
+      <c r="KE103" t="n">
+        <v>0</v>
+      </c>
+      <c r="KF103" t="n">
+        <v>0</v>
+      </c>
+      <c r="KG103" t="n">
+        <v>0</v>
+      </c>
+      <c r="KH103" t="n">
+        <v>0</v>
+      </c>
+      <c r="KI103" t="n">
+        <v>0</v>
+      </c>
+      <c r="KJ103" t="n">
+        <v>0</v>
+      </c>
+      <c r="KK103" t="n">
+        <v>0</v>
+      </c>
+      <c r="KL103" t="n">
+        <v>0</v>
+      </c>
+      <c r="KM103" t="n">
+        <v>0</v>
+      </c>
+      <c r="KN103" t="n">
+        <v>0</v>
+      </c>
+      <c r="KO103" t="n">
+        <v>0</v>
+      </c>
+      <c r="KP103" t="n">
+        <v>0</v>
+      </c>
+      <c r="KQ103" t="n">
+        <v>0</v>
+      </c>
+      <c r="KR103" t="n">
+        <v>0</v>
+      </c>
+      <c r="KS103" t="n">
+        <v>0</v>
+      </c>
+      <c r="KT103" t="n">
+        <v>0</v>
+      </c>
+      <c r="KU103" t="n">
+        <v>0</v>
+      </c>
+      <c r="KV103" t="n">
+        <v>0</v>
+      </c>
+      <c r="KW103" t="n">
+        <v>0</v>
+      </c>
+      <c r="KX103" t="n">
+        <v>0</v>
+      </c>
+      <c r="KY103" t="n">
+        <v>0</v>
+      </c>
+      <c r="KZ103" t="n">
+        <v>0</v>
+      </c>
+      <c r="LA103" t="n">
+        <v>0</v>
+      </c>
+      <c r="LB103" t="n">
+        <v>0</v>
+      </c>
+      <c r="LC103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-04-22 09:17:59</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>10</v>
+      </c>
+      <c r="C104" t="n">
+        <v>100</v>
+      </c>
+      <c r="D104" t="n">
+        <v>50</v>
+      </c>
+      <c r="E104" t="n">
+        <v>200</v>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>0.1309674614782952</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0.9662902902902903</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0.9684243501793534</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0.5128266921273362</v>
+      </c>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr"/>
+      <c r="S104" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="T104" t="n">
+        <v>0.3522046053287754</v>
+      </c>
+      <c r="U104" t="inlineStr"/>
+      <c r="V104" t="inlineStr"/>
+      <c r="W104" t="inlineStr"/>
+      <c r="X104" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>0.497798503723377</v>
+      </c>
+      <c r="Z104" t="inlineStr"/>
+      <c r="AA104" t="inlineStr"/>
+      <c r="AB104" t="inlineStr"/>
+      <c r="AC104" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AD104" t="n">
+        <v>0.4256935492390026</v>
+      </c>
+      <c r="AE104" t="inlineStr"/>
+      <c r="AF104" t="inlineStr"/>
+      <c r="AG104" t="inlineStr"/>
+      <c r="AH104" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AI104" t="n">
+        <v>0.4283675759600179</v>
+      </c>
+      <c r="AJ104" t="inlineStr"/>
+      <c r="AK104" t="inlineStr"/>
+      <c r="AL104" t="inlineStr"/>
+      <c r="AM104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO104" t="inlineStr"/>
+      <c r="AP104" t="inlineStr"/>
+      <c r="AQ104" t="inlineStr"/>
+      <c r="AR104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AU104" t="inlineStr"/>
+      <c r="AV104" t="inlineStr"/>
+      <c r="AW104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr"/>
+      <c r="BA104" t="inlineStr"/>
+      <c r="BB104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD104" t="inlineStr"/>
+      <c r="BE104" t="inlineStr"/>
+      <c r="BF104" t="inlineStr"/>
+      <c r="BG104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI104" t="inlineStr"/>
+      <c r="BJ104" t="inlineStr"/>
+      <c r="BK104" t="inlineStr"/>
+      <c r="BL104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN104" t="inlineStr"/>
+      <c r="BO104" t="inlineStr"/>
+      <c r="BP104" t="inlineStr"/>
+      <c r="BQ104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS104" t="inlineStr"/>
+      <c r="BT104" t="inlineStr"/>
+      <c r="BU104" t="inlineStr"/>
+      <c r="BV104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX104" t="inlineStr"/>
+      <c r="BY104" t="inlineStr"/>
+      <c r="BZ104" t="inlineStr"/>
+      <c r="CA104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC104" t="inlineStr"/>
+      <c r="CD104" t="inlineStr"/>
+      <c r="CE104" t="inlineStr"/>
+      <c r="CF104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG104" t="n">
+        <v>-0.02106113767444692</v>
+      </c>
+      <c r="CH104" t="inlineStr"/>
+      <c r="CI104" t="inlineStr"/>
+      <c r="CJ104" t="inlineStr"/>
+      <c r="CK104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM104" t="inlineStr"/>
+      <c r="CN104" t="inlineStr"/>
+      <c r="CO104" t="inlineStr"/>
+      <c r="CP104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR104" t="inlineStr"/>
+      <c r="CS104" t="inlineStr"/>
+      <c r="CT104" t="inlineStr"/>
+      <c r="CU104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW104" t="inlineStr"/>
+      <c r="CX104" t="inlineStr"/>
+      <c r="CY104" t="inlineStr"/>
+      <c r="CZ104" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA104" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB104" t="inlineStr"/>
+      <c r="DC104" t="inlineStr"/>
+      <c r="DD104" t="inlineStr"/>
+      <c r="DE104" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF104" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG104" t="inlineStr"/>
+      <c r="DH104" t="inlineStr"/>
+      <c r="DI104" t="inlineStr"/>
+      <c r="DJ104" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK104" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL104" t="inlineStr"/>
+      <c r="DM104" t="inlineStr"/>
+      <c r="DN104" t="inlineStr"/>
+      <c r="DO104" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP104" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ104" t="inlineStr"/>
+      <c r="DR104" t="inlineStr"/>
+      <c r="DS104" t="inlineStr"/>
+      <c r="DT104" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU104" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV104" t="inlineStr"/>
+      <c r="DW104" t="inlineStr"/>
+      <c r="DX104" t="inlineStr"/>
+      <c r="DY104" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ104" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA104" t="inlineStr"/>
+      <c r="EB104" t="inlineStr"/>
+      <c r="EC104" t="inlineStr"/>
+      <c r="ED104" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE104" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF104" t="inlineStr"/>
+      <c r="EG104" t="inlineStr"/>
+      <c r="EH104" t="inlineStr"/>
+      <c r="EI104" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ104" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK104" t="inlineStr"/>
+      <c r="EL104" t="inlineStr"/>
+      <c r="EM104" t="inlineStr"/>
+      <c r="EN104" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO104" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP104" t="inlineStr"/>
+      <c r="EQ104" t="inlineStr"/>
+      <c r="ER104" t="inlineStr"/>
+      <c r="ES104" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET104" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU104" t="inlineStr"/>
+      <c r="EV104" t="inlineStr"/>
+      <c r="EW104" t="inlineStr"/>
+      <c r="EX104" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY104" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ104" t="inlineStr"/>
+      <c r="FA104" t="inlineStr"/>
+      <c r="FB104" t="inlineStr"/>
+      <c r="FC104" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD104" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE104" t="inlineStr"/>
+      <c r="FF104" t="inlineStr"/>
+      <c r="FG104" t="inlineStr"/>
+      <c r="FH104" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI104" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ104" t="inlineStr"/>
+      <c r="FK104" t="inlineStr"/>
+      <c r="FL104" t="inlineStr"/>
+      <c r="FM104" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN104" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO104" t="inlineStr"/>
+      <c r="FP104" t="inlineStr"/>
+      <c r="FQ104" t="inlineStr"/>
+      <c r="FR104" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS104" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT104" t="inlineStr"/>
+      <c r="FU104" t="inlineStr"/>
+      <c r="FV104" t="inlineStr"/>
+      <c r="FW104" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX104" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY104" t="inlineStr"/>
+      <c r="FZ104" t="inlineStr"/>
+      <c r="GA104" t="inlineStr"/>
+      <c r="GB104" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC104" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD104" t="inlineStr"/>
+      <c r="GE104" t="inlineStr"/>
+      <c r="GF104" t="inlineStr"/>
+      <c r="GG104" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH104" t="n">
+        <v>0</v>
+      </c>
+      <c r="GI104" t="inlineStr"/>
+      <c r="GJ104" t="inlineStr"/>
+      <c r="GK104" t="inlineStr"/>
+      <c r="GL104" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM104" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN104" t="inlineStr"/>
+      <c r="GO104" t="inlineStr"/>
+      <c r="GP104" t="inlineStr"/>
+      <c r="GQ104" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR104" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS104" t="inlineStr"/>
+      <c r="GT104" t="inlineStr"/>
+      <c r="GU104" t="inlineStr"/>
+      <c r="GV104" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW104" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX104" t="inlineStr"/>
+      <c r="GY104" t="inlineStr"/>
+      <c r="GZ104" t="inlineStr"/>
+      <c r="HA104" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB104" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC104" t="inlineStr"/>
+      <c r="HD104" t="inlineStr"/>
+      <c r="HE104" t="inlineStr"/>
+      <c r="HF104" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG104" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH104" t="inlineStr"/>
+      <c r="HI104" t="inlineStr"/>
+      <c r="HJ104" t="inlineStr"/>
+      <c r="HK104" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL104" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM104" t="inlineStr"/>
+      <c r="HN104" t="inlineStr"/>
+      <c r="HO104" t="inlineStr"/>
+      <c r="HP104" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ104" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR104" t="inlineStr"/>
+      <c r="HS104" t="inlineStr"/>
+      <c r="HT104" t="inlineStr"/>
+      <c r="HU104" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV104" t="n">
+        <v>0</v>
+      </c>
+      <c r="HW104" t="inlineStr"/>
+      <c r="HX104" t="inlineStr"/>
+      <c r="HY104" t="inlineStr"/>
+      <c r="HZ104" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA104" t="n">
+        <v>0</v>
+      </c>
+      <c r="IB104" t="inlineStr"/>
+      <c r="IC104" t="inlineStr"/>
+      <c r="ID104" t="inlineStr"/>
+      <c r="IE104" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF104" t="n">
+        <v>0</v>
+      </c>
+      <c r="IG104" t="inlineStr"/>
+      <c r="IH104" t="inlineStr"/>
+      <c r="II104" t="inlineStr"/>
+      <c r="IJ104" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK104" t="n">
+        <v>0</v>
+      </c>
+      <c r="IL104" t="inlineStr"/>
+      <c r="IM104" t="inlineStr"/>
+      <c r="IN104" t="inlineStr"/>
+      <c r="IO104" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP104" t="n">
+        <v>0</v>
+      </c>
+      <c r="IQ104" t="inlineStr"/>
+      <c r="IR104" t="inlineStr"/>
+      <c r="IS104" t="inlineStr"/>
+      <c r="IT104" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU104" t="n">
+        <v>0</v>
+      </c>
+      <c r="IV104" t="inlineStr"/>
+      <c r="IW104" t="inlineStr"/>
+      <c r="IX104" t="inlineStr"/>
+      <c r="IY104" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ104" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA104" t="inlineStr"/>
+      <c r="JB104" t="inlineStr"/>
+      <c r="JC104" t="inlineStr"/>
+      <c r="JD104" t="n">
+        <v>5</v>
+      </c>
+      <c r="JE104" t="n">
+        <v>0.4772980109637561</v>
+      </c>
+      <c r="JF104" t="n">
+        <v>0.6063512388167147</v>
+      </c>
+      <c r="JG104" t="n">
+        <v>0.05238475883749157</v>
+      </c>
+      <c r="JH104" t="n">
+        <v>0.6165780585311385</v>
+      </c>
+      <c r="JI104" t="n">
+        <v>0.3441747699161475</v>
+      </c>
+      <c r="JJ104" t="n">
+        <v>0.3617982975102138</v>
+      </c>
+      <c r="JK104" t="n">
+        <v>9.704572193938761e-05</v>
+      </c>
+      <c r="JL104" t="n">
+        <v>0.0001482701750111976</v>
+      </c>
+      <c r="JM104" t="n">
+        <v>0.0002914696424433022</v>
+      </c>
+      <c r="JN104" t="n">
+        <v>0.0003580765971588898</v>
+      </c>
+      <c r="JO104" t="n">
+        <v>0</v>
+      </c>
+      <c r="JP104" t="n">
+        <v>0</v>
+      </c>
+      <c r="JQ104" t="n">
+        <v>0</v>
+      </c>
+      <c r="JR104" t="n">
+        <v>0</v>
+      </c>
+      <c r="JS104" t="n">
+        <v>0</v>
+      </c>
+      <c r="JT104" t="n">
+        <v>0</v>
+      </c>
+      <c r="JU104" t="n">
+        <v>0.0001449348041355984</v>
+      </c>
+      <c r="JV104" t="n">
+        <v>4.393855404454453e-05</v>
+      </c>
+      <c r="JW104" t="n">
+        <v>0</v>
+      </c>
+      <c r="JX104" t="n">
+        <v>0</v>
+      </c>
+      <c r="JY104" t="n">
+        <v>0.0002182378633411841</v>
+      </c>
+      <c r="JZ104" t="n">
+        <v>0</v>
+      </c>
+      <c r="KA104" t="n">
+        <v>0</v>
+      </c>
+      <c r="KB104" t="n">
+        <v>0.0002223774321637768</v>
+      </c>
+      <c r="KC104" t="n">
+        <v>0</v>
+      </c>
+      <c r="KD104" t="n">
+        <v>-0.0004568208870296003</v>
+      </c>
+      <c r="KE104" t="n">
+        <v>2.399746371530633e-05</v>
+      </c>
+      <c r="KF104" t="n">
+        <v>-0.0003486656810820396</v>
+      </c>
+      <c r="KG104" t="n">
+        <v>0</v>
+      </c>
+      <c r="KH104" t="n">
+        <v>3.791972475505479e-06</v>
+      </c>
+      <c r="KI104" t="n">
+        <v>0</v>
+      </c>
+      <c r="KJ104" t="n">
+        <v>0</v>
+      </c>
+      <c r="KK104" t="n">
+        <v>0</v>
+      </c>
+      <c r="KL104" t="n">
+        <v>-1.18753642309836e-05</v>
+      </c>
+      <c r="KM104" t="n">
+        <v>5.380225709897396e-05</v>
+      </c>
+      <c r="KN104" t="n">
+        <v>0.0002544470406766452</v>
+      </c>
+      <c r="KO104" t="n">
+        <v>0.0001082757804655983</v>
+      </c>
+      <c r="KP104" t="n">
+        <v>3.220586099229581e-05</v>
+      </c>
+      <c r="KQ104" t="n">
+        <v>5.941965819237467e-05</v>
+      </c>
+      <c r="KR104" t="n">
+        <v>0</v>
+      </c>
+      <c r="KS104" t="n">
+        <v>0</v>
+      </c>
+      <c r="KT104" t="n">
+        <v>0</v>
+      </c>
+      <c r="KU104" t="n">
+        <v>-0.0009426956541049835</v>
+      </c>
+      <c r="KV104" t="n">
+        <v>0.0001391356053204909</v>
+      </c>
+      <c r="KW104" t="n">
+        <v>6.663662441172583e-05</v>
+      </c>
+      <c r="KX104" t="n">
+        <v>-7.121764211486602e-05</v>
+      </c>
+      <c r="KY104" t="n">
+        <v>0</v>
+      </c>
+      <c r="KZ104" t="n">
+        <v>0</v>
+      </c>
+      <c r="LA104" t="n">
+        <v>1.978630834228543e-05</v>
+      </c>
+      <c r="LB104" t="n">
+        <v>0</v>
+      </c>
+      <c r="LC104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-04-22 10:14:43</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>10</v>
+      </c>
+      <c r="C105" t="n">
+        <v>100</v>
+      </c>
+      <c r="D105" t="n">
+        <v>50</v>
+      </c>
+      <c r="E105" t="n">
+        <v>200</v>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>0.1309674614782952</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0.9662902902902903</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0.9684243501793534</v>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0.5128266921273362</v>
+      </c>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr"/>
+      <c r="S105" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="T105" t="n">
+        <v>0.3522046053287754</v>
+      </c>
+      <c r="U105" t="inlineStr"/>
+      <c r="V105" t="inlineStr"/>
+      <c r="W105" t="inlineStr"/>
+      <c r="X105" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>0.497798503723377</v>
+      </c>
+      <c r="Z105" t="inlineStr"/>
+      <c r="AA105" t="inlineStr"/>
+      <c r="AB105" t="inlineStr"/>
+      <c r="AC105" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AD105" t="n">
+        <v>0.4256935492390026</v>
+      </c>
+      <c r="AE105" t="inlineStr"/>
+      <c r="AF105" t="inlineStr"/>
+      <c r="AG105" t="inlineStr"/>
+      <c r="AH105" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AI105" t="n">
+        <v>0.4283675759600179</v>
+      </c>
+      <c r="AJ105" t="inlineStr"/>
+      <c r="AK105" t="inlineStr"/>
+      <c r="AL105" t="inlineStr"/>
+      <c r="AM105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO105" t="inlineStr"/>
+      <c r="AP105" t="inlineStr"/>
+      <c r="AQ105" t="inlineStr"/>
+      <c r="AR105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AU105" t="inlineStr"/>
+      <c r="AV105" t="inlineStr"/>
+      <c r="AW105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr"/>
+      <c r="BA105" t="inlineStr"/>
+      <c r="BB105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD105" t="inlineStr"/>
+      <c r="BE105" t="inlineStr"/>
+      <c r="BF105" t="inlineStr"/>
+      <c r="BG105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI105" t="inlineStr"/>
+      <c r="BJ105" t="inlineStr"/>
+      <c r="BK105" t="inlineStr"/>
+      <c r="BL105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN105" t="inlineStr"/>
+      <c r="BO105" t="inlineStr"/>
+      <c r="BP105" t="inlineStr"/>
+      <c r="BQ105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS105" t="inlineStr"/>
+      <c r="BT105" t="inlineStr"/>
+      <c r="BU105" t="inlineStr"/>
+      <c r="BV105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX105" t="inlineStr"/>
+      <c r="BY105" t="inlineStr"/>
+      <c r="BZ105" t="inlineStr"/>
+      <c r="CA105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC105" t="inlineStr"/>
+      <c r="CD105" t="inlineStr"/>
+      <c r="CE105" t="inlineStr"/>
+      <c r="CF105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG105" t="n">
+        <v>-0.02106113767444692</v>
+      </c>
+      <c r="CH105" t="inlineStr"/>
+      <c r="CI105" t="inlineStr"/>
+      <c r="CJ105" t="inlineStr"/>
+      <c r="CK105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM105" t="inlineStr"/>
+      <c r="CN105" t="inlineStr"/>
+      <c r="CO105" t="inlineStr"/>
+      <c r="CP105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR105" t="inlineStr"/>
+      <c r="CS105" t="inlineStr"/>
+      <c r="CT105" t="inlineStr"/>
+      <c r="CU105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW105" t="inlineStr"/>
+      <c r="CX105" t="inlineStr"/>
+      <c r="CY105" t="inlineStr"/>
+      <c r="CZ105" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA105" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB105" t="inlineStr"/>
+      <c r="DC105" t="inlineStr"/>
+      <c r="DD105" t="inlineStr"/>
+      <c r="DE105" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF105" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG105" t="inlineStr"/>
+      <c r="DH105" t="inlineStr"/>
+      <c r="DI105" t="inlineStr"/>
+      <c r="DJ105" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK105" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL105" t="inlineStr"/>
+      <c r="DM105" t="inlineStr"/>
+      <c r="DN105" t="inlineStr"/>
+      <c r="DO105" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP105" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ105" t="inlineStr"/>
+      <c r="DR105" t="inlineStr"/>
+      <c r="DS105" t="inlineStr"/>
+      <c r="DT105" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU105" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV105" t="inlineStr"/>
+      <c r="DW105" t="inlineStr"/>
+      <c r="DX105" t="inlineStr"/>
+      <c r="DY105" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ105" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA105" t="inlineStr"/>
+      <c r="EB105" t="inlineStr"/>
+      <c r="EC105" t="inlineStr"/>
+      <c r="ED105" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE105" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF105" t="inlineStr"/>
+      <c r="EG105" t="inlineStr"/>
+      <c r="EH105" t="inlineStr"/>
+      <c r="EI105" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ105" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK105" t="inlineStr"/>
+      <c r="EL105" t="inlineStr"/>
+      <c r="EM105" t="inlineStr"/>
+      <c r="EN105" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO105" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP105" t="inlineStr"/>
+      <c r="EQ105" t="inlineStr"/>
+      <c r="ER105" t="inlineStr"/>
+      <c r="ES105" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET105" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU105" t="inlineStr"/>
+      <c r="EV105" t="inlineStr"/>
+      <c r="EW105" t="inlineStr"/>
+      <c r="EX105" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY105" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ105" t="inlineStr"/>
+      <c r="FA105" t="inlineStr"/>
+      <c r="FB105" t="inlineStr"/>
+      <c r="FC105" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD105" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE105" t="inlineStr"/>
+      <c r="FF105" t="inlineStr"/>
+      <c r="FG105" t="inlineStr"/>
+      <c r="FH105" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI105" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ105" t="inlineStr"/>
+      <c r="FK105" t="inlineStr"/>
+      <c r="FL105" t="inlineStr"/>
+      <c r="FM105" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN105" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO105" t="inlineStr"/>
+      <c r="FP105" t="inlineStr"/>
+      <c r="FQ105" t="inlineStr"/>
+      <c r="FR105" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS105" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT105" t="inlineStr"/>
+      <c r="FU105" t="inlineStr"/>
+      <c r="FV105" t="inlineStr"/>
+      <c r="FW105" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX105" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY105" t="inlineStr"/>
+      <c r="FZ105" t="inlineStr"/>
+      <c r="GA105" t="inlineStr"/>
+      <c r="GB105" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC105" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD105" t="inlineStr"/>
+      <c r="GE105" t="inlineStr"/>
+      <c r="GF105" t="inlineStr"/>
+      <c r="GG105" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH105" t="n">
+        <v>0</v>
+      </c>
+      <c r="GI105" t="inlineStr"/>
+      <c r="GJ105" t="inlineStr"/>
+      <c r="GK105" t="inlineStr"/>
+      <c r="GL105" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM105" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN105" t="inlineStr"/>
+      <c r="GO105" t="inlineStr"/>
+      <c r="GP105" t="inlineStr"/>
+      <c r="GQ105" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR105" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS105" t="inlineStr"/>
+      <c r="GT105" t="inlineStr"/>
+      <c r="GU105" t="inlineStr"/>
+      <c r="GV105" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW105" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX105" t="inlineStr"/>
+      <c r="GY105" t="inlineStr"/>
+      <c r="GZ105" t="inlineStr"/>
+      <c r="HA105" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB105" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC105" t="inlineStr"/>
+      <c r="HD105" t="inlineStr"/>
+      <c r="HE105" t="inlineStr"/>
+      <c r="HF105" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG105" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH105" t="inlineStr"/>
+      <c r="HI105" t="inlineStr"/>
+      <c r="HJ105" t="inlineStr"/>
+      <c r="HK105" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL105" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM105" t="inlineStr"/>
+      <c r="HN105" t="inlineStr"/>
+      <c r="HO105" t="inlineStr"/>
+      <c r="HP105" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ105" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR105" t="inlineStr"/>
+      <c r="HS105" t="inlineStr"/>
+      <c r="HT105" t="inlineStr"/>
+      <c r="HU105" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV105" t="n">
+        <v>0</v>
+      </c>
+      <c r="HW105" t="inlineStr"/>
+      <c r="HX105" t="inlineStr"/>
+      <c r="HY105" t="inlineStr"/>
+      <c r="HZ105" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA105" t="n">
+        <v>0</v>
+      </c>
+      <c r="IB105" t="inlineStr"/>
+      <c r="IC105" t="inlineStr"/>
+      <c r="ID105" t="inlineStr"/>
+      <c r="IE105" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF105" t="n">
+        <v>0</v>
+      </c>
+      <c r="IG105" t="inlineStr"/>
+      <c r="IH105" t="inlineStr"/>
+      <c r="II105" t="inlineStr"/>
+      <c r="IJ105" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK105" t="n">
+        <v>0</v>
+      </c>
+      <c r="IL105" t="inlineStr"/>
+      <c r="IM105" t="inlineStr"/>
+      <c r="IN105" t="inlineStr"/>
+      <c r="IO105" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP105" t="n">
+        <v>0</v>
+      </c>
+      <c r="IQ105" t="inlineStr"/>
+      <c r="IR105" t="inlineStr"/>
+      <c r="IS105" t="inlineStr"/>
+      <c r="IT105" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU105" t="n">
+        <v>0</v>
+      </c>
+      <c r="IV105" t="inlineStr"/>
+      <c r="IW105" t="inlineStr"/>
+      <c r="IX105" t="inlineStr"/>
+      <c r="IY105" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ105" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA105" t="inlineStr"/>
+      <c r="JB105" t="inlineStr"/>
+      <c r="JC105" t="inlineStr"/>
+      <c r="JD105" t="n">
+        <v>5</v>
+      </c>
+      <c r="JE105" t="n">
+        <v>0.3241792844913579</v>
+      </c>
+      <c r="JF105" t="n">
+        <v>0.4570464713458618</v>
+      </c>
+      <c r="JG105" t="n">
+        <v>0.3969452377100968</v>
+      </c>
+      <c r="JH105" t="n">
+        <v>0.4425127669981145</v>
+      </c>
+      <c r="JI105" t="n">
+        <v>0.4175896162728797</v>
+      </c>
+      <c r="JJ105" t="n">
+        <v>0.4037405306476526</v>
+      </c>
+      <c r="JK105" t="n">
+        <v>0.001883186822246266</v>
+      </c>
+      <c r="JL105" t="n">
+        <v>0.06179548123226593</v>
+      </c>
+      <c r="JM105" t="n">
+        <v>0.05665374423458978</v>
+      </c>
+      <c r="JN105" t="n">
+        <v>0.127798860659619</v>
+      </c>
+      <c r="JO105" t="n">
+        <v>-0.0005527403335011504</v>
+      </c>
+      <c r="JP105" t="n">
+        <v>-0.1143542710738193</v>
+      </c>
+      <c r="JQ105" t="n">
+        <v>0.004539268625601669</v>
+      </c>
+      <c r="JR105" t="n">
+        <v>-0.001954506525842352</v>
+      </c>
+      <c r="JS105" t="n">
+        <v>0.0006663936844838488</v>
+      </c>
+      <c r="JT105" t="n">
+        <v>-0.1229843292948814</v>
+      </c>
+      <c r="JU105" t="n">
+        <v>0.004638153862185334</v>
+      </c>
+      <c r="JV105" t="n">
+        <v>0.04751024085227594</v>
+      </c>
+      <c r="JW105" t="n">
+        <v>-0.0008559340267932734</v>
+      </c>
+      <c r="JX105" t="n">
+        <v>0.05784183853099204</v>
+      </c>
+      <c r="JY105" t="n">
+        <v>-0.002318292919861099</v>
+      </c>
+      <c r="JZ105" t="n">
+        <v>0.0009524275847331648</v>
+      </c>
+      <c r="KA105" t="n">
+        <v>0.002565974188247144</v>
+      </c>
+      <c r="KB105" t="n">
+        <v>-0.01681800008316379</v>
+      </c>
+      <c r="KC105" t="n">
+        <v>-0.0001868434060453706</v>
+      </c>
+      <c r="KD105" t="n">
+        <v>-0.02245604586856667</v>
+      </c>
+      <c r="KE105" t="n">
+        <v>-0.001160296907681224</v>
+      </c>
+      <c r="KF105" t="n">
+        <v>-0.1032386103616744</v>
+      </c>
+      <c r="KG105" t="n">
+        <v>-0.0005231122575973725</v>
+      </c>
+      <c r="KH105" t="n">
+        <v>0.0433413710095452</v>
+      </c>
+      <c r="KI105" t="n">
+        <v>-0.001290797582659177</v>
+      </c>
+      <c r="KJ105" t="n">
+        <v>-0.02810339261865388</v>
+      </c>
+      <c r="KK105" t="n">
+        <v>-0.01300549838627558</v>
+      </c>
+      <c r="KL105" t="n">
+        <v>-0.0426705695029506</v>
+      </c>
+      <c r="KM105" t="n">
+        <v>0.05230339983946834</v>
+      </c>
+      <c r="KN105" t="n">
+        <v>0.1061135078796943</v>
+      </c>
+      <c r="KO105" t="n">
+        <v>0.0009280038667421452</v>
+      </c>
+      <c r="KP105" t="n">
+        <v>-0.002313660529512462</v>
+      </c>
+      <c r="KQ105" t="n">
+        <v>-0.0002441379691545926</v>
+      </c>
+      <c r="KR105" t="n">
+        <v>0.002725588516278705</v>
+      </c>
+      <c r="KS105" t="n">
+        <v>-0.006710578097584345</v>
+      </c>
+      <c r="KT105" t="n">
+        <v>0.004439957037519181</v>
+      </c>
+      <c r="KU105" t="n">
+        <v>-0.08218302932821801</v>
+      </c>
+      <c r="KV105" t="n">
+        <v>0.04256750763326109</v>
+      </c>
+      <c r="KW105" t="n">
+        <v>0.004935517230993731</v>
+      </c>
+      <c r="KX105" t="n">
+        <v>-0.001684317914994348</v>
+      </c>
+      <c r="KY105" t="n">
+        <v>-0.001219018664400665</v>
+      </c>
+      <c r="KZ105" t="n">
+        <v>0.0006578805834460144</v>
+      </c>
+      <c r="LA105" t="n">
+        <v>-0.0604783823890471</v>
+      </c>
+      <c r="LB105" t="n">
+        <v>0.003944881171827484</v>
+      </c>
+      <c r="LC105" t="n">
+        <v>-6.237251040373975e-05</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-04-22 10:24:23</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>10</v>
+      </c>
+      <c r="C106" t="n">
+        <v>100</v>
+      </c>
+      <c r="D106" t="n">
+        <v>50</v>
+      </c>
+      <c r="E106" t="n">
+        <v>200</v>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>0.1309674614782952</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0.9662902902902903</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0.9684243501793534</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0.5128266921273362</v>
+      </c>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr"/>
+      <c r="S106" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="T106" t="n">
+        <v>0.3522046053287754</v>
+      </c>
+      <c r="U106" t="inlineStr"/>
+      <c r="V106" t="inlineStr"/>
+      <c r="W106" t="inlineStr"/>
+      <c r="X106" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>0.497798503723377</v>
+      </c>
+      <c r="Z106" t="inlineStr"/>
+      <c r="AA106" t="inlineStr"/>
+      <c r="AB106" t="inlineStr"/>
+      <c r="AC106" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AD106" t="n">
+        <v>0.4256935492390026</v>
+      </c>
+      <c r="AE106" t="inlineStr"/>
+      <c r="AF106" t="inlineStr"/>
+      <c r="AG106" t="inlineStr"/>
+      <c r="AH106" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AI106" t="n">
+        <v>0.4283675759600179</v>
+      </c>
+      <c r="AJ106" t="inlineStr"/>
+      <c r="AK106" t="inlineStr"/>
+      <c r="AL106" t="inlineStr"/>
+      <c r="AM106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO106" t="inlineStr"/>
+      <c r="AP106" t="inlineStr"/>
+      <c r="AQ106" t="inlineStr"/>
+      <c r="AR106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AU106" t="inlineStr"/>
+      <c r="AV106" t="inlineStr"/>
+      <c r="AW106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr"/>
+      <c r="BA106" t="inlineStr"/>
+      <c r="BB106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD106" t="inlineStr"/>
+      <c r="BE106" t="inlineStr"/>
+      <c r="BF106" t="inlineStr"/>
+      <c r="BG106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI106" t="inlineStr"/>
+      <c r="BJ106" t="inlineStr"/>
+      <c r="BK106" t="inlineStr"/>
+      <c r="BL106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN106" t="inlineStr"/>
+      <c r="BO106" t="inlineStr"/>
+      <c r="BP106" t="inlineStr"/>
+      <c r="BQ106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS106" t="inlineStr"/>
+      <c r="BT106" t="inlineStr"/>
+      <c r="BU106" t="inlineStr"/>
+      <c r="BV106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX106" t="inlineStr"/>
+      <c r="BY106" t="inlineStr"/>
+      <c r="BZ106" t="inlineStr"/>
+      <c r="CA106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC106" t="inlineStr"/>
+      <c r="CD106" t="inlineStr"/>
+      <c r="CE106" t="inlineStr"/>
+      <c r="CF106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG106" t="n">
+        <v>-0.02106113767444692</v>
+      </c>
+      <c r="CH106" t="inlineStr"/>
+      <c r="CI106" t="inlineStr"/>
+      <c r="CJ106" t="inlineStr"/>
+      <c r="CK106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM106" t="inlineStr"/>
+      <c r="CN106" t="inlineStr"/>
+      <c r="CO106" t="inlineStr"/>
+      <c r="CP106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR106" t="inlineStr"/>
+      <c r="CS106" t="inlineStr"/>
+      <c r="CT106" t="inlineStr"/>
+      <c r="CU106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW106" t="inlineStr"/>
+      <c r="CX106" t="inlineStr"/>
+      <c r="CY106" t="inlineStr"/>
+      <c r="CZ106" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA106" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB106" t="inlineStr"/>
+      <c r="DC106" t="inlineStr"/>
+      <c r="DD106" t="inlineStr"/>
+      <c r="DE106" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF106" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG106" t="inlineStr"/>
+      <c r="DH106" t="inlineStr"/>
+      <c r="DI106" t="inlineStr"/>
+      <c r="DJ106" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK106" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL106" t="inlineStr"/>
+      <c r="DM106" t="inlineStr"/>
+      <c r="DN106" t="inlineStr"/>
+      <c r="DO106" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP106" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ106" t="inlineStr"/>
+      <c r="DR106" t="inlineStr"/>
+      <c r="DS106" t="inlineStr"/>
+      <c r="DT106" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU106" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV106" t="inlineStr"/>
+      <c r="DW106" t="inlineStr"/>
+      <c r="DX106" t="inlineStr"/>
+      <c r="DY106" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ106" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA106" t="inlineStr"/>
+      <c r="EB106" t="inlineStr"/>
+      <c r="EC106" t="inlineStr"/>
+      <c r="ED106" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE106" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF106" t="inlineStr"/>
+      <c r="EG106" t="inlineStr"/>
+      <c r="EH106" t="inlineStr"/>
+      <c r="EI106" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ106" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK106" t="inlineStr"/>
+      <c r="EL106" t="inlineStr"/>
+      <c r="EM106" t="inlineStr"/>
+      <c r="EN106" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO106" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP106" t="inlineStr"/>
+      <c r="EQ106" t="inlineStr"/>
+      <c r="ER106" t="inlineStr"/>
+      <c r="ES106" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET106" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU106" t="inlineStr"/>
+      <c r="EV106" t="inlineStr"/>
+      <c r="EW106" t="inlineStr"/>
+      <c r="EX106" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY106" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ106" t="inlineStr"/>
+      <c r="FA106" t="inlineStr"/>
+      <c r="FB106" t="inlineStr"/>
+      <c r="FC106" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD106" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE106" t="inlineStr"/>
+      <c r="FF106" t="inlineStr"/>
+      <c r="FG106" t="inlineStr"/>
+      <c r="FH106" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI106" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ106" t="inlineStr"/>
+      <c r="FK106" t="inlineStr"/>
+      <c r="FL106" t="inlineStr"/>
+      <c r="FM106" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN106" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO106" t="inlineStr"/>
+      <c r="FP106" t="inlineStr"/>
+      <c r="FQ106" t="inlineStr"/>
+      <c r="FR106" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS106" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT106" t="inlineStr"/>
+      <c r="FU106" t="inlineStr"/>
+      <c r="FV106" t="inlineStr"/>
+      <c r="FW106" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX106" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY106" t="inlineStr"/>
+      <c r="FZ106" t="inlineStr"/>
+      <c r="GA106" t="inlineStr"/>
+      <c r="GB106" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC106" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD106" t="inlineStr"/>
+      <c r="GE106" t="inlineStr"/>
+      <c r="GF106" t="inlineStr"/>
+      <c r="GG106" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH106" t="n">
+        <v>0</v>
+      </c>
+      <c r="GI106" t="inlineStr"/>
+      <c r="GJ106" t="inlineStr"/>
+      <c r="GK106" t="inlineStr"/>
+      <c r="GL106" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM106" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN106" t="inlineStr"/>
+      <c r="GO106" t="inlineStr"/>
+      <c r="GP106" t="inlineStr"/>
+      <c r="GQ106" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR106" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS106" t="inlineStr"/>
+      <c r="GT106" t="inlineStr"/>
+      <c r="GU106" t="inlineStr"/>
+      <c r="GV106" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW106" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX106" t="inlineStr"/>
+      <c r="GY106" t="inlineStr"/>
+      <c r="GZ106" t="inlineStr"/>
+      <c r="HA106" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB106" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC106" t="inlineStr"/>
+      <c r="HD106" t="inlineStr"/>
+      <c r="HE106" t="inlineStr"/>
+      <c r="HF106" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG106" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH106" t="inlineStr"/>
+      <c r="HI106" t="inlineStr"/>
+      <c r="HJ106" t="inlineStr"/>
+      <c r="HK106" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL106" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM106" t="inlineStr"/>
+      <c r="HN106" t="inlineStr"/>
+      <c r="HO106" t="inlineStr"/>
+      <c r="HP106" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ106" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR106" t="inlineStr"/>
+      <c r="HS106" t="inlineStr"/>
+      <c r="HT106" t="inlineStr"/>
+      <c r="HU106" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV106" t="n">
+        <v>0</v>
+      </c>
+      <c r="HW106" t="inlineStr"/>
+      <c r="HX106" t="inlineStr"/>
+      <c r="HY106" t="inlineStr"/>
+      <c r="HZ106" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA106" t="n">
+        <v>0</v>
+      </c>
+      <c r="IB106" t="inlineStr"/>
+      <c r="IC106" t="inlineStr"/>
+      <c r="ID106" t="inlineStr"/>
+      <c r="IE106" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF106" t="n">
+        <v>0</v>
+      </c>
+      <c r="IG106" t="inlineStr"/>
+      <c r="IH106" t="inlineStr"/>
+      <c r="II106" t="inlineStr"/>
+      <c r="IJ106" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK106" t="n">
+        <v>0</v>
+      </c>
+      <c r="IL106" t="inlineStr"/>
+      <c r="IM106" t="inlineStr"/>
+      <c r="IN106" t="inlineStr"/>
+      <c r="IO106" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP106" t="n">
+        <v>0</v>
+      </c>
+      <c r="IQ106" t="inlineStr"/>
+      <c r="IR106" t="inlineStr"/>
+      <c r="IS106" t="inlineStr"/>
+      <c r="IT106" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU106" t="n">
+        <v>0</v>
+      </c>
+      <c r="IV106" t="inlineStr"/>
+      <c r="IW106" t="inlineStr"/>
+      <c r="IX106" t="inlineStr"/>
+      <c r="IY106" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ106" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA106" t="inlineStr"/>
+      <c r="JB106" t="inlineStr"/>
+      <c r="JC106" t="inlineStr"/>
+      <c r="JD106" t="n">
+        <v>5</v>
+      </c>
+      <c r="JE106" t="n">
+        <v>0.3224166928100825</v>
+      </c>
+      <c r="JF106" t="n">
+        <v>0.4560727008205214</v>
+      </c>
+      <c r="JG106" t="n">
+        <v>0.3959071434238662</v>
+      </c>
+      <c r="JH106" t="n">
+        <v>0.4424415271946069</v>
+      </c>
+      <c r="JI106" t="n">
+        <v>0.4180478475983545</v>
+      </c>
+      <c r="JJ106" t="n">
+        <v>0.4047231661747006</v>
+      </c>
+      <c r="JK106" t="n">
+        <v>0.003422169084252399</v>
+      </c>
+      <c r="JL106" t="n">
+        <v>0.06150648936526152</v>
+      </c>
+      <c r="JM106" t="n">
+        <v>0.05387833495532111</v>
+      </c>
+      <c r="JN106" t="n">
+        <v>0.1263875253828085</v>
+      </c>
+      <c r="JO106" t="n">
+        <v>-0.001175154726391611</v>
+      </c>
+      <c r="JP106" t="n">
+        <v>-0.1114382869445422</v>
+      </c>
+      <c r="JQ106" t="n">
+        <v>0.008220999686192802</v>
+      </c>
+      <c r="JR106" t="n">
+        <v>-0.003180169720072009</v>
+      </c>
+      <c r="JS106" t="n">
+        <v>0.0012191742448338</v>
+      </c>
+      <c r="JT106" t="n">
+        <v>-0.122313343687167</v>
+      </c>
+      <c r="JU106" t="n">
+        <v>0.007919871796831821</v>
+      </c>
+      <c r="JV106" t="n">
+        <v>0.04793995083294687</v>
+      </c>
+      <c r="JW106" t="n">
+        <v>-0.001651884110004892</v>
+      </c>
+      <c r="JX106" t="n">
+        <v>0.05730321072788005</v>
+      </c>
+      <c r="JY106" t="n">
+        <v>-0.004012543812832789</v>
+      </c>
+      <c r="JZ106" t="n">
+        <v>0.001720006668434046</v>
+      </c>
+      <c r="KA106" t="n">
+        <v>0.004182079945218749</v>
+      </c>
+      <c r="KB106" t="n">
+        <v>-0.02083779867494101</v>
+      </c>
+      <c r="KC106" t="n">
+        <v>0.0005413550980427175</v>
+      </c>
+      <c r="KD106" t="n">
+        <v>-0.0214066839024115</v>
+      </c>
+      <c r="KE106" t="n">
+        <v>-0.00139724767701508</v>
+      </c>
+      <c r="KF106" t="n">
+        <v>-0.104467396355409</v>
+      </c>
+      <c r="KG106" t="n">
+        <v>-0.001287831639165833</v>
+      </c>
+      <c r="KH106" t="n">
+        <v>0.0433302647057197</v>
+      </c>
+      <c r="KI106" t="n">
+        <v>-0.00247158289709276</v>
+      </c>
+      <c r="KJ106" t="n">
+        <v>-0.02782036541449457</v>
+      </c>
+      <c r="KK106" t="n">
+        <v>-0.01184488737949215</v>
+      </c>
+      <c r="KL106" t="n">
+        <v>-0.04271262210909572</v>
+      </c>
+      <c r="KM106" t="n">
+        <v>0.05140303427539685</v>
+      </c>
+      <c r="KN106" t="n">
+        <v>0.105632031294014</v>
+      </c>
+      <c r="KO106" t="n">
+        <v>0.001262630938823786</v>
+      </c>
+      <c r="KP106" t="n">
+        <v>-0.004536693615723208</v>
+      </c>
+      <c r="KQ106" t="n">
+        <v>-0.0001675936758648935</v>
+      </c>
+      <c r="KR106" t="n">
+        <v>0.004741168180535766</v>
+      </c>
+      <c r="KS106" t="n">
+        <v>-0.01203414726033895</v>
+      </c>
+      <c r="KT106" t="n">
+        <v>0.008390604721835986</v>
+      </c>
+      <c r="KU106" t="n">
+        <v>-0.08190890155607911</v>
+      </c>
+      <c r="KV106" t="n">
+        <v>0.04225596774599712</v>
+      </c>
+      <c r="KW106" t="n">
+        <v>0.008264936340698666</v>
+      </c>
+      <c r="KX106" t="n">
+        <v>-0.003209439424217353</v>
+      </c>
+      <c r="KY106" t="n">
+        <v>-0.002388737952411846</v>
+      </c>
+      <c r="KZ106" t="n">
+        <v>0.001189221692622971</v>
+      </c>
+      <c r="LA106" t="n">
+        <v>-0.06037749026178833</v>
+      </c>
+      <c r="LB106" t="n">
+        <v>0.005445123016740251</v>
+      </c>
+      <c r="LC106" t="n">
+        <v>-0.0002531871759941083</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:54:54</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>10</v>
+      </c>
+      <c r="C107" t="n">
+        <v>100</v>
+      </c>
+      <c r="D107" t="n">
+        <v>50</v>
+      </c>
+      <c r="E107" t="n">
+        <v>200</v>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>0.1309674614782952</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0.9662902902902903</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0.9684243501793534</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0.5128266921273362</v>
+      </c>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="inlineStr"/>
+      <c r="S107" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="T107" t="n">
+        <v>0.3522046053287754</v>
+      </c>
+      <c r="U107" t="inlineStr"/>
+      <c r="V107" t="inlineStr"/>
+      <c r="W107" t="inlineStr"/>
+      <c r="X107" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>0.497798503723377</v>
+      </c>
+      <c r="Z107" t="inlineStr"/>
+      <c r="AA107" t="inlineStr"/>
+      <c r="AB107" t="inlineStr"/>
+      <c r="AC107" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AD107" t="n">
+        <v>0.4256935492390026</v>
+      </c>
+      <c r="AE107" t="inlineStr"/>
+      <c r="AF107" t="inlineStr"/>
+      <c r="AG107" t="inlineStr"/>
+      <c r="AH107" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AI107" t="n">
+        <v>0.4283675759600179</v>
+      </c>
+      <c r="AJ107" t="inlineStr"/>
+      <c r="AK107" t="inlineStr"/>
+      <c r="AL107" t="inlineStr"/>
+      <c r="AM107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO107" t="inlineStr"/>
+      <c r="AP107" t="inlineStr"/>
+      <c r="AQ107" t="inlineStr"/>
+      <c r="AR107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AU107" t="inlineStr"/>
+      <c r="AV107" t="inlineStr"/>
+      <c r="AW107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr"/>
+      <c r="BA107" t="inlineStr"/>
+      <c r="BB107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD107" t="inlineStr"/>
+      <c r="BE107" t="inlineStr"/>
+      <c r="BF107" t="inlineStr"/>
+      <c r="BG107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI107" t="inlineStr"/>
+      <c r="BJ107" t="inlineStr"/>
+      <c r="BK107" t="inlineStr"/>
+      <c r="BL107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN107" t="inlineStr"/>
+      <c r="BO107" t="inlineStr"/>
+      <c r="BP107" t="inlineStr"/>
+      <c r="BQ107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS107" t="inlineStr"/>
+      <c r="BT107" t="inlineStr"/>
+      <c r="BU107" t="inlineStr"/>
+      <c r="BV107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX107" t="inlineStr"/>
+      <c r="BY107" t="inlineStr"/>
+      <c r="BZ107" t="inlineStr"/>
+      <c r="CA107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC107" t="inlineStr"/>
+      <c r="CD107" t="inlineStr"/>
+      <c r="CE107" t="inlineStr"/>
+      <c r="CF107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG107" t="n">
+        <v>-0.02106113767444692</v>
+      </c>
+      <c r="CH107" t="inlineStr"/>
+      <c r="CI107" t="inlineStr"/>
+      <c r="CJ107" t="inlineStr"/>
+      <c r="CK107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM107" t="inlineStr"/>
+      <c r="CN107" t="inlineStr"/>
+      <c r="CO107" t="inlineStr"/>
+      <c r="CP107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR107" t="inlineStr"/>
+      <c r="CS107" t="inlineStr"/>
+      <c r="CT107" t="inlineStr"/>
+      <c r="CU107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW107" t="inlineStr"/>
+      <c r="CX107" t="inlineStr"/>
+      <c r="CY107" t="inlineStr"/>
+      <c r="CZ107" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA107" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB107" t="inlineStr"/>
+      <c r="DC107" t="inlineStr"/>
+      <c r="DD107" t="inlineStr"/>
+      <c r="DE107" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF107" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG107" t="inlineStr"/>
+      <c r="DH107" t="inlineStr"/>
+      <c r="DI107" t="inlineStr"/>
+      <c r="DJ107" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK107" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL107" t="inlineStr"/>
+      <c r="DM107" t="inlineStr"/>
+      <c r="DN107" t="inlineStr"/>
+      <c r="DO107" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP107" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ107" t="inlineStr"/>
+      <c r="DR107" t="inlineStr"/>
+      <c r="DS107" t="inlineStr"/>
+      <c r="DT107" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU107" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV107" t="inlineStr"/>
+      <c r="DW107" t="inlineStr"/>
+      <c r="DX107" t="inlineStr"/>
+      <c r="DY107" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ107" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA107" t="inlineStr"/>
+      <c r="EB107" t="inlineStr"/>
+      <c r="EC107" t="inlineStr"/>
+      <c r="ED107" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE107" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF107" t="inlineStr"/>
+      <c r="EG107" t="inlineStr"/>
+      <c r="EH107" t="inlineStr"/>
+      <c r="EI107" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ107" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK107" t="inlineStr"/>
+      <c r="EL107" t="inlineStr"/>
+      <c r="EM107" t="inlineStr"/>
+      <c r="EN107" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO107" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP107" t="inlineStr"/>
+      <c r="EQ107" t="inlineStr"/>
+      <c r="ER107" t="inlineStr"/>
+      <c r="ES107" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET107" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU107" t="inlineStr"/>
+      <c r="EV107" t="inlineStr"/>
+      <c r="EW107" t="inlineStr"/>
+      <c r="EX107" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY107" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ107" t="inlineStr"/>
+      <c r="FA107" t="inlineStr"/>
+      <c r="FB107" t="inlineStr"/>
+      <c r="FC107" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD107" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE107" t="inlineStr"/>
+      <c r="FF107" t="inlineStr"/>
+      <c r="FG107" t="inlineStr"/>
+      <c r="FH107" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI107" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ107" t="inlineStr"/>
+      <c r="FK107" t="inlineStr"/>
+      <c r="FL107" t="inlineStr"/>
+      <c r="FM107" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN107" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO107" t="inlineStr"/>
+      <c r="FP107" t="inlineStr"/>
+      <c r="FQ107" t="inlineStr"/>
+      <c r="FR107" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS107" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT107" t="inlineStr"/>
+      <c r="FU107" t="inlineStr"/>
+      <c r="FV107" t="inlineStr"/>
+      <c r="FW107" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX107" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY107" t="inlineStr"/>
+      <c r="FZ107" t="inlineStr"/>
+      <c r="GA107" t="inlineStr"/>
+      <c r="GB107" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC107" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD107" t="inlineStr"/>
+      <c r="GE107" t="inlineStr"/>
+      <c r="GF107" t="inlineStr"/>
+      <c r="GG107" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH107" t="n">
+        <v>0</v>
+      </c>
+      <c r="GI107" t="inlineStr"/>
+      <c r="GJ107" t="inlineStr"/>
+      <c r="GK107" t="inlineStr"/>
+      <c r="GL107" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM107" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN107" t="inlineStr"/>
+      <c r="GO107" t="inlineStr"/>
+      <c r="GP107" t="inlineStr"/>
+      <c r="GQ107" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR107" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS107" t="inlineStr"/>
+      <c r="GT107" t="inlineStr"/>
+      <c r="GU107" t="inlineStr"/>
+      <c r="GV107" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW107" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX107" t="inlineStr"/>
+      <c r="GY107" t="inlineStr"/>
+      <c r="GZ107" t="inlineStr"/>
+      <c r="HA107" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB107" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC107" t="inlineStr"/>
+      <c r="HD107" t="inlineStr"/>
+      <c r="HE107" t="inlineStr"/>
+      <c r="HF107" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG107" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH107" t="inlineStr"/>
+      <c r="HI107" t="inlineStr"/>
+      <c r="HJ107" t="inlineStr"/>
+      <c r="HK107" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL107" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM107" t="inlineStr"/>
+      <c r="HN107" t="inlineStr"/>
+      <c r="HO107" t="inlineStr"/>
+      <c r="HP107" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ107" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR107" t="inlineStr"/>
+      <c r="HS107" t="inlineStr"/>
+      <c r="HT107" t="inlineStr"/>
+      <c r="HU107" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV107" t="n">
+        <v>0</v>
+      </c>
+      <c r="HW107" t="inlineStr"/>
+      <c r="HX107" t="inlineStr"/>
+      <c r="HY107" t="inlineStr"/>
+      <c r="HZ107" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA107" t="n">
+        <v>0</v>
+      </c>
+      <c r="IB107" t="inlineStr"/>
+      <c r="IC107" t="inlineStr"/>
+      <c r="ID107" t="inlineStr"/>
+      <c r="IE107" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF107" t="n">
+        <v>0</v>
+      </c>
+      <c r="IG107" t="inlineStr"/>
+      <c r="IH107" t="inlineStr"/>
+      <c r="II107" t="inlineStr"/>
+      <c r="IJ107" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK107" t="n">
+        <v>0</v>
+      </c>
+      <c r="IL107" t="inlineStr"/>
+      <c r="IM107" t="inlineStr"/>
+      <c r="IN107" t="inlineStr"/>
+      <c r="IO107" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP107" t="n">
+        <v>0</v>
+      </c>
+      <c r="IQ107" t="inlineStr"/>
+      <c r="IR107" t="inlineStr"/>
+      <c r="IS107" t="inlineStr"/>
+      <c r="IT107" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU107" t="n">
+        <v>0</v>
+      </c>
+      <c r="IV107" t="inlineStr"/>
+      <c r="IW107" t="inlineStr"/>
+      <c r="IX107" t="inlineStr"/>
+      <c r="IY107" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ107" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA107" t="inlineStr"/>
+      <c r="JB107" t="inlineStr"/>
+      <c r="JC107" t="inlineStr"/>
+      <c r="JD107" t="n">
+        <v>5</v>
+      </c>
+      <c r="JE107" t="n">
+        <v>0.4361365447381242</v>
+      </c>
+      <c r="JF107" t="n">
+        <v>0.6277416574543553</v>
+      </c>
+      <c r="JG107" t="n">
+        <v>0.1068827691200671</v>
+      </c>
+      <c r="JH107" t="n">
+        <v>0.5941580093946782</v>
+      </c>
+      <c r="JI107" t="n">
+        <v>0.3379628352352489</v>
+      </c>
+      <c r="JJ107" t="n">
+        <v>0.3563229580577139</v>
+      </c>
+      <c r="JK107" t="n">
+        <v>0.0002718379645280649</v>
+      </c>
+      <c r="JL107" t="n">
+        <v>0.0003861834355577599</v>
+      </c>
+      <c r="JM107" t="n">
+        <v>0.0006868817518786514</v>
+      </c>
+      <c r="JN107" t="n">
+        <v>0.00086736199326743</v>
+      </c>
+      <c r="JO107" t="n">
+        <v>0</v>
+      </c>
+      <c r="JP107" t="n">
+        <v>0</v>
+      </c>
+      <c r="JQ107" t="n">
+        <v>0</v>
+      </c>
+      <c r="JR107" t="n">
+        <v>0</v>
+      </c>
+      <c r="JS107" t="n">
+        <v>1.828640072268327e-06</v>
+      </c>
+      <c r="JT107" t="n">
+        <v>-7.717869375838979e-05</v>
+      </c>
+      <c r="JU107" t="n">
+        <v>0.0003734691227146457</v>
+      </c>
+      <c r="JV107" t="n">
+        <v>0.0001336103820960282</v>
+      </c>
+      <c r="JW107" t="n">
+        <v>0</v>
+      </c>
+      <c r="JX107" t="n">
+        <v>2.021617347389254e-05</v>
+      </c>
+      <c r="JY107" t="n">
+        <v>0.0003805378000487467</v>
+      </c>
+      <c r="JZ107" t="n">
+        <v>0</v>
+      </c>
+      <c r="KA107" t="n">
+        <v>0</v>
+      </c>
+      <c r="KB107" t="n">
+        <v>0.0003303268493739666</v>
+      </c>
+      <c r="KC107" t="n">
+        <v>0</v>
+      </c>
+      <c r="KD107" t="n">
+        <v>-0.00134781778870733</v>
+      </c>
+      <c r="KE107" t="n">
+        <v>7.6714260180383e-05</v>
+      </c>
+      <c r="KF107" t="n">
+        <v>-0.0009216573819736879</v>
+      </c>
+      <c r="KG107" t="n">
+        <v>0</v>
+      </c>
+      <c r="KH107" t="n">
+        <v>3.862322242230186e-05</v>
+      </c>
+      <c r="KI107" t="n">
+        <v>-4.938737111282197e-05</v>
+      </c>
+      <c r="KJ107" t="n">
+        <v>0</v>
+      </c>
+      <c r="KK107" t="n">
+        <v>0</v>
+      </c>
+      <c r="KL107" t="n">
+        <v>-0.0001771155507561588</v>
+      </c>
+      <c r="KM107" t="n">
+        <v>0.0001452471525510368</v>
+      </c>
+      <c r="KN107" t="n">
+        <v>0.0006273492577082396</v>
+      </c>
+      <c r="KO107" t="n">
+        <v>0.0002423466130958564</v>
+      </c>
+      <c r="KP107" t="n">
+        <v>-0.0002014469358086093</v>
+      </c>
+      <c r="KQ107" t="n">
+        <v>0.0001451150737555128</v>
+      </c>
+      <c r="KR107" t="n">
+        <v>0</v>
+      </c>
+      <c r="KS107" t="n">
+        <v>0</v>
+      </c>
+      <c r="KT107" t="n">
+        <v>0</v>
+      </c>
+      <c r="KU107" t="n">
+        <v>-0.002195881737913246</v>
+      </c>
+      <c r="KV107" t="n">
+        <v>0.00029144974351754</v>
+      </c>
+      <c r="KW107" t="n">
+        <v>0.0001708313299684973</v>
+      </c>
+      <c r="KX107" t="n">
+        <v>-0.0002852081602510348</v>
+      </c>
+      <c r="KY107" t="n">
+        <v>-8.926234497136997e-06</v>
+      </c>
+      <c r="KZ107" t="n">
+        <v>4.857872449576054e-05</v>
+      </c>
+      <c r="LA107" t="n">
+        <v>8.285268290341376e-05</v>
+      </c>
+      <c r="LB107" t="n">
+        <v>4.486444219861743e-05</v>
+      </c>
+      <c r="LC107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-04-22 19:06:10</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>10</v>
+      </c>
+      <c r="C108" t="n">
+        <v>100</v>
+      </c>
+      <c r="D108" t="n">
+        <v>50</v>
+      </c>
+      <c r="E108" t="n">
+        <v>200</v>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>0.1309674614782952</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0.9662902902902903</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0.9684243501793534</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0.5128266921273362</v>
+      </c>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr"/>
+      <c r="S108" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="T108" t="n">
+        <v>0.3522046053287754</v>
+      </c>
+      <c r="U108" t="inlineStr"/>
+      <c r="V108" t="inlineStr"/>
+      <c r="W108" t="inlineStr"/>
+      <c r="X108" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>0.497798503723377</v>
+      </c>
+      <c r="Z108" t="inlineStr"/>
+      <c r="AA108" t="inlineStr"/>
+      <c r="AB108" t="inlineStr"/>
+      <c r="AC108" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>0.4256935492390026</v>
+      </c>
+      <c r="AE108" t="inlineStr"/>
+      <c r="AF108" t="inlineStr"/>
+      <c r="AG108" t="inlineStr"/>
+      <c r="AH108" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AI108" t="n">
+        <v>0.4283675759600179</v>
+      </c>
+      <c r="AJ108" t="inlineStr"/>
+      <c r="AK108" t="inlineStr"/>
+      <c r="AL108" t="inlineStr"/>
+      <c r="AM108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO108" t="inlineStr"/>
+      <c r="AP108" t="inlineStr"/>
+      <c r="AQ108" t="inlineStr"/>
+      <c r="AR108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AU108" t="inlineStr"/>
+      <c r="AV108" t="inlineStr"/>
+      <c r="AW108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr"/>
+      <c r="BA108" t="inlineStr"/>
+      <c r="BB108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD108" t="inlineStr"/>
+      <c r="BE108" t="inlineStr"/>
+      <c r="BF108" t="inlineStr"/>
+      <c r="BG108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI108" t="inlineStr"/>
+      <c r="BJ108" t="inlineStr"/>
+      <c r="BK108" t="inlineStr"/>
+      <c r="BL108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN108" t="inlineStr"/>
+      <c r="BO108" t="inlineStr"/>
+      <c r="BP108" t="inlineStr"/>
+      <c r="BQ108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS108" t="inlineStr"/>
+      <c r="BT108" t="inlineStr"/>
+      <c r="BU108" t="inlineStr"/>
+      <c r="BV108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX108" t="inlineStr"/>
+      <c r="BY108" t="inlineStr"/>
+      <c r="BZ108" t="inlineStr"/>
+      <c r="CA108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC108" t="inlineStr"/>
+      <c r="CD108" t="inlineStr"/>
+      <c r="CE108" t="inlineStr"/>
+      <c r="CF108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG108" t="n">
+        <v>-0.02106113767444692</v>
+      </c>
+      <c r="CH108" t="inlineStr"/>
+      <c r="CI108" t="inlineStr"/>
+      <c r="CJ108" t="inlineStr"/>
+      <c r="CK108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM108" t="inlineStr"/>
+      <c r="CN108" t="inlineStr"/>
+      <c r="CO108" t="inlineStr"/>
+      <c r="CP108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR108" t="inlineStr"/>
+      <c r="CS108" t="inlineStr"/>
+      <c r="CT108" t="inlineStr"/>
+      <c r="CU108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW108" t="inlineStr"/>
+      <c r="CX108" t="inlineStr"/>
+      <c r="CY108" t="inlineStr"/>
+      <c r="CZ108" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA108" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB108" t="inlineStr"/>
+      <c r="DC108" t="inlineStr"/>
+      <c r="DD108" t="inlineStr"/>
+      <c r="DE108" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF108" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG108" t="inlineStr"/>
+      <c r="DH108" t="inlineStr"/>
+      <c r="DI108" t="inlineStr"/>
+      <c r="DJ108" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK108" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL108" t="inlineStr"/>
+      <c r="DM108" t="inlineStr"/>
+      <c r="DN108" t="inlineStr"/>
+      <c r="DO108" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP108" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ108" t="inlineStr"/>
+      <c r="DR108" t="inlineStr"/>
+      <c r="DS108" t="inlineStr"/>
+      <c r="DT108" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU108" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV108" t="inlineStr"/>
+      <c r="DW108" t="inlineStr"/>
+      <c r="DX108" t="inlineStr"/>
+      <c r="DY108" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ108" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA108" t="inlineStr"/>
+      <c r="EB108" t="inlineStr"/>
+      <c r="EC108" t="inlineStr"/>
+      <c r="ED108" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE108" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF108" t="inlineStr"/>
+      <c r="EG108" t="inlineStr"/>
+      <c r="EH108" t="inlineStr"/>
+      <c r="EI108" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ108" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK108" t="inlineStr"/>
+      <c r="EL108" t="inlineStr"/>
+      <c r="EM108" t="inlineStr"/>
+      <c r="EN108" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO108" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP108" t="inlineStr"/>
+      <c r="EQ108" t="inlineStr"/>
+      <c r="ER108" t="inlineStr"/>
+      <c r="ES108" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET108" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU108" t="inlineStr"/>
+      <c r="EV108" t="inlineStr"/>
+      <c r="EW108" t="inlineStr"/>
+      <c r="EX108" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY108" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ108" t="inlineStr"/>
+      <c r="FA108" t="inlineStr"/>
+      <c r="FB108" t="inlineStr"/>
+      <c r="FC108" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD108" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE108" t="inlineStr"/>
+      <c r="FF108" t="inlineStr"/>
+      <c r="FG108" t="inlineStr"/>
+      <c r="FH108" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI108" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ108" t="inlineStr"/>
+      <c r="FK108" t="inlineStr"/>
+      <c r="FL108" t="inlineStr"/>
+      <c r="FM108" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN108" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO108" t="inlineStr"/>
+      <c r="FP108" t="inlineStr"/>
+      <c r="FQ108" t="inlineStr"/>
+      <c r="FR108" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS108" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT108" t="inlineStr"/>
+      <c r="FU108" t="inlineStr"/>
+      <c r="FV108" t="inlineStr"/>
+      <c r="FW108" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX108" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY108" t="inlineStr"/>
+      <c r="FZ108" t="inlineStr"/>
+      <c r="GA108" t="inlineStr"/>
+      <c r="GB108" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC108" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD108" t="inlineStr"/>
+      <c r="GE108" t="inlineStr"/>
+      <c r="GF108" t="inlineStr"/>
+      <c r="GG108" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH108" t="n">
+        <v>0</v>
+      </c>
+      <c r="GI108" t="inlineStr"/>
+      <c r="GJ108" t="inlineStr"/>
+      <c r="GK108" t="inlineStr"/>
+      <c r="GL108" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM108" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN108" t="inlineStr"/>
+      <c r="GO108" t="inlineStr"/>
+      <c r="GP108" t="inlineStr"/>
+      <c r="GQ108" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR108" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS108" t="inlineStr"/>
+      <c r="GT108" t="inlineStr"/>
+      <c r="GU108" t="inlineStr"/>
+      <c r="GV108" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW108" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX108" t="inlineStr"/>
+      <c r="GY108" t="inlineStr"/>
+      <c r="GZ108" t="inlineStr"/>
+      <c r="HA108" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB108" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC108" t="inlineStr"/>
+      <c r="HD108" t="inlineStr"/>
+      <c r="HE108" t="inlineStr"/>
+      <c r="HF108" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG108" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH108" t="inlineStr"/>
+      <c r="HI108" t="inlineStr"/>
+      <c r="HJ108" t="inlineStr"/>
+      <c r="HK108" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL108" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM108" t="inlineStr"/>
+      <c r="HN108" t="inlineStr"/>
+      <c r="HO108" t="inlineStr"/>
+      <c r="HP108" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ108" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR108" t="inlineStr"/>
+      <c r="HS108" t="inlineStr"/>
+      <c r="HT108" t="inlineStr"/>
+      <c r="HU108" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV108" t="n">
+        <v>0</v>
+      </c>
+      <c r="HW108" t="inlineStr"/>
+      <c r="HX108" t="inlineStr"/>
+      <c r="HY108" t="inlineStr"/>
+      <c r="HZ108" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA108" t="n">
+        <v>0</v>
+      </c>
+      <c r="IB108" t="inlineStr"/>
+      <c r="IC108" t="inlineStr"/>
+      <c r="ID108" t="inlineStr"/>
+      <c r="IE108" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF108" t="n">
+        <v>0</v>
+      </c>
+      <c r="IG108" t="inlineStr"/>
+      <c r="IH108" t="inlineStr"/>
+      <c r="II108" t="inlineStr"/>
+      <c r="IJ108" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK108" t="n">
+        <v>0</v>
+      </c>
+      <c r="IL108" t="inlineStr"/>
+      <c r="IM108" t="inlineStr"/>
+      <c r="IN108" t="inlineStr"/>
+      <c r="IO108" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP108" t="n">
+        <v>0</v>
+      </c>
+      <c r="IQ108" t="inlineStr"/>
+      <c r="IR108" t="inlineStr"/>
+      <c r="IS108" t="inlineStr"/>
+      <c r="IT108" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU108" t="n">
+        <v>0</v>
+      </c>
+      <c r="IV108" t="inlineStr"/>
+      <c r="IW108" t="inlineStr"/>
+      <c r="IX108" t="inlineStr"/>
+      <c r="IY108" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ108" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA108" t="inlineStr"/>
+      <c r="JB108" t="inlineStr"/>
+      <c r="JC108" t="inlineStr"/>
+      <c r="JD108" t="n">
+        <v>5</v>
+      </c>
+      <c r="JE108" t="n">
+        <v>0.4993152115609931</v>
+      </c>
+      <c r="JF108" t="n">
+        <v>0.6408393403366187</v>
+      </c>
+      <c r="JG108" t="n">
+        <v>0.05283261730965357</v>
+      </c>
+      <c r="JH108" t="n">
+        <v>0.6110194028812821</v>
+      </c>
+      <c r="JI108" t="n">
+        <v>0.3176806055229832</v>
+      </c>
+      <c r="JJ108" t="n">
+        <v>0.3346512183775046</v>
+      </c>
+      <c r="JK108" t="n">
+        <v>0.0002604837162790996</v>
+      </c>
+      <c r="JL108" t="n">
+        <v>0.0003713303043604957</v>
+      </c>
+      <c r="JM108" t="n">
+        <v>0.0006697261576265564</v>
+      </c>
+      <c r="JN108" t="n">
+        <v>0.0008138356571902469</v>
+      </c>
+      <c r="JO108" t="n">
+        <v>0</v>
+      </c>
+      <c r="JP108" t="n">
+        <v>0</v>
+      </c>
+      <c r="JQ108" t="n">
+        <v>0</v>
+      </c>
+      <c r="JR108" t="n">
+        <v>0</v>
+      </c>
+      <c r="JS108" t="n">
+        <v>4.044353871456867e-06</v>
+      </c>
+      <c r="JT108" t="n">
+        <v>0</v>
+      </c>
+      <c r="JU108" t="n">
+        <v>0.000349302091537835</v>
+      </c>
+      <c r="JV108" t="n">
+        <v>0.0001055567923221927</v>
+      </c>
+      <c r="JW108" t="n">
+        <v>0</v>
+      </c>
+      <c r="JX108" t="n">
+        <v>7.188582359491643e-06</v>
+      </c>
+      <c r="JY108" t="n">
+        <v>0.0004798649456696859</v>
+      </c>
+      <c r="JZ108" t="n">
+        <v>0</v>
+      </c>
+      <c r="KA108" t="n">
+        <v>0</v>
+      </c>
+      <c r="KB108" t="n">
+        <v>0.000530826592828771</v>
+      </c>
+      <c r="KC108" t="n">
+        <v>0</v>
+      </c>
+      <c r="KD108" t="n">
+        <v>-0.0008215721097690207</v>
+      </c>
+      <c r="KE108" t="n">
+        <v>9.344561420773723e-05</v>
+      </c>
+      <c r="KF108" t="n">
+        <v>-0.0006857771238419501</v>
+      </c>
+      <c r="KG108" t="n">
+        <v>0</v>
+      </c>
+      <c r="KH108" t="n">
+        <v>2.692674807278002e-05</v>
+      </c>
+      <c r="KI108" t="n">
+        <v>2.320901219878289e-05</v>
+      </c>
+      <c r="KJ108" t="n">
+        <v>0</v>
+      </c>
+      <c r="KK108" t="n">
+        <v>0</v>
+      </c>
+      <c r="KL108" t="n">
+        <v>0</v>
+      </c>
+      <c r="KM108" t="n">
+        <v>0.0001425031323356299</v>
+      </c>
+      <c r="KN108" t="n">
+        <v>0.0006153694670794967</v>
+      </c>
+      <c r="KO108" t="n">
+        <v>0.0002372645402662545</v>
+      </c>
+      <c r="KP108" t="n">
+        <v>0.0002313909563609851</v>
+      </c>
+      <c r="KQ108" t="n">
+        <v>0.0001537228190811622</v>
+      </c>
+      <c r="KR108" t="n">
+        <v>0</v>
+      </c>
+      <c r="KS108" t="n">
+        <v>0</v>
+      </c>
+      <c r="KT108" t="n">
+        <v>0</v>
+      </c>
+      <c r="KU108" t="n">
+        <v>-0.001792025028195758</v>
+      </c>
+      <c r="KV108" t="n">
+        <v>0.0002596693608979316</v>
+      </c>
+      <c r="KW108" t="n">
+        <v>0.000146459702455072</v>
+      </c>
+      <c r="KX108" t="n">
+        <v>-0.000113197218243252</v>
+      </c>
+      <c r="KY108" t="n">
+        <v>0</v>
+      </c>
+      <c r="KZ108" t="n">
+        <v>2.412978943722674e-05</v>
+      </c>
+      <c r="LA108" t="n">
+        <v>6.609840671297989e-05</v>
+      </c>
+      <c r="LB108" t="n">
+        <v>3.346599889840037e-05</v>
+      </c>
+      <c r="LC108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-04-22 19:30:43</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>10</v>
+      </c>
+      <c r="C109" t="n">
+        <v>100</v>
+      </c>
+      <c r="D109" t="n">
+        <v>50</v>
+      </c>
+      <c r="E109" t="n">
+        <v>200</v>
+      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>0.1309674614782952</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0.9662902902902903</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0.9684243501793534</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0.5128266921273362</v>
+      </c>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr"/>
+      <c r="S109" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="T109" t="n">
+        <v>0.3522046053287754</v>
+      </c>
+      <c r="U109" t="inlineStr"/>
+      <c r="V109" t="inlineStr"/>
+      <c r="W109" t="inlineStr"/>
+      <c r="X109" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>0.497798503723377</v>
+      </c>
+      <c r="Z109" t="inlineStr"/>
+      <c r="AA109" t="inlineStr"/>
+      <c r="AB109" t="inlineStr"/>
+      <c r="AC109" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>0.4256935492390026</v>
+      </c>
+      <c r="AE109" t="inlineStr"/>
+      <c r="AF109" t="inlineStr"/>
+      <c r="AG109" t="inlineStr"/>
+      <c r="AH109" t="n">
+        <v>0.4472135954999579</v>
+      </c>
+      <c r="AI109" t="n">
+        <v>0.4283675759600179</v>
+      </c>
+      <c r="AJ109" t="inlineStr"/>
+      <c r="AK109" t="inlineStr"/>
+      <c r="AL109" t="inlineStr"/>
+      <c r="AM109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO109" t="inlineStr"/>
+      <c r="AP109" t="inlineStr"/>
+      <c r="AQ109" t="inlineStr"/>
+      <c r="AR109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AU109" t="inlineStr"/>
+      <c r="AV109" t="inlineStr"/>
+      <c r="AW109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr"/>
+      <c r="BA109" t="inlineStr"/>
+      <c r="BB109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD109" t="inlineStr"/>
+      <c r="BE109" t="inlineStr"/>
+      <c r="BF109" t="inlineStr"/>
+      <c r="BG109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH109" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI109" t="inlineStr"/>
+      <c r="BJ109" t="inlineStr"/>
+      <c r="BK109" t="inlineStr"/>
+      <c r="BL109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM109" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN109" t="inlineStr"/>
+      <c r="BO109" t="inlineStr"/>
+      <c r="BP109" t="inlineStr"/>
+      <c r="BQ109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR109" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS109" t="inlineStr"/>
+      <c r="BT109" t="inlineStr"/>
+      <c r="BU109" t="inlineStr"/>
+      <c r="BV109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW109" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX109" t="inlineStr"/>
+      <c r="BY109" t="inlineStr"/>
+      <c r="BZ109" t="inlineStr"/>
+      <c r="CA109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB109" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC109" t="inlineStr"/>
+      <c r="CD109" t="inlineStr"/>
+      <c r="CE109" t="inlineStr"/>
+      <c r="CF109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG109" t="n">
+        <v>-0.02106113767444692</v>
+      </c>
+      <c r="CH109" t="inlineStr"/>
+      <c r="CI109" t="inlineStr"/>
+      <c r="CJ109" t="inlineStr"/>
+      <c r="CK109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL109" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM109" t="inlineStr"/>
+      <c r="CN109" t="inlineStr"/>
+      <c r="CO109" t="inlineStr"/>
+      <c r="CP109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR109" t="inlineStr"/>
+      <c r="CS109" t="inlineStr"/>
+      <c r="CT109" t="inlineStr"/>
+      <c r="CU109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV109" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW109" t="inlineStr"/>
+      <c r="CX109" t="inlineStr"/>
+      <c r="CY109" t="inlineStr"/>
+      <c r="CZ109" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA109" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB109" t="inlineStr"/>
+      <c r="DC109" t="inlineStr"/>
+      <c r="DD109" t="inlineStr"/>
+      <c r="DE109" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF109" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG109" t="inlineStr"/>
+      <c r="DH109" t="inlineStr"/>
+      <c r="DI109" t="inlineStr"/>
+      <c r="DJ109" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK109" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL109" t="inlineStr"/>
+      <c r="DM109" t="inlineStr"/>
+      <c r="DN109" t="inlineStr"/>
+      <c r="DO109" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP109" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ109" t="inlineStr"/>
+      <c r="DR109" t="inlineStr"/>
+      <c r="DS109" t="inlineStr"/>
+      <c r="DT109" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU109" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV109" t="inlineStr"/>
+      <c r="DW109" t="inlineStr"/>
+      <c r="DX109" t="inlineStr"/>
+      <c r="DY109" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ109" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA109" t="inlineStr"/>
+      <c r="EB109" t="inlineStr"/>
+      <c r="EC109" t="inlineStr"/>
+      <c r="ED109" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE109" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF109" t="inlineStr"/>
+      <c r="EG109" t="inlineStr"/>
+      <c r="EH109" t="inlineStr"/>
+      <c r="EI109" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ109" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK109" t="inlineStr"/>
+      <c r="EL109" t="inlineStr"/>
+      <c r="EM109" t="inlineStr"/>
+      <c r="EN109" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO109" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP109" t="inlineStr"/>
+      <c r="EQ109" t="inlineStr"/>
+      <c r="ER109" t="inlineStr"/>
+      <c r="ES109" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET109" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU109" t="inlineStr"/>
+      <c r="EV109" t="inlineStr"/>
+      <c r="EW109" t="inlineStr"/>
+      <c r="EX109" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY109" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ109" t="inlineStr"/>
+      <c r="FA109" t="inlineStr"/>
+      <c r="FB109" t="inlineStr"/>
+      <c r="FC109" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD109" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE109" t="inlineStr"/>
+      <c r="FF109" t="inlineStr"/>
+      <c r="FG109" t="inlineStr"/>
+      <c r="FH109" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI109" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ109" t="inlineStr"/>
+      <c r="FK109" t="inlineStr"/>
+      <c r="FL109" t="inlineStr"/>
+      <c r="FM109" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN109" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO109" t="inlineStr"/>
+      <c r="FP109" t="inlineStr"/>
+      <c r="FQ109" t="inlineStr"/>
+      <c r="FR109" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS109" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT109" t="inlineStr"/>
+      <c r="FU109" t="inlineStr"/>
+      <c r="FV109" t="inlineStr"/>
+      <c r="FW109" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX109" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY109" t="inlineStr"/>
+      <c r="FZ109" t="inlineStr"/>
+      <c r="GA109" t="inlineStr"/>
+      <c r="GB109" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC109" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD109" t="inlineStr"/>
+      <c r="GE109" t="inlineStr"/>
+      <c r="GF109" t="inlineStr"/>
+      <c r="GG109" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH109" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GI109" t="inlineStr"/>
+      <c r="GJ109" t="inlineStr"/>
+      <c r="GK109" t="inlineStr"/>
+      <c r="GL109" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM109" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GN109" t="inlineStr"/>
+      <c r="GO109" t="inlineStr"/>
+      <c r="GP109" t="inlineStr"/>
+      <c r="GQ109" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR109" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GS109" t="inlineStr"/>
+      <c r="GT109" t="inlineStr"/>
+      <c r="GU109" t="inlineStr"/>
+      <c r="GV109" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW109" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GX109" t="inlineStr"/>
+      <c r="GY109" t="inlineStr"/>
+      <c r="GZ109" t="inlineStr"/>
+      <c r="HA109" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB109" t="n">
+        <v>-0</v>
+      </c>
+      <c r="HC109" t="inlineStr"/>
+      <c r="HD109" t="inlineStr"/>
+      <c r="HE109" t="inlineStr"/>
+      <c r="HF109" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG109" t="n">
+        <v>-0</v>
+      </c>
+      <c r="HH109" t="inlineStr"/>
+      <c r="HI109" t="inlineStr"/>
+      <c r="HJ109" t="inlineStr"/>
+      <c r="HK109" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL109" t="n">
+        <v>-0</v>
+      </c>
+      <c r="HM109" t="inlineStr"/>
+      <c r="HN109" t="inlineStr"/>
+      <c r="HO109" t="inlineStr"/>
+      <c r="HP109" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ109" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR109" t="inlineStr"/>
+      <c r="HS109" t="inlineStr"/>
+      <c r="HT109" t="inlineStr"/>
+      <c r="HU109" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV109" t="n">
+        <v>-0</v>
+      </c>
+      <c r="HW109" t="inlineStr"/>
+      <c r="HX109" t="inlineStr"/>
+      <c r="HY109" t="inlineStr"/>
+      <c r="HZ109" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA109" t="n">
+        <v>-0</v>
+      </c>
+      <c r="IB109" t="inlineStr"/>
+      <c r="IC109" t="inlineStr"/>
+      <c r="ID109" t="inlineStr"/>
+      <c r="IE109" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF109" t="n">
+        <v>-0</v>
+      </c>
+      <c r="IG109" t="inlineStr"/>
+      <c r="IH109" t="inlineStr"/>
+      <c r="II109" t="inlineStr"/>
+      <c r="IJ109" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK109" t="n">
+        <v>-0</v>
+      </c>
+      <c r="IL109" t="inlineStr"/>
+      <c r="IM109" t="inlineStr"/>
+      <c r="IN109" t="inlineStr"/>
+      <c r="IO109" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP109" t="n">
+        <v>-0</v>
+      </c>
+      <c r="IQ109" t="inlineStr"/>
+      <c r="IR109" t="inlineStr"/>
+      <c r="IS109" t="inlineStr"/>
+      <c r="IT109" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU109" t="n">
+        <v>-0</v>
+      </c>
+      <c r="IV109" t="inlineStr"/>
+      <c r="IW109" t="inlineStr"/>
+      <c r="IX109" t="inlineStr"/>
+      <c r="IY109" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ109" t="n">
+        <v>-0</v>
+      </c>
+      <c r="JA109" t="inlineStr"/>
+      <c r="JB109" t="inlineStr"/>
+      <c r="JC109" t="inlineStr"/>
+      <c r="JD109" t="n">
+        <v>5</v>
+      </c>
+      <c r="JE109" t="n">
+        <v>0.3120696143109354</v>
+      </c>
+      <c r="JF109" t="n">
+        <v>0.4579080892357991</v>
+      </c>
+      <c r="JG109" t="n">
+        <v>0.3961557640297577</v>
+      </c>
+      <c r="JH109" t="n">
+        <v>0.4444974384344664</v>
+      </c>
+      <c r="JI109" t="n">
+        <v>0.4194151462713087</v>
+      </c>
+      <c r="JJ109" t="n">
+        <v>0.4065913106265503</v>
+      </c>
+      <c r="JK109" t="n">
+        <v>0.003130743931265131</v>
+      </c>
+      <c r="JL109" t="n">
+        <v>0.05859096841023985</v>
+      </c>
+      <c r="JM109" t="n">
+        <v>0.05069688438581782</v>
+      </c>
+      <c r="JN109" t="n">
+        <v>0.1227449338822055</v>
+      </c>
+      <c r="JO109" t="n">
+        <v>-0.001185778674008597</v>
+      </c>
+      <c r="JP109" t="n">
+        <v>-0.1092507903340783</v>
+      </c>
+      <c r="JQ109" t="n">
+        <v>0.007595283105973957</v>
+      </c>
+      <c r="JR109" t="n">
+        <v>-0.003096442320274959</v>
+      </c>
+      <c r="JS109" t="n">
+        <v>0.001130855201492788</v>
+      </c>
+      <c r="JT109" t="n">
+        <v>-0.1206844224986117</v>
+      </c>
+      <c r="JU109" t="n">
+        <v>0.007606765836653125</v>
+      </c>
+      <c r="JV109" t="n">
+        <v>0.0458800192659097</v>
+      </c>
+      <c r="JW109" t="n">
+        <v>-0.001595815188165181</v>
+      </c>
+      <c r="JX109" t="n">
+        <v>0.05491146290312975</v>
+      </c>
+      <c r="JY109" t="n">
+        <v>-0.003431261618623362</v>
+      </c>
+      <c r="JZ109" t="n">
+        <v>0.001637273437959243</v>
+      </c>
+      <c r="KA109" t="n">
+        <v>0.003962580895763816</v>
+      </c>
+      <c r="KB109" t="n">
+        <v>-0.02045582860931901</v>
+      </c>
+      <c r="KC109" t="n">
+        <v>0.0004804064459376146</v>
+      </c>
+      <c r="KD109" t="n">
+        <v>-0.01837524018500783</v>
+      </c>
+      <c r="KE109" t="n">
+        <v>-0.001222019937687266</v>
+      </c>
+      <c r="KF109" t="n">
+        <v>-0.102372427654734</v>
+      </c>
+      <c r="KG109" t="n">
+        <v>-0.001323646504936242</v>
+      </c>
+      <c r="KH109" t="n">
+        <v>0.0404343738429019</v>
+      </c>
+      <c r="KI109" t="n">
+        <v>-0.002303008895132634</v>
+      </c>
+      <c r="KJ109" t="n">
+        <v>-0.02514756112541415</v>
+      </c>
+      <c r="KK109" t="n">
+        <v>-0.008806118217188387</v>
+      </c>
+      <c r="KL109" t="n">
+        <v>-0.03993984543027417</v>
+      </c>
+      <c r="KM109" t="n">
+        <v>0.04772256928087014</v>
+      </c>
+      <c r="KN109" t="n">
+        <v>0.1026993262686154</v>
+      </c>
+      <c r="KO109" t="n">
+        <v>0.001191298172706165</v>
+      </c>
+      <c r="KP109" t="n">
+        <v>-0.0045068431963339</v>
+      </c>
+      <c r="KQ109" t="n">
+        <v>-6.192687128386259e-05</v>
+      </c>
+      <c r="KR109" t="n">
+        <v>0.004147637038692864</v>
+      </c>
+      <c r="KS109" t="n">
+        <v>-0.01146851203952393</v>
+      </c>
+      <c r="KT109" t="n">
+        <v>0.008005541326006109</v>
+      </c>
+      <c r="KU109" t="n">
+        <v>-0.07942367395281481</v>
+      </c>
+      <c r="KV109" t="n">
+        <v>0.0389715290902054</v>
+      </c>
+      <c r="KW109" t="n">
+        <v>0.005520191375356137</v>
+      </c>
+      <c r="KX109" t="n">
+        <v>-0.003184715729313765</v>
+      </c>
+      <c r="KY109" t="n">
+        <v>-0.002334497563397864</v>
+      </c>
+      <c r="KZ109" t="n">
+        <v>0.00115551186398129</v>
+      </c>
+      <c r="LA109" t="n">
+        <v>-0.05684671869743967</v>
+      </c>
+      <c r="LB109" t="n">
+        <v>0.005030973749074693</v>
+      </c>
+      <c r="LC109" t="n">
+        <v>-0.0002557415319253705</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
